--- a/financas.xlsx
+++ b/financas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="362" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78543C44-ABD6-4823-8F6D-B177A98B3AB2}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09D21FCF-1DF7-421D-AC92-8322B8783B7C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="243">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -414,15 +414,42 @@
     <t>Serviço de nuvem da câmera</t>
   </si>
   <si>
+    <t>Rappi</t>
+  </si>
+  <si>
     <t>Gasolina</t>
   </si>
   <si>
-    <t>Rappi</t>
-  </si>
-  <si>
     <t>Lanche</t>
   </si>
   <si>
+    <t>Gibis</t>
+  </si>
+  <si>
+    <t>Bonffas Beer</t>
+  </si>
+  <si>
+    <t>Gasolina Pirassunusng</t>
+  </si>
+  <si>
+    <t>Hot Wheels</t>
+  </si>
+  <si>
+    <t>Pagamento Hot Wheels</t>
+  </si>
+  <si>
+    <t>Kikão</t>
+  </si>
+  <si>
+    <t>Gasolina de Volta</t>
+  </si>
+  <si>
+    <t>Odisseia</t>
+  </si>
+  <si>
+    <t>Pagamento Odisseia</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -618,6 +645,12 @@
     <t>Pagamento Edilson</t>
   </si>
   <si>
+    <t>Dinheiro Nano</t>
+  </si>
+  <si>
+    <t>Recolhimento Receita</t>
+  </si>
+  <si>
     <t>Ilumeo Julho - 1º PPT</t>
   </si>
   <si>
@@ -717,37 +750,31 @@
     <t>Dera</t>
   </si>
   <si>
-    <t>Gibis</t>
-  </si>
-  <si>
-    <t>Bonffas Beer</t>
-  </si>
-  <si>
-    <t>Gasolina Pirassunusng</t>
-  </si>
-  <si>
-    <t>Hot Wheels</t>
-  </si>
-  <si>
-    <t>Pagamento Hot Wheels</t>
-  </si>
-  <si>
-    <t>Kikão</t>
-  </si>
-  <si>
-    <t>Gasolina de Volta</t>
-  </si>
-  <si>
-    <t>Odisseia</t>
-  </si>
-  <si>
-    <t>Pagamento Odisseia</t>
-  </si>
-  <si>
-    <t>Dinheiro Nano</t>
-  </si>
-  <si>
-    <t>Recolhimento Receita</t>
+    <t>Ifood</t>
+  </si>
+  <si>
+    <t>Mercado</t>
+  </si>
+  <si>
+    <t>Rappi 1</t>
+  </si>
+  <si>
+    <t>Rappi 2</t>
+  </si>
+  <si>
+    <t>Saco de lixo e copo descartável</t>
+  </si>
+  <si>
+    <t>Mr Jones</t>
+  </si>
+  <si>
+    <t>Renner - Presente Stella</t>
+  </si>
+  <si>
+    <t>Renner Stella</t>
+  </si>
+  <si>
+    <t>Baked Potato</t>
   </si>
 </sst>
 </file>
@@ -1232,20 +1259,20 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="15">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1320,14 +1347,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1661,7 +1680,7 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="75" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1673,15 +1692,15 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="78"/>
+      <c r="B3" s="76"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C22+C23+C7</f>
-        <v>1732.8714047619037</v>
+        <v>2098.2464047619037</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E22+E23</f>
-        <v>3729.3575000000001</v>
+        <v>3520.8625000000011</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1690,7 +1709,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="8">
-        <v>10000</v>
+        <v>10200</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8">
@@ -1703,12 +1722,12 @@
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-7605.1285952380968</v>
+        <v>-7939.7535952380968</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-5270.6424999999999</v>
+        <v>-5479.1374999999998</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1739,12 +1758,12 @@
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5182.8969285714293</v>
+        <v>5517.5219285714293</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1888.5724999999998</v>
+        <v>2097.0674999999997</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -1753,12 +1772,12 @@
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5182.8969285714293</v>
+        <v>5517.5219285714293</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1888.5724999999998</v>
+        <v>2097.0674999999997</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
@@ -1895,7 +1914,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="8">
@@ -2131,11 +2150,11 @@
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1888.5724999999998</v>
+        <v>2097.0674999999997</v>
       </c>
       <c r="D4" s="27">
         <f>Saldo!C9+D5</f>
-        <v>5182.8969285714293</v>
+        <v>5517.5219285714293</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -2239,7 +2258,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>3936.2574999999997</v>
+        <v>4144.7524999999996</v>
       </c>
       <c r="D17" s="30"/>
     </row>
@@ -3012,15 +3031,15 @@
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="48">
         <f>SUM(L6:L377)</f>
-        <v>7121.4694285714277</v>
+        <v>7681.5594285714278</v>
       </c>
       <c r="E2" s="35">
         <f>SUMIF($E$6:$E$377,E1,$M$6:$M$377)</f>
-        <v>5182.8969285714293</v>
+        <v>5517.5219285714293</v>
       </c>
       <c r="F2" s="35">
         <f>SUMIF($F$6:$F$377,F1,$M$6:$M$377)</f>
-        <v>1888.5724999999998</v>
+        <v>2097.0674999999997</v>
       </c>
       <c r="G2" s="35">
         <f>SUMIF($G$6:$G$377,G1,$M$6:$M$377)</f>
@@ -5741,7 +5760,7 @@
     <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="38"/>
       <c r="D65" s="49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E65" s="40" t="s">
         <v>1</v>
@@ -5783,7 +5802,7 @@
     <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="38"/>
       <c r="D66" s="49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E66" s="40"/>
       <c r="F66" s="40" t="s">
@@ -5823,7 +5842,7 @@
     <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="38"/>
       <c r="D67" s="49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E67" s="40" t="s">
         <v>1</v>
@@ -5903,7 +5922,7 @@
     <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="38"/>
       <c r="D69" s="49" t="s">
-        <v>223</v>
+        <v>125</v>
       </c>
       <c r="E69" s="40" t="s">
         <v>1</v>
@@ -5943,7 +5962,7 @@
     <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="38"/>
       <c r="D70" s="49" t="s">
-        <v>224</v>
+        <v>126</v>
       </c>
       <c r="E70" s="40" t="s">
         <v>1</v>
@@ -5983,7 +6002,7 @@
     <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="38"/>
       <c r="D71" s="49" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="E71" s="40" t="s">
         <v>1</v>
@@ -6025,7 +6044,7 @@
     <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="38"/>
       <c r="D72" s="49" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="E72" s="40" t="s">
         <v>1</v>
@@ -6065,7 +6084,7 @@
     <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="38"/>
       <c r="D73" s="49" t="s">
-        <v>227</v>
+        <v>129</v>
       </c>
       <c r="E73" s="40" t="s">
         <v>1</v>
@@ -6105,7 +6124,7 @@
     <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="38"/>
       <c r="D74" s="49" t="s">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="E74" s="40" t="s">
         <v>1</v>
@@ -6147,7 +6166,7 @@
     <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="38"/>
       <c r="D75" s="49" t="s">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="E75" s="40"/>
       <c r="F75" s="40" t="s">
@@ -6187,7 +6206,7 @@
     <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="38"/>
       <c r="D76" s="49" t="s">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="E76" s="40" t="s">
         <v>1</v>
@@ -6229,7 +6248,7 @@
     <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="38"/>
       <c r="D77" s="49" t="s">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="E77" s="40" t="s">
         <v>1</v>
@@ -6268,24 +6287,32 @@
     </row>
     <row r="78" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C78" s="38"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
+      <c r="D78" s="49" t="s">
+        <v>234</v>
+      </c>
+      <c r="E78" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G78" s="40"/>
       <c r="H78" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I78" s="41">
+        <v>79</v>
+      </c>
       <c r="J78" s="41"/>
       <c r="K78" s="41"/>
       <c r="L78" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M78" s="41" t="str">
+        <v>79</v>
+      </c>
+      <c r="M78" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>39.5</v>
       </c>
       <c r="N78" s="42">
         <v>1</v>
@@ -6302,24 +6329,32 @@
     </row>
     <row r="79" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C79" s="38"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
+      <c r="D79" s="49" t="s">
+        <v>235</v>
+      </c>
+      <c r="E79" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G79" s="40"/>
       <c r="H79" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I79" s="41">
+        <v>56.27</v>
+      </c>
       <c r="J79" s="41"/>
       <c r="K79" s="41"/>
       <c r="L79" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M79" s="41" t="str">
+        <v>56.27</v>
+      </c>
+      <c r="M79" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>28.135000000000002</v>
       </c>
       <c r="N79" s="42">
         <v>1</v>
@@ -6336,24 +6371,32 @@
     </row>
     <row r="80" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C80" s="38"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
+      <c r="D80" s="49" t="s">
+        <v>236</v>
+      </c>
+      <c r="E80" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G80" s="40"/>
       <c r="H80" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I80" s="41">
+        <v>82.49</v>
+      </c>
       <c r="J80" s="41"/>
       <c r="K80" s="41"/>
       <c r="L80" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M80" s="41" t="str">
+        <v>82.49</v>
+      </c>
+      <c r="M80" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>41.244999999999997</v>
       </c>
       <c r="N80" s="42">
         <v>1</v>
@@ -6370,24 +6413,32 @@
     </row>
     <row r="81" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C81" s="38"/>
-      <c r="D81" s="49"/>
-      <c r="E81" s="40"/>
-      <c r="F81" s="40"/>
+      <c r="D81" s="49" t="s">
+        <v>237</v>
+      </c>
+      <c r="E81" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G81" s="40"/>
       <c r="H81" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I81" s="41">
+        <v>49.91</v>
+      </c>
       <c r="J81" s="41"/>
       <c r="K81" s="41"/>
       <c r="L81" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M81" s="41" t="str">
+        <v>49.91</v>
+      </c>
+      <c r="M81" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>24.954999999999998</v>
       </c>
       <c r="N81" s="42">
         <v>1</v>
@@ -6404,24 +6455,32 @@
     </row>
     <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C82" s="38"/>
-      <c r="D82" s="49"/>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40"/>
+      <c r="D82" s="49" t="s">
+        <v>238</v>
+      </c>
+      <c r="E82" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G82" s="40"/>
       <c r="H82" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I82" s="41">
+        <v>41.5</v>
+      </c>
       <c r="J82" s="41"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="41" t="str">
+        <v>41.5</v>
+      </c>
+      <c r="M82" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>20.75</v>
       </c>
       <c r="N82" s="42">
         <v>1</v>
@@ -6438,24 +6497,30 @@
     </row>
     <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="38"/>
-      <c r="D83" s="49"/>
-      <c r="E83" s="40"/>
+      <c r="D83" s="49" t="s">
+        <v>239</v>
+      </c>
+      <c r="E83" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F83" s="40"/>
       <c r="G83" s="40"/>
       <c r="H83" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I83" s="41">
+        <v>106.04</v>
+      </c>
       <c r="J83" s="41"/>
       <c r="K83" s="41"/>
       <c r="L83" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M83" s="41" t="str">
+        <v>106.04</v>
+      </c>
+      <c r="M83" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>106.04</v>
       </c>
       <c r="N83" s="42">
         <v>1</v>
@@ -6472,7 +6537,9 @@
     </row>
     <row r="84" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C84" s="38"/>
-      <c r="D84" s="49"/>
+      <c r="D84" s="49" t="s">
+        <v>119</v>
+      </c>
       <c r="E84" s="40"/>
       <c r="F84" s="40"/>
       <c r="G84" s="40"/>
@@ -6480,12 +6547,14 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I84" s="41"/>
+      <c r="I84" s="41">
+        <v>16.97</v>
+      </c>
       <c r="J84" s="41"/>
       <c r="K84" s="41"/>
       <c r="L84" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16.97</v>
       </c>
       <c r="M84" s="41" t="str">
         <f t="shared" si="13"/>
@@ -6506,32 +6575,42 @@
     </row>
     <row r="85" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C85" s="38"/>
-      <c r="D85" s="49"/>
-      <c r="E85" s="40"/>
+      <c r="D85" s="49" t="s">
+        <v>240</v>
+      </c>
+      <c r="E85" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F85" s="40"/>
       <c r="G85" s="40"/>
       <c r="H85" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="41"/>
-      <c r="J85" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I85" s="41">
+        <v>72</v>
+      </c>
+      <c r="J85" s="41" t="s">
+        <v>44</v>
+      </c>
       <c r="K85" s="41"/>
       <c r="L85" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="41" t="str">
+        <v>24</v>
+      </c>
+      <c r="M85" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>24</v>
       </c>
       <c r="N85" s="42">
-        <v>1</v>
-      </c>
-      <c r="O85" s="38"/>
-      <c r="P85" s="38" t="str">
+        <v>3</v>
+      </c>
+      <c r="O85" s="67">
+        <v>46240</v>
+      </c>
+      <c r="P85" s="67">
         <f t="shared" si="14"/>
-        <v/>
+        <v>46301</v>
       </c>
       <c r="Q85" s="40" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6540,32 +6619,42 @@
     </row>
     <row r="86" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C86" s="38"/>
-      <c r="D86" s="49"/>
+      <c r="D86" s="49" t="s">
+        <v>241</v>
+      </c>
       <c r="E86" s="40"/>
-      <c r="F86" s="40"/>
+      <c r="F86" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G86" s="40"/>
       <c r="H86" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="41"/>
-      <c r="J86" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I86" s="41">
+        <v>161.72999999999999</v>
+      </c>
+      <c r="J86" s="41" t="s">
+        <v>44</v>
+      </c>
       <c r="K86" s="41"/>
       <c r="L86" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M86" s="41" t="str">
+        <v>53.91</v>
+      </c>
+      <c r="M86" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>53.91</v>
       </c>
       <c r="N86" s="42">
-        <v>1</v>
-      </c>
-      <c r="O86" s="38"/>
-      <c r="P86" s="38" t="str">
+        <v>3</v>
+      </c>
+      <c r="O86" s="67">
+        <v>46240</v>
+      </c>
+      <c r="P86" s="67">
         <f t="shared" si="14"/>
-        <v/>
+        <v>46301</v>
       </c>
       <c r="Q86" s="40" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6574,24 +6663,30 @@
     </row>
     <row r="87" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C87" s="38"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="40"/>
+      <c r="D87" s="49" t="s">
+        <v>242</v>
+      </c>
+      <c r="E87" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F87" s="40"/>
       <c r="G87" s="40"/>
       <c r="H87" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I87" s="41">
+        <v>50</v>
+      </c>
       <c r="J87" s="41"/>
       <c r="K87" s="41"/>
       <c r="L87" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="41" t="str">
+        <v>50</v>
+      </c>
+      <c r="M87" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>50</v>
       </c>
       <c r="N87" s="42">
         <v>1</v>
@@ -8734,7 +8829,7 @@
   </sheetData>
   <autoFilter ref="C5:Q150" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q150">
-      <sortCondition sortBy="cellColor" ref="J5:J150" dxfId="15"/>
+      <sortCondition sortBy="cellColor" ref="J5:J150" dxfId="14"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="I6:I150">
@@ -8851,7 +8946,7 @@
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="58" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E4" s="59" t="s">
         <v>1</v>
@@ -8892,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>1</v>
@@ -8934,7 +9029,7 @@
         <v>2382.0700000000002</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E6" s="39" t="s">
         <v>1</v>
@@ -8972,7 +9067,7 @@
     <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="63"/>
       <c r="D7" s="57" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E7" s="39" t="s">
         <v>1</v>
@@ -9053,7 +9148,7 @@
         <v>3382.07</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E9" s="39" t="s">
         <v>1</v>
@@ -9091,7 +9186,7 @@
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D10" s="57" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="40" t="s">
@@ -9292,7 +9387,7 @@
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" s="2"/>
       <c r="N1" s="50" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9302,10 +9397,10 @@
     <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
       <c r="L3" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="M3" s="75" t="s">
-        <v>133</v>
+        <v>141</v>
+      </c>
+      <c r="M3" s="77" t="s">
+        <v>142</v>
       </c>
       <c r="N3" s="46">
         <f>SUM(N5:N21)</f>
@@ -9316,9 +9411,9 @@
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="2"/>
       <c r="L4" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="M4" s="76"/>
+        <v>143</v>
+      </c>
+      <c r="M4" s="78"/>
       <c r="N4" s="52"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
@@ -9327,7 +9422,7 @@
       <c r="F5" s="16"/>
       <c r="G5" s="31"/>
       <c r="L5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N5" s="1">
         <v>4912</v>
@@ -9337,7 +9432,7 @@
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="N6" s="1">
         <v>101</v>
@@ -9351,10 +9446,10 @@
       <c r="F8" s="16"/>
       <c r="G8" s="53"/>
       <c r="L8" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="M8" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N8" s="1">
         <v>338</v>
@@ -9362,41 +9457,41 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F9" s="50" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G9" s="31"/>
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>164.15000000000146</v>
+        <v>4597.1500000000015</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I10" s="54" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="N10" s="46"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>164.15000000000146</v>
+        <v>4597.1500000000015</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>164.15000000000146</v>
+        <v>4597.1500000000015</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -9410,7 +9505,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
@@ -9419,7 +9514,7 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F13" s="74" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="74"/>
@@ -9430,7 +9525,7 @@
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
       <c r="F14" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="56"/>
@@ -9441,7 +9536,7 @@
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
       <c r="F15" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G15" s="56">
         <v>773.35</v>
@@ -9454,7 +9549,7 @@
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
       <c r="F16" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G16" s="56">
         <v>-5148</v>
@@ -9467,7 +9562,7 @@
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
       <c r="F17" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G17" s="56">
         <v>-168</v>
@@ -9480,7 +9575,7 @@
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
       <c r="F18" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="G18" s="56">
         <v>-1700</v>
@@ -9493,7 +9588,7 @@
       <c r="C19" s="56"/>
       <c r="D19" s="56"/>
       <c r="F19" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G19" s="56">
         <v>5148</v>
@@ -9506,7 +9601,7 @@
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
       <c r="F20" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G20" s="56">
         <v>-4938</v>
@@ -9519,7 +9614,7 @@
       <c r="C21" s="56"/>
       <c r="D21" s="56"/>
       <c r="F21" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G21" s="56">
         <v>-1595</v>
@@ -9532,7 +9627,7 @@
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
       <c r="F22" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G22" s="56">
         <v>-4677</v>
@@ -9545,7 +9640,7 @@
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
       <c r="F23" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G23" s="56">
         <v>-200</v>
@@ -9558,7 +9653,7 @@
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
       <c r="F24" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G24" s="56">
         <v>4677</v>
@@ -9571,7 +9666,7 @@
       <c r="C25" s="56"/>
       <c r="D25" s="56"/>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G25" s="56">
         <v>-750</v>
@@ -9584,7 +9679,7 @@
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
       <c r="F26" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G26" s="56">
         <v>-652</v>
@@ -9597,7 +9692,7 @@
       <c r="C27" s="56"/>
       <c r="D27" s="56"/>
       <c r="F27" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G27" s="56">
         <v>11100</v>
@@ -9610,7 +9705,7 @@
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
       <c r="F28" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G28" s="56">
         <v>-396</v>
@@ -9623,7 +9718,7 @@
       <c r="C29" s="56"/>
       <c r="D29" s="56"/>
       <c r="F29" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G29" s="56">
         <v>-4211</v>
@@ -9636,7 +9731,7 @@
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
       <c r="F30" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G30" s="56">
         <v>-450</v>
@@ -9649,7 +9744,7 @@
       <c r="C31" s="56"/>
       <c r="D31" s="56"/>
       <c r="F31" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G31" s="56">
         <v>-1197</v>
@@ -9675,7 +9770,7 @@
       <c r="C33" s="56"/>
       <c r="D33" s="56"/>
       <c r="F33" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G33" s="56">
         <v>-830</v>
@@ -9688,7 +9783,7 @@
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
       <c r="F34" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G34" s="56">
         <v>4211</v>
@@ -9701,7 +9796,7 @@
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
       <c r="F35" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="G35" s="56">
         <v>-200</v>
@@ -9714,7 +9809,7 @@
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
       <c r="F36" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G36" s="56">
         <v>10000</v>
@@ -9727,7 +9822,7 @@
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
       <c r="F37" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G37" s="56">
         <v>-200</v>
@@ -9740,7 +9835,7 @@
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
       <c r="F38" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G38" s="56">
         <v>-381</v>
@@ -9753,7 +9848,7 @@
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
       <c r="F39" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G39" s="56">
         <v>-4911</v>
@@ -9767,7 +9862,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G40" s="56">
         <v>-5700</v>
@@ -9780,7 +9875,7 @@
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
       <c r="F41" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G41" s="56">
         <v>-400</v>
@@ -9793,7 +9888,7 @@
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
       <c r="F42" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G42" s="56">
         <v>-450</v>
@@ -9806,7 +9901,7 @@
       <c r="C43" s="56"/>
       <c r="D43" s="56"/>
       <c r="F43" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G43" s="56">
         <v>-640</v>
@@ -9820,7 +9915,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G44" s="56">
         <v>5700</v>
@@ -9833,7 +9928,7 @@
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
       <c r="F45" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G45" s="56">
         <v>-130</v>
@@ -9846,7 +9941,7 @@
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
       <c r="F46" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G46" s="56">
         <v>-250</v>
@@ -9859,7 +9954,7 @@
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
       <c r="F47" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G47" s="56">
         <v>-112.2</v>
@@ -9872,7 +9967,7 @@
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
       <c r="F48" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G48" s="56">
         <v>4911</v>
@@ -9885,7 +9980,7 @@
       <c r="C49" s="56"/>
       <c r="D49" s="56"/>
       <c r="F49" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G49" s="56">
         <v>-3000</v>
@@ -9898,7 +9993,7 @@
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
       <c r="F50" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G50" s="56">
         <v>-4000</v>
@@ -9911,7 +10006,7 @@
       <c r="C51" s="56"/>
       <c r="D51" s="56"/>
       <c r="F51" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="G51" s="56">
         <v>-200</v>
@@ -9924,7 +10019,7 @@
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
       <c r="F52" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G52" s="56">
         <v>-4612</v>
@@ -9935,7 +10030,7 @@
     </row>
     <row r="53" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F53" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="G53" s="56">
         <v>-700</v>
@@ -9946,7 +10041,7 @@
     </row>
     <row r="54" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F54" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G54" s="56">
         <v>-880</v>
@@ -9957,7 +10052,7 @@
     </row>
     <row r="55" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F55" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G55" s="56">
         <v>-310</v>
@@ -9968,7 +10063,7 @@
     </row>
     <row r="56" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F56" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G56" s="56">
         <v>-250</v>
@@ -9979,7 +10074,7 @@
     </row>
     <row r="57" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G57" s="56">
         <v>4690</v>
@@ -9990,7 +10085,7 @@
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G58" s="56">
         <v>-4440</v>
@@ -10001,7 +10096,7 @@
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G59" s="56">
         <v>-4697</v>
@@ -10011,7 +10106,7 @@
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G60" s="56">
         <v>-2500</v>
@@ -10021,7 +10116,7 @@
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G61" s="56">
         <v>-126</v>
@@ -10031,7 +10126,7 @@
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G62" s="56">
         <v>4742</v>
@@ -10041,7 +10136,7 @@
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G63" s="56">
         <v>-410</v>
@@ -10056,7 +10151,7 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G65" s="56">
         <v>3320</v>
@@ -10066,7 +10161,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G66" s="56">
         <v>4090</v>
@@ -10076,7 +10171,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="G67" s="56">
         <v>-5688</v>
@@ -10086,7 +10181,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G68" s="56">
         <v>-4433</v>
@@ -10096,7 +10191,7 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F69" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G69" s="56">
         <v>-250</v>
@@ -10108,7 +10203,7 @@
       <c r="C70" s="56"/>
       <c r="D70" s="56"/>
       <c r="F70" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="G70" s="56">
         <v>-99</v>
@@ -10118,7 +10213,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="G71" s="56">
         <v>320</v>
@@ -10128,7 +10223,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F72" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="G72" s="56">
         <v>-1572</v>
@@ -10142,16 +10237,23 @@
       <c r="I73" s="56"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G74" s="56"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="F74" t="s">
+        <v>159</v>
+      </c>
+      <c r="G74" s="56">
+        <v>4433</v>
+      </c>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="C75" s="56">
-        <v>4433</v>
+        <v>8000</v>
       </c>
       <c r="D75" s="56"/>
       <c r="G75" s="56"/>
@@ -10159,19 +10261,19 @@
       <c r="I75" s="56"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>190</v>
-      </c>
-      <c r="C76" s="56">
-        <v>8000</v>
-      </c>
+      <c r="C76" s="56"/>
       <c r="D76" s="56"/>
       <c r="G76" s="56"/>
       <c r="H76" s="56"/>
       <c r="I76" s="56"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C77" s="56"/>
+      <c r="B77" t="s">
+        <v>202</v>
+      </c>
+      <c r="C77" s="56">
+        <v>-50</v>
+      </c>
       <c r="D77" s="56"/>
       <c r="G77" s="56"/>
       <c r="H77" s="56"/>
@@ -10179,44 +10281,44 @@
     </row>
     <row r="78" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C78" s="56">
-        <v>-90</v>
-      </c>
-      <c r="D78" s="56"/>
+        <v>500</v>
+      </c>
+      <c r="D78" s="56">
+        <v>300</v>
+      </c>
       <c r="G78" s="56"/>
       <c r="H78" s="56"/>
       <c r="I78" s="56"/>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C79" s="56">
-        <v>1000</v>
-      </c>
-      <c r="D79" s="56">
-        <v>300</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="D79" s="56"/>
       <c r="G79" s="56"/>
       <c r="H79" s="56"/>
       <c r="I79" s="56"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>193</v>
-      </c>
-      <c r="C80" s="56">
-        <v>8000</v>
-      </c>
+      <c r="C80" s="56"/>
       <c r="D80" s="56"/>
       <c r="G80" s="56"/>
       <c r="H80" s="56"/>
       <c r="I80" s="56"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C81" s="56"/>
+      <c r="B81" t="s">
+        <v>202</v>
+      </c>
+      <c r="C81" s="56">
+        <v>-90</v>
+      </c>
       <c r="D81" s="56"/>
       <c r="G81" s="56"/>
       <c r="H81" s="56"/>
@@ -10224,88 +10326,88 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="C82" s="56">
-        <v>-90</v>
-      </c>
-      <c r="D82" s="56"/>
+        <v>2000</v>
+      </c>
+      <c r="D82" s="56">
+        <v>300</v>
+      </c>
       <c r="G82" s="56"/>
       <c r="H82" s="56"/>
       <c r="I82" s="56"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="C83" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D83" s="56">
-        <v>300</v>
-      </c>
+        <v>-12807</v>
+      </c>
+      <c r="D83" s="56"/>
       <c r="G83" s="56"/>
       <c r="H83" s="56"/>
       <c r="I83" s="56"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>195</v>
-      </c>
-      <c r="C84" s="56">
-        <v>-12807</v>
-      </c>
+      <c r="C84" s="56"/>
       <c r="D84" s="56"/>
       <c r="G84" s="56"/>
       <c r="H84" s="56"/>
       <c r="I84" s="56"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C85" s="56"/>
+      <c r="B85" t="s">
+        <v>207</v>
+      </c>
+      <c r="C85" s="56">
+        <v>5520</v>
+      </c>
       <c r="D85" s="56"/>
       <c r="G85" s="56"/>
       <c r="H85" s="56"/>
       <c r="I85" s="56"/>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
-        <v>196</v>
-      </c>
-      <c r="C86" s="56">
-        <v>5520</v>
-      </c>
+      <c r="C86" s="56"/>
       <c r="D86" s="56"/>
       <c r="G86" s="56"/>
       <c r="H86" s="56"/>
       <c r="I86" s="56"/>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C87" s="56"/>
-      <c r="D87" s="56"/>
+      <c r="B87" t="s">
+        <v>208</v>
+      </c>
+      <c r="C87" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D87" s="56">
+        <v>300</v>
+      </c>
       <c r="G87" s="56"/>
       <c r="H87" s="56"/>
       <c r="I87" s="56"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C88" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D88" s="56">
-        <v>300</v>
-      </c>
+        <v>-90</v>
+      </c>
+      <c r="D88" s="56"/>
       <c r="G88" s="56"/>
       <c r="H88" s="56"/>
       <c r="I88" s="56"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C89" s="56">
-        <v>-90</v>
+        <v>240</v>
       </c>
       <c r="D89" s="56"/>
       <c r="G89" s="56"/>
@@ -10313,44 +10415,44 @@
       <c r="I89" s="56"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>198</v>
-      </c>
-      <c r="C90" s="56">
-        <v>240</v>
-      </c>
+      <c r="C90" s="56"/>
       <c r="D90" s="56"/>
       <c r="G90" s="56"/>
       <c r="H90" s="56"/>
       <c r="I90" s="56"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C91" s="56"/>
-      <c r="D91" s="56"/>
+      <c r="B91" t="s">
+        <v>210</v>
+      </c>
+      <c r="C91" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D91" s="56">
+        <v>300</v>
+      </c>
       <c r="G91" s="56"/>
       <c r="H91" s="56"/>
       <c r="I91" s="56"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C92" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D92" s="56">
-        <v>300</v>
-      </c>
+        <v>-50</v>
+      </c>
+      <c r="D92" s="56"/>
       <c r="G92" s="56"/>
       <c r="H92" s="56"/>
       <c r="I92" s="56"/>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C93" s="56">
-        <v>-50</v>
+        <v>300</v>
       </c>
       <c r="D93" s="56"/>
       <c r="G93" s="56"/>
@@ -10358,44 +10460,44 @@
       <c r="I93" s="56"/>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
-        <v>201</v>
-      </c>
-      <c r="C94" s="56">
-        <v>300</v>
-      </c>
+      <c r="C94" s="56"/>
       <c r="D94" s="56"/>
       <c r="G94" s="56"/>
       <c r="H94" s="56"/>
       <c r="I94" s="56"/>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C95" s="56"/>
-      <c r="D95" s="56"/>
+      <c r="B95" t="s">
+        <v>213</v>
+      </c>
+      <c r="C95" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D95" s="56">
+        <v>300</v>
+      </c>
       <c r="G95" s="56"/>
       <c r="H95" s="56"/>
       <c r="I95" s="56"/>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C96" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D96" s="56">
-        <v>300</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="D96" s="56"/>
       <c r="G96" s="56"/>
       <c r="H96" s="56"/>
       <c r="I96" s="56"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C97" s="56">
-        <v>8000</v>
+        <v>4180</v>
       </c>
       <c r="D97" s="56"/>
       <c r="G97" s="56"/>
@@ -10403,27 +10505,29 @@
       <c r="I97" s="56"/>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>204</v>
-      </c>
-      <c r="C98" s="56">
-        <v>4180</v>
-      </c>
+      <c r="C98" s="56"/>
       <c r="D98" s="56"/>
       <c r="G98" s="56"/>
       <c r="H98" s="56"/>
       <c r="I98" s="56"/>
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C99" s="56"/>
-      <c r="D99" s="56"/>
+      <c r="B99" t="s">
+        <v>216</v>
+      </c>
+      <c r="C99" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D99" s="56">
+        <v>300</v>
+      </c>
       <c r="G99" s="56"/>
       <c r="H99" s="56"/>
       <c r="I99" s="56"/>
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C100" s="56">
         <v>2000</v>
@@ -10437,7 +10541,7 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C101" s="56">
         <v>2000</v>
@@ -10450,48 +10554,48 @@
       <c r="I101" s="56"/>
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B102" t="s">
-        <v>207</v>
-      </c>
-      <c r="C102" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D102" s="56">
-        <v>300</v>
-      </c>
+      <c r="C102" s="56"/>
+      <c r="D102" s="56"/>
       <c r="G102" s="56"/>
       <c r="H102" s="56"/>
       <c r="I102" s="56"/>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C103" s="56"/>
+      <c r="B103" t="s">
+        <v>219</v>
+      </c>
+      <c r="C103" s="56">
+        <v>-20000</v>
+      </c>
       <c r="D103" s="56"/>
       <c r="G103" s="56"/>
       <c r="H103" s="56"/>
       <c r="I103" s="56"/>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
-        <v>208</v>
-      </c>
-      <c r="C104" s="56">
-        <v>-20000</v>
-      </c>
+      <c r="C104" s="56"/>
       <c r="D104" s="56"/>
       <c r="G104" s="56"/>
       <c r="H104" s="56"/>
       <c r="I104" s="56"/>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C105" s="56"/>
-      <c r="D105" s="56"/>
+      <c r="B105" t="s">
+        <v>220</v>
+      </c>
+      <c r="C105" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D105" s="56">
+        <v>300</v>
+      </c>
       <c r="G105" s="56"/>
       <c r="H105" s="56"/>
       <c r="I105" s="56"/>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C106" s="56">
         <v>2000</v>
@@ -10505,33 +10609,33 @@
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C107" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D107" s="56">
-        <v>300</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="D107" s="56"/>
       <c r="G107" s="56"/>
       <c r="H107" s="56"/>
       <c r="I107" s="56"/>
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C108" s="56">
-        <v>8000</v>
-      </c>
-      <c r="D108" s="56"/>
+        <v>2000</v>
+      </c>
+      <c r="D108" s="56">
+        <v>300</v>
+      </c>
       <c r="G108" s="56"/>
       <c r="H108" s="56"/>
       <c r="I108" s="56"/>
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C109" s="56">
         <v>2000</v>
@@ -10544,15 +10648,6 @@
       <c r="I109" s="56"/>
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
-        <v>213</v>
-      </c>
-      <c r="C110" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D110" s="56">
-        <v>300</v>
-      </c>
       <c r="G110" s="56"/>
       <c r="H110" s="56"/>
       <c r="I110" s="56"/>
@@ -11757,43 +11852,43 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
-  <conditionalFormatting sqref="B5:C5 C70:D70 C75:D110">
-    <cfRule type="cellIs" dxfId="9" priority="67" operator="greaterThan">
+  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D109">
+    <cfRule type="cellIs" dxfId="9" priority="85" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="68" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="86" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:D52">
-    <cfRule type="cellIs" dxfId="7" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="79" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="80" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G120:G1048576">
-    <cfRule type="cellIs" dxfId="5" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="81" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="64" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="82" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:I119">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H120:I266">
-    <cfRule type="cellIs" dxfId="1" priority="65" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="83" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="66" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11815,13 +11910,13 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="65" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -11829,77 +11924,77 @@
         <v>22</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D2" s="57"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="57" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="57" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D4" s="57"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="57" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D5" s="57"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="57" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D6" s="57"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="57" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D7" s="57"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="57" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D8" s="57"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="57" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C9" s="40"/>
       <c r="D9" s="57"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="57" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D10" s="57"/>
     </row>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09D21FCF-1DF7-421D-AC92-8322B8783B7C}"/>
+  <xr:revisionPtr revIDLastSave="502" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F272B33-3F1B-4C41-9739-6500E325DEFA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="249">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -378,15 +378,9 @@
     <t>Psicóloga</t>
   </si>
   <si>
-    <t>pontual</t>
-  </si>
-  <si>
     <t>Bonfas Chope</t>
   </si>
   <si>
-    <t>Cm</t>
-  </si>
-  <si>
     <t>Bonfas Lanche</t>
   </si>
   <si>
@@ -775,6 +769,30 @@
   </si>
   <si>
     <t>Baked Potato</t>
+  </si>
+  <si>
+    <t>Pão e Frios</t>
+  </si>
+  <si>
+    <t>Bares Augusta</t>
+  </si>
+  <si>
+    <t>Ajuste</t>
+  </si>
+  <si>
+    <t>PAGAMENTO</t>
+  </si>
+  <si>
+    <t>Comida</t>
+  </si>
+  <si>
+    <t>Pet</t>
+  </si>
+  <si>
+    <t>Roupas</t>
+  </si>
+  <si>
+    <t>Carro</t>
   </si>
 </sst>
 </file>
@@ -1326,6 +1344,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79989013336588644"/>
         </patternFill>
       </fill>
@@ -1347,14 +1372,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1437,10 +1454,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1695,12 +1708,12 @@
       <c r="B3" s="76"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C22+C23+C7</f>
-        <v>2098.2464047619037</v>
+        <v>2125.3614047619035</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E22+E23</f>
-        <v>3520.8625000000011</v>
+        <v>3643.8775000000005</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1722,12 +1735,12 @@
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-7939.7535952380968</v>
+        <v>-7912.638595238097</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-5479.1374999999998</v>
+        <v>-5356.1225000000004</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1758,12 +1771,12 @@
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5517.5219285714293</v>
+        <v>5490.4069285714295</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>2097.0674999999997</v>
+        <v>1974.0525000000002</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -1772,12 +1785,12 @@
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5517.5219285714293</v>
+        <v>5490.4069285714295</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>2097.0674999999997</v>
+        <v>1974.0525000000002</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
@@ -2150,11 +2163,11 @@
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>2097.0674999999997</v>
+        <v>1974.0525000000002</v>
       </c>
       <c r="D4" s="27">
         <f>Saldo!C9+D5</f>
-        <v>5517.5219285714293</v>
+        <v>5490.4069285714295</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -2258,7 +2271,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4144.7524999999996</v>
+        <v>4021.7375000000002</v>
       </c>
       <c r="D17" s="30"/>
     </row>
@@ -2982,7 +2995,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3031,15 +3044,15 @@
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="48">
         <f>SUM(L6:L377)</f>
-        <v>7681.5594285714278</v>
+        <v>7531.4294285714286</v>
       </c>
       <c r="E2" s="35">
         <f>SUMIF($E$6:$E$377,E1,$M$6:$M$377)</f>
-        <v>5517.5219285714293</v>
+        <v>5490.4069285714295</v>
       </c>
       <c r="F2" s="35">
         <f>SUMIF($F$6:$F$377,F1,$M$6:$M$377)</f>
-        <v>2097.0674999999997</v>
+        <v>1974.0525000000002</v>
       </c>
       <c r="G2" s="35">
         <f>SUMIF($G$6:$G$377,G1,$M$6:$M$377)</f>
@@ -3102,148 +3115,148 @@
     </row>
     <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="38"/>
-      <c r="D6" s="39" t="s">
-        <v>48</v>
+      <c r="D6" s="49" t="s">
+        <v>104</v>
       </c>
       <c r="E6" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="40"/>
+      <c r="F6" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G6" s="40"/>
       <c r="H6" s="40">
         <f t="shared" ref="H6:H37" si="0">COUNTA(E6:G6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="41">
-        <v>258</v>
-      </c>
-      <c r="J6" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="40" t="s">
-        <v>50</v>
+        <v>1780</v>
+      </c>
+      <c r="J6" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="L6" s="41">
         <f t="shared" ref="L6:L37" si="1">I6/N6</f>
-        <v>86</v>
+        <v>222.5</v>
       </c>
       <c r="M6" s="41">
         <f t="shared" ref="M6:M37" si="2">IFERROR(L6/H6,"")</f>
-        <v>86</v>
+        <v>111.25</v>
       </c>
       <c r="N6" s="42">
-        <v>3</v>
-      </c>
-      <c r="O6" s="67">
-        <v>46056</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O6" s="67"/>
       <c r="P6" s="67">
         <f t="shared" ref="P6:P37" si="3">IF(N6&lt;&gt;1,EDATE(O6,N6-1),"")</f>
-        <v>46115</v>
-      </c>
-      <c r="Q6" s="40">
-        <f t="shared" ref="Q6:Q17" ca="1" si="4">IF(O6&lt;&gt;"",IFERROR(DATEDIF(O6,TODAY(),"m")+1,""),"")</f>
-        <v>6</v>
+        <v>213</v>
+      </c>
+      <c r="Q6" s="40" t="str">
+        <f ca="1">IF(O6&lt;&gt;"",IFERROR(DATEDIF(O6,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="38"/>
-      <c r="D7" s="49" t="s">
-        <v>51</v>
+      <c r="D7" s="39" t="s">
+        <v>72</v>
       </c>
       <c r="E7" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="40"/>
+      <c r="F7" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G7" s="40"/>
       <c r="H7" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="41">
-        <v>1909.3</v>
+        <v>392</v>
       </c>
       <c r="J7" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="41" t="s">
-        <v>52</v>
+        <v>44</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>54</v>
       </c>
       <c r="L7" s="41">
         <f t="shared" si="1"/>
-        <v>190.93</v>
+        <v>196</v>
       </c>
       <c r="M7" s="41">
         <f t="shared" si="2"/>
-        <v>190.93</v>
+        <v>98</v>
       </c>
       <c r="N7" s="42">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O7" s="67">
-        <v>46025</v>
+        <v>46056</v>
       </c>
       <c r="P7" s="67">
         <f t="shared" si="3"/>
-        <v>46298</v>
+        <v>46084</v>
       </c>
       <c r="Q7" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <f ca="1">IF(O7&lt;&gt;"",IFERROR(DATEDIF(O7,TODAY(),"m")+1,""),"")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C8" s="38"/>
       <c r="D8" s="39" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E8" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F8" s="40"/>
       <c r="G8" s="40"/>
       <c r="H8" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="41">
-        <v>1017.6</v>
+        <v>258</v>
       </c>
       <c r="J8" s="41" t="s">
         <v>49</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L8" s="41">
         <f t="shared" si="1"/>
-        <v>84.8</v>
+        <v>86</v>
       </c>
       <c r="M8" s="41">
         <f t="shared" si="2"/>
-        <v>42.4</v>
+        <v>86</v>
       </c>
       <c r="N8" s="42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O8" s="67">
-        <v>46084</v>
+        <v>46056</v>
       </c>
       <c r="P8" s="67">
         <f t="shared" si="3"/>
-        <v>46421</v>
+        <v>46115</v>
       </c>
       <c r="Q8" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <f ca="1">IF(O8&lt;&gt;"",IFERROR(DATEDIF(O8,TODAY(),"m")+1,""),"")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="38"/>
-      <c r="D9" s="49" t="s">
-        <v>55</v>
+      <c r="D9" s="69" t="s">
+        <v>73</v>
       </c>
       <c r="E9" s="40" t="s">
         <v>1</v>
@@ -3257,317 +3270,311 @@
         <v>2</v>
       </c>
       <c r="I9" s="41">
-        <v>224.24</v>
+        <v>3219</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K9" s="41" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L9" s="41">
         <f t="shared" si="1"/>
-        <v>18.686666666666667</v>
+        <v>268.25</v>
       </c>
       <c r="M9" s="41">
         <f t="shared" si="2"/>
-        <v>9.3433333333333337</v>
+        <v>134.125</v>
       </c>
       <c r="N9" s="42">
         <v>12</v>
       </c>
       <c r="O9" s="67">
-        <v>46176</v>
+        <v>45903</v>
       </c>
       <c r="P9" s="67">
         <f t="shared" si="3"/>
-        <v>46510</v>
+        <v>46237</v>
       </c>
       <c r="Q9" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <f ca="1">IF(O9&lt;&gt;"",IFERROR(DATEDIF(O9,TODAY(),"m")+1,""),"")</f>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="38"/>
-      <c r="D10" s="39" t="s">
-        <v>57</v>
+      <c r="D10" s="69" t="s">
+        <v>75</v>
       </c>
       <c r="E10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F10" s="40"/>
       <c r="G10" s="40"/>
       <c r="H10" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="41">
-        <v>22.45</v>
+        <v>1700</v>
       </c>
       <c r="J10" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="40" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="K10" s="41" t="s">
+        <v>52</v>
       </c>
       <c r="L10" s="41">
         <f t="shared" si="1"/>
-        <v>22.45</v>
+        <v>283.33333333333331</v>
       </c>
       <c r="M10" s="41">
         <f t="shared" si="2"/>
-        <v>11.225</v>
+        <v>283.33333333333331</v>
       </c>
       <c r="N10" s="42">
-        <v>1</v>
-      </c>
-      <c r="O10" s="67"/>
-      <c r="P10" s="67" t="str">
+        <v>6</v>
+      </c>
+      <c r="O10" s="67">
+        <v>46084</v>
+      </c>
+      <c r="P10" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q10" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>46237</v>
+      </c>
+      <c r="Q10" s="40">
+        <f ca="1">IF(O10&lt;&gt;"",IFERROR(DATEDIF(O10,TODAY(),"m")+1,""),"")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C11" s="38"/>
-      <c r="D11" s="49" t="s">
-        <v>58</v>
+      <c r="D11" s="69" t="s">
+        <v>76</v>
       </c>
       <c r="E11" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F11" s="40"/>
       <c r="G11" s="40"/>
       <c r="H11" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="41">
-        <v>60</v>
+        <v>208</v>
       </c>
       <c r="J11" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="40" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="L11" s="41">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="M11" s="41">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="N11" s="42">
-        <v>1</v>
-      </c>
-      <c r="O11" s="67"/>
-      <c r="P11" s="67" t="str">
+        <v>4</v>
+      </c>
+      <c r="O11" s="67">
+        <v>46145</v>
+      </c>
+      <c r="P11" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q11" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
+        <v>46237</v>
+      </c>
+      <c r="Q11" s="40"/>
     </row>
     <row r="12" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C12" s="38"/>
-      <c r="D12" s="39" t="s">
-        <v>59</v>
+      <c r="D12" s="69" t="s">
+        <v>77</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F12" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F12" s="40"/>
       <c r="G12" s="40"/>
       <c r="H12" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="41">
-        <v>395.54</v>
+        <v>128.99</v>
       </c>
       <c r="J12" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="40" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="K12" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="L12" s="41">
         <f t="shared" si="1"/>
-        <v>395.54</v>
+        <v>42.99666666666667</v>
       </c>
       <c r="M12" s="41">
         <f t="shared" si="2"/>
-        <v>197.77</v>
+        <v>42.99666666666667</v>
       </c>
       <c r="N12" s="42">
-        <v>1</v>
-      </c>
-      <c r="O12" s="67"/>
-      <c r="P12" s="67" t="str">
+        <v>3</v>
+      </c>
+      <c r="O12" s="67">
+        <v>46176</v>
+      </c>
+      <c r="P12" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q12" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>46237</v>
+      </c>
+      <c r="Q12" s="40">
+        <f ca="1">IF(O12&lt;&gt;"",IFERROR(DATEDIF(O12,TODAY(),"m")+1,""),"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C13" s="38"/>
-      <c r="D13" s="39" t="s">
-        <v>60</v>
+      <c r="D13" s="68" t="s">
+        <v>78</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F13" s="40"/>
       <c r="G13" s="40"/>
       <c r="H13" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="41">
-        <v>215</v>
+        <v>419</v>
       </c>
       <c r="J13" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="40" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="K13" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="L13" s="41">
         <f t="shared" si="1"/>
-        <v>215</v>
+        <v>41.9</v>
       </c>
       <c r="M13" s="41">
         <f t="shared" si="2"/>
-        <v>107.5</v>
+        <v>41.9</v>
       </c>
       <c r="N13" s="42">
-        <v>1</v>
-      </c>
-      <c r="O13" s="67"/>
-      <c r="P13" s="67" t="str">
+        <v>10</v>
+      </c>
+      <c r="O13" s="67">
+        <v>45994</v>
+      </c>
+      <c r="P13" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q13" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>46268</v>
+      </c>
+      <c r="Q13" s="40">
+        <f ca="1">IF(O13&lt;&gt;"",IFERROR(DATEDIF(O13,TODAY(),"m")+1,""),"")</f>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="38"/>
-      <c r="D14" s="49" t="s">
-        <v>61</v>
+      <c r="D14" s="68" t="s">
+        <v>79</v>
       </c>
       <c r="E14" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F14" s="40"/>
       <c r="G14" s="40"/>
       <c r="H14" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="41">
-        <v>225</v>
+        <v>419</v>
       </c>
       <c r="J14" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="40" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="K14" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="L14" s="41">
         <f t="shared" si="1"/>
-        <v>225</v>
+        <v>41.9</v>
       </c>
       <c r="M14" s="41">
         <f t="shared" si="2"/>
-        <v>112.5</v>
+        <v>41.9</v>
       </c>
       <c r="N14" s="42">
-        <v>1</v>
-      </c>
-      <c r="O14" s="67"/>
-      <c r="P14" s="67" t="str">
+        <v>10</v>
+      </c>
+      <c r="O14" s="67">
+        <v>45994</v>
+      </c>
+      <c r="P14" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q14" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>46268</v>
+      </c>
+      <c r="Q14" s="40">
+        <f ca="1">IF(O14&lt;&gt;"",IFERROR(DATEDIF(O14,TODAY(),"m")+1,""),"")</f>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="38"/>
-      <c r="D15" s="39" t="s">
-        <v>62</v>
+      <c r="D15" s="68" t="s">
+        <v>80</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F15" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F15" s="40"/>
       <c r="G15" s="40"/>
       <c r="H15" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="41">
-        <v>166.15</v>
+        <v>440</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" s="40" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="L15" s="41">
         <f t="shared" si="1"/>
-        <v>166.15</v>
+        <v>88</v>
       </c>
       <c r="M15" s="41">
         <f t="shared" si="2"/>
-        <v>83.075000000000003</v>
+        <v>88</v>
       </c>
       <c r="N15" s="42">
-        <v>1</v>
-      </c>
-      <c r="O15" s="67"/>
-      <c r="P15" s="67" t="str">
+        <v>5</v>
+      </c>
+      <c r="O15" s="67">
+        <v>46145</v>
+      </c>
+      <c r="P15" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q15" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
+        <v>46268</v>
+      </c>
+      <c r="Q15" s="40"/>
     </row>
     <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" s="38"/>
-      <c r="D16" s="49" t="s">
-        <v>63</v>
+      <c r="D16" s="68" t="s">
+        <v>81</v>
       </c>
       <c r="E16" s="40" t="s">
         <v>1</v>
@@ -3579,83 +3586,87 @@
         <v>1</v>
       </c>
       <c r="I16" s="41">
-        <v>284.05</v>
+        <v>313.83999999999997</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K16" s="41" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="L16" s="41">
         <f t="shared" si="1"/>
-        <v>284.05</v>
+        <v>78.459999999999994</v>
       </c>
       <c r="M16" s="41">
         <f t="shared" si="2"/>
-        <v>284.05</v>
+        <v>78.459999999999994</v>
       </c>
       <c r="N16" s="42">
-        <v>1</v>
-      </c>
-      <c r="O16" s="67"/>
-      <c r="P16" s="67" t="str">
+        <v>4</v>
+      </c>
+      <c r="O16" s="67">
+        <v>46176</v>
+      </c>
+      <c r="P16" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q16" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>46268</v>
+      </c>
+      <c r="Q16" s="40">
+        <f t="shared" ref="Q16:Q29" ca="1" si="4">IF(O16&lt;&gt;"",IFERROR(DATEDIF(O16,TODAY(),"m")+1,""),"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="38"/>
-      <c r="D17" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="40"/>
+      <c r="D17" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G17" s="40"/>
       <c r="H17" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I17" s="41">
-        <v>110</v>
+        <v>244.51</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K17" s="41" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="L17" s="41">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>61.127499999999998</v>
       </c>
       <c r="M17" s="41">
         <f t="shared" si="2"/>
-        <v>110</v>
+        <v>61.127499999999998</v>
       </c>
       <c r="N17" s="42">
-        <v>1</v>
-      </c>
-      <c r="O17" s="67"/>
-      <c r="P17" s="67" t="str">
+        <v>4</v>
+      </c>
+      <c r="O17" s="67">
+        <v>46176</v>
+      </c>
+      <c r="P17" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q17" s="40" t="str">
+        <v>46268</v>
+      </c>
+      <c r="Q17" s="40">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="38"/>
-      <c r="D18" s="49" t="s">
-        <v>65</v>
+      <c r="D18" s="68" t="s">
+        <v>84</v>
       </c>
       <c r="E18" s="40" t="s">
         <v>1</v>
@@ -3667,82 +3678,87 @@
         <v>1</v>
       </c>
       <c r="I18" s="41">
-        <v>117</v>
+        <v>628</v>
       </c>
       <c r="J18" s="41" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K18" s="41" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="L18" s="41">
         <f t="shared" si="1"/>
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="M18" s="41">
         <f t="shared" si="2"/>
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="N18" s="42">
-        <v>1</v>
-      </c>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67" t="str">
+        <v>4</v>
+      </c>
+      <c r="O18" s="67">
+        <v>46176</v>
+      </c>
+      <c r="P18" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q18" s="40"/>
+        <v>46268</v>
+      </c>
+      <c r="Q18" s="40">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" s="38"/>
-      <c r="D19" s="39" t="s">
-        <v>67</v>
+      <c r="D19" s="72" t="s">
+        <v>51</v>
       </c>
       <c r="E19" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F19" s="40"/>
       <c r="G19" s="40"/>
       <c r="H19" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="41">
-        <v>19.899999999999999</v>
+        <v>1909.3</v>
       </c>
       <c r="J19" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="K19" s="40" t="s">
-        <v>49</v>
+      <c r="K19" s="41" t="s">
+        <v>52</v>
       </c>
       <c r="L19" s="41">
         <f t="shared" si="1"/>
-        <v>19.899999999999999</v>
+        <v>190.93</v>
       </c>
       <c r="M19" s="41">
         <f t="shared" si="2"/>
-        <v>9.9499999999999993</v>
+        <v>190.93</v>
       </c>
       <c r="N19" s="42">
-        <v>1</v>
-      </c>
-      <c r="O19" s="67"/>
-      <c r="P19" s="67" t="str">
+        <v>10</v>
+      </c>
+      <c r="O19" s="67">
+        <v>46025</v>
+      </c>
+      <c r="P19" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q19" s="40" t="str">
-        <f ca="1">IF(O19&lt;&gt;"",IFERROR(DATEDIF(O19,TODAY(),"m")+1,""),"")</f>
-        <v/>
+        <v>46298</v>
+      </c>
+      <c r="Q19" s="40">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" s="38"/>
-      <c r="D20" s="39" t="s">
-        <v>68</v>
+      <c r="D20" s="72" t="s">
+        <v>86</v>
       </c>
       <c r="E20" s="40" t="s">
         <v>1</v>
@@ -3754,39 +3770,41 @@
         <v>1</v>
       </c>
       <c r="I20" s="41">
-        <v>26.9</v>
+        <v>659</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="40" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="K20" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="L20" s="41">
         <f t="shared" si="1"/>
-        <v>26.9</v>
+        <v>54.916666666666664</v>
       </c>
       <c r="M20" s="41">
         <f t="shared" si="2"/>
-        <v>26.9</v>
+        <v>54.916666666666664</v>
       </c>
       <c r="N20" s="42">
-        <v>1</v>
-      </c>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67" t="str">
+        <v>12</v>
+      </c>
+      <c r="O20" s="67">
+        <v>45964</v>
+      </c>
+      <c r="P20" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q20" s="40" t="str">
-        <f ca="1">IF(O20&lt;&gt;"",IFERROR(DATEDIF(O20,TODAY(),"m")+1,""),"")</f>
-        <v/>
+        <v>46298</v>
+      </c>
+      <c r="Q20" s="40">
+        <f t="shared" ca="1" si="4"/>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" s="38"/>
-      <c r="D21" s="49" t="s">
-        <v>69</v>
+      <c r="D21" s="72" t="s">
+        <v>87</v>
       </c>
       <c r="E21" s="40" t="s">
         <v>1</v>
@@ -3798,36 +3816,41 @@
         <v>1</v>
       </c>
       <c r="I21" s="41">
-        <v>70</v>
+        <v>2319.3000000000002</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K21" s="41" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="L21" s="41">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>193.27500000000001</v>
       </c>
       <c r="M21" s="41">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>193.27500000000001</v>
       </c>
       <c r="N21" s="42">
-        <v>1</v>
-      </c>
-      <c r="O21" s="67"/>
-      <c r="P21" s="67" t="str">
+        <v>12</v>
+      </c>
+      <c r="O21" s="67">
+        <v>45964</v>
+      </c>
+      <c r="P21" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q21" s="40"/>
+        <v>46298</v>
+      </c>
+      <c r="Q21" s="40">
+        <f t="shared" ca="1" si="4"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" s="38"/>
-      <c r="D22" s="70" t="s">
-        <v>70</v>
+      <c r="D22" s="72" t="s">
+        <v>88</v>
       </c>
       <c r="E22" s="40" t="s">
         <v>1</v>
@@ -3839,39 +3862,41 @@
         <v>1</v>
       </c>
       <c r="I22" s="41">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="J22" s="41" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K22" s="41" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="L22" s="41">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>166.66666666666666</v>
       </c>
       <c r="M22" s="41">
         <f t="shared" si="2"/>
-        <v>400</v>
+        <v>166.66666666666666</v>
       </c>
       <c r="N22" s="42">
-        <v>1</v>
-      </c>
-      <c r="O22" s="67"/>
-      <c r="P22" s="67" t="str">
+        <v>12</v>
+      </c>
+      <c r="O22" s="67">
+        <v>45964</v>
+      </c>
+      <c r="P22" s="67">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q22" s="40" t="str">
-        <f ca="1">IF(O22&lt;&gt;"",IFERROR(DATEDIF(O22,TODAY(),"m")+1,""),"")</f>
-        <v/>
+        <v>46298</v>
+      </c>
+      <c r="Q22" s="40">
+        <f t="shared" ca="1" si="4"/>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" s="38"/>
-      <c r="D23" s="49" t="s">
-        <v>71</v>
+      <c r="D23" s="72" t="s">
+        <v>90</v>
       </c>
       <c r="E23" s="40" t="s">
         <v>1</v>
@@ -3885,226 +3910,221 @@
         <v>2</v>
       </c>
       <c r="I23" s="41">
-        <v>22</v>
+        <v>725</v>
       </c>
       <c r="J23" s="41" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K23" s="41" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="L23" s="41">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>120.83333333333333</v>
       </c>
       <c r="M23" s="41">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>60.416666666666664</v>
       </c>
       <c r="N23" s="42">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O23" s="67">
-        <v>46206</v>
-      </c>
-      <c r="P23" s="67" t="str">
+        <v>46145</v>
+      </c>
+      <c r="P23" s="67">
         <f t="shared" si="3"/>
-        <v/>
+        <v>46298</v>
       </c>
       <c r="Q23" s="40">
-        <f ca="1">IF(O23&lt;&gt;"",IFERROR(DATEDIF(O23,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" s="38"/>
-      <c r="D24" s="39" t="s">
-        <v>72</v>
+      <c r="D24" s="72" t="s">
+        <v>102</v>
       </c>
       <c r="E24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F24" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F24" s="40"/>
       <c r="G24" s="40"/>
       <c r="H24" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="41">
-        <v>392</v>
+        <v>372.43</v>
       </c>
       <c r="J24" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="K24" s="40" t="s">
-        <v>54</v>
+      <c r="K24" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="L24" s="41">
         <f t="shared" si="1"/>
-        <v>196</v>
+        <v>93.107500000000002</v>
       </c>
       <c r="M24" s="41">
         <f t="shared" si="2"/>
-        <v>98</v>
+        <v>93.107500000000002</v>
       </c>
       <c r="N24" s="42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O24" s="67">
-        <v>46056</v>
+        <v>46206</v>
       </c>
       <c r="P24" s="67">
         <f t="shared" si="3"/>
-        <v>46084</v>
+        <v>46298</v>
       </c>
       <c r="Q24" s="40">
-        <f ca="1">IF(O24&lt;&gt;"",IFERROR(DATEDIF(O24,TODAY(),"m")+1,""),"")</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" s="38"/>
-      <c r="D25" s="69" t="s">
-        <v>73</v>
+      <c r="D25" s="72" t="s">
+        <v>238</v>
       </c>
       <c r="E25" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F25" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F25" s="40"/>
       <c r="G25" s="40"/>
       <c r="H25" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="41">
-        <v>3219</v>
+        <v>72</v>
       </c>
       <c r="J25" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="K25" s="41" t="s">
-        <v>74</v>
-      </c>
+      <c r="K25" s="41"/>
       <c r="L25" s="41">
         <f t="shared" si="1"/>
-        <v>268.25</v>
+        <v>24</v>
       </c>
       <c r="M25" s="41">
         <f t="shared" si="2"/>
-        <v>134.125</v>
+        <v>24</v>
       </c>
       <c r="N25" s="42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O25" s="67">
-        <v>45903</v>
+        <v>46240</v>
       </c>
       <c r="P25" s="67">
         <f t="shared" si="3"/>
-        <v>46237</v>
-      </c>
-      <c r="Q25" s="40">
-        <f ca="1">IF(O25&lt;&gt;"",IFERROR(DATEDIF(O25,TODAY(),"m")+1,""),"")</f>
-        <v>11</v>
+        <v>46301</v>
+      </c>
+      <c r="Q25" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="38"/>
-      <c r="D26" s="69" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="40"/>
+      <c r="D26" s="72" t="s">
+        <v>239</v>
+      </c>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G26" s="40"/>
       <c r="H26" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I26" s="41">
-        <v>1700</v>
+        <v>161.72999999999999</v>
       </c>
       <c r="J26" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="K26" s="41" t="s">
-        <v>52</v>
-      </c>
+      <c r="K26" s="41"/>
       <c r="L26" s="41">
         <f t="shared" si="1"/>
-        <v>283.33333333333331</v>
+        <v>53.91</v>
       </c>
       <c r="M26" s="41">
         <f t="shared" si="2"/>
-        <v>283.33333333333331</v>
+        <v>53.91</v>
       </c>
       <c r="N26" s="42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O26" s="67">
-        <v>46084</v>
+        <v>46240</v>
       </c>
       <c r="P26" s="67">
         <f t="shared" si="3"/>
-        <v>46237</v>
-      </c>
-      <c r="Q26" s="40">
-        <f ca="1">IF(O26&lt;&gt;"",IFERROR(DATEDIF(O26,TODAY(),"m")+1,""),"")</f>
-        <v>5</v>
+        <v>46301</v>
+      </c>
+      <c r="Q26" s="40" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="38"/>
-      <c r="D27" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="40"/>
+      <c r="D27" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G27" s="40"/>
       <c r="H27" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I27" s="41">
-        <v>208</v>
+        <v>973.02</v>
       </c>
       <c r="J27" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K27" s="41" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="L27" s="41">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>81.084999999999994</v>
       </c>
       <c r="M27" s="41">
         <f t="shared" si="2"/>
-        <v>52</v>
+        <v>81.084999999999994</v>
       </c>
       <c r="N27" s="42">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O27" s="67">
-        <v>46145</v>
+        <v>45994</v>
       </c>
       <c r="P27" s="67">
         <f t="shared" si="3"/>
-        <v>46237</v>
-      </c>
-      <c r="Q27" s="40"/>
+        <v>46329</v>
+      </c>
+      <c r="Q27" s="40">
+        <f t="shared" ca="1" si="4"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="38"/>
-      <c r="D28" s="69" t="s">
-        <v>77</v>
+      <c r="D28" s="49" t="s">
+        <v>92</v>
       </c>
       <c r="E28" s="40" t="s">
         <v>1</v>
@@ -4116,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="41">
-        <v>128.99</v>
+        <v>379</v>
       </c>
       <c r="J28" s="41" t="s">
         <v>44</v>
@@ -4126,31 +4146,31 @@
       </c>
       <c r="L28" s="41">
         <f t="shared" si="1"/>
-        <v>42.99666666666667</v>
+        <v>54.142857142857146</v>
       </c>
       <c r="M28" s="41">
         <f t="shared" si="2"/>
-        <v>42.99666666666667</v>
+        <v>54.142857142857146</v>
       </c>
       <c r="N28" s="42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O28" s="67">
-        <v>46176</v>
+        <v>46145</v>
       </c>
       <c r="P28" s="67">
         <f t="shared" si="3"/>
-        <v>46237</v>
+        <v>46329</v>
       </c>
       <c r="Q28" s="40">
-        <f ca="1">IF(O28&lt;&gt;"",IFERROR(DATEDIF(O28,TODAY(),"m")+1,""),"")</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="38"/>
-      <c r="D29" s="68" t="s">
-        <v>78</v>
+      <c r="D29" s="49" t="s">
+        <v>93</v>
       </c>
       <c r="E29" s="40" t="s">
         <v>1</v>
@@ -4162,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="41">
-        <v>419</v>
+        <v>297</v>
       </c>
       <c r="J29" s="41" t="s">
         <v>44</v>
@@ -4172,43 +4192,45 @@
       </c>
       <c r="L29" s="41">
         <f t="shared" si="1"/>
-        <v>41.9</v>
+        <v>49.5</v>
       </c>
       <c r="M29" s="41">
         <f t="shared" si="2"/>
-        <v>41.9</v>
+        <v>49.5</v>
       </c>
       <c r="N29" s="42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O29" s="67">
-        <v>45994</v>
+        <v>46176</v>
       </c>
       <c r="P29" s="67">
         <f t="shared" si="3"/>
-        <v>46268</v>
+        <v>46329</v>
       </c>
       <c r="Q29" s="40">
-        <f ca="1">IF(O29&lt;&gt;"",IFERROR(DATEDIF(O29,TODAY(),"m")+1,""),"")</f>
-        <v>8</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="38"/>
-      <c r="D30" s="68" t="s">
-        <v>79</v>
+      <c r="D30" s="49" t="s">
+        <v>94</v>
       </c>
       <c r="E30" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="40"/>
+      <c r="F30" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="41">
-        <v>419</v>
+        <v>506</v>
       </c>
       <c r="J30" s="41" t="s">
         <v>44</v>
@@ -4218,31 +4240,28 @@
       </c>
       <c r="L30" s="41">
         <f t="shared" si="1"/>
-        <v>41.9</v>
+        <v>50.6</v>
       </c>
       <c r="M30" s="41">
         <f t="shared" si="2"/>
-        <v>41.9</v>
+        <v>25.3</v>
       </c>
       <c r="N30" s="42">
         <v>10</v>
       </c>
       <c r="O30" s="67">
-        <v>45994</v>
+        <v>46115</v>
       </c>
       <c r="P30" s="67">
         <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q30" s="40">
-        <f ca="1">IF(O30&lt;&gt;"",IFERROR(DATEDIF(O30,TODAY(),"m")+1,""),"")</f>
-        <v>8</v>
-      </c>
+        <v>46390</v>
+      </c>
+      <c r="Q30" s="40"/>
     </row>
     <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="38"/>
-      <c r="D31" s="68" t="s">
-        <v>80</v>
+      <c r="D31" s="49" t="s">
+        <v>101</v>
       </c>
       <c r="E31" s="40" t="s">
         <v>1</v>
@@ -4254,50 +4273,51 @@
         <v>1</v>
       </c>
       <c r="I31" s="41">
-        <v>440</v>
+        <v>399.9</v>
       </c>
       <c r="J31" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K31" s="41" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="L31" s="41">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>57.128571428571426</v>
       </c>
       <c r="M31" s="41">
         <f t="shared" si="2"/>
-        <v>88</v>
+        <v>57.128571428571426</v>
       </c>
       <c r="N31" s="42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O31" s="67">
-        <v>46145</v>
+        <v>46206</v>
       </c>
       <c r="P31" s="67">
         <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q31" s="40"/>
+        <v>46390</v>
+      </c>
+      <c r="Q31" s="40">
+        <f t="shared" ref="Q31:Q48" ca="1" si="5">IF(O31&lt;&gt;"",IFERROR(DATEDIF(O31,TODAY(),"m")+1,""),"")</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="38"/>
-      <c r="D32" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>1</v>
-      </c>
+      <c r="D32" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32" s="40"/>
       <c r="F32" s="40"/>
       <c r="G32" s="40"/>
       <c r="H32" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="41">
-        <v>313.83999999999997</v>
+        <v>300</v>
       </c>
       <c r="J32" s="41" t="s">
         <v>44</v>
@@ -4307,123 +4327,125 @@
       </c>
       <c r="L32" s="41">
         <f t="shared" si="1"/>
-        <v>78.459999999999994</v>
-      </c>
-      <c r="M32" s="41">
+        <v>50</v>
+      </c>
+      <c r="M32" s="41" t="str">
         <f t="shared" si="2"/>
-        <v>78.459999999999994</v>
+        <v/>
       </c>
       <c r="N32" s="42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O32" s="67">
-        <v>46176</v>
+        <v>46237</v>
       </c>
       <c r="P32" s="67">
         <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q32" s="40">
-        <f t="shared" ref="Q32:Q41" ca="1" si="5">IF(O32&lt;&gt;"",IFERROR(DATEDIF(O32,TODAY(),"m")+1,""),"")</f>
-        <v>2</v>
+        <v>46390</v>
+      </c>
+      <c r="Q32" s="40" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
       </c>
     </row>
     <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C33" s="38"/>
-      <c r="D33" s="68" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="D33" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="40"/>
       <c r="G33" s="40"/>
       <c r="H33" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I33" s="41">
-        <v>244.51</v>
+        <v>284</v>
       </c>
       <c r="J33" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K33" s="41" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L33" s="41">
         <f t="shared" si="1"/>
-        <v>61.127499999999998</v>
+        <v>47.333333333333336</v>
       </c>
       <c r="M33" s="41">
         <f t="shared" si="2"/>
-        <v>61.127499999999998</v>
+        <v>47.333333333333336</v>
       </c>
       <c r="N33" s="42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O33" s="67">
-        <v>46176</v>
+        <v>46237</v>
       </c>
       <c r="P33" s="67">
         <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q33" s="40">
+        <v>46390</v>
+      </c>
+      <c r="Q33" s="40" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="34" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C34" s="38"/>
-      <c r="D34" s="68" t="s">
-        <v>84</v>
+      <c r="D34" s="39" t="s">
+        <v>53</v>
       </c>
       <c r="E34" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F34" s="40"/>
+      <c r="F34" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G34" s="40"/>
       <c r="H34" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="41">
-        <v>628</v>
+        <v>1017.6</v>
       </c>
       <c r="J34" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K34" s="41" t="s">
-        <v>85</v>
+        <v>49</v>
+      </c>
+      <c r="K34" s="40" t="s">
+        <v>54</v>
       </c>
       <c r="L34" s="41">
         <f t="shared" si="1"/>
-        <v>157</v>
+        <v>84.8</v>
       </c>
       <c r="M34" s="41">
         <f t="shared" si="2"/>
-        <v>157</v>
+        <v>42.4</v>
       </c>
       <c r="N34" s="42">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O34" s="67">
-        <v>46187</v>
+        <v>46084</v>
       </c>
       <c r="P34" s="67">
         <f t="shared" si="3"/>
-        <v>46279</v>
+        <v>46421</v>
       </c>
       <c r="Q34" s="40">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C35" s="38"/>
-      <c r="D35" s="72" t="s">
-        <v>86</v>
+      <c r="D35" s="49" t="s">
+        <v>95</v>
       </c>
       <c r="E35" s="40" t="s">
         <v>1</v>
@@ -4435,7 +4457,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="41">
-        <v>659</v>
+        <v>1900</v>
       </c>
       <c r="J35" s="41" t="s">
         <v>44</v>
@@ -4445,31 +4467,31 @@
       </c>
       <c r="L35" s="41">
         <f t="shared" si="1"/>
-        <v>54.916666666666664</v>
+        <v>190</v>
       </c>
       <c r="M35" s="41">
         <f t="shared" si="2"/>
-        <v>54.916666666666664</v>
+        <v>190</v>
       </c>
       <c r="N35" s="42">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O35" s="67">
-        <v>45964</v>
+        <v>46145</v>
       </c>
       <c r="P35" s="67">
         <f t="shared" si="3"/>
-        <v>46298</v>
+        <v>46421</v>
       </c>
       <c r="Q35" s="40">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C36" s="38"/>
-      <c r="D36" s="72" t="s">
-        <v>87</v>
+      <c r="D36" s="49" t="s">
+        <v>96</v>
       </c>
       <c r="E36" s="40" t="s">
         <v>1</v>
@@ -4481,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="41">
-        <v>2319.3000000000002</v>
+        <v>474.33</v>
       </c>
       <c r="J36" s="41" t="s">
         <v>44</v>
@@ -4491,31 +4513,31 @@
       </c>
       <c r="L36" s="41">
         <f t="shared" si="1"/>
-        <v>193.27500000000001</v>
+        <v>52.703333333333333</v>
       </c>
       <c r="M36" s="41">
         <f t="shared" si="2"/>
-        <v>193.27500000000001</v>
+        <v>52.703333333333333</v>
       </c>
       <c r="N36" s="42">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O36" s="67">
-        <v>45964</v>
+        <v>46176</v>
       </c>
       <c r="P36" s="67">
         <f t="shared" si="3"/>
-        <v>46298</v>
+        <v>46421</v>
       </c>
       <c r="Q36" s="40">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C37" s="38"/>
-      <c r="D37" s="72" t="s">
-        <v>88</v>
+      <c r="D37" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E37" s="40" t="s">
         <v>1</v>
@@ -4527,55 +4549,53 @@
         <v>1</v>
       </c>
       <c r="I37" s="41">
-        <v>2000</v>
+        <v>286.39</v>
       </c>
       <c r="J37" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K37" s="41" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="L37" s="41">
         <f t="shared" si="1"/>
-        <v>166.66666666666666</v>
+        <v>28.638999999999999</v>
       </c>
       <c r="M37" s="41">
         <f t="shared" si="2"/>
-        <v>166.66666666666666</v>
+        <v>28.638999999999999</v>
       </c>
       <c r="N37" s="42">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O37" s="67">
-        <v>45964</v>
+        <v>46176</v>
       </c>
       <c r="P37" s="67">
         <f t="shared" si="3"/>
-        <v>46298</v>
+        <v>46449</v>
       </c>
       <c r="Q37" s="40">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C38" s="38"/>
-      <c r="D38" s="72" t="s">
-        <v>90</v>
+      <c r="D38" s="49" t="s">
+        <v>103</v>
       </c>
       <c r="E38" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F38" s="40"/>
       <c r="G38" s="40"/>
       <c r="H38" s="40">
-        <f t="shared" ref="H38:H68" si="6">COUNTA(E38:G38)</f>
-        <v>2</v>
+        <f t="shared" ref="H38:H69" si="6">COUNTA(E38:G38)</f>
+        <v>1</v>
       </c>
       <c r="I38" s="41">
-        <v>725</v>
+        <v>1181.1400000000001</v>
       </c>
       <c r="J38" s="41" t="s">
         <v>44</v>
@@ -4584,78 +4604,82 @@
         <v>74</v>
       </c>
       <c r="L38" s="41">
-        <f t="shared" ref="L38:L68" si="7">I38/N38</f>
-        <v>120.83333333333333</v>
+        <f t="shared" ref="L38:L69" si="7">I38/N38</f>
+        <v>118.114</v>
       </c>
       <c r="M38" s="41">
-        <f t="shared" ref="M38:M68" si="8">IFERROR(L38/H38,"")</f>
-        <v>60.416666666666664</v>
+        <f t="shared" ref="M38:M69" si="8">IFERROR(L38/H38,"")</f>
+        <v>118.114</v>
       </c>
       <c r="N38" s="42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O38" s="67">
-        <v>46145</v>
+        <v>46206</v>
       </c>
       <c r="P38" s="67">
-        <f t="shared" ref="P38:P68" si="9">IF(N38&lt;&gt;1,EDATE(O38,N38-1),"")</f>
-        <v>46298</v>
+        <f t="shared" ref="P38:P69" si="9">IF(N38&lt;&gt;1,EDATE(O38,N38-1),"")</f>
+        <v>46480</v>
       </c>
       <c r="Q38" s="40">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C39" s="38"/>
       <c r="D39" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="E39" s="40"/>
+        <v>55</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F39" s="40" t="s">
         <v>2</v>
       </c>
       <c r="G39" s="40"/>
       <c r="H39" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="41">
-        <v>973.02</v>
+        <v>224.24</v>
       </c>
       <c r="J39" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K39" s="41" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="L39" s="41">
         <f t="shared" si="7"/>
-        <v>81.084999999999994</v>
+        <v>18.686666666666667</v>
       </c>
       <c r="M39" s="41">
         <f t="shared" si="8"/>
-        <v>81.084999999999994</v>
+        <v>9.3433333333333337</v>
       </c>
       <c r="N39" s="42">
         <v>12</v>
       </c>
       <c r="O39" s="67">
-        <v>45994</v>
+        <v>46176</v>
       </c>
       <c r="P39" s="67">
         <f t="shared" si="9"/>
-        <v>46329</v>
+        <v>46510</v>
       </c>
       <c r="Q39" s="40">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C40" s="38"/>
+      <c r="C40" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="D40" s="49" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E40" s="40" t="s">
         <v>1</v>
@@ -4667,87 +4691,87 @@
         <v>1</v>
       </c>
       <c r="I40" s="41">
-        <v>379</v>
+        <v>279</v>
       </c>
       <c r="J40" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K40" s="41" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="L40" s="41">
         <f t="shared" si="7"/>
-        <v>54.142857142857146</v>
+        <v>27.9</v>
       </c>
       <c r="M40" s="41">
         <f t="shared" si="8"/>
-        <v>54.142857142857146</v>
+        <v>27.9</v>
       </c>
       <c r="N40" s="42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O40" s="67">
-        <v>46145</v>
+        <v>46237</v>
       </c>
       <c r="P40" s="67">
         <f t="shared" si="9"/>
-        <v>46329</v>
-      </c>
-      <c r="Q40" s="40">
+        <v>46510</v>
+      </c>
+      <c r="Q40" s="40" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v/>
       </c>
     </row>
     <row r="41" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C41" s="38"/>
-      <c r="D41" s="49" t="s">
-        <v>93</v>
+      <c r="D41" s="39" t="s">
+        <v>57</v>
       </c>
       <c r="E41" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F41" s="40"/>
+      <c r="F41" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="41">
-        <v>297</v>
+        <v>22.45</v>
       </c>
       <c r="J41" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K41" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="K41" s="40" t="s">
+        <v>49</v>
       </c>
       <c r="L41" s="41">
         <f t="shared" si="7"/>
-        <v>49.5</v>
+        <v>22.45</v>
       </c>
       <c r="M41" s="41">
         <f t="shared" si="8"/>
-        <v>49.5</v>
+        <v>11.225</v>
       </c>
       <c r="N41" s="42">
-        <v>6</v>
-      </c>
-      <c r="O41" s="67">
-        <v>46176</v>
-      </c>
-      <c r="P41" s="67">
+        <v>1</v>
+      </c>
+      <c r="O41" s="67"/>
+      <c r="P41" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46329</v>
-      </c>
-      <c r="Q41" s="40">
+        <v/>
+      </c>
+      <c r="Q41" s="40" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="42" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C42" s="38"/>
       <c r="D42" s="49" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="E42" s="40" t="s">
         <v>1</v>
@@ -4761,156 +4785,159 @@
         <v>2</v>
       </c>
       <c r="I42" s="41">
-        <v>506</v>
+        <v>60</v>
       </c>
       <c r="J42" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K42" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="K42" s="40" t="s">
+        <v>50</v>
       </c>
       <c r="L42" s="41">
         <f t="shared" si="7"/>
-        <v>50.6</v>
+        <v>60</v>
       </c>
       <c r="M42" s="41">
         <f t="shared" si="8"/>
-        <v>25.3</v>
+        <v>30</v>
       </c>
       <c r="N42" s="42">
-        <v>10</v>
-      </c>
-      <c r="O42" s="67">
-        <v>46115</v>
-      </c>
-      <c r="P42" s="67">
+        <v>1</v>
+      </c>
+      <c r="O42" s="67"/>
+      <c r="P42" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46390</v>
-      </c>
-      <c r="Q42" s="40"/>
+        <v/>
+      </c>
+      <c r="Q42" s="40" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="43" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C43" s="38"/>
-      <c r="D43" s="49" t="s">
-        <v>95</v>
+      <c r="D43" s="39" t="s">
+        <v>59</v>
       </c>
       <c r="E43" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F43" s="40"/>
+      <c r="F43" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="41">
-        <v>1900</v>
+        <v>395.54</v>
       </c>
       <c r="J43" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K43" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="K43" s="40" t="s">
+        <v>49</v>
       </c>
       <c r="L43" s="41">
         <f t="shared" si="7"/>
-        <v>190</v>
+        <v>395.54</v>
       </c>
       <c r="M43" s="41">
         <f t="shared" si="8"/>
-        <v>190</v>
+        <v>197.77</v>
       </c>
       <c r="N43" s="42">
-        <v>10</v>
-      </c>
-      <c r="O43" s="67">
-        <v>46145</v>
-      </c>
-      <c r="P43" s="67">
+        <v>1</v>
+      </c>
+      <c r="O43" s="67"/>
+      <c r="P43" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46421</v>
-      </c>
-      <c r="Q43" s="40">
-        <f t="shared" ref="Q43:Q73" ca="1" si="10">IF(O43&lt;&gt;"",IFERROR(DATEDIF(O43,TODAY(),"m")+1,""),"")</f>
-        <v>3</v>
+        <v/>
+      </c>
+      <c r="Q43" s="40" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
       </c>
     </row>
     <row r="44" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C44" s="38"/>
-      <c r="D44" s="49" t="s">
-        <v>96</v>
+      <c r="D44" s="39" t="s">
+        <v>60</v>
       </c>
       <c r="E44" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F44" s="40"/>
+      <c r="F44" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G44" s="40"/>
       <c r="H44" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="41">
-        <v>474.33</v>
+        <v>215</v>
       </c>
       <c r="J44" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K44" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="K44" s="40" t="s">
+        <v>49</v>
       </c>
       <c r="L44" s="41">
         <f t="shared" si="7"/>
-        <v>52.703333333333333</v>
+        <v>215</v>
       </c>
       <c r="M44" s="41">
         <f t="shared" si="8"/>
-        <v>52.703333333333333</v>
+        <v>107.5</v>
       </c>
       <c r="N44" s="42">
-        <v>9</v>
-      </c>
-      <c r="O44" s="67">
-        <v>46176</v>
-      </c>
-      <c r="P44" s="67">
+        <v>1</v>
+      </c>
+      <c r="O44" s="67"/>
+      <c r="P44" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46421</v>
-      </c>
-      <c r="Q44" s="40">
-        <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v/>
+      </c>
+      <c r="Q44" s="40" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
       </c>
     </row>
     <row r="45" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C45" s="38"/>
       <c r="D45" s="49" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="E45" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F45" s="40"/>
+      <c r="F45" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G45" s="40"/>
       <c r="H45" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" s="41">
-        <v>-42.08</v>
+        <v>225</v>
       </c>
       <c r="J45" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K45" s="41" t="s">
-        <v>98</v>
+        <v>49</v>
+      </c>
+      <c r="K45" s="40" t="s">
+        <v>50</v>
       </c>
       <c r="L45" s="41">
         <f t="shared" si="7"/>
-        <v>-42.08</v>
+        <v>225</v>
       </c>
       <c r="M45" s="41">
         <f t="shared" si="8"/>
-        <v>-42.08</v>
+        <v>112.5</v>
       </c>
       <c r="N45" s="42">
         <v>1</v>
@@ -4921,40 +4948,42 @@
         <v/>
       </c>
       <c r="Q45" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C46" s="38"/>
-      <c r="D46" s="49" t="s">
-        <v>99</v>
+      <c r="D46" s="39" t="s">
+        <v>62</v>
       </c>
       <c r="E46" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="40"/>
+      <c r="F46" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G46" s="40"/>
       <c r="H46" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" s="41">
-        <v>-64.42</v>
+        <v>166.15</v>
       </c>
       <c r="J46" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K46" s="41" t="s">
-        <v>98</v>
+        <v>49</v>
+      </c>
+      <c r="K46" s="40" t="s">
+        <v>49</v>
       </c>
       <c r="L46" s="41">
         <f t="shared" si="7"/>
-        <v>-64.42</v>
+        <v>166.15</v>
       </c>
       <c r="M46" s="41">
         <f t="shared" si="8"/>
-        <v>-64.42</v>
+        <v>83.075000000000003</v>
       </c>
       <c r="N46" s="42">
         <v>1</v>
@@ -4965,14 +4994,14 @@
         <v/>
       </c>
       <c r="Q46" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C47" s="38"/>
       <c r="D47" s="49" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E47" s="40" t="s">
         <v>1</v>
@@ -4984,41 +5013,39 @@
         <v>1</v>
       </c>
       <c r="I47" s="41">
-        <v>286.39</v>
+        <v>284.05</v>
       </c>
       <c r="J47" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K47" s="41" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="L47" s="41">
         <f t="shared" si="7"/>
-        <v>28.638999999999999</v>
+        <v>284.05</v>
       </c>
       <c r="M47" s="41">
         <f t="shared" si="8"/>
-        <v>28.638999999999999</v>
+        <v>284.05</v>
       </c>
       <c r="N47" s="42">
-        <v>10</v>
-      </c>
-      <c r="O47" s="67">
-        <v>46176</v>
-      </c>
-      <c r="P47" s="67">
+        <v>1</v>
+      </c>
+      <c r="O47" s="67"/>
+      <c r="P47" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46449</v>
-      </c>
-      <c r="Q47" s="40">
-        <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v/>
+      </c>
+      <c r="Q47" s="40" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
       </c>
     </row>
     <row r="48" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C48" s="38"/>
       <c r="D48" s="49" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="E48" s="40" t="s">
         <v>1</v>
@@ -5030,41 +5057,39 @@
         <v>1</v>
       </c>
       <c r="I48" s="41">
-        <v>399.9</v>
+        <v>110</v>
       </c>
       <c r="J48" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K48" s="41" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="L48" s="41">
         <f t="shared" si="7"/>
-        <v>57.128571428571426</v>
+        <v>110</v>
       </c>
       <c r="M48" s="41">
         <f t="shared" si="8"/>
-        <v>57.128571428571426</v>
+        <v>110</v>
       </c>
       <c r="N48" s="42">
-        <v>7</v>
-      </c>
-      <c r="O48" s="67">
-        <v>46206</v>
-      </c>
-      <c r="P48" s="67">
+        <v>1</v>
+      </c>
+      <c r="O48" s="67"/>
+      <c r="P48" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46390</v>
-      </c>
-      <c r="Q48" s="40">
-        <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="Q48" s="40" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
       </c>
     </row>
     <row r="49" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C49" s="38"/>
       <c r="D49" s="49" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="E49" s="40" t="s">
         <v>1</v>
@@ -5076,177 +5101,167 @@
         <v>1</v>
       </c>
       <c r="I49" s="41">
-        <v>372.43</v>
+        <v>117</v>
       </c>
       <c r="J49" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K49" s="41" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="L49" s="41">
         <f t="shared" si="7"/>
-        <v>93.107500000000002</v>
+        <v>117</v>
       </c>
       <c r="M49" s="41">
         <f t="shared" si="8"/>
-        <v>93.107500000000002</v>
+        <v>117</v>
       </c>
       <c r="N49" s="42">
-        <v>4</v>
-      </c>
-      <c r="O49" s="67">
-        <v>46206</v>
-      </c>
-      <c r="P49" s="67">
+        <v>1</v>
+      </c>
+      <c r="O49" s="67"/>
+      <c r="P49" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46298</v>
-      </c>
-      <c r="Q49" s="40">
-        <f t="shared" ca="1" si="10"/>
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+      <c r="Q49" s="40"/>
     </row>
     <row r="50" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C50" s="38"/>
-      <c r="D50" s="49" t="s">
-        <v>103</v>
+      <c r="D50" s="39" t="s">
+        <v>67</v>
       </c>
       <c r="E50" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="40"/>
+      <c r="F50" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G50" s="40"/>
       <c r="H50" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="41">
-        <v>1181.1400000000001</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="J50" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K50" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="K50" s="40" t="s">
+        <v>49</v>
       </c>
       <c r="L50" s="41">
         <f t="shared" si="7"/>
-        <v>118.114</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="M50" s="41">
         <f t="shared" si="8"/>
-        <v>118.114</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="N50" s="42">
-        <v>10</v>
-      </c>
-      <c r="O50" s="67">
-        <v>46206</v>
-      </c>
-      <c r="P50" s="67">
+        <v>1</v>
+      </c>
+      <c r="O50" s="67"/>
+      <c r="P50" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46480</v>
-      </c>
-      <c r="Q50" s="40">
-        <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="Q50" s="40" t="str">
+        <f ca="1">IF(O50&lt;&gt;"",IFERROR(DATEDIF(O50,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="51" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C51" s="38"/>
-      <c r="D51" s="49" t="s">
-        <v>104</v>
+      <c r="D51" s="39" t="s">
+        <v>68</v>
       </c>
       <c r="E51" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F51" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F51" s="40"/>
       <c r="G51" s="40"/>
       <c r="H51" s="40">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="41">
-        <v>1780</v>
-      </c>
-      <c r="J51" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="K51" s="41" t="s">
-        <v>74</v>
+        <v>26.9</v>
+      </c>
+      <c r="J51" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="K51" s="40" t="s">
+        <v>49</v>
       </c>
       <c r="L51" s="41">
         <f t="shared" si="7"/>
-        <v>222.5</v>
+        <v>26.9</v>
       </c>
       <c r="M51" s="41">
         <f t="shared" si="8"/>
-        <v>111.25</v>
+        <v>26.9</v>
       </c>
       <c r="N51" s="42">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O51" s="67"/>
-      <c r="P51" s="67">
+      <c r="P51" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>213</v>
+        <v/>
       </c>
       <c r="Q51" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O51&lt;&gt;"",IFERROR(DATEDIF(O51,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="52" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C52" s="38"/>
       <c r="D52" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="E52" s="40"/>
+        <v>69</v>
+      </c>
+      <c r="E52" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F52" s="40"/>
       <c r="G52" s="40"/>
       <c r="H52" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="41">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="J52" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K52" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L52" s="41">
         <f t="shared" si="7"/>
-        <v>50</v>
-      </c>
-      <c r="M52" s="41" t="str">
+        <v>70</v>
+      </c>
+      <c r="M52" s="41">
         <f t="shared" si="8"/>
-        <v/>
+        <v>70</v>
       </c>
       <c r="N52" s="42">
-        <v>6</v>
-      </c>
-      <c r="O52" s="67">
-        <v>46237</v>
-      </c>
-      <c r="P52" s="67">
+        <v>1</v>
+      </c>
+      <c r="O52" s="67"/>
+      <c r="P52" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46390</v>
-      </c>
-      <c r="Q52" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
+        <v/>
+      </c>
+      <c r="Q52" s="40"/>
     </row>
     <row r="53" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C53" s="38"/>
-      <c r="D53" s="49" t="s">
-        <v>106</v>
+      <c r="D53" s="70" t="s">
+        <v>70</v>
       </c>
       <c r="E53" s="40" t="s">
         <v>1</v>
@@ -5258,87 +5273,87 @@
         <v>1</v>
       </c>
       <c r="I53" s="41">
-        <v>284</v>
+        <v>400</v>
       </c>
       <c r="J53" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K53" s="41" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="L53" s="41">
         <f t="shared" si="7"/>
-        <v>47.333333333333336</v>
+        <v>400</v>
       </c>
       <c r="M53" s="41">
         <f t="shared" si="8"/>
-        <v>47.333333333333336</v>
+        <v>400</v>
       </c>
       <c r="N53" s="42">
-        <v>6</v>
-      </c>
-      <c r="O53" s="67">
-        <v>46237</v>
-      </c>
-      <c r="P53" s="67">
+        <v>1</v>
+      </c>
+      <c r="O53" s="67"/>
+      <c r="P53" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46390</v>
+        <v/>
       </c>
       <c r="Q53" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ref="Q53:Q84" ca="1" si="10">IF(O53&lt;&gt;"",IFERROR(DATEDIF(O53,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="54" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C54" s="38"/>
       <c r="D54" s="49" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="E54" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F54" s="40"/>
+      <c r="F54" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G54" s="40"/>
       <c r="H54" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" s="41">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="J54" s="41" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="K54" s="41" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="L54" s="41">
         <f t="shared" si="7"/>
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="M54" s="41">
         <f t="shared" si="8"/>
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="N54" s="42">
         <v>1</v>
       </c>
       <c r="O54" s="67">
-        <v>46237</v>
+        <v>46206</v>
       </c>
       <c r="P54" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q54" s="40" t="str">
+      <c r="Q54" s="40">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="38"/>
       <c r="D55" s="49" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E55" s="40" t="s">
         <v>1</v>
@@ -5350,21 +5365,21 @@
         <v>1</v>
       </c>
       <c r="I55" s="41">
-        <v>498</v>
+        <v>-42.08</v>
       </c>
       <c r="J55" s="41" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="K55" s="41" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="L55" s="41">
         <f t="shared" si="7"/>
-        <v>498</v>
+        <v>-42.08</v>
       </c>
       <c r="M55" s="41">
         <f t="shared" si="8"/>
-        <v>498</v>
+        <v>-42.08</v>
       </c>
       <c r="N55" s="42">
         <v>1</v>
@@ -5382,35 +5397,33 @@
     <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="38"/>
       <c r="D56" s="49" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E56" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F56" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F56" s="40"/>
       <c r="G56" s="40"/>
       <c r="H56" s="40">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I56" s="41">
-        <v>40</v>
+        <v>-64.42</v>
       </c>
       <c r="J56" s="41" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="K56" s="41" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L56" s="41">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>-64.42</v>
       </c>
       <c r="M56" s="41">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>-64.42</v>
       </c>
       <c r="N56" s="42">
         <v>1</v>
@@ -5428,7 +5441,7 @@
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="38"/>
       <c r="D57" s="49" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E57" s="40" t="s">
         <v>1</v>
@@ -5440,22 +5453,28 @@
         <v>1</v>
       </c>
       <c r="I57" s="41">
-        <v>32</v>
-      </c>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
+        <v>55</v>
+      </c>
+      <c r="J57" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K57" s="41" t="s">
+        <v>45</v>
+      </c>
       <c r="L57" s="41">
         <f t="shared" si="7"/>
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M57" s="41">
         <f t="shared" si="8"/>
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="N57" s="42">
         <v>1</v>
       </c>
-      <c r="O57" s="67"/>
+      <c r="O57" s="67">
+        <v>46237</v>
+      </c>
       <c r="P57" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5468,29 +5487,33 @@
     <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="38"/>
       <c r="D58" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40" t="s">
-        <v>2</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="E58" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="40"/>
       <c r="G58" s="40"/>
       <c r="H58" s="40">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I58" s="41">
-        <v>166</v>
-      </c>
-      <c r="J58" s="41"/>
-      <c r="K58" s="41"/>
+        <v>498</v>
+      </c>
+      <c r="J58" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K58" s="41" t="s">
+        <v>52</v>
+      </c>
       <c r="L58" s="41">
         <f t="shared" si="7"/>
-        <v>166</v>
+        <v>498</v>
       </c>
       <c r="M58" s="41">
         <f t="shared" si="8"/>
-        <v>166</v>
+        <v>498</v>
       </c>
       <c r="N58" s="42">
         <v>1</v>
@@ -5508,7 +5531,7 @@
     <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="38"/>
       <c r="D59" s="49" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E59" s="40" t="s">
         <v>1</v>
@@ -5522,17 +5545,21 @@
         <v>2</v>
       </c>
       <c r="I59" s="41">
-        <v>74</v>
-      </c>
-      <c r="J59" s="41"/>
-      <c r="K59" s="41"/>
+        <v>40</v>
+      </c>
+      <c r="J59" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K59" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L59" s="41">
         <f t="shared" si="7"/>
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="M59" s="41">
         <f t="shared" si="8"/>
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="N59" s="42">
         <v>1</v>
@@ -5550,7 +5577,7 @@
     <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="38"/>
       <c r="D60" s="49" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E60" s="40" t="s">
         <v>1</v>
@@ -5562,17 +5589,21 @@
         <v>1</v>
       </c>
       <c r="I60" s="41">
-        <v>-37</v>
-      </c>
-      <c r="J60" s="41"/>
-      <c r="K60" s="41"/>
+        <v>32</v>
+      </c>
+      <c r="J60" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K60" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L60" s="41">
         <f t="shared" si="7"/>
-        <v>-37</v>
+        <v>32</v>
       </c>
       <c r="M60" s="41">
         <f t="shared" si="8"/>
-        <v>-37</v>
+        <v>32</v>
       </c>
       <c r="N60" s="42">
         <v>1</v>
@@ -5588,45 +5619,43 @@
       </c>
     </row>
     <row r="61" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C61" s="38" t="s">
-        <v>117</v>
-      </c>
+      <c r="C61" s="38"/>
       <c r="D61" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="E61" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="40"/>
+        <v>112</v>
+      </c>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G61" s="40"/>
       <c r="H61" s="40">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I61" s="41">
-        <v>279</v>
+        <v>166</v>
       </c>
       <c r="J61" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K61" s="41"/>
+        <v>108</v>
+      </c>
+      <c r="K61" s="41" t="s">
+        <v>52</v>
+      </c>
       <c r="L61" s="41">
         <f t="shared" si="7"/>
-        <v>27.9</v>
+        <v>166</v>
       </c>
       <c r="M61" s="41">
         <f t="shared" si="8"/>
-        <v>27.9</v>
+        <v>166</v>
       </c>
       <c r="N61" s="42">
-        <v>10</v>
-      </c>
-      <c r="O61" s="67">
-        <v>46237</v>
-      </c>
-      <c r="P61" s="67">
+        <v>1</v>
+      </c>
+      <c r="O61" s="67"/>
+      <c r="P61" s="67" t="str">
         <f t="shared" si="9"/>
-        <v>46510</v>
+        <v/>
       </c>
       <c r="Q61" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -5636,7 +5665,7 @@
     <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="38"/>
       <c r="D62" s="49" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E62" s="40" t="s">
         <v>1</v>
@@ -5650,17 +5679,21 @@
         <v>2</v>
       </c>
       <c r="I62" s="41">
-        <v>36</v>
-      </c>
-      <c r="J62" s="41"/>
-      <c r="K62" s="41"/>
+        <v>74</v>
+      </c>
+      <c r="J62" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K62" s="41" t="s">
+        <v>246</v>
+      </c>
       <c r="L62" s="41">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="M62" s="41">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="N62" s="42">
         <v>1</v>
@@ -5678,7 +5711,7 @@
     <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="38"/>
       <c r="D63" s="49" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E63" s="40" t="s">
         <v>1</v>
@@ -5690,17 +5723,21 @@
         <v>1</v>
       </c>
       <c r="I63" s="41">
-        <v>35</v>
-      </c>
-      <c r="J63" s="41"/>
-      <c r="K63" s="41"/>
+        <v>-37</v>
+      </c>
+      <c r="J63" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="K63" s="41" t="s">
+        <v>244</v>
+      </c>
       <c r="L63" s="41">
         <f t="shared" si="7"/>
-        <v>35</v>
+        <v>-37</v>
       </c>
       <c r="M63" s="41">
         <f t="shared" si="8"/>
-        <v>35</v>
+        <v>-37</v>
       </c>
       <c r="N63" s="42">
         <v>1</v>
@@ -5718,7 +5755,7 @@
     <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="38"/>
       <c r="D64" s="49" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E64" s="40" t="s">
         <v>1</v>
@@ -5732,17 +5769,21 @@
         <v>2</v>
       </c>
       <c r="I64" s="41">
-        <v>75</v>
-      </c>
-      <c r="J64" s="41"/>
-      <c r="K64" s="41"/>
+        <v>36</v>
+      </c>
+      <c r="J64" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K64" s="41" t="s">
+        <v>85</v>
+      </c>
       <c r="L64" s="41">
         <f t="shared" si="7"/>
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="M64" s="41">
         <f t="shared" si="8"/>
-        <v>37.5</v>
+        <v>18</v>
       </c>
       <c r="N64" s="42">
         <v>1</v>
@@ -5760,31 +5801,33 @@
     <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="38"/>
       <c r="D65" s="49" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E65" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F65" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F65" s="40"/>
       <c r="G65" s="40"/>
       <c r="H65" s="40">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65" s="41">
+        <v>35</v>
+      </c>
+      <c r="J65" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K65" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="J65" s="41"/>
-      <c r="K65" s="41"/>
       <c r="L65" s="41">
         <f t="shared" si="7"/>
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="M65" s="41">
         <f t="shared" si="8"/>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N65" s="42">
         <v>1</v>
@@ -5802,29 +5845,35 @@
     <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="38"/>
       <c r="D66" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="E66" s="40"/>
+        <v>119</v>
+      </c>
+      <c r="E66" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F66" s="40" t="s">
         <v>2</v>
       </c>
       <c r="G66" s="40"/>
       <c r="H66" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" s="41">
-        <v>107.5</v>
-      </c>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
+        <v>75</v>
+      </c>
+      <c r="J66" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K66" s="41" t="s">
+        <v>56</v>
+      </c>
       <c r="L66" s="41">
         <f t="shared" si="7"/>
-        <v>107.5</v>
+        <v>75</v>
       </c>
       <c r="M66" s="41">
         <f t="shared" si="8"/>
-        <v>107.5</v>
+        <v>37.5</v>
       </c>
       <c r="N66" s="42">
         <v>1</v>
@@ -5842,29 +5891,35 @@
     <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="38"/>
       <c r="D67" s="49" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E67" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F67" s="40"/>
+      <c r="F67" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G67" s="40"/>
       <c r="H67" s="40">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" s="41">
-        <v>37.5</v>
-      </c>
-      <c r="J67" s="41"/>
-      <c r="K67" s="41"/>
+        <v>74</v>
+      </c>
+      <c r="J67" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K67" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L67" s="41">
         <f t="shared" si="7"/>
-        <v>37.5</v>
+        <v>74</v>
       </c>
       <c r="M67" s="41">
         <f t="shared" si="8"/>
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="N67" s="42">
         <v>1</v>
@@ -5882,35 +5937,39 @@
     <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="38"/>
       <c r="D68" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="E68" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="40"/>
+        <v>121</v>
+      </c>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G68" s="40"/>
       <c r="H68" s="40">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I68" s="41">
-        <v>50</v>
-      </c>
-      <c r="J68" s="41"/>
-      <c r="K68" s="41"/>
+        <v>107.5</v>
+      </c>
+      <c r="J68" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K68" s="41" t="s">
+        <v>248</v>
+      </c>
       <c r="L68" s="41">
         <f t="shared" si="7"/>
-        <v>50</v>
+        <v>107.5</v>
       </c>
       <c r="M68" s="41">
         <f t="shared" si="8"/>
-        <v>50</v>
+        <v>107.5</v>
       </c>
       <c r="N68" s="42">
         <v>1</v>
       </c>
-      <c r="O68" s="38"/>
-      <c r="P68" s="38" t="str">
+      <c r="O68" s="67"/>
+      <c r="P68" s="67" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5922,7 +5981,7 @@
     <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="38"/>
       <c r="D69" s="49" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E69" s="40" t="s">
         <v>1</v>
@@ -5930,28 +5989,32 @@
       <c r="F69" s="40"/>
       <c r="G69" s="40"/>
       <c r="H69" s="40">
-        <f t="shared" ref="H69:H100" si="11">COUNTA(E69:G69)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I69" s="41">
-        <v>35</v>
-      </c>
-      <c r="J69" s="41"/>
-      <c r="K69" s="41"/>
+        <v>37.5</v>
+      </c>
+      <c r="J69" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K69" s="41" t="s">
+        <v>248</v>
+      </c>
       <c r="L69" s="41">
-        <f t="shared" ref="L69:L100" si="12">I69/N69</f>
-        <v>35</v>
+        <f t="shared" si="7"/>
+        <v>37.5</v>
       </c>
       <c r="M69" s="41">
-        <f t="shared" ref="M69:M100" si="13">IFERROR(L69/H69,"")</f>
-        <v>35</v>
+        <f t="shared" si="8"/>
+        <v>37.5</v>
       </c>
       <c r="N69" s="42">
         <v>1</v>
       </c>
-      <c r="O69" s="38"/>
-      <c r="P69" s="38" t="str">
-        <f t="shared" ref="P69:P100" si="14">IF(N69&lt;&gt;1,EDATE(O69,N69-1),"")</f>
+      <c r="O69" s="67"/>
+      <c r="P69" s="67" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q69" s="40" t="str">
@@ -5962,7 +6025,7 @@
     <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="38"/>
       <c r="D70" s="49" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E70" s="40" t="s">
         <v>1</v>
@@ -5970,28 +6033,32 @@
       <c r="F70" s="40"/>
       <c r="G70" s="40"/>
       <c r="H70" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="H70:H101" si="11">COUNTA(E70:G70)</f>
         <v>1</v>
       </c>
       <c r="I70" s="41">
-        <v>52.14</v>
-      </c>
-      <c r="J70" s="41"/>
-      <c r="K70" s="41"/>
+        <v>50</v>
+      </c>
+      <c r="J70" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K70" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L70" s="41">
-        <f t="shared" si="12"/>
-        <v>52.14</v>
+        <f t="shared" ref="L70:L101" si="12">I70/N70</f>
+        <v>50</v>
       </c>
       <c r="M70" s="41">
-        <f t="shared" si="13"/>
-        <v>52.14</v>
+        <f t="shared" ref="M70:M101" si="13">IFERROR(L70/H70,"")</f>
+        <v>50</v>
       </c>
       <c r="N70" s="42">
         <v>1</v>
       </c>
       <c r="O70" s="38"/>
       <c r="P70" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="P70:P101" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
         <v/>
       </c>
       <c r="Q70" s="40" t="str">
@@ -6002,31 +6069,33 @@
     <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="38"/>
       <c r="D71" s="49" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E71" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F71" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F71" s="40"/>
       <c r="G71" s="40"/>
       <c r="H71" s="40">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71" s="41">
-        <v>130.01</v>
-      </c>
-      <c r="J71" s="41"/>
-      <c r="K71" s="41"/>
+        <v>35</v>
+      </c>
+      <c r="J71" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K71" s="41" t="s">
+        <v>74</v>
+      </c>
       <c r="L71" s="41">
         <f t="shared" si="12"/>
-        <v>130.01</v>
+        <v>35</v>
       </c>
       <c r="M71" s="41">
         <f t="shared" si="13"/>
-        <v>65.004999999999995</v>
+        <v>35</v>
       </c>
       <c r="N71" s="42">
         <v>1</v>
@@ -6044,7 +6113,7 @@
     <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="38"/>
       <c r="D72" s="49" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E72" s="40" t="s">
         <v>1</v>
@@ -6056,17 +6125,21 @@
         <v>1</v>
       </c>
       <c r="I72" s="41">
-        <v>99</v>
-      </c>
-      <c r="J72" s="41"/>
-      <c r="K72" s="41"/>
+        <v>52.14</v>
+      </c>
+      <c r="J72" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K72" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L72" s="41">
         <f t="shared" si="12"/>
-        <v>99</v>
+        <v>52.14</v>
       </c>
       <c r="M72" s="41">
         <f t="shared" si="13"/>
-        <v>99</v>
+        <v>52.14</v>
       </c>
       <c r="N72" s="42">
         <v>1</v>
@@ -6084,29 +6157,35 @@
     <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="38"/>
       <c r="D73" s="49" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E73" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F73" s="40"/>
+      <c r="F73" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G73" s="40"/>
       <c r="H73" s="40">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73" s="41">
-        <v>-99</v>
-      </c>
-      <c r="J73" s="41"/>
-      <c r="K73" s="41"/>
+        <v>130.01</v>
+      </c>
+      <c r="J73" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K73" s="41" t="s">
+        <v>248</v>
+      </c>
       <c r="L73" s="41">
         <f t="shared" si="12"/>
-        <v>-99</v>
+        <v>130.01</v>
       </c>
       <c r="M73" s="41">
         <f t="shared" si="13"/>
-        <v>-99</v>
+        <v>65.004999999999995</v>
       </c>
       <c r="N73" s="42">
         <v>1</v>
@@ -6124,31 +6203,33 @@
     <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="38"/>
       <c r="D74" s="49" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E74" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F74" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F74" s="40"/>
       <c r="G74" s="40"/>
       <c r="H74" s="40">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I74" s="41">
-        <v>139</v>
-      </c>
-      <c r="J74" s="41"/>
-      <c r="K74" s="41"/>
+        <v>99</v>
+      </c>
+      <c r="J74" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K74" s="41" t="s">
+        <v>74</v>
+      </c>
       <c r="L74" s="41">
         <f t="shared" si="12"/>
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="M74" s="41">
         <f t="shared" si="13"/>
-        <v>69.5</v>
+        <v>99</v>
       </c>
       <c r="N74" s="42">
         <v>1</v>
@@ -6159,36 +6240,40 @@
         <v/>
       </c>
       <c r="Q74" s="40" t="str">
-        <f t="shared" ref="Q74:Q105" ca="1" si="15">IF(O74&lt;&gt;"",IFERROR(DATEDIF(O74,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="38"/>
       <c r="D75" s="49" t="s">
-        <v>131</v>
-      </c>
-      <c r="E75" s="40"/>
-      <c r="F75" s="40" t="s">
-        <v>2</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="E75" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="40"/>
       <c r="G75" s="40"/>
       <c r="H75" s="40">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I75" s="41">
-        <v>100</v>
-      </c>
-      <c r="J75" s="41"/>
-      <c r="K75" s="41"/>
+        <v>-99</v>
+      </c>
+      <c r="J75" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="K75" s="41" t="s">
+        <v>244</v>
+      </c>
       <c r="L75" s="41">
         <f t="shared" si="12"/>
-        <v>100</v>
+        <v>-99</v>
       </c>
       <c r="M75" s="41">
         <f t="shared" si="13"/>
-        <v>100</v>
+        <v>-99</v>
       </c>
       <c r="N75" s="42">
         <v>1</v>
@@ -6199,14 +6284,14 @@
         <v/>
       </c>
       <c r="Q75" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="38"/>
       <c r="D76" s="49" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E76" s="40" t="s">
         <v>1</v>
@@ -6220,17 +6305,21 @@
         <v>2</v>
       </c>
       <c r="I76" s="41">
-        <v>90</v>
-      </c>
-      <c r="J76" s="41"/>
-      <c r="K76" s="41"/>
+        <v>139</v>
+      </c>
+      <c r="J76" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K76" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L76" s="41">
         <f t="shared" si="12"/>
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="M76" s="41">
         <f t="shared" si="13"/>
-        <v>45</v>
+        <v>69.5</v>
       </c>
       <c r="N76" s="42">
         <v>1</v>
@@ -6241,36 +6330,40 @@
         <v/>
       </c>
       <c r="Q76" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="38"/>
       <c r="D77" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="E77" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="40"/>
+        <v>129</v>
+      </c>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G77" s="40"/>
       <c r="H77" s="40">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I77" s="41">
-        <v>-45</v>
-      </c>
-      <c r="J77" s="41"/>
-      <c r="K77" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="J77" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K77" s="41" t="s">
+        <v>248</v>
+      </c>
       <c r="L77" s="41">
         <f t="shared" si="12"/>
-        <v>-45</v>
+        <v>100</v>
       </c>
       <c r="M77" s="41">
         <f t="shared" si="13"/>
-        <v>-45</v>
+        <v>100</v>
       </c>
       <c r="N77" s="42">
         <v>1</v>
@@ -6281,14 +6374,14 @@
         <v/>
       </c>
       <c r="Q77" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C78" s="38"/>
       <c r="D78" s="49" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="E78" s="40" t="s">
         <v>1</v>
@@ -6302,17 +6395,21 @@
         <v>2</v>
       </c>
       <c r="I78" s="41">
-        <v>79</v>
-      </c>
-      <c r="J78" s="41"/>
-      <c r="K78" s="41"/>
+        <v>90</v>
+      </c>
+      <c r="J78" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K78" s="41" t="s">
+        <v>74</v>
+      </c>
       <c r="L78" s="41">
         <f t="shared" si="12"/>
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="M78" s="41">
         <f t="shared" si="13"/>
-        <v>39.5</v>
+        <v>45</v>
       </c>
       <c r="N78" s="42">
         <v>1</v>
@@ -6323,38 +6420,40 @@
         <v/>
       </c>
       <c r="Q78" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C79" s="38"/>
       <c r="D79" s="49" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="E79" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F79" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F79" s="40"/>
       <c r="G79" s="40"/>
       <c r="H79" s="40">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" s="41">
-        <v>56.27</v>
-      </c>
-      <c r="J79" s="41"/>
-      <c r="K79" s="41"/>
+        <v>-45</v>
+      </c>
+      <c r="J79" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="K79" s="41" t="s">
+        <v>244</v>
+      </c>
       <c r="L79" s="41">
         <f t="shared" si="12"/>
-        <v>56.27</v>
+        <v>-45</v>
       </c>
       <c r="M79" s="41">
         <f t="shared" si="13"/>
-        <v>28.135000000000002</v>
+        <v>-45</v>
       </c>
       <c r="N79" s="42">
         <v>1</v>
@@ -6365,14 +6464,14 @@
         <v/>
       </c>
       <c r="Q79" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C80" s="38"/>
       <c r="D80" s="49" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E80" s="40" t="s">
         <v>1</v>
@@ -6386,17 +6485,21 @@
         <v>2</v>
       </c>
       <c r="I80" s="41">
-        <v>82.49</v>
-      </c>
-      <c r="J80" s="41"/>
-      <c r="K80" s="41"/>
+        <v>79</v>
+      </c>
+      <c r="J80" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K80" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L80" s="41">
         <f t="shared" si="12"/>
-        <v>82.49</v>
+        <v>79</v>
       </c>
       <c r="M80" s="41">
         <f t="shared" si="13"/>
-        <v>41.244999999999997</v>
+        <v>39.5</v>
       </c>
       <c r="N80" s="42">
         <v>1</v>
@@ -6407,14 +6510,14 @@
         <v/>
       </c>
       <c r="Q80" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C81" s="38"/>
       <c r="D81" s="49" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E81" s="40" t="s">
         <v>1</v>
@@ -6428,17 +6531,21 @@
         <v>2</v>
       </c>
       <c r="I81" s="41">
-        <v>49.91</v>
-      </c>
-      <c r="J81" s="41"/>
-      <c r="K81" s="41"/>
+        <v>56.27</v>
+      </c>
+      <c r="J81" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K81" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L81" s="41">
         <f t="shared" si="12"/>
-        <v>49.91</v>
+        <v>56.27</v>
       </c>
       <c r="M81" s="41">
         <f t="shared" si="13"/>
-        <v>24.954999999999998</v>
+        <v>28.135000000000002</v>
       </c>
       <c r="N81" s="42">
         <v>1</v>
@@ -6449,14 +6556,14 @@
         <v/>
       </c>
       <c r="Q81" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C82" s="38"/>
       <c r="D82" s="49" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E82" s="40" t="s">
         <v>1</v>
@@ -6470,17 +6577,21 @@
         <v>2</v>
       </c>
       <c r="I82" s="41">
-        <v>41.5</v>
-      </c>
-      <c r="J82" s="41"/>
-      <c r="K82" s="41"/>
+        <v>82.49</v>
+      </c>
+      <c r="J82" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K82" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L82" s="41">
         <f t="shared" si="12"/>
-        <v>41.5</v>
+        <v>82.49</v>
       </c>
       <c r="M82" s="41">
         <f t="shared" si="13"/>
-        <v>20.75</v>
+        <v>41.244999999999997</v>
       </c>
       <c r="N82" s="42">
         <v>1</v>
@@ -6491,36 +6602,42 @@
         <v/>
       </c>
       <c r="Q82" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="38"/>
       <c r="D83" s="49" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E83" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F83" s="40"/>
+      <c r="F83" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G83" s="40"/>
       <c r="H83" s="40">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I83" s="41">
-        <v>106.04</v>
-      </c>
-      <c r="J83" s="41"/>
-      <c r="K83" s="41"/>
+        <v>49.91</v>
+      </c>
+      <c r="J83" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K83" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L83" s="41">
         <f t="shared" si="12"/>
-        <v>106.04</v>
+        <v>49.91</v>
       </c>
       <c r="M83" s="41">
         <f t="shared" si="13"/>
-        <v>106.04</v>
+        <v>24.954999999999998</v>
       </c>
       <c r="N83" s="42">
         <v>1</v>
@@ -6531,34 +6648,42 @@
         <v/>
       </c>
       <c r="Q83" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C84" s="38"/>
       <c r="D84" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="E84" s="40"/>
-      <c r="F84" s="40"/>
+        <v>236</v>
+      </c>
+      <c r="E84" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G84" s="40"/>
       <c r="H84" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I84" s="41">
-        <v>16.97</v>
-      </c>
-      <c r="J84" s="41"/>
-      <c r="K84" s="41"/>
+        <v>41.5</v>
+      </c>
+      <c r="J84" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K84" s="41" t="s">
+        <v>74</v>
+      </c>
       <c r="L84" s="41">
         <f t="shared" si="12"/>
-        <v>16.97</v>
-      </c>
-      <c r="M84" s="41" t="str">
+        <v>41.5</v>
+      </c>
+      <c r="M84" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>20.75</v>
       </c>
       <c r="N84" s="42">
         <v>1</v>
@@ -6569,14 +6694,14 @@
         <v/>
       </c>
       <c r="Q84" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="85" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C85" s="38"/>
       <c r="D85" s="49" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E85" s="40" t="s">
         <v>1</v>
@@ -6588,73 +6713,71 @@
         <v>1</v>
       </c>
       <c r="I85" s="41">
-        <v>72</v>
+        <v>106.04</v>
       </c>
       <c r="J85" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K85" s="41"/>
+        <v>108</v>
+      </c>
+      <c r="K85" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L85" s="41">
         <f t="shared" si="12"/>
-        <v>24</v>
+        <v>106.04</v>
       </c>
       <c r="M85" s="41">
         <f t="shared" si="13"/>
-        <v>24</v>
+        <v>106.04</v>
       </c>
       <c r="N85" s="42">
-        <v>3</v>
-      </c>
-      <c r="O85" s="67">
-        <v>46240</v>
-      </c>
-      <c r="P85" s="67">
+        <v>1</v>
+      </c>
+      <c r="O85" s="38"/>
+      <c r="P85" s="38" t="str">
         <f t="shared" si="14"/>
-        <v>46301</v>
+        <v/>
       </c>
       <c r="Q85" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ref="Q85:Q116" ca="1" si="15">IF(O85&lt;&gt;"",IFERROR(DATEDIF(O85,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="86" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C86" s="38"/>
       <c r="D86" s="49" t="s">
-        <v>241</v>
+        <v>117</v>
       </c>
       <c r="E86" s="40"/>
-      <c r="F86" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F86" s="40"/>
       <c r="G86" s="40"/>
       <c r="H86" s="40">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="41">
-        <v>161.72999999999999</v>
+        <v>16.97</v>
       </c>
       <c r="J86" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K86" s="41"/>
+        <v>108</v>
+      </c>
+      <c r="K86" s="41" t="s">
+        <v>85</v>
+      </c>
       <c r="L86" s="41">
         <f t="shared" si="12"/>
-        <v>53.91</v>
-      </c>
-      <c r="M86" s="41">
+        <v>16.97</v>
+      </c>
+      <c r="M86" s="41" t="str">
         <f t="shared" si="13"/>
-        <v>53.91</v>
+        <v/>
       </c>
       <c r="N86" s="42">
-        <v>3</v>
-      </c>
-      <c r="O86" s="67">
-        <v>46240</v>
-      </c>
-      <c r="P86" s="67">
+        <v>1</v>
+      </c>
+      <c r="O86" s="38"/>
+      <c r="P86" s="38" t="str">
         <f t="shared" si="14"/>
-        <v>46301</v>
+        <v/>
       </c>
       <c r="Q86" s="40" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -6664,7 +6787,7 @@
     <row r="87" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C87" s="38"/>
       <c r="D87" s="49" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E87" s="40" t="s">
         <v>1</v>
@@ -6678,8 +6801,12 @@
       <c r="I87" s="41">
         <v>50</v>
       </c>
-      <c r="J87" s="41"/>
-      <c r="K87" s="41"/>
+      <c r="J87" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K87" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L87" s="41">
         <f t="shared" si="12"/>
         <v>50</v>
@@ -6703,24 +6830,36 @@
     </row>
     <row r="88" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C88" s="38"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="40"/>
-      <c r="F88" s="40"/>
+      <c r="D88" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E88" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G88" s="40"/>
       <c r="H88" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="41"/>
-      <c r="J88" s="41"/>
-      <c r="K88" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I88" s="41">
+        <v>53.97</v>
+      </c>
+      <c r="J88" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K88" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L88" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="41" t="str">
+        <v>53.97</v>
+      </c>
+      <c r="M88" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>26.984999999999999</v>
       </c>
       <c r="N88" s="42">
         <v>1</v>
@@ -6737,24 +6876,35 @@
     </row>
     <row r="89" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C89" s="38"/>
-      <c r="D89" s="49"/>
-      <c r="E89" s="40"/>
+      <c r="D89" s="49" t="s">
+        <v>242</v>
+      </c>
+      <c r="E89" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F89" s="40"/>
       <c r="G89" s="40"/>
       <c r="H89" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="41"/>
-      <c r="J89" s="41"/>
-      <c r="K89" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I89" s="41">
+        <f>28+47.9+20</f>
+        <v>95.9</v>
+      </c>
+      <c r="J89" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K89" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="L89" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="41" t="str">
+        <v>95.9</v>
+      </c>
+      <c r="M89" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>95.9</v>
       </c>
       <c r="N89" s="42">
         <v>1</v>
@@ -6771,24 +6921,36 @@
     </row>
     <row r="90" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C90" s="38"/>
-      <c r="D90" s="49"/>
-      <c r="E90" s="40"/>
-      <c r="F90" s="40"/>
+      <c r="D90" s="49" t="s">
+        <v>243</v>
+      </c>
+      <c r="E90" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G90" s="40"/>
       <c r="H90" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="41"/>
-      <c r="J90" s="41"/>
-      <c r="K90" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I90" s="41">
+        <v>-300</v>
+      </c>
+      <c r="J90" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="K90" s="41" t="s">
+        <v>244</v>
+      </c>
       <c r="L90" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="41" t="str">
+        <v>-300</v>
+      </c>
+      <c r="M90" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="N90" s="42">
         <v>1</v>
@@ -7150,18 +7312,18 @@
       <c r="F101" s="40"/>
       <c r="G101" s="40"/>
       <c r="H101" s="40">
-        <f t="shared" ref="H101:H132" si="16">COUNTA(E101:G101)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I101" s="41"/>
       <c r="J101" s="41"/>
       <c r="K101" s="41"/>
       <c r="L101" s="41">
-        <f t="shared" ref="L101:L132" si="17">I101/N101</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M101" s="41" t="str">
-        <f t="shared" ref="M101:M132" si="18">IFERROR(L101/H101,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N101" s="42">
@@ -7169,7 +7331,7 @@
       </c>
       <c r="O101" s="38"/>
       <c r="P101" s="38" t="str">
-        <f t="shared" ref="P101:P132" si="19">IF(N101&lt;&gt;1,EDATE(O101,N101-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q101" s="40" t="str">
@@ -7184,18 +7346,18 @@
       <c r="F102" s="40"/>
       <c r="G102" s="40"/>
       <c r="H102" s="40">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="H102:H133" si="16">COUNTA(E102:G102)</f>
         <v>0</v>
       </c>
       <c r="I102" s="41"/>
       <c r="J102" s="41"/>
       <c r="K102" s="41"/>
       <c r="L102" s="41">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="L102:L133" si="17">I102/N102</f>
         <v>0</v>
       </c>
       <c r="M102" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="M102:M133" si="18">IFERROR(L102/H102,"")</f>
         <v/>
       </c>
       <c r="N102" s="42">
@@ -7203,7 +7365,7 @@
       </c>
       <c r="O102" s="38"/>
       <c r="P102" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="P102:P133" si="19">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
         <v/>
       </c>
       <c r="Q102" s="40" t="str">
@@ -7343,7 +7505,7 @@
         <v/>
       </c>
       <c r="Q106" s="40" t="str">
-        <f t="shared" ref="Q106:Q137" ca="1" si="20">IF(O106&lt;&gt;"",IFERROR(DATEDIF(O106,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7377,7 +7539,7 @@
         <v/>
       </c>
       <c r="Q107" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7411,7 +7573,7 @@
         <v/>
       </c>
       <c r="Q108" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7445,7 +7607,7 @@
         <v/>
       </c>
       <c r="Q109" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7479,7 +7641,7 @@
         <v/>
       </c>
       <c r="Q110" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7513,7 +7675,7 @@
         <v/>
       </c>
       <c r="Q111" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7547,7 +7709,7 @@
         <v/>
       </c>
       <c r="Q112" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7581,7 +7743,7 @@
         <v/>
       </c>
       <c r="Q113" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7615,7 +7777,7 @@
         <v/>
       </c>
       <c r="Q114" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7649,7 +7811,7 @@
         <v/>
       </c>
       <c r="Q115" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7683,7 +7845,7 @@
         <v/>
       </c>
       <c r="Q116" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7717,7 +7879,7 @@
         <v/>
       </c>
       <c r="Q117" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ref="Q117:Q149" ca="1" si="20">IF(O117&lt;&gt;"",IFERROR(DATEDIF(O117,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8238,18 +8400,18 @@
       <c r="F133" s="40"/>
       <c r="G133" s="40"/>
       <c r="H133" s="40">
-        <f t="shared" ref="H133:H149" si="21">COUNTA(E133:G133)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I133" s="41"/>
       <c r="J133" s="41"/>
       <c r="K133" s="41"/>
       <c r="L133" s="41">
-        <f t="shared" ref="L133:L149" si="22">I133/N133</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M133" s="41" t="str">
-        <f t="shared" ref="M133:M149" si="23">IFERROR(L133/H133,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N133" s="42">
@@ -8257,7 +8419,7 @@
       </c>
       <c r="O133" s="38"/>
       <c r="P133" s="38" t="str">
-        <f t="shared" ref="P133:P149" si="24">IF(N133&lt;&gt;1,EDATE(O133,N133-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q133" s="40" t="str">
@@ -8272,18 +8434,18 @@
       <c r="F134" s="40"/>
       <c r="G134" s="40"/>
       <c r="H134" s="40">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="H134:H149" si="21">COUNTA(E134:G134)</f>
         <v>0</v>
       </c>
       <c r="I134" s="41"/>
       <c r="J134" s="41"/>
       <c r="K134" s="41"/>
       <c r="L134" s="41">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="L134:L149" si="22">I134/N134</f>
         <v>0</v>
       </c>
       <c r="M134" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="M134:M149" si="23">IFERROR(L134/H134,"")</f>
         <v/>
       </c>
       <c r="N134" s="42">
@@ -8291,7 +8453,7 @@
       </c>
       <c r="O134" s="38"/>
       <c r="P134" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="P134:P149" si="24">IF(N134&lt;&gt;1,EDATE(O134,N134-1),"")</f>
         <v/>
       </c>
       <c r="Q134" s="40" t="str">
@@ -8431,7 +8593,7 @@
         <v/>
       </c>
       <c r="Q138" s="40" t="str">
-        <f t="shared" ref="Q138:Q149" ca="1" si="25">IF(O138&lt;&gt;"",IFERROR(DATEDIF(O138,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8465,7 +8627,7 @@
         <v/>
       </c>
       <c r="Q139" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8499,7 +8661,7 @@
         <v/>
       </c>
       <c r="Q140" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8533,7 +8695,7 @@
         <v/>
       </c>
       <c r="Q141" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8567,7 +8729,7 @@
         <v/>
       </c>
       <c r="Q142" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8601,7 +8763,7 @@
         <v/>
       </c>
       <c r="Q143" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8635,7 +8797,7 @@
         <v/>
       </c>
       <c r="Q144" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8669,7 +8831,7 @@
         <v/>
       </c>
       <c r="Q145" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8703,7 +8865,7 @@
         <v/>
       </c>
       <c r="Q146" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8737,7 +8899,7 @@
         <v/>
       </c>
       <c r="Q147" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8771,7 +8933,7 @@
         <v/>
       </c>
       <c r="Q148" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8805,7 +8967,7 @@
         <v/>
       </c>
       <c r="Q149" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8829,22 +8991,27 @@
   </sheetData>
   <autoFilter ref="C5:Q150" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q150">
-      <sortCondition sortBy="cellColor" ref="J5:J150" dxfId="14"/>
+      <sortCondition ref="P5:P150"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="I6:I150">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J150">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K150">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"Parcelado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K60">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+      <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8946,7 +9113,7 @@
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="58" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E4" s="59" t="s">
         <v>1</v>
@@ -8987,7 +9154,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>1</v>
@@ -9029,7 +9196,7 @@
         <v>2382.0700000000002</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E6" s="39" t="s">
         <v>1</v>
@@ -9067,7 +9234,7 @@
     <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="63"/>
       <c r="D7" s="57" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E7" s="39" t="s">
         <v>1</v>
@@ -9148,7 +9315,7 @@
         <v>3382.07</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E9" s="39" t="s">
         <v>1</v>
@@ -9186,7 +9353,7 @@
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D10" s="57" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="40" t="s">
@@ -9387,7 +9554,7 @@
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" s="2"/>
       <c r="N1" s="50" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9397,10 +9564,10 @@
     <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
       <c r="L3" s="50" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M3" s="77" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N3" s="46">
         <f>SUM(N5:N21)</f>
@@ -9411,7 +9578,7 @@
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="2"/>
       <c r="L4" s="51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M4" s="78"/>
       <c r="N4" s="52"/>
@@ -9422,7 +9589,7 @@
       <c r="F5" s="16"/>
       <c r="G5" s="31"/>
       <c r="L5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N5" s="1">
         <v>4912</v>
@@ -9432,7 +9599,7 @@
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N6" s="1">
         <v>101</v>
@@ -9446,10 +9613,10 @@
       <c r="F8" s="16"/>
       <c r="G8" s="53"/>
       <c r="L8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N8" s="1">
         <v>338</v>
@@ -9457,33 +9624,33 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F9" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G9" s="31"/>
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
         <v>4597.1500000000015</v>
       </c>
       <c r="G10" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="I10" s="54" t="s">
         <v>150</v>
-      </c>
-      <c r="H10" s="54" t="s">
-        <v>151</v>
-      </c>
-      <c r="I10" s="54" t="s">
-        <v>152</v>
       </c>
       <c r="N10" s="46"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
@@ -9505,7 +9672,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
@@ -9514,7 +9681,7 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F13" s="74" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="74"/>
@@ -9525,7 +9692,7 @@
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
       <c r="F14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="56"/>
@@ -9536,7 +9703,7 @@
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
       <c r="F15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G15" s="56">
         <v>773.35</v>
@@ -9549,7 +9716,7 @@
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
       <c r="F16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G16" s="56">
         <v>-5148</v>
@@ -9562,7 +9729,7 @@
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
       <c r="F17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G17" s="56">
         <v>-168</v>
@@ -9575,7 +9742,7 @@
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
       <c r="F18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G18" s="56">
         <v>-1700</v>
@@ -9588,7 +9755,7 @@
       <c r="C19" s="56"/>
       <c r="D19" s="56"/>
       <c r="F19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G19" s="56">
         <v>5148</v>
@@ -9601,7 +9768,7 @@
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
       <c r="F20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G20" s="56">
         <v>-4938</v>
@@ -9614,7 +9781,7 @@
       <c r="C21" s="56"/>
       <c r="D21" s="56"/>
       <c r="F21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G21" s="56">
         <v>-1595</v>
@@ -9627,7 +9794,7 @@
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
       <c r="F22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G22" s="56">
         <v>-4677</v>
@@ -9640,7 +9807,7 @@
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
       <c r="F23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G23" s="56">
         <v>-200</v>
@@ -9653,7 +9820,7 @@
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
       <c r="F24" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G24" s="56">
         <v>4677</v>
@@ -9666,7 +9833,7 @@
       <c r="C25" s="56"/>
       <c r="D25" s="56"/>
       <c r="F25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G25" s="56">
         <v>-750</v>
@@ -9679,7 +9846,7 @@
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
       <c r="F26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G26" s="56">
         <v>-652</v>
@@ -9692,7 +9859,7 @@
       <c r="C27" s="56"/>
       <c r="D27" s="56"/>
       <c r="F27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G27" s="56">
         <v>11100</v>
@@ -9705,7 +9872,7 @@
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
       <c r="F28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G28" s="56">
         <v>-396</v>
@@ -9718,7 +9885,7 @@
       <c r="C29" s="56"/>
       <c r="D29" s="56"/>
       <c r="F29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G29" s="56">
         <v>-4211</v>
@@ -9731,7 +9898,7 @@
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
       <c r="F30" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G30" s="56">
         <v>-450</v>
@@ -9744,7 +9911,7 @@
       <c r="C31" s="56"/>
       <c r="D31" s="56"/>
       <c r="F31" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G31" s="56">
         <v>-1197</v>
@@ -9770,7 +9937,7 @@
       <c r="C33" s="56"/>
       <c r="D33" s="56"/>
       <c r="F33" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G33" s="56">
         <v>-830</v>
@@ -9783,7 +9950,7 @@
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
       <c r="F34" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G34" s="56">
         <v>4211</v>
@@ -9796,7 +9963,7 @@
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
       <c r="F35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G35" s="56">
         <v>-200</v>
@@ -9809,7 +9976,7 @@
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
       <c r="F36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G36" s="56">
         <v>10000</v>
@@ -9822,7 +9989,7 @@
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
       <c r="F37" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G37" s="56">
         <v>-200</v>
@@ -9835,7 +10002,7 @@
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
       <c r="F38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G38" s="56">
         <v>-381</v>
@@ -9848,7 +10015,7 @@
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
       <c r="F39" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G39" s="56">
         <v>-4911</v>
@@ -9862,7 +10029,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G40" s="56">
         <v>-5700</v>
@@ -9875,7 +10042,7 @@
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
       <c r="F41" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G41" s="56">
         <v>-400</v>
@@ -9888,7 +10055,7 @@
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
       <c r="F42" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G42" s="56">
         <v>-450</v>
@@ -9901,7 +10068,7 @@
       <c r="C43" s="56"/>
       <c r="D43" s="56"/>
       <c r="F43" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G43" s="56">
         <v>-640</v>
@@ -9915,7 +10082,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G44" s="56">
         <v>5700</v>
@@ -9928,7 +10095,7 @@
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
       <c r="F45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G45" s="56">
         <v>-130</v>
@@ -9941,7 +10108,7 @@
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
       <c r="F46" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G46" s="56">
         <v>-250</v>
@@ -9954,7 +10121,7 @@
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
       <c r="F47" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G47" s="56">
         <v>-112.2</v>
@@ -9967,7 +10134,7 @@
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
       <c r="F48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G48" s="56">
         <v>4911</v>
@@ -9980,7 +10147,7 @@
       <c r="C49" s="56"/>
       <c r="D49" s="56"/>
       <c r="F49" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G49" s="56">
         <v>-3000</v>
@@ -9993,7 +10160,7 @@
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
       <c r="F50" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G50" s="56">
         <v>-4000</v>
@@ -10006,7 +10173,7 @@
       <c r="C51" s="56"/>
       <c r="D51" s="56"/>
       <c r="F51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G51" s="56">
         <v>-200</v>
@@ -10019,7 +10186,7 @@
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
       <c r="F52" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G52" s="56">
         <v>-4612</v>
@@ -10030,7 +10197,7 @@
     </row>
     <row r="53" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F53" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G53" s="56">
         <v>-700</v>
@@ -10041,7 +10208,7 @@
     </row>
     <row r="54" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F54" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G54" s="56">
         <v>-880</v>
@@ -10052,7 +10219,7 @@
     </row>
     <row r="55" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F55" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G55" s="56">
         <v>-310</v>
@@ -10063,7 +10230,7 @@
     </row>
     <row r="56" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F56" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G56" s="56">
         <v>-250</v>
@@ -10074,7 +10241,7 @@
     </row>
     <row r="57" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G57" s="56">
         <v>4690</v>
@@ -10085,7 +10252,7 @@
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G58" s="56">
         <v>-4440</v>
@@ -10096,7 +10263,7 @@
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G59" s="56">
         <v>-4697</v>
@@ -10106,7 +10273,7 @@
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G60" s="56">
         <v>-2500</v>
@@ -10116,7 +10283,7 @@
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G61" s="56">
         <v>-126</v>
@@ -10126,7 +10293,7 @@
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G62" s="56">
         <v>4742</v>
@@ -10136,7 +10303,7 @@
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G63" s="56">
         <v>-410</v>
@@ -10151,7 +10318,7 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G65" s="56">
         <v>3320</v>
@@ -10161,7 +10328,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G66" s="56">
         <v>4090</v>
@@ -10171,7 +10338,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G67" s="56">
         <v>-5688</v>
@@ -10181,7 +10348,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G68" s="56">
         <v>-4433</v>
@@ -10191,7 +10358,7 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F69" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G69" s="56">
         <v>-250</v>
@@ -10203,7 +10370,7 @@
       <c r="C70" s="56"/>
       <c r="D70" s="56"/>
       <c r="F70" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G70" s="56">
         <v>-99</v>
@@ -10213,7 +10380,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G71" s="56">
         <v>320</v>
@@ -10223,7 +10390,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F72" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G72" s="56">
         <v>-1572</v>
@@ -10240,7 +10407,7 @@
       <c r="C74" s="56"/>
       <c r="D74" s="56"/>
       <c r="F74" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G74" s="56">
         <v>4433</v>
@@ -10250,7 +10417,7 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C75" s="56">
         <v>8000</v>
@@ -10269,7 +10436,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C77" s="56">
         <v>-50</v>
@@ -10281,7 +10448,7 @@
     </row>
     <row r="78" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C78" s="56">
         <v>500</v>
@@ -10295,7 +10462,7 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C79" s="56">
         <v>8000</v>
@@ -10314,7 +10481,7 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C81" s="56">
         <v>-90</v>
@@ -10326,7 +10493,7 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C82" s="56">
         <v>2000</v>
@@ -10340,7 +10507,7 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C83" s="56">
         <v>-12807</v>
@@ -10359,7 +10526,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C85" s="56">
         <v>5520</v>
@@ -10378,7 +10545,7 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C87" s="56">
         <v>2000</v>
@@ -10392,7 +10559,7 @@
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C88" s="56">
         <v>-90</v>
@@ -10404,7 +10571,7 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C89" s="56">
         <v>240</v>
@@ -10423,7 +10590,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C91" s="56">
         <v>2000</v>
@@ -10437,7 +10604,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C92" s="56">
         <v>-50</v>
@@ -10449,7 +10616,7 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C93" s="56">
         <v>300</v>
@@ -10468,7 +10635,7 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C95" s="56">
         <v>2000</v>
@@ -10482,7 +10649,7 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C96" s="56">
         <v>8000</v>
@@ -10494,7 +10661,7 @@
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C97" s="56">
         <v>4180</v>
@@ -10513,7 +10680,7 @@
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C99" s="56">
         <v>2000</v>
@@ -10527,7 +10694,7 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C100" s="56">
         <v>2000</v>
@@ -10541,7 +10708,7 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C101" s="56">
         <v>2000</v>
@@ -10562,7 +10729,7 @@
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C103" s="56">
         <v>-20000</v>
@@ -10581,7 +10748,7 @@
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C105" s="56">
         <v>2000</v>
@@ -10595,7 +10762,7 @@
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C106" s="56">
         <v>2000</v>
@@ -10609,7 +10776,7 @@
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C107" s="56">
         <v>8000</v>
@@ -10621,7 +10788,7 @@
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C108" s="56">
         <v>2000</v>
@@ -10635,7 +10802,7 @@
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C109" s="56">
         <v>2000</v>
@@ -11910,13 +12077,13 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="65" t="s">
         <v>225</v>
-      </c>
-      <c r="C1" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D1" s="65" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -11924,77 +12091,77 @@
         <v>22</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D2" s="57"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="57" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D4" s="57"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="57" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D5" s="57"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="57" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D6" s="57"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="57" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D7" s="57"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="57" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D8" s="57"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="57" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C9" s="40"/>
       <c r="D9" s="57"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="57" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D10" s="57"/>
     </row>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="502" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F272B33-3F1B-4C41-9739-6500E325DEFA}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FEBE841-6662-4C7C-881E-9840CD4E16A5}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Itaú!$C$4:$Q$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$149</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="250">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -777,9 +777,6 @@
     <t>Bares Augusta</t>
   </si>
   <si>
-    <t>Ajuste</t>
-  </si>
-  <si>
     <t>PAGAMENTO</t>
   </si>
   <si>
@@ -793,6 +790,12 @@
   </si>
   <si>
     <t>Carro</t>
+  </si>
+  <si>
+    <t>Café Cotia</t>
+  </si>
+  <si>
+    <t>Estacionamento Cotia</t>
   </si>
 </sst>
 </file>
@@ -1456,6 +1459,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
@@ -1708,12 +1715,12 @@
       <c r="B3" s="76"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C22+C23+C7</f>
-        <v>2125.3614047619035</v>
+        <v>1920.3914047619032</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E22+E23</f>
-        <v>3643.8775000000005</v>
+        <v>3455.8775000000005</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1735,12 +1742,12 @@
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-7912.638595238097</v>
+        <v>-8117.6085952380963</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-5356.1225000000004</v>
+        <v>-5544.1225000000004</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1771,12 +1778,12 @@
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5490.4069285714295</v>
+        <v>5695.3769285714297</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1974.0525000000002</v>
+        <v>2162.0525000000002</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -1785,12 +1792,12 @@
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5490.4069285714295</v>
+        <v>5695.3769285714297</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1974.0525000000002</v>
+        <v>2162.0525000000002</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
@@ -2163,11 +2170,11 @@
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1974.0525000000002</v>
+        <v>2162.0525000000002</v>
       </c>
       <c r="D4" s="27">
         <f>Saldo!C9+D5</f>
-        <v>5490.4069285714295</v>
+        <v>5695.3769285714297</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -2271,7 +2278,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4021.7375000000002</v>
+        <v>4209.7375000000002</v>
       </c>
       <c r="D17" s="30"/>
     </row>
@@ -3009,7 +3016,7 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="C1:Q150"/>
+  <dimension ref="C1:Q149"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
@@ -3043,19 +3050,19 @@
     </row>
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="48">
-        <f>SUM(L6:L377)</f>
-        <v>7531.4294285714286</v>
+        <f>SUM(L6:L376)</f>
+        <v>7907.4294285714286</v>
       </c>
       <c r="E2" s="35">
-        <f>SUMIF($E$6:$E$377,E1,$M$6:$M$377)</f>
-        <v>5490.4069285714295</v>
+        <f>SUMIF($E$6:$E$376,E1,$M$6:$M$376)</f>
+        <v>5695.3769285714297</v>
       </c>
       <c r="F2" s="35">
-        <f>SUMIF($F$6:$F$377,F1,$M$6:$M$377)</f>
-        <v>1974.0525000000002</v>
+        <f>SUMIF($F$6:$F$376,F1,$M$6:$M$376)</f>
+        <v>2162.0525000000002</v>
       </c>
       <c r="G2" s="35">
-        <f>SUMIF($G$6:$G$377,G1,$M$6:$M$377)</f>
+        <f>SUMIF($G$6:$G$376,G1,$M$6:$M$376)</f>
         <v>0</v>
       </c>
       <c r="L2" s="46"/>
@@ -4697,7 +4704,7 @@
         <v>44</v>
       </c>
       <c r="K40" s="41" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L40" s="41">
         <f t="shared" si="7"/>
@@ -5551,7 +5558,7 @@
         <v>108</v>
       </c>
       <c r="K59" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L59" s="41">
         <f t="shared" si="7"/>
@@ -5595,7 +5602,7 @@
         <v>108</v>
       </c>
       <c r="K60" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L60" s="41">
         <f t="shared" si="7"/>
@@ -5685,7 +5692,7 @@
         <v>108</v>
       </c>
       <c r="K62" s="41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L62" s="41">
         <f t="shared" si="7"/>
@@ -5726,10 +5733,10 @@
         <v>-37</v>
       </c>
       <c r="J63" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K63" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L63" s="41">
         <f t="shared" si="7"/>
@@ -5911,7 +5918,7 @@
         <v>108</v>
       </c>
       <c r="K67" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L67" s="41">
         <f t="shared" si="7"/>
@@ -5955,7 +5962,7 @@
         <v>108</v>
       </c>
       <c r="K68" s="41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L68" s="41">
         <f t="shared" si="7"/>
@@ -5999,7 +6006,7 @@
         <v>108</v>
       </c>
       <c r="K69" s="41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L69" s="41">
         <f t="shared" si="7"/>
@@ -6033,7 +6040,7 @@
       <c r="F70" s="40"/>
       <c r="G70" s="40"/>
       <c r="H70" s="40">
-        <f t="shared" ref="H70:H101" si="11">COUNTA(E70:G70)</f>
+        <f t="shared" ref="H70:H100" si="11">COUNTA(E70:G70)</f>
         <v>1</v>
       </c>
       <c r="I70" s="41">
@@ -6043,14 +6050,14 @@
         <v>108</v>
       </c>
       <c r="K70" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L70" s="41">
-        <f t="shared" ref="L70:L101" si="12">I70/N70</f>
+        <f t="shared" ref="L70:L100" si="12">I70/N70</f>
         <v>50</v>
       </c>
       <c r="M70" s="41">
-        <f t="shared" ref="M70:M101" si="13">IFERROR(L70/H70,"")</f>
+        <f t="shared" ref="M70:M100" si="13">IFERROR(L70/H70,"")</f>
         <v>50</v>
       </c>
       <c r="N70" s="42">
@@ -6058,7 +6065,7 @@
       </c>
       <c r="O70" s="38"/>
       <c r="P70" s="38" t="str">
-        <f t="shared" ref="P70:P101" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
+        <f t="shared" ref="P70:P100" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
         <v/>
       </c>
       <c r="Q70" s="40" t="str">
@@ -6131,7 +6138,7 @@
         <v>108</v>
       </c>
       <c r="K72" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L72" s="41">
         <f t="shared" si="12"/>
@@ -6177,7 +6184,7 @@
         <v>108</v>
       </c>
       <c r="K73" s="41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L73" s="41">
         <f t="shared" si="12"/>
@@ -6262,10 +6269,10 @@
         <v>-99</v>
       </c>
       <c r="J75" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K75" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L75" s="41">
         <f t="shared" si="12"/>
@@ -6311,7 +6318,7 @@
         <v>108</v>
       </c>
       <c r="K76" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L76" s="41">
         <f t="shared" si="12"/>
@@ -6355,7 +6362,7 @@
         <v>108</v>
       </c>
       <c r="K77" s="41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L77" s="41">
         <f t="shared" si="12"/>
@@ -6442,10 +6449,10 @@
         <v>-45</v>
       </c>
       <c r="J79" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K79" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L79" s="41">
         <f t="shared" si="12"/>
@@ -6491,7 +6498,7 @@
         <v>108</v>
       </c>
       <c r="K80" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L80" s="41">
         <f t="shared" si="12"/>
@@ -6537,7 +6544,7 @@
         <v>108</v>
       </c>
       <c r="K81" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L81" s="41">
         <f t="shared" si="12"/>
@@ -6583,7 +6590,7 @@
         <v>108</v>
       </c>
       <c r="K82" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L82" s="41">
         <f t="shared" si="12"/>
@@ -6629,7 +6636,7 @@
         <v>108</v>
       </c>
       <c r="K83" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L83" s="41">
         <f t="shared" si="12"/>
@@ -6719,7 +6726,7 @@
         <v>108</v>
       </c>
       <c r="K85" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L85" s="41">
         <f t="shared" si="12"/>
@@ -6738,7 +6745,7 @@
         <v/>
       </c>
       <c r="Q85" s="40" t="str">
-        <f t="shared" ref="Q85:Q116" ca="1" si="15">IF(O85&lt;&gt;"",IFERROR(DATEDIF(O85,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q85:Q115" ca="1" si="15">IF(O85&lt;&gt;"",IFERROR(DATEDIF(O85,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -6747,12 +6754,14 @@
       <c r="D86" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="E86" s="40"/>
+      <c r="E86" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F86" s="40"/>
       <c r="G86" s="40"/>
       <c r="H86" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="41">
         <v>16.97</v>
@@ -6767,9 +6776,9 @@
         <f t="shared" si="12"/>
         <v>16.97</v>
       </c>
-      <c r="M86" s="41" t="str">
+      <c r="M86" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>16.97</v>
       </c>
       <c r="N86" s="42">
         <v>1</v>
@@ -6805,7 +6814,7 @@
         <v>108</v>
       </c>
       <c r="K87" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L87" s="41">
         <f t="shared" si="12"/>
@@ -6851,7 +6860,7 @@
         <v>108</v>
       </c>
       <c r="K88" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L88" s="41">
         <f t="shared" si="12"/>
@@ -6896,7 +6905,7 @@
         <v>108</v>
       </c>
       <c r="K89" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L89" s="41">
         <f t="shared" si="12"/>
@@ -6922,7 +6931,7 @@
     <row r="90" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C90" s="38"/>
       <c r="D90" s="49" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E90" s="40" t="s">
         <v>1</v>
@@ -6936,21 +6945,21 @@
         <v>2</v>
       </c>
       <c r="I90" s="41">
-        <v>-300</v>
+        <v>56</v>
       </c>
       <c r="J90" s="41" t="s">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="K90" s="41" t="s">
         <v>244</v>
       </c>
       <c r="L90" s="41">
         <f t="shared" si="12"/>
-        <v>-300</v>
+        <v>56</v>
       </c>
       <c r="M90" s="41">
         <f t="shared" si="13"/>
-        <v>-150</v>
+        <v>28</v>
       </c>
       <c r="N90" s="42">
         <v>1</v>
@@ -6967,24 +6976,36 @@
     </row>
     <row r="91" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C91" s="38"/>
-      <c r="D91" s="49"/>
-      <c r="E91" s="40"/>
-      <c r="F91" s="40"/>
+      <c r="D91" s="49" t="s">
+        <v>249</v>
+      </c>
+      <c r="E91" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G91" s="40"/>
       <c r="H91" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="41"/>
-      <c r="J91" s="41"/>
-      <c r="K91" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I91" s="41">
+        <v>20</v>
+      </c>
+      <c r="J91" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="K91" s="41" t="s">
+        <v>85</v>
+      </c>
       <c r="L91" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="41" t="str">
+        <v>20</v>
+      </c>
+      <c r="M91" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="N91" s="42">
         <v>1</v>
@@ -7312,18 +7333,18 @@
       <c r="F101" s="40"/>
       <c r="G101" s="40"/>
       <c r="H101" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="H101:H132" si="16">COUNTA(E101:G101)</f>
         <v>0</v>
       </c>
       <c r="I101" s="41"/>
       <c r="J101" s="41"/>
       <c r="K101" s="41"/>
       <c r="L101" s="41">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="L101:L132" si="17">I101/N101</f>
         <v>0</v>
       </c>
       <c r="M101" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="M101:M132" si="18">IFERROR(L101/H101,"")</f>
         <v/>
       </c>
       <c r="N101" s="42">
@@ -7331,7 +7352,7 @@
       </c>
       <c r="O101" s="38"/>
       <c r="P101" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="P101:P132" si="19">IF(N101&lt;&gt;1,EDATE(O101,N101-1),"")</f>
         <v/>
       </c>
       <c r="Q101" s="40" t="str">
@@ -7346,18 +7367,18 @@
       <c r="F102" s="40"/>
       <c r="G102" s="40"/>
       <c r="H102" s="40">
-        <f t="shared" ref="H102:H133" si="16">COUNTA(E102:G102)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I102" s="41"/>
       <c r="J102" s="41"/>
       <c r="K102" s="41"/>
       <c r="L102" s="41">
-        <f t="shared" ref="L102:L133" si="17">I102/N102</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M102" s="41" t="str">
-        <f t="shared" ref="M102:M133" si="18">IFERROR(L102/H102,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N102" s="42">
@@ -7365,7 +7386,7 @@
       </c>
       <c r="O102" s="38"/>
       <c r="P102" s="38" t="str">
-        <f t="shared" ref="P102:P133" si="19">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q102" s="40" t="str">
@@ -7845,7 +7866,7 @@
         <v/>
       </c>
       <c r="Q116" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ref="Q116:Q148" ca="1" si="20">IF(O116&lt;&gt;"",IFERROR(DATEDIF(O116,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7879,7 +7900,7 @@
         <v/>
       </c>
       <c r="Q117" s="40" t="str">
-        <f t="shared" ref="Q117:Q149" ca="1" si="20">IF(O117&lt;&gt;"",IFERROR(DATEDIF(O117,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8400,18 +8421,18 @@
       <c r="F133" s="40"/>
       <c r="G133" s="40"/>
       <c r="H133" s="40">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="H133:H148" si="21">COUNTA(E133:G133)</f>
         <v>0</v>
       </c>
       <c r="I133" s="41"/>
       <c r="J133" s="41"/>
       <c r="K133" s="41"/>
       <c r="L133" s="41">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="L133:L148" si="22">I133/N133</f>
         <v>0</v>
       </c>
       <c r="M133" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="M133:M148" si="23">IFERROR(L133/H133,"")</f>
         <v/>
       </c>
       <c r="N133" s="42">
@@ -8419,7 +8440,7 @@
       </c>
       <c r="O133" s="38"/>
       <c r="P133" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="P133:P148" si="24">IF(N133&lt;&gt;1,EDATE(O133,N133-1),"")</f>
         <v/>
       </c>
       <c r="Q133" s="40" t="str">
@@ -8434,18 +8455,18 @@
       <c r="F134" s="40"/>
       <c r="G134" s="40"/>
       <c r="H134" s="40">
-        <f t="shared" ref="H134:H149" si="21">COUNTA(E134:G134)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I134" s="41"/>
       <c r="J134" s="41"/>
       <c r="K134" s="41"/>
       <c r="L134" s="41">
-        <f t="shared" ref="L134:L149" si="22">I134/N134</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M134" s="41" t="str">
-        <f t="shared" ref="M134:M149" si="23">IFERROR(L134/H134,"")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N134" s="42">
@@ -8453,7 +8474,7 @@
       </c>
       <c r="O134" s="38"/>
       <c r="P134" s="38" t="str">
-        <f t="shared" ref="P134:P149" si="24">IF(N134&lt;&gt;1,EDATE(O134,N134-1),"")</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Q134" s="40" t="str">
@@ -8893,7 +8914,7 @@
       <c r="N147" s="42">
         <v>1</v>
       </c>
-      <c r="O147" s="38"/>
+      <c r="O147" s="44"/>
       <c r="P147" s="38" t="str">
         <f t="shared" si="24"/>
         <v/>
@@ -8927,7 +8948,7 @@
       <c r="N148" s="42">
         <v>1</v>
       </c>
-      <c r="O148" s="44"/>
+      <c r="O148" s="38"/>
       <c r="P148" s="38" t="str">
         <f t="shared" si="24"/>
         <v/>
@@ -8943,68 +8964,34 @@
       <c r="E149" s="40"/>
       <c r="F149" s="40"/>
       <c r="G149" s="40"/>
-      <c r="H149" s="40">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
+      <c r="H149" s="40"/>
       <c r="I149" s="41"/>
       <c r="J149" s="41"/>
       <c r="K149" s="41"/>
-      <c r="L149" s="41">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M149" s="41" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N149" s="42">
-        <v>1</v>
-      </c>
-      <c r="O149" s="38"/>
-      <c r="P149" s="38" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="Q149" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="38"/>
-      <c r="D150" s="49"/>
-      <c r="E150" s="40"/>
-      <c r="F150" s="40"/>
-      <c r="G150" s="40"/>
-      <c r="H150" s="40"/>
-      <c r="I150" s="41"/>
-      <c r="J150" s="41"/>
-      <c r="K150" s="41"/>
-      <c r="L150" s="41"/>
-      <c r="M150" s="41"/>
-      <c r="N150" s="42"/>
-      <c r="O150" s="67"/>
-      <c r="P150" s="67"/>
-      <c r="Q150" s="40"/>
+      <c r="L149" s="41"/>
+      <c r="M149" s="41"/>
+      <c r="N149" s="42"/>
+      <c r="O149" s="67"/>
+      <c r="P149" s="67"/>
+      <c r="Q149" s="40"/>
     </row>
   </sheetData>
-  <autoFilter ref="C5:Q150" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q150">
-      <sortCondition ref="P5:P150"/>
+  <autoFilter ref="C5:Q149" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q149">
+      <sortCondition ref="P5:P149"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="I6:I150">
+  <conditionalFormatting sqref="I6:I149">
     <cfRule type="cellIs" dxfId="13" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J150">
+  <conditionalFormatting sqref="J6:J149">
     <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:K150">
+  <conditionalFormatting sqref="J6:K149">
     <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
@@ -12153,7 +12140,9 @@
       <c r="B9" s="57" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="40"/>
+      <c r="C9" s="40" t="s">
+        <v>227</v>
+      </c>
       <c r="D9" s="57"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FEBE841-6662-4C7C-881E-9840CD4E16A5}"/>
+  <xr:revisionPtr revIDLastSave="518" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C4124B0-3E44-4C72-9B68-D830C4D7227F}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -1715,7 +1715,7 @@
       <c r="B3" s="76"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C22+C23+C7</f>
-        <v>1920.3914047619032</v>
+        <v>1920.2114047619029</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-8117.6085952380963</v>
+        <v>-8117.7885952380966</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5695.3769285714297</v>
+        <v>5695.55692857143</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5695.3769285714297</v>
+        <v>5695.55692857143</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="D4" s="27">
         <f>Saldo!C9+D5</f>
-        <v>5695.3769285714297</v>
+        <v>5695.55692857143</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -3051,11 +3051,11 @@
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="48">
         <f>SUM(L6:L376)</f>
-        <v>7907.4294285714286</v>
+        <v>7907.6094285714289</v>
       </c>
       <c r="E2" s="35">
         <f>SUMIF($E$6:$E$376,E1,$M$6:$M$376)</f>
-        <v>5695.3769285714297</v>
+        <v>5695.55692857143</v>
       </c>
       <c r="F2" s="35">
         <f>SUMIF($F$6:$F$376,F1,$M$6:$M$376)</f>
@@ -5372,7 +5372,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="41">
-        <v>-42.08</v>
+        <v>-419</v>
       </c>
       <c r="J55" s="41" t="s">
         <v>44</v>
@@ -5382,23 +5382,25 @@
       </c>
       <c r="L55" s="41">
         <f t="shared" si="7"/>
-        <v>-42.08</v>
+        <v>-41.9</v>
       </c>
       <c r="M55" s="41">
         <f t="shared" si="8"/>
-        <v>-42.08</v>
+        <v>-41.9</v>
       </c>
       <c r="N55" s="42">
-        <v>1</v>
-      </c>
-      <c r="O55" s="67"/>
-      <c r="P55" s="67" t="str">
+        <v>10</v>
+      </c>
+      <c r="O55" s="67">
+        <v>45994</v>
+      </c>
+      <c r="P55" s="67">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q55" s="40" t="str">
+        <v>46268</v>
+      </c>
+      <c r="Q55" s="40">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="3:17" x14ac:dyDescent="0.25">
@@ -5416,7 +5418,8 @@
         <v>1</v>
       </c>
       <c r="I56" s="41">
-        <v>-64.42</v>
+        <f>(-64.42*12)</f>
+        <v>-773.04</v>
       </c>
       <c r="J56" s="41" t="s">
         <v>44</v>
@@ -5433,16 +5436,18 @@
         <v>-64.42</v>
       </c>
       <c r="N56" s="42">
-        <v>1</v>
-      </c>
-      <c r="O56" s="67"/>
-      <c r="P56" s="67" t="str">
+        <v>12</v>
+      </c>
+      <c r="O56" s="67">
+        <v>45964</v>
+      </c>
+      <c r="P56" s="67">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q56" s="40" t="str">
+        <v>46298</v>
+      </c>
+      <c r="Q56" s="40">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="518" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C4124B0-3E44-4C72-9B68-D830C4D7227F}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB7BCCD0-7C8E-4AE5-B842-C977499CAFDB}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -3156,10 +3156,12 @@
       <c r="N6" s="42">
         <v>8</v>
       </c>
-      <c r="O6" s="67"/>
+      <c r="O6" s="67">
+        <v>46237</v>
+      </c>
       <c r="P6" s="67">
         <f t="shared" ref="P6:P37" si="3">IF(N6&lt;&gt;1,EDATE(O6,N6-1),"")</f>
-        <v>213</v>
+        <v>46449</v>
       </c>
       <c r="Q6" s="40" t="str">
         <f ca="1">IF(O6&lt;&gt;"",IFERROR(DATEDIF(O6,TODAY(),"m")+1,""),"")</f>
@@ -8981,11 +8983,7 @@
       <c r="Q149" s="40"/>
     </row>
   </sheetData>
-  <autoFilter ref="C5:Q149" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q149">
-      <sortCondition ref="P5:P149"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="C5:Q149" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="I6:I149">
     <cfRule type="cellIs" dxfId="13" priority="5" operator="lessThan">
       <formula>0</formula>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="521" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB7BCCD0-7C8E-4AE5-B842-C977499CAFDB}"/>
+  <xr:revisionPtr revIDLastSave="606" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9020F2C2-9B53-45FA-9756-09231AE7151F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="257">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -192,6 +192,18 @@
     <t>Modo de Pagamento</t>
   </si>
   <si>
+    <t>Pedrinho Bancos</t>
+  </si>
+  <si>
+    <t>Produtos</t>
+  </si>
+  <si>
+    <t>Ração</t>
+  </si>
+  <si>
+    <t>Fixo</t>
+  </si>
+  <si>
     <t>Manual</t>
   </si>
   <si>
@@ -201,16 +213,106 @@
     <t>Assinaturas-Fixo</t>
   </si>
   <si>
+    <t>Lavadora Midea</t>
+  </si>
+  <si>
+    <t>Pacote Psiquiatra</t>
+  </si>
+  <si>
+    <t>Saúde</t>
+  </si>
+  <si>
+    <t>Cinto Sabot</t>
+  </si>
+  <si>
+    <t>Calça moletom</t>
+  </si>
+  <si>
+    <t>Tênis Puma - A ser estornado</t>
+  </si>
+  <si>
+    <t>Tênis Puma - Correto</t>
+  </si>
+  <si>
+    <t>Case+Película</t>
+  </si>
+  <si>
+    <t>GPS Moto</t>
+  </si>
+  <si>
+    <t>Calça Sabot</t>
+  </si>
+  <si>
+    <t>Roupa</t>
+  </si>
+  <si>
+    <t>Revisão Royal Enfield</t>
+  </si>
+  <si>
+    <t>Transporte</t>
+  </si>
+  <si>
     <t>Muay Thai</t>
   </si>
   <si>
-    <t>Saúde</t>
+    <t>Calça Kevlar</t>
+  </si>
+  <si>
+    <t>Equipamentos Grid Motors</t>
+  </si>
+  <si>
+    <t>Racing Rabbit</t>
+  </si>
+  <si>
+    <t>Moto</t>
+  </si>
+  <si>
+    <t>PS Plus Samuel</t>
+  </si>
+  <si>
+    <t>Jogos PSN</t>
+  </si>
+  <si>
+    <t>Renner - Presente Stella</t>
+  </si>
+  <si>
+    <t>Renner Stella</t>
+  </si>
+  <si>
+    <t>Capacete Stella</t>
+  </si>
+  <si>
+    <t>HDMI Splitter</t>
+  </si>
+  <si>
+    <t>Caderno Azadi Store</t>
+  </si>
+  <si>
+    <t>Multiprocessador</t>
+  </si>
+  <si>
+    <t>Wolverine Pré venda</t>
+  </si>
+  <si>
+    <t>Blood of the Dawnwalker</t>
+  </si>
+  <si>
+    <t>Escapamento JBK</t>
   </si>
   <si>
     <t>Clube Literatura Clássica</t>
   </si>
   <si>
-    <t>Fixo</t>
+    <t>Jaqueta Stella</t>
+  </si>
+  <si>
+    <t>Segunda Pele Kevlar</t>
+  </si>
+  <si>
+    <t>Rog Ally Dock</t>
+  </si>
+  <si>
+    <t>Luva Fairtex</t>
   </si>
   <si>
     <t>Hostinger Nano</t>
@@ -219,6 +321,15 @@
     <t>Serviços</t>
   </si>
   <si>
+    <t>TENTAR ADIATNAR</t>
+  </si>
+  <si>
+    <t>Moletom Brutal Kill</t>
+  </si>
+  <si>
+    <t>Roupas</t>
+  </si>
+  <si>
     <t>HBO</t>
   </si>
   <si>
@@ -264,81 +375,6 @@
     <t>Câmera</t>
   </si>
   <si>
-    <t>Ração</t>
-  </si>
-  <si>
-    <t>Lavadora Midea</t>
-  </si>
-  <si>
-    <t>Produtos</t>
-  </si>
-  <si>
-    <t>Pacote Psiquiatra</t>
-  </si>
-  <si>
-    <t>Cinto Sabot</t>
-  </si>
-  <si>
-    <t>Calça moletom</t>
-  </si>
-  <si>
-    <t>Tênis Puma - A ser estornado</t>
-  </si>
-  <si>
-    <t>Tênis Puma - Correto</t>
-  </si>
-  <si>
-    <t>Case+Película</t>
-  </si>
-  <si>
-    <t>GPS Moto</t>
-  </si>
-  <si>
-    <t>Calça Sabot</t>
-  </si>
-  <si>
-    <t>Roupa</t>
-  </si>
-  <si>
-    <t>Revisão Royal Enfield</t>
-  </si>
-  <si>
-    <t>Transporte</t>
-  </si>
-  <si>
-    <t>Calça Kevlar</t>
-  </si>
-  <si>
-    <t>Equipamentos Grid Motors</t>
-  </si>
-  <si>
-    <t>Racing Rabbit</t>
-  </si>
-  <si>
-    <t>Moto</t>
-  </si>
-  <si>
-    <t>PS Plus Samuel</t>
-  </si>
-  <si>
-    <t>Capacete Stella</t>
-  </si>
-  <si>
-    <t>HDMI Splitter</t>
-  </si>
-  <si>
-    <t>Caderno Azadi Store</t>
-  </si>
-  <si>
-    <t>Multiprocessador</t>
-  </si>
-  <si>
-    <t>Jaqueta Stella</t>
-  </si>
-  <si>
-    <t>Segunda Pele Kevlar</t>
-  </si>
-  <si>
     <t>Estorno Puma</t>
   </si>
   <si>
@@ -348,27 +384,6 @@
     <t>Estorno Jaqueta Grid Motors</t>
   </si>
   <si>
-    <t>Rog Ally Dock</t>
-  </si>
-  <si>
-    <t>Wolverine Pré venda</t>
-  </si>
-  <si>
-    <t>Jogos PSN</t>
-  </si>
-  <si>
-    <t>Luva Fairtex</t>
-  </si>
-  <si>
-    <t>Pedrinho Bancos</t>
-  </si>
-  <si>
-    <t>Blood of the Dawnwalker</t>
-  </si>
-  <si>
-    <t>Escapamento JBK</t>
-  </si>
-  <si>
     <t>The Alters</t>
   </si>
   <si>
@@ -381,6 +396,9 @@
     <t>Bonfas Chope</t>
   </si>
   <si>
+    <t>Comida</t>
+  </si>
+  <si>
     <t>Bonfas Lanche</t>
   </si>
   <si>
@@ -390,13 +408,13 @@
     <t>Ração Brida</t>
   </si>
   <si>
+    <t>Pet</t>
+  </si>
+  <si>
     <t>Pagamento Ração Brida</t>
   </si>
   <si>
-    <t>TENTAR ADIATNAR</t>
-  </si>
-  <si>
-    <t>Moletom Brutal Kill</t>
+    <t>PAGAMENTO</t>
   </si>
   <si>
     <t>Uber Mr. Jones</t>
@@ -414,6 +432,9 @@
     <t>Gasolina</t>
   </si>
   <si>
+    <t>Carro</t>
+  </si>
+  <si>
     <t>Lanche</t>
   </si>
   <si>
@@ -444,6 +465,60 @@
     <t>Pagamento Odisseia</t>
   </si>
   <si>
+    <t>Ifood</t>
+  </si>
+  <si>
+    <t>Mercado</t>
+  </si>
+  <si>
+    <t>Rappi 1</t>
+  </si>
+  <si>
+    <t>Rappi 2</t>
+  </si>
+  <si>
+    <t>Saco de lixo e copo descartável</t>
+  </si>
+  <si>
+    <t>Mr Jones</t>
+  </si>
+  <si>
+    <t>Baked Potato</t>
+  </si>
+  <si>
+    <t>Pão e Frios</t>
+  </si>
+  <si>
+    <t>Bares Augusta</t>
+  </si>
+  <si>
+    <t>Café Cotia</t>
+  </si>
+  <si>
+    <t>Estacionamento Cotia</t>
+  </si>
+  <si>
+    <t>Bar do Alemão</t>
+  </si>
+  <si>
+    <t>Pagamento Bar do Alemão</t>
+  </si>
+  <si>
+    <t>Luva Pai</t>
+  </si>
+  <si>
+    <t>Veda Escape</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>APC+Puscifer</t>
+  </si>
+  <si>
+    <t>APC+Puscifer Pagamento</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -742,60 +817,6 @@
   </si>
   <si>
     <t>Dera</t>
-  </si>
-  <si>
-    <t>Ifood</t>
-  </si>
-  <si>
-    <t>Mercado</t>
-  </si>
-  <si>
-    <t>Rappi 1</t>
-  </si>
-  <si>
-    <t>Rappi 2</t>
-  </si>
-  <si>
-    <t>Saco de lixo e copo descartável</t>
-  </si>
-  <si>
-    <t>Mr Jones</t>
-  </si>
-  <si>
-    <t>Renner - Presente Stella</t>
-  </si>
-  <si>
-    <t>Renner Stella</t>
-  </si>
-  <si>
-    <t>Baked Potato</t>
-  </si>
-  <si>
-    <t>Pão e Frios</t>
-  </si>
-  <si>
-    <t>Bares Augusta</t>
-  </si>
-  <si>
-    <t>PAGAMENTO</t>
-  </si>
-  <si>
-    <t>Comida</t>
-  </si>
-  <si>
-    <t>Pet</t>
-  </si>
-  <si>
-    <t>Roupas</t>
-  </si>
-  <si>
-    <t>Carro</t>
-  </si>
-  <si>
-    <t>Café Cotia</t>
-  </si>
-  <si>
-    <t>Estacionamento Cotia</t>
   </si>
 </sst>
 </file>
@@ -807,7 +828,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1280,20 +1301,20 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="25">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1343,6 +1364,60 @@
       <font>
         <color rgb="FF00B050"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1457,10 +1532,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1689,7 +1760,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F37"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
@@ -1698,9 +1769,9 @@
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="75" t="s">
+    <row r="1" spans="2:6" ht="15.75" customHeight="1"/>
+    <row r="2" spans="2:6" ht="23.25" customHeight="1">
+      <c r="B2" s="77" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1711,20 +1782,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="76"/>
+    <row r="3" spans="2:6" ht="24" customHeight="1">
+      <c r="B3" s="78"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C22+C23+C7</f>
-        <v>1920.2114047619029</v>
+        <v>1823.6447380952363</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E22+E23</f>
-        <v>3455.8775000000005</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+        <v>3417.8775000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="7.5" customHeight="1"/>
+    <row r="5" spans="2:6">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1736,21 +1807,21 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-8117.7885952380966</v>
+        <v>-8214.3552619047641</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-5544.1225000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+        <v>-5582.1225000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1758,7 +1829,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6">
       <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1772,35 +1843,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6">
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5695.55692857143</v>
+        <v>5792.1235952380966</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>2162.0525000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2200.0525000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5695.55692857143</v>
+        <v>5792.1235952380966</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>2162.0525000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2200.0525000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
@@ -1814,7 +1885,7 @@
         <v>3382.07</v>
       </c>
     </row>
-    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" outlineLevel="1">
       <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
@@ -1828,7 +1899,7 @@
         <v>1617.835</v>
       </c>
     </row>
-    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" outlineLevel="1">
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1842,7 +1913,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" outlineLevel="1">
       <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
@@ -1857,7 +1928,7 @@
       </c>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" outlineLevel="1">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
@@ -1871,7 +1942,7 @@
         <v>43.35</v>
       </c>
     </row>
-    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" outlineLevel="1">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
@@ -1885,7 +1956,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" outlineLevel="1">
       <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
@@ -1899,7 +1970,7 @@
         <v>183.5</v>
       </c>
     </row>
-    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" outlineLevel="1">
       <c r="B18" s="17" t="s">
         <v>16</v>
       </c>
@@ -1909,7 +1980,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" outlineLevel="1">
       <c r="B19" s="20" t="s">
         <v>17</v>
       </c>
@@ -1917,19 +1988,19 @@
       <c r="D19" s="22"/>
       <c r="E19" s="21"/>
     </row>
-    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" outlineLevel="1">
       <c r="B20" s="13"/>
       <c r="C20" s="14"/>
       <c r="D20" s="15"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" outlineLevel="1">
       <c r="B21" s="13"/>
       <c r="C21" s="14"/>
       <c r="D21" s="15"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5">
       <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
@@ -1941,7 +2012,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5">
       <c r="B23" s="7" t="s">
         <v>19</v>
       </c>
@@ -1955,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" outlineLevel="1">
       <c r="B24" s="13" t="s">
         <v>20</v>
       </c>
@@ -1966,7 +2037,7 @@
       <c r="D24" s="15"/>
       <c r="E24" s="14"/>
     </row>
-    <row r="25" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" outlineLevel="1">
       <c r="B25" s="13" t="s">
         <v>21</v>
       </c>
@@ -1974,7 +2045,7 @@
       <c r="D25" s="23"/>
       <c r="E25" s="24"/>
     </row>
-    <row r="26" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" outlineLevel="1">
       <c r="B26" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
         <v xml:space="preserve">       </v>
@@ -1986,7 +2057,7 @@
       <c r="D26" s="23"/>
       <c r="E26" s="24"/>
     </row>
-    <row r="27" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" outlineLevel="1">
       <c r="B27" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       Reembolso Psicóloga</v>
@@ -1998,7 +2069,7 @@
       <c r="D27" s="23"/>
       <c r="E27" s="24"/>
     </row>
-    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" outlineLevel="1">
       <c r="B28" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
@@ -2010,7 +2081,7 @@
       <c r="D28" s="23"/>
       <c r="E28" s="24"/>
     </row>
-    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" outlineLevel="1">
       <c r="B29" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
@@ -2022,7 +2093,7 @@
       <c r="D29" s="23"/>
       <c r="E29" s="24"/>
     </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" outlineLevel="1">
       <c r="B30" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
@@ -2034,7 +2105,7 @@
       <c r="D30" s="23"/>
       <c r="E30" s="24"/>
     </row>
-    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" outlineLevel="1">
       <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
@@ -2046,7 +2117,7 @@
       <c r="D31" s="23"/>
       <c r="E31" s="24"/>
     </row>
-    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" outlineLevel="1">
       <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
@@ -2058,7 +2129,7 @@
       <c r="D32" s="23"/>
       <c r="E32" s="24"/>
     </row>
-    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" outlineLevel="1">
       <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
@@ -2070,7 +2141,7 @@
       <c r="D33" s="23"/>
       <c r="E33" s="24"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6">
       <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
@@ -2083,7 +2154,7 @@
       <c r="E34" s="24"/>
       <c r="F34" s="16"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6">
       <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L17</f>
         <v xml:space="preserve">       </v>
@@ -2096,7 +2167,7 @@
       <c r="E35" s="24"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6">
       <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
@@ -2108,7 +2179,7 @@
       <c r="D36" s="23"/>
       <c r="E36" s="24"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6">
       <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
@@ -2132,7 +2203,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:D19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" customWidth="1"/>
@@ -2141,8 +2212,8 @@
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="39" customHeight="1"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1">
       <c r="B2" s="25"/>
       <c r="C2" s="26" t="s">
         <v>2</v>
@@ -2151,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2164,45 +2235,45 @@
         <v>40.161666666666669</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>2162.0525000000002</v>
+        <v>2200.0525000000002</v>
       </c>
       <c r="D4" s="27">
         <f>Saldo!C9+D5</f>
-        <v>5695.55692857143</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+        <v>5792.1235952380966</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
       <c r="D7" s="27"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="13"/>
       <c r="C8" s="8"/>
       <c r="D8" s="27"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="13"/>
       <c r="C9" s="8"/>
       <c r="D9" s="27"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
@@ -2212,7 +2283,7 @@
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4">
       <c r="B11" s="13" t="s">
         <v>22</v>
       </c>
@@ -2222,7 +2293,7 @@
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4">
       <c r="B12" s="28" t="s">
         <v>23</v>
       </c>
@@ -2232,7 +2303,7 @@
       </c>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4">
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
@@ -2242,7 +2313,7 @@
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4">
       <c r="B14" s="13" t="s">
         <v>13</v>
       </c>
@@ -2252,7 +2323,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4">
       <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
@@ -2262,7 +2333,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4">
       <c r="B16" s="13" t="s">
         <v>15</v>
       </c>
@@ -2272,20 +2343,20 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4">
       <c r="B17" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4209.7375000000002</v>
+        <v>4247.7375000000002</v>
       </c>
       <c r="D17" s="30"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4">
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4">
       <c r="C19" s="31"/>
     </row>
   </sheetData>
@@ -2300,7 +2371,7 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="C1:Q67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="2" customWidth="1"/>
@@ -2315,7 +2386,7 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1">
       <c r="D1" s="32" t="s">
         <v>25</v>
       </c>
@@ -2329,7 +2400,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="34">
         <f>SUM(L5:L21)</f>
         <v>40.161666666666669</v>
@@ -2347,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17" ht="30" customHeight="1">
       <c r="C4" s="36" t="s">
         <v>27</v>
       </c>
@@ -2394,7 +2465,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="16.5" customHeight="1">
       <c r="C5" s="73" t="s">
         <v>42</v>
       </c>
@@ -2442,7 +2513,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17" ht="16.5" customHeight="1">
       <c r="C6" s="40"/>
       <c r="D6" s="39"/>
       <c r="E6" s="40"/>
@@ -2474,7 +2545,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" ht="16.5" customHeight="1">
       <c r="C7" s="38"/>
       <c r="D7" s="39"/>
       <c r="E7" s="40"/>
@@ -2503,7 +2574,7 @@
       <c r="P7" s="38"/>
       <c r="Q7" s="40"/>
     </row>
-    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17" ht="16.5" customHeight="1">
       <c r="C8" s="38"/>
       <c r="D8" s="39"/>
       <c r="E8" s="40"/>
@@ -2532,7 +2603,7 @@
       <c r="P8" s="38"/>
       <c r="Q8" s="40"/>
     </row>
-    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17" ht="16.5" customHeight="1">
       <c r="C9" s="38"/>
       <c r="D9" s="39"/>
       <c r="E9" s="40"/>
@@ -2561,7 +2632,7 @@
       <c r="P9" s="38"/>
       <c r="Q9" s="40"/>
     </row>
-    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" ht="16.5" customHeight="1">
       <c r="C10" s="38"/>
       <c r="D10" s="39"/>
       <c r="E10" s="40"/>
@@ -2593,7 +2664,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17" ht="16.5" customHeight="1">
       <c r="C11" s="38"/>
       <c r="D11" s="39"/>
       <c r="E11" s="40"/>
@@ -2622,7 +2693,7 @@
       <c r="P11" s="38"/>
       <c r="Q11" s="40"/>
     </row>
-    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17" ht="16.5" customHeight="1">
       <c r="C12" s="40"/>
       <c r="D12" s="39"/>
       <c r="E12" s="40"/>
@@ -2651,7 +2722,7 @@
       <c r="P12" s="38"/>
       <c r="Q12" s="40"/>
     </row>
-    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" ht="16.5" customHeight="1">
       <c r="C13" s="40"/>
       <c r="D13" s="39"/>
       <c r="E13" s="40"/>
@@ -2680,7 +2751,7 @@
       <c r="P13" s="38"/>
       <c r="Q13" s="40"/>
     </row>
-    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17" ht="16.5" customHeight="1">
       <c r="C14" s="40"/>
       <c r="D14" s="39"/>
       <c r="E14" s="40"/>
@@ -2709,7 +2780,7 @@
       <c r="P14" s="38"/>
       <c r="Q14" s="40"/>
     </row>
-    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17" ht="16.5" customHeight="1">
       <c r="C15" s="40"/>
       <c r="D15" s="39"/>
       <c r="E15" s="40"/>
@@ -2738,7 +2809,7 @@
       <c r="P15" s="38"/>
       <c r="Q15" s="40"/>
     </row>
-    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" ht="16.5" customHeight="1">
       <c r="C16" s="40"/>
       <c r="D16" s="39"/>
       <c r="E16" s="40"/>
@@ -2755,7 +2826,7 @@
       <c r="P16" s="38"/>
       <c r="Q16" s="40"/>
     </row>
-    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" ht="16.5" customHeight="1">
       <c r="C17" s="38"/>
       <c r="D17" s="39"/>
       <c r="E17" s="40"/>
@@ -2772,7 +2843,7 @@
       <c r="P17" s="38"/>
       <c r="Q17" s="40"/>
     </row>
-    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" ht="16.5" customHeight="1">
       <c r="C18" s="38"/>
       <c r="D18" s="39"/>
       <c r="E18" s="40"/>
@@ -2789,7 +2860,7 @@
       <c r="P18" s="38"/>
       <c r="Q18" s="40"/>
     </row>
-    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" ht="16.5" customHeight="1">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -2800,198 +2871,198 @@
       <c r="O19" s="44"/>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17">
       <c r="H20" s="2"/>
       <c r="O20" s="45"/>
       <c r="P20" s="45"/>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17">
       <c r="H21" s="2"/>
       <c r="O21" s="45"/>
       <c r="P21" s="45"/>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17">
       <c r="H22" s="2"/>
       <c r="O22" s="45"/>
       <c r="P22" s="45"/>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17">
       <c r="O23" s="45"/>
       <c r="P23" s="45"/>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17">
       <c r="O24" s="45"/>
       <c r="P24" s="45"/>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17">
       <c r="O25" s="45"/>
       <c r="P25" s="45"/>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17">
       <c r="O26" s="45"/>
       <c r="P26" s="45"/>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17">
       <c r="O27" s="45"/>
       <c r="P27" s="45"/>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17">
       <c r="O28" s="45"/>
       <c r="P28" s="45"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17">
       <c r="O29" s="45"/>
       <c r="P29" s="45"/>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17">
       <c r="O30" s="45"/>
       <c r="P30" s="45"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17">
       <c r="O31" s="45"/>
       <c r="P31" s="45"/>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17">
       <c r="O32" s="45"/>
       <c r="P32" s="45"/>
     </row>
-    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="15:16">
       <c r="O33" s="45"/>
       <c r="P33" s="45"/>
     </row>
-    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="15:16">
       <c r="O34" s="45"/>
       <c r="P34" s="45"/>
     </row>
-    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="15:16">
       <c r="O35" s="45"/>
       <c r="P35" s="45"/>
     </row>
-    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="15:16">
       <c r="O36" s="45"/>
       <c r="P36" s="45"/>
     </row>
-    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="15:16">
       <c r="O37" s="45"/>
       <c r="P37" s="45"/>
     </row>
-    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="15:16">
       <c r="O38" s="45"/>
       <c r="P38" s="45"/>
     </row>
-    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="15:16">
       <c r="O39" s="45"/>
       <c r="P39" s="45"/>
     </row>
-    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="15:16">
       <c r="O40" s="45"/>
       <c r="P40" s="45"/>
     </row>
-    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="15:16">
       <c r="O41" s="45"/>
       <c r="P41" s="45"/>
     </row>
-    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="15:16">
       <c r="O42" s="45"/>
       <c r="P42" s="45"/>
     </row>
-    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="15:16">
       <c r="O43" s="45"/>
       <c r="P43" s="45"/>
     </row>
-    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="15:16">
       <c r="O44" s="45"/>
       <c r="P44" s="45"/>
     </row>
-    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="15:16">
       <c r="O45" s="45"/>
       <c r="P45" s="45"/>
     </row>
-    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="15:16">
       <c r="O46" s="45"/>
       <c r="P46" s="45"/>
     </row>
-    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="15:16">
       <c r="O47" s="45"/>
       <c r="P47" s="45"/>
     </row>
-    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="15:16">
       <c r="O48" s="45"/>
       <c r="P48" s="45"/>
     </row>
-    <row r="49" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="15:16">
       <c r="O49" s="45"/>
       <c r="P49" s="45"/>
     </row>
-    <row r="50" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="15:16">
       <c r="O50" s="45"/>
       <c r="P50" s="45"/>
     </row>
-    <row r="51" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="15:16">
       <c r="O51" s="45"/>
       <c r="P51" s="45"/>
     </row>
-    <row r="52" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="15:16">
       <c r="O52" s="45"/>
       <c r="P52" s="45"/>
     </row>
-    <row r="53" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="15:16">
       <c r="O53" s="45"/>
       <c r="P53" s="45"/>
     </row>
-    <row r="54" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="15:16">
       <c r="O54" s="45"/>
       <c r="P54" s="45"/>
     </row>
-    <row r="55" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="15:16">
       <c r="O55" s="45"/>
       <c r="P55" s="45"/>
     </row>
-    <row r="56" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="15:16">
       <c r="O56" s="45"/>
       <c r="P56" s="45"/>
     </row>
-    <row r="57" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="15:16">
       <c r="O57" s="45"/>
       <c r="P57" s="45"/>
     </row>
-    <row r="58" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="15:16">
       <c r="O58" s="45"/>
       <c r="P58" s="45"/>
     </row>
-    <row r="59" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="15:16">
       <c r="O59" s="45"/>
       <c r="P59" s="45"/>
     </row>
-    <row r="60" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="15:16">
       <c r="O60" s="45"/>
       <c r="P60" s="45"/>
     </row>
-    <row r="61" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="15:16">
       <c r="O61" s="45"/>
       <c r="P61" s="45"/>
     </row>
-    <row r="62" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="15:16">
       <c r="O62" s="45"/>
       <c r="P62" s="45"/>
     </row>
-    <row r="63" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="15:16">
       <c r="O63" s="45"/>
       <c r="P63" s="45"/>
     </row>
-    <row r="64" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="15:16">
       <c r="O64" s="45"/>
       <c r="P64" s="45"/>
     </row>
-    <row r="65" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="15:16">
       <c r="O65" s="45"/>
       <c r="P65" s="45"/>
     </row>
-    <row r="66" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="15:16">
       <c r="O66" s="45"/>
       <c r="P66" s="45"/>
     </row>
-    <row r="67" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="15:16">
       <c r="O67" s="45"/>
       <c r="P67" s="45"/>
     </row>
@@ -3002,7 +3073,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3017,7 +3088,7 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="C1:Q149"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
@@ -3032,7 +3103,7 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1">
       <c r="D1" s="47" t="s">
         <v>46</v>
       </c>
@@ -3048,18 +3119,18 @@
       <c r="L1" s="46"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="48">
         <f>SUM(L6:L376)</f>
-        <v>7907.6094285714289</v>
+        <v>8042.4360952380957</v>
       </c>
       <c r="E2" s="35">
         <f>SUMIF($E$6:$E$376,E1,$M$6:$M$376)</f>
-        <v>5695.55692857143</v>
+        <v>5792.1235952380966</v>
       </c>
       <c r="F2" s="35">
         <f>SUMIF($F$6:$F$376,F1,$M$6:$M$376)</f>
-        <v>2162.0525000000002</v>
+        <v>2200.0525000000002</v>
       </c>
       <c r="G2" s="35">
         <f>SUMIF($G$6:$G$376,G1,$M$6:$M$376)</f>
@@ -3068,14 +3139,14 @@
       <c r="L2" s="46"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17">
       <c r="L3" s="46"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17">
       <c r="M4" s="46"/>
     </row>
-    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="32.25" customHeight="1">
       <c r="C5" s="36"/>
       <c r="D5" s="36" t="s">
         <v>28</v>
@@ -3120,10 +3191,10 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17">
       <c r="C6" s="38"/>
       <c r="D6" s="49" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="E6" s="40" t="s">
         <v>1</v>
@@ -3143,7 +3214,7 @@
         <v>44</v>
       </c>
       <c r="K6" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L6" s="41">
         <f t="shared" ref="L6:L37" si="1">I6/N6</f>
@@ -3168,10 +3239,10 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17">
       <c r="C7" s="38"/>
       <c r="D7" s="39" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="E7" s="40" t="s">
         <v>1</v>
@@ -3191,7 +3262,7 @@
         <v>44</v>
       </c>
       <c r="K7" s="40" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L7" s="41">
         <f t="shared" si="1"/>
@@ -3216,10 +3287,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17">
       <c r="C8" s="38"/>
       <c r="D8" s="39" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E8" s="40" t="s">
         <v>1</v>
@@ -3234,10 +3305,10 @@
         <v>258</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L8" s="41">
         <f t="shared" si="1"/>
@@ -3262,10 +3333,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17">
       <c r="C9" s="38"/>
       <c r="D9" s="69" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E9" s="40" t="s">
         <v>1</v>
@@ -3285,7 +3356,7 @@
         <v>44</v>
       </c>
       <c r="K9" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L9" s="41">
         <f t="shared" si="1"/>
@@ -3310,10 +3381,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17">
       <c r="C10" s="38"/>
       <c r="D10" s="69" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="E10" s="40" t="s">
         <v>1</v>
@@ -3331,7 +3402,7 @@
         <v>44</v>
       </c>
       <c r="K10" s="41" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L10" s="41">
         <f t="shared" si="1"/>
@@ -3356,10 +3427,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17">
       <c r="C11" s="38"/>
       <c r="D11" s="69" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E11" s="40" t="s">
         <v>1</v>
@@ -3377,7 +3448,7 @@
         <v>44</v>
       </c>
       <c r="K11" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L11" s="41">
         <f t="shared" si="1"/>
@@ -3399,10 +3470,10 @@
       </c>
       <c r="Q11" s="40"/>
     </row>
-    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17">
       <c r="C12" s="38"/>
       <c r="D12" s="69" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>1</v>
@@ -3420,7 +3491,7 @@
         <v>44</v>
       </c>
       <c r="K12" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L12" s="41">
         <f t="shared" si="1"/>
@@ -3445,10 +3516,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17">
       <c r="C13" s="38"/>
       <c r="D13" s="68" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>1</v>
@@ -3466,7 +3537,7 @@
         <v>44</v>
       </c>
       <c r="K13" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L13" s="41">
         <f t="shared" si="1"/>
@@ -3491,10 +3562,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17">
       <c r="C14" s="38"/>
       <c r="D14" s="68" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E14" s="40" t="s">
         <v>1</v>
@@ -3512,7 +3583,7 @@
         <v>44</v>
       </c>
       <c r="K14" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L14" s="41">
         <f t="shared" si="1"/>
@@ -3537,10 +3608,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17">
       <c r="C15" s="38"/>
       <c r="D15" s="68" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>1</v>
@@ -3558,7 +3629,7 @@
         <v>44</v>
       </c>
       <c r="K15" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L15" s="41">
         <f t="shared" si="1"/>
@@ -3580,10 +3651,10 @@
       </c>
       <c r="Q15" s="40"/>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17">
       <c r="C16" s="38"/>
       <c r="D16" s="68" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E16" s="40" t="s">
         <v>1</v>
@@ -3601,7 +3672,7 @@
         <v>44</v>
       </c>
       <c r="K16" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L16" s="41">
         <f t="shared" si="1"/>
@@ -3626,10 +3697,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17">
       <c r="C17" s="38"/>
       <c r="D17" s="68" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="40" t="s">
@@ -3647,7 +3718,7 @@
         <v>44</v>
       </c>
       <c r="K17" s="41" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="L17" s="41">
         <f t="shared" si="1"/>
@@ -3672,10 +3743,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17">
       <c r="C18" s="38"/>
       <c r="D18" s="68" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E18" s="40" t="s">
         <v>1</v>
@@ -3693,7 +3764,7 @@
         <v>44</v>
       </c>
       <c r="K18" s="41" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L18" s="41">
         <f t="shared" si="1"/>
@@ -3718,10 +3789,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17">
       <c r="C19" s="38"/>
       <c r="D19" s="72" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E19" s="40" t="s">
         <v>1</v>
@@ -3736,10 +3807,10 @@
         <v>1909.3</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K19" s="41" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L19" s="41">
         <f t="shared" si="1"/>
@@ -3764,10 +3835,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17">
       <c r="C20" s="38"/>
       <c r="D20" s="72" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E20" s="40" t="s">
         <v>1</v>
@@ -3785,7 +3856,7 @@
         <v>44</v>
       </c>
       <c r="K20" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L20" s="41">
         <f t="shared" si="1"/>
@@ -3810,10 +3881,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17">
       <c r="C21" s="38"/>
       <c r="D21" s="72" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E21" s="40" t="s">
         <v>1</v>
@@ -3831,7 +3902,7 @@
         <v>44</v>
       </c>
       <c r="K21" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L21" s="41">
         <f t="shared" si="1"/>
@@ -3856,10 +3927,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17">
       <c r="C22" s="38"/>
       <c r="D22" s="72" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E22" s="40" t="s">
         <v>1</v>
@@ -3877,7 +3948,7 @@
         <v>44</v>
       </c>
       <c r="K22" s="41" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="L22" s="41">
         <f t="shared" si="1"/>
@@ -3902,10 +3973,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17">
       <c r="C23" s="38"/>
       <c r="D23" s="72" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E23" s="40" t="s">
         <v>1</v>
@@ -3925,7 +3996,7 @@
         <v>44</v>
       </c>
       <c r="K23" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L23" s="41">
         <f t="shared" si="1"/>
@@ -3950,10 +4021,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17">
       <c r="C24" s="38"/>
       <c r="D24" s="72" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="E24" s="40" t="s">
         <v>1</v>
@@ -3971,7 +4042,7 @@
         <v>44</v>
       </c>
       <c r="K24" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L24" s="41">
         <f t="shared" si="1"/>
@@ -3996,10 +4067,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17">
       <c r="C25" s="38"/>
       <c r="D25" s="72" t="s">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="E25" s="40" t="s">
         <v>1</v>
@@ -4040,10 +4111,10 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17">
       <c r="C26" s="38"/>
       <c r="D26" s="72" t="s">
-        <v>239</v>
+        <v>76</v>
       </c>
       <c r="E26" s="40"/>
       <c r="F26" s="40" t="s">
@@ -4084,10 +4155,10 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17">
       <c r="C27" s="38"/>
       <c r="D27" s="49" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E27" s="40"/>
       <c r="F27" s="40" t="s">
@@ -4105,7 +4176,7 @@
         <v>44</v>
       </c>
       <c r="K27" s="41" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="L27" s="41">
         <f t="shared" si="1"/>
@@ -4130,10 +4201,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17">
       <c r="C28" s="38"/>
       <c r="D28" s="49" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E28" s="40" t="s">
         <v>1</v>
@@ -4151,7 +4222,7 @@
         <v>44</v>
       </c>
       <c r="K28" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L28" s="41">
         <f t="shared" si="1"/>
@@ -4176,10 +4247,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17">
       <c r="C29" s="38"/>
       <c r="D29" s="49" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E29" s="40" t="s">
         <v>1</v>
@@ -4197,7 +4268,7 @@
         <v>44</v>
       </c>
       <c r="K29" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L29" s="41">
         <f t="shared" si="1"/>
@@ -4222,10 +4293,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17">
       <c r="C30" s="38"/>
       <c r="D30" s="49" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E30" s="40" t="s">
         <v>1</v>
@@ -4245,7 +4316,7 @@
         <v>44</v>
       </c>
       <c r="K30" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L30" s="41">
         <f t="shared" si="1"/>
@@ -4267,10 +4338,10 @@
       </c>
       <c r="Q30" s="40"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17">
       <c r="C31" s="38"/>
       <c r="D31" s="49" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="E31" s="40" t="s">
         <v>1</v>
@@ -4288,7 +4359,7 @@
         <v>44</v>
       </c>
       <c r="K31" s="41" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="L31" s="41">
         <f t="shared" si="1"/>
@@ -4313,10 +4384,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17">
       <c r="C32" s="38"/>
       <c r="D32" s="49" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="E32" s="40"/>
       <c r="F32" s="40"/>
@@ -4332,7 +4403,7 @@
         <v>44</v>
       </c>
       <c r="K32" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L32" s="41">
         <f t="shared" si="1"/>
@@ -4357,10 +4428,10 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:17">
       <c r="C33" s="38"/>
       <c r="D33" s="49" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="E33" s="40" t="s">
         <v>1</v>
@@ -4378,7 +4449,7 @@
         <v>44</v>
       </c>
       <c r="K33" s="41" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="L33" s="41">
         <f t="shared" si="1"/>
@@ -4403,10 +4474,10 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:17">
       <c r="C34" s="38"/>
       <c r="D34" s="39" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E34" s="40" t="s">
         <v>1</v>
@@ -4423,10 +4494,10 @@
         <v>1017.6</v>
       </c>
       <c r="J34" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K34" s="40" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L34" s="41">
         <f t="shared" si="1"/>
@@ -4451,10 +4522,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:17">
       <c r="C35" s="38"/>
       <c r="D35" s="49" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E35" s="40" t="s">
         <v>1</v>
@@ -4472,7 +4543,7 @@
         <v>44</v>
       </c>
       <c r="K35" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L35" s="41">
         <f t="shared" si="1"/>
@@ -4497,10 +4568,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:17">
       <c r="C36" s="38"/>
       <c r="D36" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E36" s="40" t="s">
         <v>1</v>
@@ -4518,7 +4589,7 @@
         <v>44</v>
       </c>
       <c r="K36" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L36" s="41">
         <f t="shared" si="1"/>
@@ -4543,10 +4614,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:17">
       <c r="C37" s="38"/>
       <c r="D37" s="49" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E37" s="40" t="s">
         <v>1</v>
@@ -4564,7 +4635,7 @@
         <v>44</v>
       </c>
       <c r="K37" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L37" s="41">
         <f t="shared" si="1"/>
@@ -4589,10 +4660,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:17">
       <c r="C38" s="38"/>
       <c r="D38" s="49" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E38" s="40" t="s">
         <v>1</v>
@@ -4610,7 +4681,7 @@
         <v>44</v>
       </c>
       <c r="K38" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L38" s="41">
         <f t="shared" ref="L38:L69" si="7">I38/N38</f>
@@ -4635,10 +4706,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:17">
       <c r="C39" s="38"/>
       <c r="D39" s="49" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="E39" s="40" t="s">
         <v>1</v>
@@ -4655,10 +4726,10 @@
         <v>224.24</v>
       </c>
       <c r="J39" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K39" s="41" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="L39" s="41">
         <f t="shared" si="7"/>
@@ -4683,12 +4754,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:17">
       <c r="C40" s="38" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="E40" s="40" t="s">
         <v>1</v>
@@ -4706,7 +4777,7 @@
         <v>44</v>
       </c>
       <c r="K40" s="41" t="s">
-        <v>246</v>
+        <v>93</v>
       </c>
       <c r="L40" s="41">
         <f t="shared" si="7"/>
@@ -4731,10 +4802,10 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:17">
       <c r="C41" s="38"/>
       <c r="D41" s="39" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="E41" s="40" t="s">
         <v>1</v>
@@ -4751,10 +4822,10 @@
         <v>22.45</v>
       </c>
       <c r="J41" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K41" s="40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L41" s="41">
         <f t="shared" si="7"/>
@@ -4777,10 +4848,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:17">
       <c r="C42" s="38"/>
       <c r="D42" s="49" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="E42" s="40" t="s">
         <v>1</v>
@@ -4797,10 +4868,10 @@
         <v>60</v>
       </c>
       <c r="J42" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K42" s="40" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L42" s="41">
         <f t="shared" si="7"/>
@@ -4823,10 +4894,10 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:17">
       <c r="C43" s="38"/>
       <c r="D43" s="39" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="E43" s="40" t="s">
         <v>1</v>
@@ -4843,10 +4914,10 @@
         <v>395.54</v>
       </c>
       <c r="J43" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K43" s="40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L43" s="41">
         <f t="shared" si="7"/>
@@ -4869,10 +4940,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:17">
       <c r="C44" s="38"/>
       <c r="D44" s="39" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E44" s="40" t="s">
         <v>1</v>
@@ -4889,10 +4960,10 @@
         <v>215</v>
       </c>
       <c r="J44" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K44" s="40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L44" s="41">
         <f t="shared" si="7"/>
@@ -4915,10 +4986,10 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:17">
       <c r="C45" s="38"/>
       <c r="D45" s="49" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="E45" s="40" t="s">
         <v>1</v>
@@ -4935,10 +5006,10 @@
         <v>225</v>
       </c>
       <c r="J45" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K45" s="40" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L45" s="41">
         <f t="shared" si="7"/>
@@ -4961,10 +5032,10 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:17">
       <c r="C46" s="38"/>
       <c r="D46" s="39" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="E46" s="40" t="s">
         <v>1</v>
@@ -4981,10 +5052,10 @@
         <v>166.15</v>
       </c>
       <c r="J46" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K46" s="40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L46" s="41">
         <f t="shared" si="7"/>
@@ -5007,10 +5078,10 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:17">
       <c r="C47" s="38"/>
       <c r="D47" s="49" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="E47" s="40" t="s">
         <v>1</v>
@@ -5025,10 +5096,10 @@
         <v>284.05</v>
       </c>
       <c r="J47" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K47" s="41" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L47" s="41">
         <f t="shared" si="7"/>
@@ -5051,10 +5122,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:17">
       <c r="C48" s="38"/>
       <c r="D48" s="49" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E48" s="40" t="s">
         <v>1</v>
@@ -5069,10 +5140,10 @@
         <v>110</v>
       </c>
       <c r="J48" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K48" s="41" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="L48" s="41">
         <f t="shared" si="7"/>
@@ -5095,10 +5166,10 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:17">
       <c r="C49" s="38"/>
       <c r="D49" s="49" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="E49" s="40" t="s">
         <v>1</v>
@@ -5113,10 +5184,10 @@
         <v>117</v>
       </c>
       <c r="J49" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K49" s="41" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="L49" s="41">
         <f t="shared" si="7"/>
@@ -5136,10 +5207,10 @@
       </c>
       <c r="Q49" s="40"/>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:17">
       <c r="C50" s="38"/>
       <c r="D50" s="39" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="E50" s="40" t="s">
         <v>1</v>
@@ -5156,10 +5227,10 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J50" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K50" s="40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L50" s="41">
         <f t="shared" si="7"/>
@@ -5182,10 +5253,10 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:17">
       <c r="C51" s="38"/>
       <c r="D51" s="39" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="E51" s="40" t="s">
         <v>1</v>
@@ -5200,10 +5271,10 @@
         <v>26.9</v>
       </c>
       <c r="J51" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K51" s="40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L51" s="41">
         <f t="shared" si="7"/>
@@ -5226,10 +5297,10 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:17">
       <c r="C52" s="38"/>
       <c r="D52" s="49" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="E52" s="40" t="s">
         <v>1</v>
@@ -5244,10 +5315,10 @@
         <v>70</v>
       </c>
       <c r="J52" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K52" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L52" s="41">
         <f t="shared" si="7"/>
@@ -5267,10 +5338,10 @@
       </c>
       <c r="Q52" s="40"/>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:17">
       <c r="C53" s="38"/>
       <c r="D53" s="70" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="E53" s="40" t="s">
         <v>1</v>
@@ -5285,10 +5356,10 @@
         <v>400</v>
       </c>
       <c r="J53" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K53" s="41" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L53" s="41">
         <f t="shared" si="7"/>
@@ -5311,10 +5382,10 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:17">
       <c r="C54" s="38"/>
       <c r="D54" s="49" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="E54" s="40" t="s">
         <v>1</v>
@@ -5331,10 +5402,10 @@
         <v>22</v>
       </c>
       <c r="J54" s="41" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K54" s="41" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L54" s="41">
         <f t="shared" si="7"/>
@@ -5359,10 +5430,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:17">
       <c r="C55" s="38"/>
       <c r="D55" s="49" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E55" s="40" t="s">
         <v>1</v>
@@ -5380,7 +5451,7 @@
         <v>44</v>
       </c>
       <c r="K55" s="41" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="L55" s="41">
         <f t="shared" si="7"/>
@@ -5405,10 +5476,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:17">
       <c r="C56" s="38"/>
       <c r="D56" s="49" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E56" s="40" t="s">
         <v>1</v>
@@ -5427,7 +5498,7 @@
         <v>44</v>
       </c>
       <c r="K56" s="41" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="L56" s="41">
         <f t="shared" si="7"/>
@@ -5452,10 +5523,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:17">
       <c r="C57" s="38"/>
       <c r="D57" s="49" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E57" s="40" t="s">
         <v>1</v>
@@ -5470,7 +5541,7 @@
         <v>55</v>
       </c>
       <c r="J57" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K57" s="41" t="s">
         <v>45</v>
@@ -5498,10 +5569,10 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:17">
       <c r="C58" s="38"/>
       <c r="D58" s="49" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E58" s="40" t="s">
         <v>1</v>
@@ -5516,10 +5587,10 @@
         <v>498</v>
       </c>
       <c r="J58" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K58" s="41" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L58" s="41">
         <f t="shared" si="7"/>
@@ -5542,10 +5613,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:17">
       <c r="C59" s="38"/>
       <c r="D59" s="49" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E59" s="40" t="s">
         <v>1</v>
@@ -5562,10 +5633,10 @@
         <v>40</v>
       </c>
       <c r="J59" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K59" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L59" s="41">
         <f t="shared" si="7"/>
@@ -5588,10 +5659,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:17">
       <c r="C60" s="38"/>
       <c r="D60" s="49" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E60" s="40" t="s">
         <v>1</v>
@@ -5606,10 +5677,10 @@
         <v>32</v>
       </c>
       <c r="J60" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K60" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L60" s="41">
         <f t="shared" si="7"/>
@@ -5632,10 +5703,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:17">
       <c r="C61" s="38"/>
       <c r="D61" s="49" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E61" s="40"/>
       <c r="F61" s="40" t="s">
@@ -5650,10 +5721,10 @@
         <v>166</v>
       </c>
       <c r="J61" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K61" s="41" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L61" s="41">
         <f t="shared" si="7"/>
@@ -5676,10 +5747,10 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:17">
       <c r="C62" s="38"/>
       <c r="D62" s="49" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E62" s="40" t="s">
         <v>1</v>
@@ -5696,10 +5767,10 @@
         <v>74</v>
       </c>
       <c r="J62" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K62" s="41" t="s">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="L62" s="41">
         <f t="shared" si="7"/>
@@ -5722,10 +5793,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:17">
       <c r="C63" s="38"/>
       <c r="D63" s="49" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E63" s="40" t="s">
         <v>1</v>
@@ -5740,10 +5811,10 @@
         <v>-37</v>
       </c>
       <c r="J63" s="41" t="s">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="K63" s="41" t="s">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="L63" s="41">
         <f t="shared" si="7"/>
@@ -5766,10 +5837,10 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:17">
       <c r="C64" s="38"/>
       <c r="D64" s="49" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E64" s="40" t="s">
         <v>1</v>
@@ -5786,10 +5857,10 @@
         <v>36</v>
       </c>
       <c r="J64" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K64" s="41" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L64" s="41">
         <f t="shared" si="7"/>
@@ -5812,10 +5883,10 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:17">
       <c r="C65" s="38"/>
       <c r="D65" s="49" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E65" s="40" t="s">
         <v>1</v>
@@ -5830,10 +5901,10 @@
         <v>35</v>
       </c>
       <c r="J65" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K65" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L65" s="41">
         <f t="shared" si="7"/>
@@ -5856,10 +5927,10 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:17">
       <c r="C66" s="38"/>
       <c r="D66" s="49" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E66" s="40" t="s">
         <v>1</v>
@@ -5876,10 +5947,10 @@
         <v>75</v>
       </c>
       <c r="J66" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K66" s="41" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="L66" s="41">
         <f t="shared" si="7"/>
@@ -5902,10 +5973,10 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:17">
       <c r="C67" s="38"/>
       <c r="D67" s="49" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E67" s="40" t="s">
         <v>1</v>
@@ -5922,10 +5993,10 @@
         <v>74</v>
       </c>
       <c r="J67" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K67" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L67" s="41">
         <f t="shared" si="7"/>
@@ -5948,10 +6019,10 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:17">
       <c r="C68" s="38"/>
       <c r="D68" s="49" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E68" s="40"/>
       <c r="F68" s="40" t="s">
@@ -5966,10 +6037,10 @@
         <v>107.5</v>
       </c>
       <c r="J68" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K68" s="41" t="s">
-        <v>247</v>
+        <v>128</v>
       </c>
       <c r="L68" s="41">
         <f t="shared" si="7"/>
@@ -5992,10 +6063,10 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:17">
       <c r="C69" s="38"/>
       <c r="D69" s="49" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E69" s="40" t="s">
         <v>1</v>
@@ -6010,10 +6081,10 @@
         <v>37.5</v>
       </c>
       <c r="J69" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K69" s="41" t="s">
-        <v>247</v>
+        <v>128</v>
       </c>
       <c r="L69" s="41">
         <f t="shared" si="7"/>
@@ -6036,10 +6107,10 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:17">
       <c r="C70" s="38"/>
       <c r="D70" s="49" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E70" s="40" t="s">
         <v>1</v>
@@ -6054,10 +6125,10 @@
         <v>50</v>
       </c>
       <c r="J70" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K70" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L70" s="41">
         <f t="shared" ref="L70:L100" si="12">I70/N70</f>
@@ -6080,10 +6151,10 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:17">
       <c r="C71" s="38"/>
       <c r="D71" s="49" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E71" s="40" t="s">
         <v>1</v>
@@ -6098,10 +6169,10 @@
         <v>35</v>
       </c>
       <c r="J71" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K71" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L71" s="41">
         <f t="shared" si="12"/>
@@ -6124,10 +6195,10 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:17">
       <c r="C72" s="38"/>
       <c r="D72" s="49" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E72" s="40" t="s">
         <v>1</v>
@@ -6142,10 +6213,10 @@
         <v>52.14</v>
       </c>
       <c r="J72" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K72" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L72" s="41">
         <f t="shared" si="12"/>
@@ -6168,10 +6239,10 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:17">
       <c r="C73" s="38"/>
       <c r="D73" s="49" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E73" s="40" t="s">
         <v>1</v>
@@ -6188,10 +6259,10 @@
         <v>130.01</v>
       </c>
       <c r="J73" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K73" s="41" t="s">
-        <v>247</v>
+        <v>128</v>
       </c>
       <c r="L73" s="41">
         <f t="shared" si="12"/>
@@ -6214,10 +6285,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:17">
       <c r="C74" s="38"/>
       <c r="D74" s="49" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E74" s="40" t="s">
         <v>1</v>
@@ -6232,10 +6303,10 @@
         <v>99</v>
       </c>
       <c r="J74" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K74" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L74" s="41">
         <f t="shared" si="12"/>
@@ -6258,10 +6329,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:17">
       <c r="C75" s="38"/>
       <c r="D75" s="49" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E75" s="40" t="s">
         <v>1</v>
@@ -6276,10 +6347,10 @@
         <v>-99</v>
       </c>
       <c r="J75" s="41" t="s">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="K75" s="41" t="s">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="L75" s="41">
         <f t="shared" si="12"/>
@@ -6302,10 +6373,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:17">
       <c r="C76" s="38"/>
       <c r="D76" s="49" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E76" s="40" t="s">
         <v>1</v>
@@ -6322,10 +6393,10 @@
         <v>139</v>
       </c>
       <c r="J76" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K76" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L76" s="41">
         <f t="shared" si="12"/>
@@ -6348,10 +6419,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:17">
       <c r="C77" s="38"/>
       <c r="D77" s="49" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E77" s="40"/>
       <c r="F77" s="40" t="s">
@@ -6366,10 +6437,10 @@
         <v>100</v>
       </c>
       <c r="J77" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K77" s="41" t="s">
-        <v>247</v>
+        <v>128</v>
       </c>
       <c r="L77" s="41">
         <f t="shared" si="12"/>
@@ -6392,10 +6463,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:17">
       <c r="C78" s="38"/>
       <c r="D78" s="49" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E78" s="40" t="s">
         <v>1</v>
@@ -6412,10 +6483,10 @@
         <v>90</v>
       </c>
       <c r="J78" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K78" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L78" s="41">
         <f t="shared" si="12"/>
@@ -6438,10 +6509,10 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:17">
       <c r="C79" s="38"/>
       <c r="D79" s="49" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E79" s="40" t="s">
         <v>1</v>
@@ -6456,10 +6527,10 @@
         <v>-45</v>
       </c>
       <c r="J79" s="41" t="s">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="K79" s="41" t="s">
-        <v>243</v>
+        <v>122</v>
       </c>
       <c r="L79" s="41">
         <f t="shared" si="12"/>
@@ -6482,10 +6553,10 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:17">
       <c r="C80" s="38"/>
       <c r="D80" s="49" t="s">
-        <v>232</v>
+        <v>139</v>
       </c>
       <c r="E80" s="40" t="s">
         <v>1</v>
@@ -6502,10 +6573,10 @@
         <v>79</v>
       </c>
       <c r="J80" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K80" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L80" s="41">
         <f t="shared" si="12"/>
@@ -6528,10 +6599,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:17">
       <c r="C81" s="38"/>
       <c r="D81" s="49" t="s">
-        <v>233</v>
+        <v>140</v>
       </c>
       <c r="E81" s="40" t="s">
         <v>1</v>
@@ -6548,10 +6619,10 @@
         <v>56.27</v>
       </c>
       <c r="J81" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K81" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L81" s="41">
         <f t="shared" si="12"/>
@@ -6574,10 +6645,10 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:17">
       <c r="C82" s="38"/>
       <c r="D82" s="49" t="s">
-        <v>234</v>
+        <v>141</v>
       </c>
       <c r="E82" s="40" t="s">
         <v>1</v>
@@ -6594,10 +6665,10 @@
         <v>82.49</v>
       </c>
       <c r="J82" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K82" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L82" s="41">
         <f t="shared" si="12"/>
@@ -6620,10 +6691,10 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:17">
       <c r="C83" s="38"/>
       <c r="D83" s="49" t="s">
-        <v>235</v>
+        <v>142</v>
       </c>
       <c r="E83" s="40" t="s">
         <v>1</v>
@@ -6640,10 +6711,10 @@
         <v>49.91</v>
       </c>
       <c r="J83" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K83" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L83" s="41">
         <f t="shared" si="12"/>
@@ -6666,10 +6737,10 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:17">
       <c r="C84" s="38"/>
       <c r="D84" s="49" t="s">
-        <v>236</v>
+        <v>143</v>
       </c>
       <c r="E84" s="40" t="s">
         <v>1</v>
@@ -6686,10 +6757,10 @@
         <v>41.5</v>
       </c>
       <c r="J84" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K84" s="41" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L84" s="41">
         <f t="shared" si="12"/>
@@ -6712,10 +6783,10 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:17">
       <c r="C85" s="38"/>
       <c r="D85" s="49" t="s">
-        <v>237</v>
+        <v>144</v>
       </c>
       <c r="E85" s="40" t="s">
         <v>1</v>
@@ -6730,10 +6801,10 @@
         <v>106.04</v>
       </c>
       <c r="J85" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K85" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L85" s="41">
         <f t="shared" si="12"/>
@@ -6756,10 +6827,10 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:17">
       <c r="C86" s="38"/>
       <c r="D86" s="49" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E86" s="40" t="s">
         <v>1</v>
@@ -6774,10 +6845,10 @@
         <v>16.97</v>
       </c>
       <c r="J86" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K86" s="41" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L86" s="41">
         <f t="shared" si="12"/>
@@ -6800,10 +6871,10 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:17">
       <c r="C87" s="38"/>
       <c r="D87" s="49" t="s">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="E87" s="40" t="s">
         <v>1</v>
@@ -6818,10 +6889,10 @@
         <v>50</v>
       </c>
       <c r="J87" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K87" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L87" s="41">
         <f t="shared" si="12"/>
@@ -6844,10 +6915,10 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:17">
       <c r="C88" s="38"/>
       <c r="D88" s="49" t="s">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="E88" s="40" t="s">
         <v>1</v>
@@ -6864,10 +6935,10 @@
         <v>53.97</v>
       </c>
       <c r="J88" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K88" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L88" s="41">
         <f t="shared" si="12"/>
@@ -6890,10 +6961,10 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:17">
       <c r="C89" s="38"/>
       <c r="D89" s="49" t="s">
-        <v>242</v>
+        <v>147</v>
       </c>
       <c r="E89" s="40" t="s">
         <v>1</v>
@@ -6909,10 +6980,10 @@
         <v>95.9</v>
       </c>
       <c r="J89" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K89" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L89" s="41">
         <f t="shared" si="12"/>
@@ -6935,10 +7006,10 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:17">
       <c r="C90" s="38"/>
       <c r="D90" s="49" t="s">
-        <v>248</v>
+        <v>148</v>
       </c>
       <c r="E90" s="40" t="s">
         <v>1</v>
@@ -6955,10 +7026,10 @@
         <v>56</v>
       </c>
       <c r="J90" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K90" s="41" t="s">
-        <v>244</v>
+        <v>116</v>
       </c>
       <c r="L90" s="41">
         <f t="shared" si="12"/>
@@ -6981,10 +7052,10 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:17">
       <c r="C91" s="38"/>
       <c r="D91" s="49" t="s">
-        <v>249</v>
+        <v>149</v>
       </c>
       <c r="E91" s="40" t="s">
         <v>1</v>
@@ -7001,10 +7072,10 @@
         <v>20</v>
       </c>
       <c r="J91" s="41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K91" s="41" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L91" s="41">
         <f t="shared" si="12"/>
@@ -7027,9 +7098,11 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:17">
       <c r="C92" s="38"/>
-      <c r="D92" s="49"/>
+      <c r="D92" s="49" t="s">
+        <v>150</v>
+      </c>
       <c r="E92" s="40"/>
       <c r="F92" s="40"/>
       <c r="G92" s="40"/>
@@ -7037,12 +7110,18 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I92" s="41"/>
-      <c r="J92" s="41"/>
-      <c r="K92" s="41"/>
+      <c r="I92" s="41">
+        <v>308.26</v>
+      </c>
+      <c r="J92" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="K92" s="41" t="s">
+        <v>116</v>
+      </c>
       <c r="L92" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>308.26</v>
       </c>
       <c r="M92" s="41" t="str">
         <f t="shared" si="13"/>
@@ -7051,7 +7130,9 @@
       <c r="N92" s="42">
         <v>1</v>
       </c>
-      <c r="O92" s="38"/>
+      <c r="O92" s="38">
+        <v>46237</v>
+      </c>
       <c r="P92" s="38" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -7061,9 +7142,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:17">
       <c r="C93" s="38"/>
-      <c r="D93" s="49"/>
+      <c r="D93" s="49" t="s">
+        <v>151</v>
+      </c>
       <c r="E93" s="40"/>
       <c r="F93" s="40"/>
       <c r="G93" s="40"/>
@@ -7071,12 +7154,18 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I93" s="41"/>
-      <c r="J93" s="41"/>
-      <c r="K93" s="41"/>
+      <c r="I93" s="41">
+        <v>-308</v>
+      </c>
+      <c r="J93" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="K93" s="41" t="s">
+        <v>122</v>
+      </c>
       <c r="L93" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>-308</v>
       </c>
       <c r="M93" s="41" t="str">
         <f t="shared" si="13"/>
@@ -7085,7 +7174,9 @@
       <c r="N93" s="42">
         <v>1</v>
       </c>
-      <c r="O93" s="38"/>
+      <c r="O93" s="38">
+        <v>46237</v>
+      </c>
       <c r="P93" s="38" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -7095,60 +7186,82 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:17">
       <c r="C94" s="38"/>
-      <c r="D94" s="49"/>
-      <c r="E94" s="40"/>
+      <c r="D94" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E94" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F94" s="40"/>
       <c r="G94" s="40"/>
       <c r="H94" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I94" s="41"/>
-      <c r="J94" s="41"/>
-      <c r="K94" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I94" s="41">
+        <v>169</v>
+      </c>
+      <c r="J94" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="K94" s="41" t="s">
+        <v>49</v>
+      </c>
       <c r="L94" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="41" t="str">
+        <v>28.166666666666668</v>
+      </c>
+      <c r="M94" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>28.166666666666668</v>
       </c>
       <c r="N94" s="42">
-        <v>1</v>
-      </c>
-      <c r="O94" s="38"/>
-      <c r="P94" s="38" t="str">
+        <v>6</v>
+      </c>
+      <c r="O94" s="38">
+        <v>46237</v>
+      </c>
+      <c r="P94" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>46390</v>
       </c>
       <c r="Q94" s="40" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:17">
       <c r="C95" s="38"/>
-      <c r="D95" s="49"/>
-      <c r="E95" s="40"/>
+      <c r="D95" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E95" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F95" s="40"/>
       <c r="G95" s="40"/>
       <c r="H95" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="41"/>
-      <c r="J95" s="41"/>
-      <c r="K95" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I95" s="41">
+        <v>30.4</v>
+      </c>
+      <c r="J95" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="K95" s="41" t="s">
+        <v>49</v>
+      </c>
       <c r="L95" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M95" s="41" t="str">
+        <v>30.4</v>
+      </c>
+      <c r="M95" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>30.4</v>
       </c>
       <c r="N95" s="42">
         <v>1</v>
@@ -7163,26 +7276,38 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:17">
       <c r="C96" s="38"/>
-      <c r="D96" s="49"/>
-      <c r="E96" s="40"/>
-      <c r="F96" s="40"/>
+      <c r="D96" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="E96" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G96" s="40"/>
       <c r="H96" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I96" s="41"/>
-      <c r="J96" s="41"/>
-      <c r="K96" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I96" s="41">
+        <v>76</v>
+      </c>
+      <c r="J96" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="K96" s="41" t="s">
+        <v>116</v>
+      </c>
       <c r="L96" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M96" s="41" t="str">
+        <v>76</v>
+      </c>
+      <c r="M96" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>38</v>
       </c>
       <c r="N96" s="42">
         <v>1</v>
@@ -7197,9 +7322,11 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:17">
       <c r="C97" s="38"/>
-      <c r="D97" s="49"/>
+      <c r="D97" s="49" t="s">
+        <v>155</v>
+      </c>
       <c r="E97" s="40"/>
       <c r="F97" s="40"/>
       <c r="G97" s="40"/>
@@ -7207,12 +7334,18 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I97" s="41"/>
-      <c r="J97" s="41"/>
-      <c r="K97" s="41"/>
+      <c r="I97" s="41">
+        <v>1344</v>
+      </c>
+      <c r="J97" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="K97" s="41" t="s">
+        <v>49</v>
+      </c>
       <c r="L97" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1344</v>
       </c>
       <c r="M97" s="41" t="str">
         <f t="shared" si="13"/>
@@ -7231,9 +7364,11 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:17">
       <c r="C98" s="38"/>
-      <c r="D98" s="49"/>
+      <c r="D98" s="49" t="s">
+        <v>156</v>
+      </c>
       <c r="E98" s="40"/>
       <c r="F98" s="40"/>
       <c r="G98" s="40"/>
@@ -7241,12 +7376,18 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I98" s="41"/>
-      <c r="J98" s="41"/>
-      <c r="K98" s="41"/>
+      <c r="I98" s="41">
+        <v>-1344</v>
+      </c>
+      <c r="J98" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="K98" s="41" t="s">
+        <v>122</v>
+      </c>
       <c r="L98" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>-1344</v>
       </c>
       <c r="M98" s="41" t="str">
         <f t="shared" si="13"/>
@@ -7265,7 +7406,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:17">
       <c r="C99" s="38"/>
       <c r="D99" s="49"/>
       <c r="E99" s="40"/>
@@ -7299,7 +7440,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:17">
       <c r="C100" s="38"/>
       <c r="D100" s="49"/>
       <c r="E100" s="40"/>
@@ -7333,7 +7474,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:17">
       <c r="C101" s="38"/>
       <c r="D101" s="49"/>
       <c r="E101" s="40"/>
@@ -7367,7 +7508,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:17">
       <c r="C102" s="38"/>
       <c r="D102" s="49"/>
       <c r="E102" s="40"/>
@@ -7401,7 +7542,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:17">
       <c r="C103" s="38"/>
       <c r="D103" s="49"/>
       <c r="E103" s="40"/>
@@ -7435,7 +7576,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:17">
       <c r="C104" s="38"/>
       <c r="D104" s="49"/>
       <c r="E104" s="40"/>
@@ -7469,7 +7610,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:17">
       <c r="C105" s="38"/>
       <c r="D105" s="49"/>
       <c r="E105" s="40"/>
@@ -7503,7 +7644,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:17">
       <c r="C106" s="38"/>
       <c r="D106" s="49"/>
       <c r="E106" s="40"/>
@@ -7537,7 +7678,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:17">
       <c r="C107" s="38"/>
       <c r="D107" s="49"/>
       <c r="E107" s="40"/>
@@ -7571,7 +7712,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:17">
       <c r="C108" s="38"/>
       <c r="D108" s="49"/>
       <c r="E108" s="40"/>
@@ -7605,7 +7746,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:17">
       <c r="C109" s="38"/>
       <c r="D109" s="49"/>
       <c r="E109" s="40"/>
@@ -7639,7 +7780,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:17">
       <c r="C110" s="38"/>
       <c r="D110" s="49"/>
       <c r="E110" s="40"/>
@@ -7673,7 +7814,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:17">
       <c r="C111" s="38"/>
       <c r="D111" s="49"/>
       <c r="E111" s="40"/>
@@ -7707,7 +7848,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:17">
       <c r="C112" s="38"/>
       <c r="D112" s="49"/>
       <c r="E112" s="40"/>
@@ -7741,7 +7882,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:17">
       <c r="C113" s="38"/>
       <c r="D113" s="49"/>
       <c r="E113" s="40"/>
@@ -7775,7 +7916,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:17">
       <c r="C114" s="38"/>
       <c r="D114" s="49"/>
       <c r="E114" s="40"/>
@@ -7809,7 +7950,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:17">
       <c r="C115" s="38"/>
       <c r="D115" s="49"/>
       <c r="E115" s="40"/>
@@ -7843,7 +7984,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:17">
       <c r="C116" s="38"/>
       <c r="D116" s="49"/>
       <c r="E116" s="40"/>
@@ -7877,7 +8018,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:17">
       <c r="C117" s="38"/>
       <c r="D117" s="49"/>
       <c r="E117" s="40"/>
@@ -7911,7 +8052,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:17">
       <c r="C118" s="38"/>
       <c r="D118" s="49"/>
       <c r="E118" s="40"/>
@@ -7945,7 +8086,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:17">
       <c r="C119" s="38"/>
       <c r="D119" s="49"/>
       <c r="E119" s="40"/>
@@ -7979,7 +8120,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:17">
       <c r="C120" s="38"/>
       <c r="D120" s="49"/>
       <c r="E120" s="40"/>
@@ -8013,7 +8154,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:17">
       <c r="C121" s="38"/>
       <c r="D121" s="49"/>
       <c r="E121" s="40"/>
@@ -8047,7 +8188,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:17">
       <c r="C122" s="38"/>
       <c r="D122" s="49"/>
       <c r="E122" s="40"/>
@@ -8081,7 +8222,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:17">
       <c r="C123" s="38"/>
       <c r="D123" s="49"/>
       <c r="E123" s="40"/>
@@ -8115,7 +8256,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:17">
       <c r="C124" s="38"/>
       <c r="D124" s="49"/>
       <c r="E124" s="40"/>
@@ -8149,7 +8290,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:17">
       <c r="C125" s="38"/>
       <c r="D125" s="49"/>
       <c r="E125" s="40"/>
@@ -8183,7 +8324,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:17">
       <c r="C126" s="38"/>
       <c r="D126" s="49"/>
       <c r="E126" s="40"/>
@@ -8217,7 +8358,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:17">
       <c r="C127" s="38"/>
       <c r="D127" s="49"/>
       <c r="E127" s="40"/>
@@ -8251,7 +8392,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:17">
       <c r="C128" s="38"/>
       <c r="D128" s="49"/>
       <c r="E128" s="40"/>
@@ -8285,7 +8426,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:17">
       <c r="C129" s="38"/>
       <c r="D129" s="49"/>
       <c r="E129" s="40"/>
@@ -8319,7 +8460,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:17">
       <c r="C130" s="38"/>
       <c r="D130" s="49"/>
       <c r="E130" s="40"/>
@@ -8353,7 +8494,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:17">
       <c r="C131" s="38"/>
       <c r="D131" s="49"/>
       <c r="E131" s="40"/>
@@ -8387,7 +8528,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:17">
       <c r="C132" s="38"/>
       <c r="D132" s="49"/>
       <c r="E132" s="40"/>
@@ -8421,7 +8562,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:17">
       <c r="C133" s="38"/>
       <c r="D133" s="49"/>
       <c r="E133" s="40"/>
@@ -8455,7 +8596,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:17">
       <c r="C134" s="38"/>
       <c r="D134" s="49"/>
       <c r="E134" s="40"/>
@@ -8489,7 +8630,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:17">
       <c r="C135" s="38"/>
       <c r="D135" s="49"/>
       <c r="E135" s="40"/>
@@ -8523,7 +8664,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:17">
       <c r="C136" s="38"/>
       <c r="D136" s="49"/>
       <c r="E136" s="40"/>
@@ -8557,7 +8698,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:17">
       <c r="C137" s="38"/>
       <c r="D137" s="49"/>
       <c r="E137" s="40"/>
@@ -8591,7 +8732,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:17">
       <c r="C138" s="38"/>
       <c r="D138" s="49"/>
       <c r="E138" s="40"/>
@@ -8625,7 +8766,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:17">
       <c r="C139" s="38"/>
       <c r="D139" s="49"/>
       <c r="E139" s="40"/>
@@ -8659,7 +8800,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:17">
       <c r="C140" s="38"/>
       <c r="D140" s="49"/>
       <c r="E140" s="40"/>
@@ -8693,7 +8834,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:17">
       <c r="C141" s="38"/>
       <c r="D141" s="49"/>
       <c r="E141" s="40"/>
@@ -8727,7 +8868,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:17">
       <c r="C142" s="38"/>
       <c r="D142" s="49"/>
       <c r="E142" s="40"/>
@@ -8761,7 +8902,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:17">
       <c r="C143" s="38"/>
       <c r="D143" s="49"/>
       <c r="E143" s="40"/>
@@ -8795,7 +8936,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:17">
       <c r="C144" s="38"/>
       <c r="D144" s="49"/>
       <c r="E144" s="40"/>
@@ -8829,7 +8970,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:17">
       <c r="C145" s="38"/>
       <c r="D145" s="49"/>
       <c r="E145" s="40"/>
@@ -8863,7 +9004,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:17">
       <c r="C146" s="38"/>
       <c r="D146" s="49"/>
       <c r="E146" s="40"/>
@@ -8897,7 +9038,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:17">
       <c r="C147" s="38"/>
       <c r="D147" s="49"/>
       <c r="E147" s="40"/>
@@ -8931,7 +9072,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:17">
       <c r="C148" s="38"/>
       <c r="D148" s="49"/>
       <c r="E148" s="40"/>
@@ -8965,7 +9106,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:17">
       <c r="C149" s="38"/>
       <c r="D149" s="49"/>
       <c r="E149" s="40"/>
@@ -8985,22 +9126,32 @@
   </sheetData>
   <autoFilter ref="C5:Q149" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="I6:I149">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J149">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K149">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K60">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K93">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K98">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9012,7 +9163,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:R20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" customWidth="1"/>
@@ -9025,7 +9176,7 @@
     <col min="18" max="18" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="30" customHeight="1">
       <c r="D2" s="36" t="s">
         <v>28</v>
       </c>
@@ -9063,7 +9214,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" ht="16.5" customHeight="1">
       <c r="D3" s="57" t="s">
         <v>22</v>
       </c>
@@ -9101,9 +9252,9 @@
       </c>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="16.5" customHeight="1">
       <c r="D4" s="58" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E4" s="59" t="s">
         <v>1</v>
@@ -9139,12 +9290,12 @@
       </c>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="16.5" customHeight="1">
       <c r="B5" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>1</v>
@@ -9180,13 +9331,13 @@
       </c>
       <c r="P5" s="62"/>
     </row>
-    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" ht="16.5" customHeight="1">
       <c r="B6" s="35">
         <f>SUMIF($E$3:$E$34,B5,$K$3:$K$34)</f>
         <v>2382.0700000000002</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="E6" s="39" t="s">
         <v>1</v>
@@ -9221,10 +9372,10 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" ht="16.5" customHeight="1">
       <c r="B7" s="63"/>
       <c r="D7" s="57" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="E7" s="39" t="s">
         <v>1</v>
@@ -9259,12 +9410,12 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" ht="16.5" customHeight="1">
       <c r="B8" s="33" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="E8" s="39" t="s">
         <v>1</v>
@@ -9299,13 +9450,13 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" ht="16.5" customHeight="1">
       <c r="B9" s="64">
         <f>SUMIF($F$3:$F$34,B8,$K$3:$K$34)</f>
         <v>3382.07</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="E9" s="39" t="s">
         <v>1</v>
@@ -9341,9 +9492,9 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18">
       <c r="D10" s="57" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="40" t="s">
@@ -9376,7 +9527,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18">
       <c r="D11" s="40"/>
       <c r="E11" s="39"/>
       <c r="F11" s="40"/>
@@ -9390,7 +9541,7 @@
       <c r="N11" s="41"/>
       <c r="O11" s="42"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18">
       <c r="D12" s="40"/>
       <c r="E12" s="39"/>
       <c r="F12" s="40"/>
@@ -9404,7 +9555,7 @@
       <c r="N12" s="41"/>
       <c r="O12" s="42"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18">
       <c r="D13" s="40"/>
       <c r="E13" s="39"/>
       <c r="F13" s="40"/>
@@ -9418,7 +9569,7 @@
       <c r="N13" s="41"/>
       <c r="O13" s="42"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18">
       <c r="D14" s="40"/>
       <c r="E14" s="39"/>
       <c r="F14" s="40"/>
@@ -9432,7 +9583,7 @@
       <c r="N14" s="41"/>
       <c r="O14" s="42"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18">
       <c r="D15" s="40"/>
       <c r="E15" s="39"/>
       <c r="F15" s="40"/>
@@ -9446,7 +9597,7 @@
       <c r="N15" s="41"/>
       <c r="O15" s="42"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18">
       <c r="D16" s="40"/>
       <c r="E16" s="39"/>
       <c r="F16" s="40"/>
@@ -9460,7 +9611,7 @@
       <c r="N16" s="41"/>
       <c r="O16" s="42"/>
     </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:15">
       <c r="D17" s="40"/>
       <c r="E17" s="39"/>
       <c r="F17" s="40"/>
@@ -9474,7 +9625,7 @@
       <c r="N17" s="41"/>
       <c r="O17" s="42"/>
     </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:15">
       <c r="D18" s="40"/>
       <c r="E18" s="39"/>
       <c r="F18" s="40"/>
@@ -9488,7 +9639,7 @@
       <c r="N18" s="41"/>
       <c r="O18" s="42"/>
     </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:15">
       <c r="D19" s="40"/>
       <c r="E19" s="39"/>
       <c r="F19" s="40"/>
@@ -9502,7 +9653,7 @@
       <c r="N19" s="41"/>
       <c r="O19" s="42"/>
     </row>
-    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:15">
       <c r="D20" s="40"/>
       <c r="E20" s="39"/>
       <c r="F20" s="40"/>
@@ -9525,7 +9676,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O404"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
@@ -9541,23 +9692,23 @@
     <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="G1" s="2"/>
       <c r="N1" s="50" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" ht="14.25" customHeight="1">
       <c r="G2" s="2"/>
       <c r="N2" s="46"/>
     </row>
-    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="27.75" customHeight="1">
       <c r="G3" s="2"/>
       <c r="L3" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="M3" s="77" t="s">
-        <v>140</v>
+        <v>164</v>
+      </c>
+      <c r="M3" s="75" t="s">
+        <v>165</v>
       </c>
       <c r="N3" s="46">
         <f>SUM(N5:N21)</f>
@@ -9565,90 +9716,90 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15">
       <c r="G4" s="2"/>
       <c r="L4" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="M4" s="78"/>
+        <v>166</v>
+      </c>
+      <c r="M4" s="76"/>
       <c r="N4" s="52"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15">
       <c r="B5" s="46"/>
       <c r="C5" s="46"/>
       <c r="F5" s="16"/>
       <c r="G5" s="31"/>
       <c r="L5" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="N5" s="1">
         <v>4912</v>
       </c>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="N6" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15">
       <c r="G7" s="2"/>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15">
       <c r="F8" s="16"/>
       <c r="G8" s="53"/>
       <c r="L8" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="M8" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="N8" s="1">
         <v>338</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15">
       <c r="F9" s="50" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="G9" s="31"/>
       <c r="N9" s="46"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15">
       <c r="E10" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>4597.1500000000015</v>
+        <v>10945.150000000001</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="I10" s="54" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="N10" s="46"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15">
       <c r="E11" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>4597.1500000000015</v>
+        <v>10945.150000000001</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>4597.1500000000015</v>
+        <v>10945.150000000001</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -9660,40 +9811,40 @@
       </c>
       <c r="N11" s="46"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15">
       <c r="F12" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
       </c>
       <c r="N12" s="46"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15">
       <c r="F13" s="74" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="74"/>
       <c r="I13" s="74"/>
       <c r="N13" s="46"/>
     </row>
-    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" outlineLevel="1">
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
       <c r="F14" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="56"/>
       <c r="I14" s="56"/>
       <c r="N14" s="46"/>
     </row>
-    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" outlineLevel="1">
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
       <c r="F15" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="G15" s="56">
         <v>773.35</v>
@@ -9702,11 +9853,11 @@
       <c r="I15" s="56"/>
       <c r="N15" s="46"/>
     </row>
-    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" outlineLevel="1">
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
       <c r="F16" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="G16" s="56">
         <v>-5148</v>
@@ -9715,11 +9866,11 @@
       <c r="I16" s="56"/>
       <c r="N16" s="46"/>
     </row>
-    <row r="17" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:14" outlineLevel="1">
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
       <c r="F17" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="G17" s="56">
         <v>-168</v>
@@ -9728,11 +9879,11 @@
       <c r="I17" s="56"/>
       <c r="N17" s="46"/>
     </row>
-    <row r="18" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:14" outlineLevel="1">
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
       <c r="F18" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G18" s="56">
         <v>-1700</v>
@@ -9741,11 +9892,11 @@
       <c r="I18" s="56"/>
       <c r="N18" s="46"/>
     </row>
-    <row r="19" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:14" outlineLevel="1">
       <c r="C19" s="56"/>
       <c r="D19" s="56"/>
       <c r="F19" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="G19" s="56">
         <v>5148</v>
@@ -9754,11 +9905,11 @@
       <c r="I19" s="56"/>
       <c r="N19" s="46"/>
     </row>
-    <row r="20" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:14" outlineLevel="1">
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
       <c r="F20" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="G20" s="56">
         <v>-4938</v>
@@ -9767,11 +9918,11 @@
       <c r="I20" s="56"/>
       <c r="N20" s="46"/>
     </row>
-    <row r="21" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:14" outlineLevel="1">
       <c r="C21" s="56"/>
       <c r="D21" s="56"/>
       <c r="F21" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="G21" s="56">
         <v>-1595</v>
@@ -9780,11 +9931,11 @@
       <c r="I21" s="56"/>
       <c r="N21" s="46"/>
     </row>
-    <row r="22" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:14" outlineLevel="1">
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
       <c r="F22" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="G22" s="56">
         <v>-4677</v>
@@ -9793,11 +9944,11 @@
       <c r="I22" s="56"/>
       <c r="N22" s="46"/>
     </row>
-    <row r="23" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:14" outlineLevel="1">
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
       <c r="F23" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="G23" s="56">
         <v>-200</v>
@@ -9806,11 +9957,11 @@
       <c r="I23" s="56"/>
       <c r="N23" s="46"/>
     </row>
-    <row r="24" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:14" outlineLevel="1">
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
       <c r="F24" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="G24" s="56">
         <v>4677</v>
@@ -9819,11 +9970,11 @@
       <c r="I24" s="56"/>
       <c r="N24" s="46"/>
     </row>
-    <row r="25" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:14" outlineLevel="1">
       <c r="C25" s="56"/>
       <c r="D25" s="56"/>
       <c r="F25" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="G25" s="56">
         <v>-750</v>
@@ -9832,11 +9983,11 @@
       <c r="I25" s="56"/>
       <c r="N25" s="46"/>
     </row>
-    <row r="26" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:14" outlineLevel="1">
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
       <c r="F26" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="G26" s="56">
         <v>-652</v>
@@ -9845,11 +9996,11 @@
       <c r="I26" s="56"/>
       <c r="N26" s="46"/>
     </row>
-    <row r="27" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:14" outlineLevel="1">
       <c r="C27" s="56"/>
       <c r="D27" s="56"/>
       <c r="F27" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="G27" s="56">
         <v>11100</v>
@@ -9858,11 +10009,11 @@
       <c r="I27" s="56"/>
       <c r="N27" s="46"/>
     </row>
-    <row r="28" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:14" outlineLevel="1">
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
       <c r="F28" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="G28" s="56">
         <v>-396</v>
@@ -9871,11 +10022,11 @@
       <c r="I28" s="56"/>
       <c r="N28" s="46"/>
     </row>
-    <row r="29" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:14" outlineLevel="1">
       <c r="C29" s="56"/>
       <c r="D29" s="56"/>
       <c r="F29" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="G29" s="56">
         <v>-4211</v>
@@ -9884,11 +10035,11 @@
       <c r="I29" s="56"/>
       <c r="N29" s="46"/>
     </row>
-    <row r="30" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:14" outlineLevel="1">
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
       <c r="F30" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="G30" s="56">
         <v>-450</v>
@@ -9897,11 +10048,11 @@
       <c r="I30" s="56"/>
       <c r="N30" s="46"/>
     </row>
-    <row r="31" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:14" outlineLevel="1">
       <c r="C31" s="56"/>
       <c r="D31" s="56"/>
       <c r="F31" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="G31" s="56">
         <v>-1197</v>
@@ -9910,11 +10061,11 @@
       <c r="I31" s="56"/>
       <c r="N31" s="46"/>
     </row>
-    <row r="32" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:14" outlineLevel="1">
       <c r="C32" s="56"/>
       <c r="D32" s="56"/>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="G32" s="56">
         <v>-315</v>
@@ -9923,11 +10074,11 @@
       <c r="I32" s="56"/>
       <c r="N32" s="46"/>
     </row>
-    <row r="33" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:14" outlineLevel="1">
       <c r="C33" s="56"/>
       <c r="D33" s="56"/>
       <c r="F33" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="G33" s="56">
         <v>-830</v>
@@ -9936,11 +10087,11 @@
       <c r="I33" s="56"/>
       <c r="N33" s="46"/>
     </row>
-    <row r="34" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" outlineLevel="1">
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
       <c r="F34" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="G34" s="56">
         <v>4211</v>
@@ -9949,11 +10100,11 @@
       <c r="I34" s="56"/>
       <c r="N34" s="46"/>
     </row>
-    <row r="35" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" outlineLevel="1">
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
       <c r="F35" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="G35" s="56">
         <v>-200</v>
@@ -9962,11 +10113,11 @@
       <c r="I35" s="56"/>
       <c r="N35" s="46"/>
     </row>
-    <row r="36" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" outlineLevel="1">
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
       <c r="F36" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="G36" s="56">
         <v>10000</v>
@@ -9975,11 +10126,11 @@
       <c r="I36" s="56"/>
       <c r="N36" s="46"/>
     </row>
-    <row r="37" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" outlineLevel="1">
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
       <c r="F37" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G37" s="56">
         <v>-200</v>
@@ -9988,11 +10139,11 @@
       <c r="I37" s="56"/>
       <c r="N37" s="46"/>
     </row>
-    <row r="38" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" outlineLevel="1">
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
       <c r="F38" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G38" s="56">
         <v>-381</v>
@@ -10001,11 +10152,11 @@
       <c r="I38" s="56"/>
       <c r="N38" s="46"/>
     </row>
-    <row r="39" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" outlineLevel="1">
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
       <c r="F39" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="G39" s="56">
         <v>-4911</v>
@@ -10014,12 +10165,12 @@
       <c r="I39" s="56"/>
       <c r="N39" s="46"/>
     </row>
-    <row r="40" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" outlineLevel="1">
       <c r="C40" s="56"/>
       <c r="D40" s="56"/>
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="G40" s="56">
         <v>-5700</v>
@@ -10028,11 +10179,11 @@
       <c r="I40" s="56"/>
       <c r="N40" s="46"/>
     </row>
-    <row r="41" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" outlineLevel="1">
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
       <c r="F41" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="G41" s="56">
         <v>-400</v>
@@ -10041,11 +10192,11 @@
       <c r="I41" s="56"/>
       <c r="N41" s="46"/>
     </row>
-    <row r="42" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" outlineLevel="1">
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
       <c r="F42" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="G42" s="56">
         <v>-450</v>
@@ -10054,11 +10205,11 @@
       <c r="I42" s="56"/>
       <c r="N42" s="46"/>
     </row>
-    <row r="43" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" outlineLevel="1">
       <c r="C43" s="56"/>
       <c r="D43" s="56"/>
       <c r="F43" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="G43" s="56">
         <v>-640</v>
@@ -10067,12 +10218,12 @@
       <c r="I43" s="56"/>
       <c r="N43" s="46"/>
     </row>
-    <row r="44" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" outlineLevel="1">
       <c r="C44" s="56"/>
       <c r="D44" s="56"/>
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="G44" s="56">
         <v>5700</v>
@@ -10081,11 +10232,11 @@
       <c r="I44" s="56"/>
       <c r="N44" s="46"/>
     </row>
-    <row r="45" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" outlineLevel="1">
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
       <c r="F45" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="G45" s="56">
         <v>-130</v>
@@ -10094,11 +10245,11 @@
       <c r="I45" s="56"/>
       <c r="N45" s="46"/>
     </row>
-    <row r="46" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" outlineLevel="1">
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
       <c r="F46" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="G46" s="56">
         <v>-250</v>
@@ -10107,11 +10258,11 @@
       <c r="I46" s="56"/>
       <c r="N46" s="46"/>
     </row>
-    <row r="47" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" outlineLevel="1">
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
       <c r="F47" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="G47" s="56">
         <v>-112.2</v>
@@ -10120,11 +10271,11 @@
       <c r="I47" s="56"/>
       <c r="N47" s="46"/>
     </row>
-    <row r="48" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" outlineLevel="1">
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
       <c r="F48" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="G48" s="56">
         <v>4911</v>
@@ -10133,11 +10284,11 @@
       <c r="I48" s="56"/>
       <c r="N48" s="46"/>
     </row>
-    <row r="49" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" outlineLevel="1">
       <c r="C49" s="56"/>
       <c r="D49" s="56"/>
       <c r="F49" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="G49" s="56">
         <v>-3000</v>
@@ -10146,11 +10297,11 @@
       <c r="I49" s="56"/>
       <c r="N49" s="46"/>
     </row>
-    <row r="50" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" outlineLevel="1">
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
       <c r="F50" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="G50" s="56">
         <v>-4000</v>
@@ -10159,11 +10310,11 @@
       <c r="I50" s="56"/>
       <c r="N50" s="46"/>
     </row>
-    <row r="51" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:14" outlineLevel="1">
       <c r="C51" s="56"/>
       <c r="D51" s="56"/>
       <c r="F51" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="G51" s="56">
         <v>-200</v>
@@ -10172,11 +10323,11 @@
       <c r="I51" s="56"/>
       <c r="N51" s="46"/>
     </row>
-    <row r="52" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:14" outlineLevel="1">
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
       <c r="F52" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="G52" s="56">
         <v>-4612</v>
@@ -10185,9 +10336,9 @@
       <c r="I52" s="56"/>
       <c r="N52" s="46"/>
     </row>
-    <row r="53" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" outlineLevel="1">
       <c r="F53" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="G53" s="56">
         <v>-700</v>
@@ -10196,9 +10347,9 @@
       <c r="I53" s="56"/>
       <c r="N53" s="46"/>
     </row>
-    <row r="54" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:14" outlineLevel="1">
       <c r="F54" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="G54" s="56">
         <v>-880</v>
@@ -10207,9 +10358,9 @@
       <c r="I54" s="56"/>
       <c r="N54" s="46"/>
     </row>
-    <row r="55" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:14" outlineLevel="1">
       <c r="F55" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="G55" s="56">
         <v>-310</v>
@@ -10218,9 +10369,9 @@
       <c r="I55" s="56"/>
       <c r="N55" s="46"/>
     </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:14">
       <c r="F56" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="G56" s="56">
         <v>-250</v>
@@ -10229,9 +10380,9 @@
       <c r="I56" s="56"/>
       <c r="N56" s="46"/>
     </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:14">
       <c r="F57" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="G57" s="56">
         <v>4690</v>
@@ -10240,9 +10391,9 @@
       <c r="I57" s="56"/>
       <c r="N57" s="46"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:14">
       <c r="F58" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="G58" s="56">
         <v>-4440</v>
@@ -10251,9 +10402,9 @@
       <c r="I58" s="56"/>
       <c r="N58" s="46"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14">
       <c r="F59" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="G59" s="56">
         <v>-4697</v>
@@ -10261,9 +10412,9 @@
       <c r="H59" s="56"/>
       <c r="I59" s="56"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14">
       <c r="F60" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="G60" s="56">
         <v>-2500</v>
@@ -10271,9 +10422,9 @@
       <c r="H60" s="56"/>
       <c r="I60" s="56"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:14">
       <c r="F61" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="G61" s="56">
         <v>-126</v>
@@ -10281,9 +10432,9 @@
       <c r="H61" s="56"/>
       <c r="I61" s="56"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:14">
       <c r="F62" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="G62" s="56">
         <v>4742</v>
@@ -10291,9 +10442,9 @@
       <c r="H62" s="56"/>
       <c r="I62" s="56"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14">
       <c r="F63" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="G63" s="56">
         <v>-410</v>
@@ -10301,14 +10452,14 @@
       <c r="H63" s="56"/>
       <c r="I63" s="56"/>
     </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:14">
       <c r="G64" s="56"/>
       <c r="H64" s="56"/>
       <c r="I64" s="56"/>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9">
       <c r="F65" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="G65" s="56">
         <v>3320</v>
@@ -10316,9 +10467,9 @@
       <c r="H65" s="56"/>
       <c r="I65" s="56"/>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9">
       <c r="F66" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="G66" s="56">
         <v>4090</v>
@@ -10326,9 +10477,9 @@
       <c r="H66" s="56"/>
       <c r="I66" s="56"/>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9">
       <c r="F67" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="G67" s="56">
         <v>-5688</v>
@@ -10336,9 +10487,9 @@
       <c r="H67" s="56"/>
       <c r="I67" s="56"/>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9">
       <c r="F68" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="G68" s="56">
         <v>-4433</v>
@@ -10346,9 +10497,9 @@
       <c r="H68" s="56"/>
       <c r="I68" s="56"/>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9">
       <c r="F69" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="G69" s="56">
         <v>-250</v>
@@ -10356,11 +10507,9 @@
       <c r="H69" s="56"/>
       <c r="I69" s="56"/>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C70" s="56"/>
-      <c r="D70" s="56"/>
+    <row r="70" spans="2:9">
       <c r="F70" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G70" s="56">
         <v>-99</v>
@@ -10368,9 +10517,9 @@
       <c r="H70" s="56"/>
       <c r="I70" s="56"/>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9">
       <c r="F71" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="G71" s="56">
         <v>320</v>
@@ -10378,9 +10527,9 @@
       <c r="H71" s="56"/>
       <c r="I71" s="56"/>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9">
       <c r="F72" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="G72" s="56">
         <v>-1572</v>
@@ -10388,16 +10537,14 @@
       <c r="H72" s="56"/>
       <c r="I72" s="56"/>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9">
       <c r="G73" s="56"/>
       <c r="H73" s="56"/>
       <c r="I73" s="56"/>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C74" s="56"/>
-      <c r="D74" s="56"/>
+    <row r="74" spans="2:9">
       <c r="F74" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="G74" s="56">
         <v>4433</v>
@@ -10405,300 +10552,288 @@
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
-        <v>199</v>
-      </c>
-      <c r="C75" s="56">
+    <row r="75" spans="2:9">
+      <c r="F75" t="s">
+        <v>224</v>
+      </c>
+      <c r="G75" s="56">
         <v>8000</v>
       </c>
-      <c r="D75" s="56"/>
-      <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C76" s="56"/>
-      <c r="D76" s="56"/>
-      <c r="G76" s="56"/>
+    <row r="76" spans="2:9">
+      <c r="F76" t="s">
+        <v>155</v>
+      </c>
+      <c r="G76" s="56">
+        <v>-1344</v>
+      </c>
       <c r="H76" s="56"/>
       <c r="I76" s="56"/>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>200</v>
-      </c>
-      <c r="C77" s="56">
-        <v>-50</v>
-      </c>
-      <c r="D77" s="56"/>
-      <c r="G77" s="56"/>
+    <row r="77" spans="2:9">
+      <c r="F77" t="s">
+        <v>150</v>
+      </c>
+      <c r="G77" s="56">
+        <v>-308</v>
+      </c>
       <c r="H77" s="56"/>
       <c r="I77" s="56"/>
     </row>
-    <row r="78" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>201</v>
-      </c>
-      <c r="C78" s="56">
-        <v>500</v>
-      </c>
-      <c r="D78" s="56">
-        <v>300</v>
-      </c>
+    <row r="78" spans="2:9" ht="14.25" customHeight="1">
       <c r="G78" s="56"/>
       <c r="H78" s="56"/>
       <c r="I78" s="56"/>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9">
       <c r="B79" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C79" s="56">
-        <v>8000</v>
+        <v>-50</v>
       </c>
       <c r="D79" s="56"/>
       <c r="G79" s="56"/>
       <c r="H79" s="56"/>
       <c r="I79" s="56"/>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C80" s="56"/>
-      <c r="D80" s="56"/>
+    <row r="80" spans="2:9">
+      <c r="B80" t="s">
+        <v>226</v>
+      </c>
+      <c r="C80" s="56">
+        <v>500</v>
+      </c>
+      <c r="D80" s="56">
+        <v>300</v>
+      </c>
       <c r="G80" s="56"/>
       <c r="H80" s="56"/>
       <c r="I80" s="56"/>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9">
       <c r="B81" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="C81" s="56">
-        <v>-90</v>
+        <v>8000</v>
       </c>
       <c r="D81" s="56"/>
       <c r="G81" s="56"/>
       <c r="H81" s="56"/>
       <c r="I81" s="56"/>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>203</v>
-      </c>
-      <c r="C82" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D82" s="56">
-        <v>300</v>
-      </c>
+    <row r="82" spans="2:9">
+      <c r="C82" s="56"/>
+      <c r="D82" s="56"/>
       <c r="G82" s="56"/>
       <c r="H82" s="56"/>
       <c r="I82" s="56"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9">
       <c r="B83" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C83" s="56">
-        <v>-12807</v>
+        <v>-90</v>
       </c>
       <c r="D83" s="56"/>
       <c r="G83" s="56"/>
       <c r="H83" s="56"/>
       <c r="I83" s="56"/>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C84" s="56"/>
-      <c r="D84" s="56"/>
+    <row r="84" spans="2:9">
+      <c r="B84" t="s">
+        <v>228</v>
+      </c>
+      <c r="C84" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D84" s="56">
+        <v>300</v>
+      </c>
       <c r="G84" s="56"/>
       <c r="H84" s="56"/>
       <c r="I84" s="56"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9">
       <c r="B85" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="C85" s="56">
-        <v>5520</v>
+        <v>-12807</v>
       </c>
       <c r="D85" s="56"/>
       <c r="G85" s="56"/>
       <c r="H85" s="56"/>
       <c r="I85" s="56"/>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9">
       <c r="C86" s="56"/>
       <c r="D86" s="56"/>
       <c r="G86" s="56"/>
       <c r="H86" s="56"/>
       <c r="I86" s="56"/>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9">
       <c r="B87" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="C87" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D87" s="56">
-        <v>300</v>
-      </c>
+        <v>5170</v>
+      </c>
+      <c r="D87" s="56"/>
       <c r="G87" s="56"/>
       <c r="H87" s="56"/>
       <c r="I87" s="56"/>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>200</v>
-      </c>
-      <c r="C88" s="56">
-        <v>-90</v>
-      </c>
+    <row r="88" spans="2:9">
+      <c r="C88" s="56"/>
       <c r="D88" s="56"/>
       <c r="G88" s="56"/>
       <c r="H88" s="56"/>
       <c r="I88" s="56"/>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9">
       <c r="B89" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="C89" s="56">
-        <v>240</v>
-      </c>
-      <c r="D89" s="56"/>
+        <v>2000</v>
+      </c>
+      <c r="D89" s="56">
+        <v>300</v>
+      </c>
       <c r="G89" s="56"/>
       <c r="H89" s="56"/>
       <c r="I89" s="56"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C90" s="56"/>
+    <row r="90" spans="2:9">
+      <c r="B90" t="s">
+        <v>225</v>
+      </c>
+      <c r="C90" s="56">
+        <v>-90</v>
+      </c>
       <c r="D90" s="56"/>
       <c r="G90" s="56"/>
       <c r="H90" s="56"/>
       <c r="I90" s="56"/>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9">
       <c r="B91" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="C91" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D91" s="56">
-        <v>300</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="D91" s="56"/>
       <c r="G91" s="56"/>
       <c r="H91" s="56"/>
       <c r="I91" s="56"/>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
-        <v>209</v>
-      </c>
-      <c r="C92" s="56">
-        <v>-50</v>
-      </c>
+    <row r="92" spans="2:9">
+      <c r="C92" s="56"/>
       <c r="D92" s="56"/>
       <c r="G92" s="56"/>
       <c r="H92" s="56"/>
       <c r="I92" s="56"/>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9">
       <c r="B93" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C93" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D93" s="56">
         <v>300</v>
       </c>
-      <c r="D93" s="56"/>
       <c r="G93" s="56"/>
       <c r="H93" s="56"/>
       <c r="I93" s="56"/>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C94" s="56"/>
+    <row r="94" spans="2:9">
+      <c r="B94" t="s">
+        <v>234</v>
+      </c>
+      <c r="C94" s="56">
+        <v>-50</v>
+      </c>
       <c r="D94" s="56"/>
       <c r="G94" s="56"/>
       <c r="H94" s="56"/>
       <c r="I94" s="56"/>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9">
       <c r="B95" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="C95" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D95" s="56">
         <v>300</v>
       </c>
+      <c r="D95" s="56"/>
       <c r="G95" s="56"/>
       <c r="H95" s="56"/>
       <c r="I95" s="56"/>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>212</v>
-      </c>
-      <c r="C96" s="56">
-        <v>8000</v>
-      </c>
+    <row r="96" spans="2:9">
+      <c r="C96" s="56"/>
       <c r="D96" s="56"/>
       <c r="G96" s="56"/>
       <c r="H96" s="56"/>
       <c r="I96" s="56"/>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9">
       <c r="B97" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="C97" s="56">
-        <v>4180</v>
-      </c>
-      <c r="D97" s="56"/>
+        <v>2000</v>
+      </c>
+      <c r="D97" s="56">
+        <v>300</v>
+      </c>
       <c r="G97" s="56"/>
       <c r="H97" s="56"/>
       <c r="I97" s="56"/>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C98" s="56"/>
+    <row r="98" spans="2:9">
+      <c r="B98" t="s">
+        <v>237</v>
+      </c>
+      <c r="C98" s="56">
+        <v>8000</v>
+      </c>
       <c r="D98" s="56"/>
       <c r="G98" s="56"/>
       <c r="H98" s="56"/>
       <c r="I98" s="56"/>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9">
       <c r="B99" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C99" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D99" s="56">
-        <v>300</v>
-      </c>
+        <v>4180</v>
+      </c>
+      <c r="D99" s="56"/>
       <c r="G99" s="56"/>
       <c r="H99" s="56"/>
       <c r="I99" s="56"/>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B100" t="s">
-        <v>215</v>
-      </c>
-      <c r="C100" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D100" s="56">
-        <v>300</v>
-      </c>
+    <row r="100" spans="2:9">
+      <c r="C100" s="56"/>
+      <c r="D100" s="56"/>
       <c r="G100" s="56"/>
       <c r="H100" s="56"/>
       <c r="I100" s="56"/>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9">
       <c r="B101" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C101" s="56">
         <v>2000</v>
@@ -10710,75 +10845,77 @@
       <c r="H101" s="56"/>
       <c r="I101" s="56"/>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C102" s="56"/>
-      <c r="D102" s="56"/>
+    <row r="102" spans="2:9">
+      <c r="B102" t="s">
+        <v>240</v>
+      </c>
+      <c r="C102" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D102" s="56">
+        <v>300</v>
+      </c>
       <c r="G102" s="56"/>
       <c r="H102" s="56"/>
       <c r="I102" s="56"/>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9">
       <c r="B103" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="C103" s="56">
-        <v>-20000</v>
-      </c>
-      <c r="D103" s="56"/>
+        <v>2000</v>
+      </c>
+      <c r="D103" s="56">
+        <v>300</v>
+      </c>
       <c r="G103" s="56"/>
       <c r="H103" s="56"/>
       <c r="I103" s="56"/>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9">
       <c r="C104" s="56"/>
       <c r="D104" s="56"/>
       <c r="G104" s="56"/>
       <c r="H104" s="56"/>
       <c r="I104" s="56"/>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9">
       <c r="B105" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="C105" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D105" s="56">
-        <v>300</v>
-      </c>
+        <v>-20000</v>
+      </c>
+      <c r="D105" s="56"/>
       <c r="G105" s="56"/>
       <c r="H105" s="56"/>
       <c r="I105" s="56"/>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B106" t="s">
-        <v>219</v>
-      </c>
-      <c r="C106" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D106" s="56">
-        <v>300</v>
-      </c>
+    <row r="106" spans="2:9">
+      <c r="C106" s="56"/>
+      <c r="D106" s="56"/>
       <c r="G106" s="56"/>
       <c r="H106" s="56"/>
       <c r="I106" s="56"/>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9">
       <c r="B107" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C107" s="56">
-        <v>8000</v>
-      </c>
-      <c r="D107" s="56"/>
+        <v>2000</v>
+      </c>
+      <c r="D107" s="56">
+        <v>300</v>
+      </c>
       <c r="G107" s="56"/>
       <c r="H107" s="56"/>
       <c r="I107" s="56"/>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9">
       <c r="B108" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C108" s="56">
         <v>2000</v>
@@ -10790,1218 +10927,1234 @@
       <c r="H108" s="56"/>
       <c r="I108" s="56"/>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9">
       <c r="B109" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C109" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D109" s="56">
-        <v>300</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="D109" s="56"/>
       <c r="G109" s="56"/>
       <c r="H109" s="56"/>
       <c r="I109" s="56"/>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9">
+      <c r="B110" t="s">
+        <v>246</v>
+      </c>
+      <c r="C110" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="56">
+        <v>300</v>
+      </c>
       <c r="G110" s="56"/>
       <c r="H110" s="56"/>
       <c r="I110" s="56"/>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9">
+      <c r="B111" t="s">
+        <v>247</v>
+      </c>
+      <c r="C111" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D111" s="56">
+        <v>300</v>
+      </c>
       <c r="G111" s="56"/>
       <c r="H111" s="56"/>
       <c r="I111" s="56"/>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9">
       <c r="G112" s="56"/>
       <c r="H112" s="56"/>
       <c r="I112" s="56"/>
     </row>
-    <row r="113" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:9">
       <c r="G113" s="56"/>
       <c r="H113" s="56"/>
       <c r="I113" s="56"/>
     </row>
-    <row r="114" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:9">
       <c r="G114" s="56"/>
       <c r="H114" s="56"/>
       <c r="I114" s="56"/>
     </row>
-    <row r="115" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:9">
       <c r="G115" s="56"/>
       <c r="H115" s="56"/>
       <c r="I115" s="56"/>
     </row>
-    <row r="116" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:9">
       <c r="G116" s="56"/>
       <c r="H116" s="56"/>
       <c r="I116" s="56"/>
     </row>
-    <row r="117" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:9">
       <c r="G117" s="56"/>
       <c r="H117" s="56"/>
       <c r="I117" s="56"/>
     </row>
-    <row r="118" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:9">
       <c r="E118" s="2"/>
       <c r="G118" s="56"/>
       <c r="H118" s="56"/>
       <c r="I118" s="56"/>
     </row>
-    <row r="119" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:9">
       <c r="G119" s="56"/>
       <c r="H119" s="56"/>
       <c r="I119" s="56"/>
     </row>
-    <row r="120" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:9">
       <c r="G120" s="56"/>
       <c r="H120" s="56"/>
       <c r="I120" s="56"/>
     </row>
-    <row r="121" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="5:9">
       <c r="G121" s="56"/>
       <c r="H121" s="56"/>
       <c r="I121" s="56"/>
     </row>
-    <row r="122" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="5:9">
       <c r="G122" s="56"/>
       <c r="H122" s="56"/>
       <c r="I122" s="56"/>
     </row>
-    <row r="123" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="5:9">
       <c r="G123" s="56"/>
       <c r="H123" s="56"/>
       <c r="I123" s="56"/>
     </row>
-    <row r="124" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="5:9">
       <c r="G124" s="56"/>
       <c r="H124" s="56"/>
       <c r="I124" s="56"/>
     </row>
-    <row r="125" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="5:9">
       <c r="G125" s="56"/>
       <c r="H125" s="56"/>
       <c r="I125" s="56"/>
     </row>
-    <row r="126" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="5:9">
       <c r="G126" s="56"/>
       <c r="H126" s="56"/>
       <c r="I126" s="56"/>
     </row>
-    <row r="127" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:9">
       <c r="G127" s="56"/>
       <c r="H127" s="56"/>
       <c r="I127" s="56"/>
     </row>
-    <row r="128" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:9">
       <c r="G128" s="56"/>
       <c r="H128" s="56"/>
       <c r="I128" s="56"/>
     </row>
-    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:9">
       <c r="G129" s="56"/>
       <c r="H129" s="56"/>
       <c r="I129" s="56"/>
     </row>
-    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:9">
       <c r="G130" s="56"/>
       <c r="H130" s="56"/>
       <c r="I130" s="56"/>
     </row>
-    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:9">
       <c r="G131" s="56"/>
       <c r="H131" s="56"/>
       <c r="I131" s="56"/>
     </row>
-    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:9">
       <c r="G132" s="56"/>
       <c r="H132" s="56"/>
       <c r="I132" s="56"/>
     </row>
-    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:9">
       <c r="G133" s="56"/>
       <c r="H133" s="56"/>
       <c r="I133" s="56"/>
     </row>
-    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:9">
       <c r="G134" s="56"/>
       <c r="H134" s="56"/>
       <c r="I134" s="56"/>
     </row>
-    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:9">
       <c r="G135" s="56"/>
       <c r="H135" s="56"/>
       <c r="I135" s="56"/>
     </row>
-    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:9">
       <c r="G136" s="56"/>
       <c r="H136" s="56"/>
       <c r="I136" s="56"/>
     </row>
-    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:9">
       <c r="G137" s="56"/>
       <c r="H137" s="56"/>
       <c r="I137" s="56"/>
     </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:9">
       <c r="G138" s="56"/>
       <c r="H138" s="56"/>
       <c r="I138" s="56"/>
     </row>
-    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:9">
       <c r="G139" s="56"/>
       <c r="H139" s="56"/>
       <c r="I139" s="56"/>
     </row>
-    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:9">
       <c r="G140" s="56"/>
       <c r="H140" s="56"/>
       <c r="I140" s="56"/>
     </row>
-    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:9">
       <c r="G141" s="56"/>
       <c r="H141" s="56"/>
       <c r="I141" s="56"/>
     </row>
-    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:9">
       <c r="G142" s="56"/>
       <c r="H142" s="56"/>
       <c r="I142" s="56"/>
     </row>
-    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:9">
       <c r="G143" s="56"/>
       <c r="H143" s="56"/>
       <c r="I143" s="56"/>
     </row>
-    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:9">
       <c r="G144" s="56"/>
       <c r="H144" s="56"/>
       <c r="I144" s="56"/>
     </row>
-    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:9">
       <c r="G145" s="56"/>
       <c r="H145" s="56"/>
       <c r="I145" s="56"/>
     </row>
-    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:9">
       <c r="G146" s="56"/>
       <c r="H146" s="56"/>
       <c r="I146" s="56"/>
     </row>
-    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:9">
       <c r="G147" s="56"/>
       <c r="H147" s="56"/>
       <c r="I147" s="56"/>
     </row>
-    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:9">
       <c r="G148" s="56"/>
       <c r="H148" s="56"/>
       <c r="I148" s="56"/>
     </row>
-    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:9">
       <c r="G149" s="56"/>
       <c r="H149" s="56"/>
       <c r="I149" s="56"/>
     </row>
-    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:9">
       <c r="G150" s="56"/>
       <c r="H150" s="56"/>
       <c r="I150" s="56"/>
     </row>
-    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:9">
       <c r="G151" s="56"/>
       <c r="H151" s="56"/>
       <c r="I151" s="56"/>
     </row>
-    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:9">
       <c r="G152" s="56"/>
       <c r="H152" s="56"/>
       <c r="I152" s="56"/>
     </row>
-    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:9">
       <c r="G153" s="56"/>
       <c r="H153" s="56"/>
       <c r="I153" s="56"/>
     </row>
-    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:9">
       <c r="G154" s="56"/>
       <c r="H154" s="56"/>
       <c r="I154" s="56"/>
     </row>
-    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:9">
       <c r="G155" s="56"/>
       <c r="H155" s="56"/>
       <c r="I155" s="56"/>
     </row>
-    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:9">
       <c r="G156" s="56"/>
       <c r="H156" s="56"/>
       <c r="I156" s="56"/>
     </row>
-    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:9">
       <c r="G157" s="56"/>
       <c r="H157" s="56"/>
       <c r="I157" s="56"/>
     </row>
-    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:9">
       <c r="G158" s="56"/>
       <c r="H158" s="56"/>
       <c r="I158" s="56"/>
     </row>
-    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:9">
       <c r="G159" s="56"/>
       <c r="H159" s="56"/>
       <c r="I159" s="56"/>
     </row>
-    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:9">
       <c r="G160" s="56"/>
       <c r="H160" s="56"/>
       <c r="I160" s="56"/>
     </row>
-    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:9">
       <c r="G161" s="56"/>
       <c r="H161" s="56"/>
       <c r="I161" s="56"/>
     </row>
-    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:9">
       <c r="G162" s="56"/>
       <c r="H162" s="56"/>
       <c r="I162" s="56"/>
     </row>
-    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:9">
       <c r="G163" s="56"/>
       <c r="H163" s="56"/>
       <c r="I163" s="56"/>
     </row>
-    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:9">
       <c r="G164" s="56"/>
       <c r="H164" s="56"/>
       <c r="I164" s="56"/>
     </row>
-    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:9">
       <c r="G165" s="56"/>
       <c r="H165" s="56"/>
       <c r="I165" s="56"/>
     </row>
-    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:9">
       <c r="G166" s="56"/>
       <c r="H166" s="56"/>
       <c r="I166" s="56"/>
     </row>
-    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:9">
       <c r="G167" s="56"/>
       <c r="H167" s="56"/>
       <c r="I167" s="56"/>
     </row>
-    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:9">
       <c r="G168" s="56"/>
       <c r="H168" s="56"/>
       <c r="I168" s="56"/>
     </row>
-    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:9">
       <c r="G169" s="56"/>
       <c r="H169" s="56"/>
       <c r="I169" s="56"/>
     </row>
-    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:9">
       <c r="G170" s="56"/>
       <c r="H170" s="56"/>
       <c r="I170" s="56"/>
     </row>
-    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:9">
       <c r="G171" s="56"/>
       <c r="H171" s="56"/>
       <c r="I171" s="56"/>
     </row>
-    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:9">
       <c r="G172" s="56"/>
       <c r="H172" s="56"/>
       <c r="I172" s="56"/>
     </row>
-    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:9">
       <c r="G173" s="56"/>
       <c r="H173" s="56"/>
       <c r="I173" s="56"/>
     </row>
-    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:9">
       <c r="G174" s="56"/>
       <c r="H174" s="56"/>
       <c r="I174" s="56"/>
     </row>
-    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:9">
       <c r="G175" s="56"/>
       <c r="H175" s="56"/>
       <c r="I175" s="56"/>
     </row>
-    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:9">
       <c r="G176" s="56"/>
       <c r="H176" s="56"/>
       <c r="I176" s="56"/>
     </row>
-    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:9">
       <c r="G177" s="56"/>
       <c r="H177" s="56"/>
       <c r="I177" s="56"/>
     </row>
-    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:9">
       <c r="G178" s="56"/>
       <c r="H178" s="56"/>
       <c r="I178" s="56"/>
     </row>
-    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:9">
       <c r="G179" s="56"/>
       <c r="H179" s="56"/>
       <c r="I179" s="56"/>
     </row>
-    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:9">
       <c r="G180" s="56"/>
       <c r="H180" s="56"/>
       <c r="I180" s="56"/>
     </row>
-    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:9">
       <c r="G181" s="56"/>
       <c r="H181" s="56"/>
       <c r="I181" s="56"/>
     </row>
-    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:9">
       <c r="G182" s="56"/>
       <c r="H182" s="56"/>
       <c r="I182" s="56"/>
     </row>
-    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:9">
       <c r="G183" s="56"/>
       <c r="H183" s="56"/>
       <c r="I183" s="56"/>
     </row>
-    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:9">
       <c r="G184" s="56"/>
       <c r="H184" s="56"/>
       <c r="I184" s="56"/>
     </row>
-    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:9">
       <c r="G185" s="56"/>
       <c r="H185" s="56"/>
       <c r="I185" s="56"/>
     </row>
-    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:9">
       <c r="G186" s="56"/>
       <c r="H186" s="56"/>
       <c r="I186" s="56"/>
     </row>
-    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:9">
       <c r="G187" s="56"/>
       <c r="H187" s="56"/>
       <c r="I187" s="56"/>
     </row>
-    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:9">
       <c r="G188" s="56"/>
       <c r="H188" s="56"/>
       <c r="I188" s="56"/>
     </row>
-    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:9">
       <c r="G189" s="56"/>
       <c r="H189" s="56"/>
       <c r="I189" s="56"/>
     </row>
-    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:9">
       <c r="G190" s="56"/>
       <c r="H190" s="56"/>
       <c r="I190" s="56"/>
     </row>
-    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:9">
       <c r="G191" s="56"/>
       <c r="H191" s="56"/>
       <c r="I191" s="56"/>
     </row>
-    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:9">
       <c r="G192" s="56"/>
       <c r="H192" s="56"/>
       <c r="I192" s="56"/>
     </row>
-    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:9">
       <c r="G193" s="56"/>
       <c r="H193" s="56"/>
       <c r="I193" s="56"/>
     </row>
-    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:9">
       <c r="G194" s="56"/>
       <c r="H194" s="56"/>
       <c r="I194" s="56"/>
     </row>
-    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:9">
       <c r="G195" s="56"/>
       <c r="H195" s="56"/>
       <c r="I195" s="56"/>
     </row>
-    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:9">
       <c r="G196" s="56"/>
       <c r="H196" s="56"/>
       <c r="I196" s="56"/>
     </row>
-    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:9">
       <c r="G197" s="56"/>
       <c r="H197" s="56"/>
       <c r="I197" s="56"/>
     </row>
-    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:9">
       <c r="G198" s="56"/>
       <c r="H198" s="56"/>
       <c r="I198" s="56"/>
     </row>
-    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:9">
       <c r="G199" s="56"/>
       <c r="H199" s="56"/>
       <c r="I199" s="56"/>
     </row>
-    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:9">
       <c r="G200" s="56"/>
       <c r="H200" s="56"/>
       <c r="I200" s="56"/>
     </row>
-    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:9">
       <c r="G201" s="56"/>
       <c r="H201" s="56"/>
       <c r="I201" s="56"/>
     </row>
-    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:9">
       <c r="G202" s="56"/>
       <c r="H202" s="56"/>
       <c r="I202" s="56"/>
     </row>
-    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:9">
       <c r="G203" s="56"/>
       <c r="H203" s="56"/>
       <c r="I203" s="56"/>
     </row>
-    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:9">
       <c r="G204" s="56"/>
       <c r="H204" s="56"/>
       <c r="I204" s="56"/>
     </row>
-    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:9">
       <c r="G205" s="56"/>
       <c r="H205" s="56"/>
       <c r="I205" s="56"/>
     </row>
-    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:9">
       <c r="G206" s="56"/>
       <c r="H206" s="56"/>
       <c r="I206" s="56"/>
     </row>
-    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:9">
       <c r="G207" s="56"/>
       <c r="H207" s="56"/>
       <c r="I207" s="56"/>
     </row>
-    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:9">
       <c r="G208" s="56"/>
       <c r="H208" s="56"/>
       <c r="I208" s="56"/>
     </row>
-    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:9">
       <c r="G209" s="56"/>
       <c r="H209" s="56"/>
       <c r="I209" s="56"/>
     </row>
-    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:9">
       <c r="G210" s="56"/>
       <c r="H210" s="56"/>
       <c r="I210" s="56"/>
     </row>
-    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:9">
       <c r="G211" s="56"/>
       <c r="H211" s="56"/>
       <c r="I211" s="56"/>
     </row>
-    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:9">
       <c r="G212" s="56"/>
       <c r="H212" s="56"/>
       <c r="I212" s="56"/>
     </row>
-    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:9">
       <c r="G213" s="56"/>
       <c r="H213" s="56"/>
       <c r="I213" s="56"/>
     </row>
-    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:9">
       <c r="G214" s="56"/>
       <c r="H214" s="56"/>
       <c r="I214" s="56"/>
     </row>
-    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:9">
       <c r="G215" s="56"/>
       <c r="H215" s="56"/>
       <c r="I215" s="56"/>
     </row>
-    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:9">
       <c r="G216" s="56"/>
       <c r="H216" s="56"/>
       <c r="I216" s="56"/>
     </row>
-    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:9">
       <c r="G217" s="56"/>
       <c r="H217" s="56"/>
       <c r="I217" s="56"/>
     </row>
-    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:9">
       <c r="G218" s="56"/>
       <c r="H218" s="56"/>
       <c r="I218" s="56"/>
     </row>
-    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:9">
       <c r="G219" s="56"/>
       <c r="H219" s="56"/>
       <c r="I219" s="56"/>
     </row>
-    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:9">
       <c r="G220" s="56"/>
       <c r="H220" s="56"/>
       <c r="I220" s="56"/>
     </row>
-    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:9">
       <c r="G221" s="56"/>
       <c r="H221" s="56"/>
       <c r="I221" s="56"/>
     </row>
-    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:9">
       <c r="G222" s="56"/>
       <c r="H222" s="56"/>
       <c r="I222" s="56"/>
     </row>
-    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:9">
       <c r="G223" s="56"/>
       <c r="H223" s="56"/>
       <c r="I223" s="56"/>
     </row>
-    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:9">
       <c r="G224" s="56"/>
       <c r="H224" s="56"/>
       <c r="I224" s="56"/>
     </row>
-    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:9">
       <c r="G225" s="56"/>
       <c r="H225" s="56"/>
       <c r="I225" s="56"/>
     </row>
-    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:9">
       <c r="G226" s="56"/>
       <c r="H226" s="56"/>
       <c r="I226" s="56"/>
     </row>
-    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:9">
       <c r="G227" s="56"/>
       <c r="H227" s="56"/>
       <c r="I227" s="56"/>
     </row>
-    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:9">
       <c r="G228" s="56"/>
       <c r="H228" s="56"/>
       <c r="I228" s="56"/>
     </row>
-    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:9">
       <c r="G229" s="56"/>
       <c r="H229" s="56"/>
       <c r="I229" s="56"/>
     </row>
-    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:9">
       <c r="G230" s="56"/>
       <c r="H230" s="56"/>
       <c r="I230" s="56"/>
     </row>
-    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:9">
       <c r="G231" s="56"/>
       <c r="H231" s="56"/>
       <c r="I231" s="56"/>
     </row>
-    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:9">
       <c r="G232" s="56"/>
       <c r="H232" s="56"/>
       <c r="I232" s="56"/>
     </row>
-    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:9">
       <c r="G233" s="56"/>
       <c r="H233" s="56"/>
       <c r="I233" s="56"/>
     </row>
-    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:9">
       <c r="G234" s="56"/>
       <c r="H234" s="56"/>
       <c r="I234" s="56"/>
     </row>
-    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:9">
       <c r="G235" s="56"/>
       <c r="H235" s="56"/>
       <c r="I235" s="56"/>
     </row>
-    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:9">
       <c r="G236" s="56"/>
       <c r="H236" s="56"/>
       <c r="I236" s="56"/>
     </row>
-    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:9">
       <c r="G237" s="56"/>
       <c r="H237" s="56"/>
       <c r="I237" s="56"/>
     </row>
-    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:9">
       <c r="G238" s="56"/>
       <c r="H238" s="56"/>
       <c r="I238" s="56"/>
     </row>
-    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:9">
       <c r="G239" s="56"/>
       <c r="H239" s="56"/>
       <c r="I239" s="56"/>
     </row>
-    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:9">
       <c r="G240" s="56"/>
       <c r="H240" s="56"/>
       <c r="I240" s="56"/>
     </row>
-    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:9">
       <c r="G241" s="56"/>
       <c r="H241" s="56"/>
       <c r="I241" s="56"/>
     </row>
-    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:9">
       <c r="G242" s="56"/>
       <c r="H242" s="56"/>
       <c r="I242" s="56"/>
     </row>
-    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:9">
       <c r="G243" s="56"/>
       <c r="H243" s="56"/>
       <c r="I243" s="56"/>
     </row>
-    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:9">
       <c r="G244" s="56"/>
       <c r="H244" s="56"/>
       <c r="I244" s="56"/>
     </row>
-    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:9">
       <c r="G245" s="56"/>
       <c r="H245" s="56"/>
       <c r="I245" s="56"/>
     </row>
-    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:9">
       <c r="G246" s="56"/>
       <c r="H246" s="56"/>
       <c r="I246" s="56"/>
     </row>
-    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:9">
       <c r="G247" s="56"/>
       <c r="H247" s="56"/>
       <c r="I247" s="56"/>
     </row>
-    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:9">
       <c r="G248" s="56"/>
       <c r="H248" s="56"/>
       <c r="I248" s="56"/>
     </row>
-    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:9">
       <c r="G249" s="56"/>
       <c r="H249" s="56"/>
       <c r="I249" s="56"/>
     </row>
-    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:9">
       <c r="G250" s="56"/>
       <c r="H250" s="56"/>
       <c r="I250" s="56"/>
     </row>
-    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:9">
       <c r="G251" s="56"/>
       <c r="H251" s="56"/>
       <c r="I251" s="56"/>
     </row>
-    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:9">
       <c r="G252" s="56"/>
       <c r="H252" s="56"/>
       <c r="I252" s="56"/>
     </row>
-    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:9">
       <c r="G253" s="56"/>
       <c r="H253" s="56"/>
       <c r="I253" s="56"/>
     </row>
-    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:9">
       <c r="G254" s="56"/>
       <c r="H254" s="56"/>
       <c r="I254" s="56"/>
     </row>
-    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:9">
       <c r="G255" s="56"/>
       <c r="H255" s="56"/>
       <c r="I255" s="56"/>
     </row>
-    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:9">
       <c r="G256" s="56"/>
       <c r="H256" s="56"/>
       <c r="I256" s="56"/>
     </row>
-    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:9">
       <c r="G257" s="56"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:9">
       <c r="G258" s="56"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:9">
       <c r="G259" s="56"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:9">
       <c r="G260" s="56"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:9">
       <c r="G261" s="56"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:9">
       <c r="G262" s="56"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:9">
       <c r="G263" s="56"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:9">
       <c r="G264" s="56"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:9">
       <c r="G265" s="56"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:9">
       <c r="G266" s="56"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:9">
       <c r="G267" s="56"/>
     </row>
-    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:9">
       <c r="G268" s="56"/>
     </row>
-    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:9">
       <c r="G269" s="56"/>
     </row>
-    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:9">
       <c r="G270" s="56"/>
     </row>
-    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:9">
       <c r="G271" s="56"/>
     </row>
-    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:9">
       <c r="G272" s="56"/>
     </row>
-    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:7">
       <c r="G273" s="56"/>
     </row>
-    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:7">
       <c r="G274" s="56"/>
     </row>
-    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:7">
       <c r="G275" s="56"/>
     </row>
-    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:7">
       <c r="G276" s="56"/>
     </row>
-    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:7">
       <c r="G277" s="56"/>
     </row>
-    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:7">
       <c r="G278" s="56"/>
     </row>
-    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:7">
       <c r="G279" s="56"/>
     </row>
-    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:7">
       <c r="G280" s="56"/>
     </row>
-    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:7">
       <c r="G281" s="56"/>
     </row>
-    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:7">
       <c r="G282" s="56"/>
     </row>
-    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:7">
       <c r="G283" s="56"/>
     </row>
-    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:7">
       <c r="G284" s="56"/>
     </row>
-    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:7">
       <c r="G285" s="56"/>
     </row>
-    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:7">
       <c r="G286" s="56"/>
     </row>
-    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:7">
       <c r="G287" s="56"/>
     </row>
-    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:7">
       <c r="G288" s="56"/>
     </row>
-    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:7">
       <c r="G289" s="56"/>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:7">
       <c r="G290" s="56"/>
     </row>
-    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:7">
       <c r="G291" s="56"/>
     </row>
-    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:7">
       <c r="G292" s="56"/>
     </row>
-    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:7">
       <c r="G293" s="56"/>
     </row>
-    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:7">
       <c r="G294" s="56"/>
     </row>
-    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:7">
       <c r="G295" s="56"/>
     </row>
-    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:7">
       <c r="G296" s="56"/>
     </row>
-    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:7">
       <c r="G297" s="56"/>
     </row>
-    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:7">
       <c r="G298" s="56"/>
     </row>
-    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:7">
       <c r="G299" s="56"/>
     </row>
-    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:7">
       <c r="G300" s="56"/>
     </row>
-    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:7">
       <c r="G301" s="56"/>
     </row>
-    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:7">
       <c r="G302" s="56"/>
     </row>
-    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:7">
       <c r="G303" s="56"/>
     </row>
-    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:7">
       <c r="G304" s="56"/>
     </row>
-    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:7">
       <c r="G305" s="56"/>
     </row>
-    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:7">
       <c r="G306" s="56"/>
     </row>
-    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:7">
       <c r="G307" s="56"/>
     </row>
-    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:7">
       <c r="G308" s="56"/>
     </row>
-    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:7">
       <c r="G309" s="56"/>
     </row>
-    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:7">
       <c r="G310" s="56"/>
     </row>
-    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:7">
       <c r="G311" s="56"/>
     </row>
-    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:7">
       <c r="G312" s="56"/>
     </row>
-    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:7">
       <c r="G313" s="56"/>
     </row>
-    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:7">
       <c r="G314" s="56"/>
     </row>
-    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:7">
       <c r="G315" s="56"/>
     </row>
-    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:7">
       <c r="G316" s="56"/>
     </row>
-    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:7">
       <c r="G317" s="56"/>
     </row>
-    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:7">
       <c r="G318" s="56"/>
     </row>
-    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:7">
       <c r="G319" s="56"/>
     </row>
-    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:7">
       <c r="G320" s="56"/>
     </row>
-    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:7">
       <c r="G321" s="56"/>
     </row>
-    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:7">
       <c r="G322" s="56"/>
     </row>
-    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:7">
       <c r="G323" s="56"/>
     </row>
-    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:7">
       <c r="G324" s="56"/>
     </row>
-    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:7">
       <c r="G325" s="56"/>
     </row>
-    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:7">
       <c r="G326" s="56"/>
     </row>
-    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:7">
       <c r="G327" s="56"/>
     </row>
-    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:7">
       <c r="G328" s="56"/>
     </row>
-    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:7">
       <c r="G329" s="56"/>
     </row>
-    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:7">
       <c r="G330" s="56"/>
     </row>
-    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:7">
       <c r="G331" s="56"/>
     </row>
-    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:7">
       <c r="G332" s="56"/>
     </row>
-    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:7">
       <c r="G333" s="56"/>
     </row>
-    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:7">
       <c r="G334" s="56"/>
     </row>
-    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:7">
       <c r="G335" s="56"/>
     </row>
-    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:7">
       <c r="G336" s="56"/>
     </row>
-    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:7">
       <c r="G337" s="56"/>
     </row>
-    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:7">
       <c r="G338" s="56"/>
     </row>
-    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:7">
       <c r="G339" s="56"/>
     </row>
-    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:7">
       <c r="G340" s="56"/>
     </row>
-    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:7">
       <c r="G341" s="56"/>
     </row>
-    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:7">
       <c r="G342" s="56"/>
     </row>
-    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:7">
       <c r="G343" s="56"/>
     </row>
-    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:7">
       <c r="G344" s="56"/>
     </row>
-    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:7">
       <c r="G345" s="56"/>
     </row>
-    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:7">
       <c r="G346" s="56"/>
     </row>
-    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:7">
       <c r="G347" s="56"/>
     </row>
-    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:7">
       <c r="G348" s="56"/>
     </row>
-    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:7">
       <c r="G349" s="56"/>
     </row>
-    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:7">
       <c r="G350" s="56"/>
     </row>
-    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:7">
       <c r="G351" s="56"/>
     </row>
-    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:7">
       <c r="G352" s="56"/>
     </row>
-    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:7">
       <c r="G353" s="56"/>
     </row>
-    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:7">
       <c r="G354" s="56"/>
     </row>
-    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:7">
       <c r="G355" s="56"/>
     </row>
-    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:7">
       <c r="G356" s="56"/>
     </row>
-    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:7">
       <c r="G357" s="56"/>
     </row>
-    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:7">
       <c r="G358" s="56"/>
     </row>
-    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:7">
       <c r="G359" s="56"/>
     </row>
-    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:7">
       <c r="G360" s="56"/>
     </row>
-    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:7">
       <c r="G361" s="56"/>
     </row>
-    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:7">
       <c r="G362" s="56"/>
     </row>
-    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:7">
       <c r="G363" s="56"/>
     </row>
-    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:7">
       <c r="G364" s="56"/>
     </row>
-    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:7">
       <c r="G365" s="56"/>
     </row>
-    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:7">
       <c r="G366" s="56"/>
     </row>
-    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:7">
       <c r="G367" s="56"/>
     </row>
-    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:7">
       <c r="G368" s="56"/>
     </row>
-    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:7">
       <c r="G369" s="56"/>
     </row>
-    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:7">
       <c r="G370" s="56"/>
     </row>
-    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:7">
       <c r="G371" s="56"/>
     </row>
-    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:7">
       <c r="G372" s="56"/>
     </row>
-    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:7">
       <c r="G373" s="56"/>
     </row>
-    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:7">
       <c r="G374" s="56"/>
     </row>
-    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:7">
       <c r="G375" s="56"/>
     </row>
-    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:7">
       <c r="G376" s="56"/>
     </row>
-    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:7">
       <c r="G377" s="56"/>
     </row>
-    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:7">
       <c r="G378" s="56"/>
     </row>
-    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:7">
       <c r="G379" s="56"/>
     </row>
-    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:7">
       <c r="G380" s="56"/>
     </row>
-    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:7">
       <c r="G381" s="56"/>
     </row>
-    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:7">
       <c r="G382" s="56"/>
     </row>
-    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:7">
       <c r="G383" s="56"/>
     </row>
-    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:7">
       <c r="G384" s="56"/>
     </row>
-    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="7:7">
       <c r="G385" s="56"/>
     </row>
-    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="7:7">
       <c r="G386" s="56"/>
     </row>
-    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="7:7">
       <c r="G387" s="56"/>
     </row>
-    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="7:7">
       <c r="G388" s="56"/>
     </row>
-    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="7:7">
       <c r="G389" s="56"/>
     </row>
-    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="7:7">
       <c r="G390" s="56"/>
     </row>
-    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="7:7">
       <c r="G391" s="56"/>
     </row>
-    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="7:7">
       <c r="G392" s="56"/>
     </row>
-    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="7:7">
       <c r="G393" s="56"/>
     </row>
-    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="7:7">
       <c r="G394" s="56"/>
     </row>
-    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="7:7">
       <c r="G395" s="56"/>
     </row>
-    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="7:7">
       <c r="G396" s="56"/>
     </row>
-    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="7:7">
       <c r="G397" s="56"/>
     </row>
-    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="7:7">
       <c r="G398" s="56"/>
     </row>
-    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="7:7">
       <c r="G399" s="56"/>
     </row>
-    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="7:7">
       <c r="G400" s="56"/>
     </row>
-    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="7:7">
       <c r="G401" s="56"/>
     </row>
-    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="7:7">
       <c r="G402" s="56"/>
     </row>
-    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="7:7">
       <c r="G403" s="56"/>
     </row>
-    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="7:7">
       <c r="G404" s="56"/>
     </row>
   </sheetData>
@@ -12009,43 +12162,75 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
-  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D109">
-    <cfRule type="cellIs" dxfId="9" priority="85" operator="greaterThan">
+  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C79:D111">
+    <cfRule type="cellIs" dxfId="17" priority="101" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="86" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="102" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:D52">
-    <cfRule type="cellIs" dxfId="7" priority="79" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="95" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="80" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="96" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G120:G1048576">
-    <cfRule type="cellIs" dxfId="5" priority="81" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="97" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="82" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="98" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I119">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="G14:I76 G102:I102 I77:I101 G110:I119 I103:I109">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H120:I266">
-    <cfRule type="cellIs" dxfId="1" priority="83" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="99" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="100" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G77:H78">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G88:H101">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G103:H109">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G79:H87">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12057,7 +12242,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
@@ -12065,99 +12250,99 @@
     <col min="4" max="4" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4">
       <c r="B1" s="65" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4">
       <c r="B2" s="57" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D2" s="57"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" s="57" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D3" s="57"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" s="57" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="D4" s="57"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4">
       <c r="B5" s="57" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D5" s="57"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" s="57" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="D6" s="57"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" s="57" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="D7" s="57"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="57" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="D8" s="57"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="57" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="D9" s="57"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" s="57" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D10" s="57"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3">
       <c r="C17" s="31"/>
     </row>
   </sheetData>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="606" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9020F2C2-9B53-45FA-9756-09231AE7151F}"/>
+  <xr:revisionPtr revIDLastSave="670" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A858728F-F877-4A4F-8D87-872F9D6EB33F}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="259">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -192,6 +192,75 @@
     <t>Modo de Pagamento</t>
   </si>
   <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>Assinatura</t>
+  </si>
+  <si>
+    <t>Muay Thai</t>
+  </si>
+  <si>
+    <t>Mensalidade</t>
+  </si>
+  <si>
+    <t>Clube Literatura Clássica</t>
+  </si>
+  <si>
+    <t>Hostinger Nano</t>
+  </si>
+  <si>
+    <t>HBO</t>
+  </si>
+  <si>
+    <t>Streaming</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Seguro Tokio Marine</t>
+  </si>
+  <si>
+    <t>Seguro</t>
+  </si>
+  <si>
+    <t>Sem Parar</t>
+  </si>
+  <si>
+    <t>Verisure</t>
+  </si>
+  <si>
+    <t>Veroo</t>
+  </si>
+  <si>
+    <t>Seguro Allianz</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>Amazon Prime</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Wellhub</t>
+  </si>
+  <si>
+    <t>Muay Thai personal</t>
+  </si>
+  <si>
+    <t>Câmera</t>
+  </si>
+  <si>
     <t>Pedrinho Bancos</t>
   </si>
   <si>
@@ -204,15 +273,6 @@
     <t>Fixo</t>
   </si>
   <si>
-    <t>Manual</t>
-  </si>
-  <si>
-    <t>Assinatura</t>
-  </si>
-  <si>
-    <t>Assinaturas-Fixo</t>
-  </si>
-  <si>
     <t>Lavadora Midea</t>
   </si>
   <si>
@@ -252,9 +312,6 @@
     <t>Transporte</t>
   </si>
   <si>
-    <t>Muay Thai</t>
-  </si>
-  <si>
     <t>Calça Kevlar</t>
   </si>
   <si>
@@ -300,9 +357,6 @@
     <t>Escapamento JBK</t>
   </si>
   <si>
-    <t>Clube Literatura Clássica</t>
-  </si>
-  <si>
     <t>Jaqueta Stella</t>
   </si>
   <si>
@@ -315,117 +369,69 @@
     <t>Luva Fairtex</t>
   </si>
   <si>
-    <t>Hostinger Nano</t>
+    <t>TENTAR ADIATNAR</t>
+  </si>
+  <si>
+    <t>Moletom Brutal Kill</t>
+  </si>
+  <si>
+    <t>Roupas</t>
+  </si>
+  <si>
+    <t>Estorno Puma</t>
+  </si>
+  <si>
+    <t>Estorno</t>
+  </si>
+  <si>
+    <t>Estorno Jaqueta Grid Motors</t>
+  </si>
+  <si>
+    <t>The Alters</t>
+  </si>
+  <si>
+    <t>Pontual</t>
+  </si>
+  <si>
+    <t>Psicóloga</t>
+  </si>
+  <si>
+    <t>Bonfas Chope</t>
+  </si>
+  <si>
+    <t>Comida</t>
+  </si>
+  <si>
+    <t>Bonfas Lanche</t>
+  </si>
+  <si>
+    <t>Remédios Stella</t>
+  </si>
+  <si>
+    <t>Ração Brida</t>
+  </si>
+  <si>
+    <t>Pet</t>
+  </si>
+  <si>
+    <t>Pagamento Ração Brida</t>
+  </si>
+  <si>
+    <t>PAGAMENTO</t>
+  </si>
+  <si>
+    <t>Uber Mr. Jones</t>
+  </si>
+  <si>
+    <t>Gibs</t>
+  </si>
+  <si>
+    <t>Serviço de nuvem da câmera</t>
   </si>
   <si>
     <t>Serviços</t>
   </si>
   <si>
-    <t>TENTAR ADIATNAR</t>
-  </si>
-  <si>
-    <t>Moletom Brutal Kill</t>
-  </si>
-  <si>
-    <t>Roupas</t>
-  </si>
-  <si>
-    <t>HBO</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Seguro Tokio Marine</t>
-  </si>
-  <si>
-    <t>Sem Parar</t>
-  </si>
-  <si>
-    <t>Verisure</t>
-  </si>
-  <si>
-    <t>Veroo</t>
-  </si>
-  <si>
-    <t>Seguro Allianz</t>
-  </si>
-  <si>
-    <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>Claude</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Amazon Prime</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Wellhub</t>
-  </si>
-  <si>
-    <t>Muay Thai personal</t>
-  </si>
-  <si>
-    <t>Câmera</t>
-  </si>
-  <si>
-    <t>Estorno Puma</t>
-  </si>
-  <si>
-    <t>Estorno</t>
-  </si>
-  <si>
-    <t>Estorno Jaqueta Grid Motors</t>
-  </si>
-  <si>
-    <t>The Alters</t>
-  </si>
-  <si>
-    <t>Pontual</t>
-  </si>
-  <si>
-    <t>Psicóloga</t>
-  </si>
-  <si>
-    <t>Bonfas Chope</t>
-  </si>
-  <si>
-    <t>Comida</t>
-  </si>
-  <si>
-    <t>Bonfas Lanche</t>
-  </si>
-  <si>
-    <t>Remédios Stella</t>
-  </si>
-  <si>
-    <t>Ração Brida</t>
-  </si>
-  <si>
-    <t>Pet</t>
-  </si>
-  <si>
-    <t>Pagamento Ração Brida</t>
-  </si>
-  <si>
-    <t>PAGAMENTO</t>
-  </si>
-  <si>
-    <t>Uber Mr. Jones</t>
-  </si>
-  <si>
-    <t>Gibs</t>
-  </si>
-  <si>
-    <t>Serviço de nuvem da câmera</t>
-  </si>
-  <si>
     <t>Rappi</t>
   </si>
   <si>
@@ -519,6 +525,15 @@
     <t>APC+Puscifer Pagamento</t>
   </si>
   <si>
+    <t>Ajuste</t>
+  </si>
+  <si>
+    <t>Cobase</t>
+  </si>
+  <si>
+    <t>AMPM</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -552,9 +567,6 @@
     <t>Adiantamento Salário</t>
   </si>
   <si>
-    <t>Seguro</t>
-  </si>
-  <si>
     <t>Reembolso Psicóloga</t>
   </si>
   <si>
@@ -567,7 +579,7 @@
     <t>Com turbo</t>
   </si>
   <si>
-    <t>Caixinha Guilherme</t>
+    <t>Caixinha Total</t>
   </si>
   <si>
     <t>Caixinha Stella</t>
@@ -799,12 +811,6 @@
   </si>
   <si>
     <t>Obs.</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>Ok</t>
   </si>
   <si>
     <t>Câmeras</t>
@@ -1301,20 +1307,20 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="32">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1404,6 +1410,44 @@
       <font>
         <color rgb="FF00B050"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E1F2"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1771,7 +1815,7 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" customHeight="1"/>
     <row r="2" spans="2:6" ht="23.25" customHeight="1">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="75" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1783,15 +1827,15 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="24" customHeight="1">
-      <c r="B3" s="78"/>
+      <c r="B3" s="76"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C22+C23+C7</f>
-        <v>1823.6447380952363</v>
+        <v>1548.3547380952373</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E22+E23</f>
-        <v>3417.8775000000005</v>
+        <v>4460.8775000000005</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="7.5" customHeight="1"/>
@@ -1800,7 +1844,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="8">
-        <v>10200</v>
+        <v>9381.7099999999991</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8">
@@ -1813,12 +1857,12 @@
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-8214.3552619047641</v>
+        <v>-8171.3552619047623</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-5582.1225000000004</v>
+        <v>-5539.1225000000004</v>
       </c>
     </row>
     <row r="7" spans="2:6">
@@ -1849,12 +1893,12 @@
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5792.1235952380966</v>
+        <v>5749.1235952380948</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>2200.0525000000002</v>
+        <v>2157.0525000000002</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1863,12 +1907,12 @@
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5792.1235952380966</v>
+        <v>5749.1235952380948</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>2200.0525000000002</v>
+        <v>2157.0525000000002</v>
       </c>
     </row>
     <row r="11" spans="2:6">
@@ -2004,13 +2048,9 @@
       <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="8">
-        <v>500</v>
-      </c>
+      <c r="C22" s="8"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="8">
-        <v>1000</v>
-      </c>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="7" t="s">
@@ -2241,11 +2281,11 @@
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>2200.0525000000002</v>
+        <v>2157.0525000000002</v>
       </c>
       <c r="D4" s="27">
         <f>Saldo!C9+D5</f>
-        <v>5792.1235952380966</v>
+        <v>5749.1235952380948</v>
       </c>
     </row>
     <row r="5" spans="2:4">
@@ -2349,7 +2389,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4247.7375000000002</v>
+        <v>4204.7375000000002</v>
       </c>
       <c r="D17" s="30"/>
     </row>
@@ -3073,7 +3113,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3122,15 +3162,15 @@
     <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="48">
         <f>SUM(L6:L376)</f>
-        <v>8042.4360952380957</v>
+        <v>7956.4360952380957</v>
       </c>
       <c r="E2" s="35">
         <f>SUMIF($E$6:$E$376,E1,$M$6:$M$376)</f>
-        <v>5792.1235952380966</v>
+        <v>5749.1235952380948</v>
       </c>
       <c r="F2" s="35">
         <f>SUMIF($F$6:$F$376,F1,$M$6:$M$376)</f>
-        <v>2200.0525000000002</v>
+        <v>2157.0525000000002</v>
       </c>
       <c r="G2" s="35">
         <f>SUMIF($G$6:$G$376,G1,$M$6:$M$376)</f>
@@ -3193,98 +3233,94 @@
     </row>
     <row r="6" spans="3:17">
       <c r="C6" s="38"/>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="39" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F6" s="40"/>
       <c r="G6" s="40"/>
       <c r="H6" s="40">
-        <f t="shared" ref="H6:H37" si="0">COUNTA(E6:G6)</f>
-        <v>2</v>
+        <f>COUNTA(E6:G6)</f>
+        <v>1</v>
       </c>
       <c r="I6" s="41">
-        <v>1780</v>
-      </c>
-      <c r="J6" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="J6" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K6" s="40" t="s">
+        <v>49</v>
+      </c>
       <c r="L6" s="41">
-        <f t="shared" ref="L6:L37" si="1">I6/N6</f>
-        <v>222.5</v>
+        <f>I6/N6</f>
+        <v>86</v>
       </c>
       <c r="M6" s="41">
-        <f t="shared" ref="M6:M37" si="2">IFERROR(L6/H6,"")</f>
-        <v>111.25</v>
+        <f>IFERROR(L6/H6,"")</f>
+        <v>86</v>
       </c>
       <c r="N6" s="42">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O6" s="67">
-        <v>46237</v>
+        <v>46056</v>
       </c>
       <c r="P6" s="67">
-        <f t="shared" ref="P6:P37" si="3">IF(N6&lt;&gt;1,EDATE(O6,N6-1),"")</f>
-        <v>46449</v>
-      </c>
-      <c r="Q6" s="40" t="str">
+        <f>IF(N6&lt;&gt;1,EDATE(O6,N6-1),"")</f>
+        <v>46115</v>
+      </c>
+      <c r="Q6" s="40">
         <f ca="1">IF(O6&lt;&gt;"",IFERROR(DATEDIF(O6,TODAY(),"m")+1,""),"")</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="3:17">
       <c r="C7" s="38"/>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="72" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F7" s="40"/>
       <c r="G7" s="40"/>
       <c r="H7" s="40">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTA(E7:G7)</f>
+        <v>1</v>
       </c>
       <c r="I7" s="41">
-        <v>392</v>
+        <v>1909.3</v>
       </c>
       <c r="J7" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="41" t="s">
         <v>51</v>
       </c>
       <c r="L7" s="41">
-        <f t="shared" si="1"/>
-        <v>196</v>
+        <f>I7/N7</f>
+        <v>190.93</v>
       </c>
       <c r="M7" s="41">
-        <f t="shared" si="2"/>
-        <v>98</v>
+        <f>IFERROR(L7/H7,"")</f>
+        <v>190.93</v>
       </c>
       <c r="N7" s="42">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O7" s="67">
-        <v>46056</v>
+        <v>46025</v>
       </c>
       <c r="P7" s="67">
-        <f t="shared" si="3"/>
-        <v>46084</v>
+        <f>IF(N7&lt;&gt;1,EDATE(O7,N7-1),"")</f>
+        <v>46298</v>
       </c>
       <c r="Q7" s="40">
         <f ca="1">IF(O7&lt;&gt;"",IFERROR(DATEDIF(O7,TODAY(),"m")+1,""),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="3:17">
@@ -3295,48 +3331,50 @@
       <c r="E8" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="40"/>
+      <c r="F8" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G8" s="40"/>
       <c r="H8" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E8:G8)</f>
+        <v>2</v>
       </c>
       <c r="I8" s="41">
-        <v>258</v>
+        <v>1017.6</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L8" s="41">
-        <f t="shared" si="1"/>
-        <v>86</v>
+        <f>I8/N8</f>
+        <v>84.8</v>
       </c>
       <c r="M8" s="41">
-        <f t="shared" si="2"/>
-        <v>86</v>
+        <f>IFERROR(L8/H8,"")</f>
+        <v>42.4</v>
       </c>
       <c r="N8" s="42">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O8" s="67">
-        <v>46056</v>
+        <v>46084</v>
       </c>
       <c r="P8" s="67">
-        <f t="shared" si="3"/>
-        <v>46115</v>
+        <f>IF(N8&lt;&gt;1,EDATE(O8,N8-1),"")</f>
+        <v>46421</v>
       </c>
       <c r="Q8" s="40">
         <f ca="1">IF(O8&lt;&gt;"",IFERROR(DATEDIF(O8,TODAY(),"m")+1,""),"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="3:17">
       <c r="C9" s="38"/>
-      <c r="D9" s="69" t="s">
-        <v>55</v>
+      <c r="D9" s="49" t="s">
+        <v>53</v>
       </c>
       <c r="E9" s="40" t="s">
         <v>1</v>
@@ -3346,315 +3384,321 @@
       </c>
       <c r="G9" s="40"/>
       <c r="H9" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E9:G9)</f>
         <v>2</v>
       </c>
       <c r="I9" s="41">
-        <v>3219</v>
+        <v>224.24</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K9" s="40" t="s">
+        <v>49</v>
+      </c>
       <c r="L9" s="41">
-        <f t="shared" si="1"/>
-        <v>268.25</v>
+        <f>I9/N9</f>
+        <v>18.686666666666667</v>
       </c>
       <c r="M9" s="41">
-        <f t="shared" si="2"/>
-        <v>134.125</v>
+        <f>IFERROR(L9/H9,"")</f>
+        <v>9.3433333333333337</v>
       </c>
       <c r="N9" s="42">
         <v>12</v>
       </c>
       <c r="O9" s="67">
-        <v>45903</v>
+        <v>46176</v>
       </c>
       <c r="P9" s="67">
-        <f t="shared" si="3"/>
-        <v>46237</v>
+        <f>IF(N9&lt;&gt;1,EDATE(O9,N9-1),"")</f>
+        <v>46510</v>
       </c>
       <c r="Q9" s="40">
         <f ca="1">IF(O9&lt;&gt;"",IFERROR(DATEDIF(O9,TODAY(),"m")+1,""),"")</f>
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="3:17">
       <c r="C10" s="38"/>
-      <c r="D10" s="69" t="s">
-        <v>56</v>
+      <c r="D10" s="39" t="s">
+        <v>54</v>
       </c>
       <c r="E10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="40"/>
+      <c r="F10" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G10" s="40"/>
       <c r="H10" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E10:G10)</f>
+        <v>2</v>
       </c>
       <c r="I10" s="41">
-        <v>1700</v>
+        <v>22.45</v>
       </c>
       <c r="J10" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>57</v>
+        <v>49</v>
+      </c>
+      <c r="K10" s="40" t="s">
+        <v>55</v>
       </c>
       <c r="L10" s="41">
-        <f t="shared" si="1"/>
-        <v>283.33333333333331</v>
+        <f>I10/N10</f>
+        <v>22.45</v>
       </c>
       <c r="M10" s="41">
-        <f t="shared" si="2"/>
-        <v>283.33333333333331</v>
+        <f>IFERROR(L10/H10,"")</f>
+        <v>11.225</v>
       </c>
       <c r="N10" s="42">
-        <v>6</v>
-      </c>
-      <c r="O10" s="67">
-        <v>46084</v>
-      </c>
-      <c r="P10" s="67">
-        <f t="shared" si="3"/>
-        <v>46237</v>
-      </c>
-      <c r="Q10" s="40">
+        <v>1</v>
+      </c>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67" t="str">
+        <f>IF(N10&lt;&gt;1,EDATE(O10,N10-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="40" t="str">
         <f ca="1">IF(O10&lt;&gt;"",IFERROR(DATEDIF(O10,TODAY(),"m")+1,""),"")</f>
-        <v>5</v>
+        <v/>
       </c>
     </row>
     <row r="11" spans="3:17">
       <c r="C11" s="38"/>
-      <c r="D11" s="69" t="s">
-        <v>58</v>
+      <c r="D11" s="49" t="s">
+        <v>56</v>
       </c>
       <c r="E11" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="40"/>
+      <c r="F11" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G11" s="40"/>
       <c r="H11" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E11:G11)</f>
+        <v>2</v>
       </c>
       <c r="I11" s="41">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="J11" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K11" s="40" t="s">
+        <v>49</v>
+      </c>
       <c r="L11" s="41">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f>I11/N11</f>
+        <v>60</v>
       </c>
       <c r="M11" s="41">
-        <f t="shared" si="2"/>
-        <v>52</v>
+        <f>IFERROR(L11/H11,"")</f>
+        <v>30</v>
       </c>
       <c r="N11" s="42">
-        <v>4</v>
-      </c>
-      <c r="O11" s="67">
-        <v>46145</v>
-      </c>
-      <c r="P11" s="67">
-        <f t="shared" si="3"/>
-        <v>46237</v>
-      </c>
-      <c r="Q11" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67" t="str">
+        <f>IF(N11&lt;&gt;1,EDATE(O11,N11-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="40" t="str">
+        <f ca="1">IF(O11&lt;&gt;"",IFERROR(DATEDIF(O11,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="3:17">
       <c r="C12" s="38"/>
-      <c r="D12" s="69" t="s">
-        <v>59</v>
+      <c r="D12" s="39" t="s">
+        <v>57</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F12" s="40"/>
+      <c r="F12" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G12" s="40"/>
       <c r="H12" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E12:G12)</f>
+        <v>2</v>
       </c>
       <c r="I12" s="41">
-        <v>128.99</v>
+        <v>395.54</v>
       </c>
       <c r="J12" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K12" s="40" t="s">
+        <v>58</v>
+      </c>
       <c r="L12" s="41">
-        <f t="shared" si="1"/>
-        <v>42.99666666666667</v>
+        <f>I12/N12</f>
+        <v>395.54</v>
       </c>
       <c r="M12" s="41">
-        <f t="shared" si="2"/>
-        <v>42.99666666666667</v>
+        <f>IFERROR(L12/H12,"")</f>
+        <v>197.77</v>
       </c>
       <c r="N12" s="42">
-        <v>3</v>
-      </c>
-      <c r="O12" s="67">
-        <v>46176</v>
-      </c>
-      <c r="P12" s="67">
-        <f t="shared" si="3"/>
-        <v>46237</v>
-      </c>
-      <c r="Q12" s="40">
+        <v>1</v>
+      </c>
+      <c r="O12" s="67"/>
+      <c r="P12" s="67" t="str">
+        <f>IF(N12&lt;&gt;1,EDATE(O12,N12-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="40" t="str">
         <f ca="1">IF(O12&lt;&gt;"",IFERROR(DATEDIF(O12,TODAY(),"m")+1,""),"")</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="3:17">
       <c r="C13" s="38"/>
-      <c r="D13" s="68" t="s">
-        <v>60</v>
+      <c r="D13" s="39" t="s">
+        <v>59</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="40"/>
+      <c r="F13" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G13" s="40"/>
       <c r="H13" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E13:G13)</f>
+        <v>2</v>
       </c>
       <c r="I13" s="41">
-        <v>419</v>
+        <v>215</v>
       </c>
       <c r="J13" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K13" s="40" t="s">
+        <v>49</v>
+      </c>
       <c r="L13" s="41">
-        <f t="shared" si="1"/>
-        <v>41.9</v>
+        <f>I13/N13</f>
+        <v>215</v>
       </c>
       <c r="M13" s="41">
-        <f t="shared" si="2"/>
-        <v>41.9</v>
+        <f>IFERROR(L13/H13,"")</f>
+        <v>107.5</v>
       </c>
       <c r="N13" s="42">
-        <v>10</v>
-      </c>
-      <c r="O13" s="67">
-        <v>45994</v>
-      </c>
-      <c r="P13" s="67">
-        <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q13" s="40">
+        <v>1</v>
+      </c>
+      <c r="O13" s="67"/>
+      <c r="P13" s="67" t="str">
+        <f>IF(N13&lt;&gt;1,EDATE(O13,N13-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="40" t="str">
         <f ca="1">IF(O13&lt;&gt;"",IFERROR(DATEDIF(O13,TODAY(),"m")+1,""),"")</f>
-        <v>8</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="3:17">
       <c r="C14" s="38"/>
-      <c r="D14" s="68" t="s">
-        <v>61</v>
+      <c r="D14" s="49" t="s">
+        <v>60</v>
       </c>
       <c r="E14" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="40"/>
+      <c r="F14" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G14" s="40"/>
       <c r="H14" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E14:G14)</f>
+        <v>2</v>
       </c>
       <c r="I14" s="41">
-        <v>419</v>
+        <v>225</v>
       </c>
       <c r="J14" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K14" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K14" s="40" t="s">
+        <v>49</v>
+      </c>
       <c r="L14" s="41">
-        <f t="shared" si="1"/>
-        <v>41.9</v>
+        <f>I14/N14</f>
+        <v>225</v>
       </c>
       <c r="M14" s="41">
-        <f t="shared" si="2"/>
-        <v>41.9</v>
+        <f>IFERROR(L14/H14,"")</f>
+        <v>112.5</v>
       </c>
       <c r="N14" s="42">
-        <v>10</v>
-      </c>
-      <c r="O14" s="67">
-        <v>45994</v>
-      </c>
-      <c r="P14" s="67">
-        <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q14" s="40">
+        <v>1</v>
+      </c>
+      <c r="O14" s="67"/>
+      <c r="P14" s="67" t="str">
+        <f>IF(N14&lt;&gt;1,EDATE(O14,N14-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="40" t="str">
         <f ca="1">IF(O14&lt;&gt;"",IFERROR(DATEDIF(O14,TODAY(),"m")+1,""),"")</f>
-        <v>8</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="3:17">
       <c r="C15" s="38"/>
-      <c r="D15" s="68" t="s">
-        <v>62</v>
+      <c r="D15" s="39" t="s">
+        <v>61</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F15" s="40"/>
+      <c r="F15" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G15" s="40"/>
       <c r="H15" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E15:G15)</f>
+        <v>2</v>
       </c>
       <c r="I15" s="41">
-        <v>440</v>
+        <v>166.15</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K15" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K15" s="40" t="s">
+        <v>49</v>
+      </c>
       <c r="L15" s="41">
-        <f t="shared" si="1"/>
-        <v>88</v>
+        <f>I15/N15</f>
+        <v>166.15</v>
       </c>
       <c r="M15" s="41">
-        <f t="shared" si="2"/>
-        <v>88</v>
+        <f>IFERROR(L15/H15,"")</f>
+        <v>83.075000000000003</v>
       </c>
       <c r="N15" s="42">
-        <v>5</v>
-      </c>
-      <c r="O15" s="67">
-        <v>46145</v>
-      </c>
-      <c r="P15" s="67">
-        <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q15" s="40"/>
+        <v>1</v>
+      </c>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67" t="str">
+        <f>IF(N15&lt;&gt;1,EDATE(O15,N15-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="40" t="str">
+        <f ca="1">IF(O15&lt;&gt;"",IFERROR(DATEDIF(O15,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="3:17">
       <c r="C16" s="38"/>
-      <c r="D16" s="68" t="s">
-        <v>63</v>
+      <c r="D16" s="49" t="s">
+        <v>62</v>
       </c>
       <c r="E16" s="40" t="s">
         <v>1</v>
@@ -3662,91 +3706,87 @@
       <c r="F16" s="40"/>
       <c r="G16" s="40"/>
       <c r="H16" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E16:G16)</f>
         <v>1</v>
       </c>
       <c r="I16" s="41">
-        <v>313.83999999999997</v>
+        <v>284.05</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K16" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K16" s="40" t="s">
+        <v>58</v>
+      </c>
       <c r="L16" s="41">
-        <f t="shared" si="1"/>
-        <v>78.459999999999994</v>
+        <f>I16/N16</f>
+        <v>284.05</v>
       </c>
       <c r="M16" s="41">
-        <f t="shared" si="2"/>
-        <v>78.459999999999994</v>
+        <f>IFERROR(L16/H16,"")</f>
+        <v>284.05</v>
       </c>
       <c r="N16" s="42">
-        <v>4</v>
-      </c>
-      <c r="O16" s="67">
-        <v>46176</v>
-      </c>
-      <c r="P16" s="67">
-        <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q16" s="40">
-        <f t="shared" ref="Q16:Q29" ca="1" si="4">IF(O16&lt;&gt;"",IFERROR(DATEDIF(O16,TODAY(),"m")+1,""),"")</f>
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="O16" s="67"/>
+      <c r="P16" s="67" t="str">
+        <f>IF(N16&lt;&gt;1,EDATE(O16,N16-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="40" t="str">
+        <f ca="1">IF(O16&lt;&gt;"",IFERROR(DATEDIF(O16,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="17" spans="3:17">
       <c r="C17" s="38"/>
-      <c r="D17" s="68" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="D17" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="40"/>
       <c r="G17" s="40"/>
       <c r="H17" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E17:G17)</f>
         <v>1</v>
       </c>
       <c r="I17" s="41">
-        <v>244.51</v>
+        <v>110</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K17" s="41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L17" s="41">
-        <f t="shared" si="1"/>
-        <v>61.127499999999998</v>
+        <f>I17/N17</f>
+        <v>110</v>
       </c>
       <c r="M17" s="41">
-        <f t="shared" si="2"/>
-        <v>61.127499999999998</v>
+        <f>IFERROR(L17/H17,"")</f>
+        <v>110</v>
       </c>
       <c r="N17" s="42">
-        <v>4</v>
-      </c>
-      <c r="O17" s="67">
-        <v>46176</v>
-      </c>
-      <c r="P17" s="67">
-        <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q17" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="O17" s="67"/>
+      <c r="P17" s="67" t="str">
+        <f>IF(N17&lt;&gt;1,EDATE(O17,N17-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="40" t="str">
+        <f ca="1">IF(O17&lt;&gt;"",IFERROR(DATEDIF(O17,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="18" spans="3:17">
       <c r="C18" s="38"/>
-      <c r="D18" s="68" t="s">
-        <v>66</v>
+      <c r="D18" s="49" t="s">
+        <v>65</v>
       </c>
       <c r="E18" s="40" t="s">
         <v>1</v>
@@ -3754,91 +3794,86 @@
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
       <c r="H18" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E18:G18)</f>
         <v>1</v>
       </c>
       <c r="I18" s="41">
-        <v>628</v>
+        <v>117</v>
       </c>
       <c r="J18" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K18" s="41" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L18" s="41">
-        <f t="shared" si="1"/>
-        <v>157</v>
+        <f>I18/N18</f>
+        <v>117</v>
       </c>
       <c r="M18" s="41">
-        <f t="shared" si="2"/>
-        <v>157</v>
+        <f>IFERROR(L18/H18,"")</f>
+        <v>117</v>
       </c>
       <c r="N18" s="42">
-        <v>4</v>
-      </c>
-      <c r="O18" s="67">
-        <v>46176</v>
-      </c>
-      <c r="P18" s="67">
-        <f t="shared" si="3"/>
-        <v>46268</v>
-      </c>
-      <c r="Q18" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67" t="str">
+        <f>IF(N18&lt;&gt;1,EDATE(O18,N18-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="40"/>
     </row>
     <row r="19" spans="3:17">
       <c r="C19" s="38"/>
-      <c r="D19" s="72" t="s">
-        <v>68</v>
+      <c r="D19" s="39" t="s">
+        <v>66</v>
       </c>
       <c r="E19" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F19" s="40"/>
+      <c r="F19" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G19" s="40"/>
       <c r="H19" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E19:G19)</f>
+        <v>2</v>
       </c>
       <c r="I19" s="41">
-        <v>1909.3</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K19" s="41" t="s">
-        <v>57</v>
+        <v>49</v>
+      </c>
+      <c r="K19" s="40" t="s">
+        <v>55</v>
       </c>
       <c r="L19" s="41">
-        <f t="shared" si="1"/>
-        <v>190.93</v>
+        <f>I19/N19</f>
+        <v>19.899999999999999</v>
       </c>
       <c r="M19" s="41">
-        <f t="shared" si="2"/>
-        <v>190.93</v>
+        <f>IFERROR(L19/H19,"")</f>
+        <v>9.9499999999999993</v>
       </c>
       <c r="N19" s="42">
-        <v>10</v>
-      </c>
-      <c r="O19" s="67">
-        <v>46025</v>
-      </c>
-      <c r="P19" s="67">
-        <f t="shared" si="3"/>
-        <v>46298</v>
-      </c>
-      <c r="Q19" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="O19" s="67"/>
+      <c r="P19" s="67" t="str">
+        <f>IF(N19&lt;&gt;1,EDATE(O19,N19-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="40" t="str">
+        <f ca="1">IF(O19&lt;&gt;"",IFERROR(DATEDIF(O19,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="20" spans="3:17">
       <c r="C20" s="38"/>
-      <c r="D20" s="72" t="s">
-        <v>69</v>
+      <c r="D20" s="39" t="s">
+        <v>67</v>
       </c>
       <c r="E20" s="40" t="s">
         <v>1</v>
@@ -3846,45 +3881,43 @@
       <c r="F20" s="40"/>
       <c r="G20" s="40"/>
       <c r="H20" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E20:G20)</f>
         <v>1</v>
       </c>
       <c r="I20" s="41">
-        <v>659</v>
+        <v>26.9</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K20" s="41" t="s">
         <v>49</v>
       </c>
+      <c r="K20" s="40" t="s">
+        <v>55</v>
+      </c>
       <c r="L20" s="41">
-        <f t="shared" si="1"/>
-        <v>54.916666666666664</v>
+        <f>I20/N20</f>
+        <v>26.9</v>
       </c>
       <c r="M20" s="41">
-        <f t="shared" si="2"/>
-        <v>54.916666666666664</v>
+        <f>IFERROR(L20/H20,"")</f>
+        <v>26.9</v>
       </c>
       <c r="N20" s="42">
-        <v>12</v>
-      </c>
-      <c r="O20" s="67">
-        <v>45964</v>
-      </c>
-      <c r="P20" s="67">
-        <f t="shared" si="3"/>
-        <v>46298</v>
-      </c>
-      <c r="Q20" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="O20" s="67"/>
+      <c r="P20" s="67" t="str">
+        <f>IF(N20&lt;&gt;1,EDATE(O20,N20-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="40" t="str">
+        <f ca="1">IF(O20&lt;&gt;"",IFERROR(DATEDIF(O20,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="21" spans="3:17">
       <c r="C21" s="38"/>
-      <c r="D21" s="72" t="s">
-        <v>70</v>
+      <c r="D21" s="49" t="s">
+        <v>68</v>
       </c>
       <c r="E21" s="40" t="s">
         <v>1</v>
@@ -3892,45 +3925,40 @@
       <c r="F21" s="40"/>
       <c r="G21" s="40"/>
       <c r="H21" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E21:G21)</f>
         <v>1</v>
       </c>
       <c r="I21" s="41">
-        <v>2319.3000000000002</v>
+        <v>70</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K21" s="41" t="s">
         <v>49</v>
       </c>
       <c r="L21" s="41">
-        <f t="shared" si="1"/>
-        <v>193.27500000000001</v>
+        <f>I21/N21</f>
+        <v>70</v>
       </c>
       <c r="M21" s="41">
-        <f t="shared" si="2"/>
-        <v>193.27500000000001</v>
+        <f>IFERROR(L21/H21,"")</f>
+        <v>70</v>
       </c>
       <c r="N21" s="42">
-        <v>12</v>
-      </c>
-      <c r="O21" s="67">
-        <v>45964</v>
-      </c>
-      <c r="P21" s="67">
-        <f t="shared" si="3"/>
-        <v>46298</v>
-      </c>
-      <c r="Q21" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>9</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O21" s="67"/>
+      <c r="P21" s="67" t="str">
+        <f>IF(N21&lt;&gt;1,EDATE(O21,N21-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="40"/>
     </row>
     <row r="22" spans="3:17">
       <c r="C22" s="38"/>
-      <c r="D22" s="72" t="s">
-        <v>71</v>
+      <c r="D22" s="70" t="s">
+        <v>69</v>
       </c>
       <c r="E22" s="40" t="s">
         <v>1</v>
@@ -3938,45 +3966,43 @@
       <c r="F22" s="40"/>
       <c r="G22" s="40"/>
       <c r="H22" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E22:G22)</f>
         <v>1</v>
       </c>
       <c r="I22" s="41">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="J22" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K22" s="41" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="L22" s="41">
-        <f t="shared" si="1"/>
-        <v>166.66666666666666</v>
+        <f>I22/N22</f>
+        <v>400</v>
       </c>
       <c r="M22" s="41">
-        <f t="shared" si="2"/>
-        <v>166.66666666666666</v>
+        <f>IFERROR(L22/H22,"")</f>
+        <v>400</v>
       </c>
       <c r="N22" s="42">
-        <v>12</v>
-      </c>
-      <c r="O22" s="67">
-        <v>45964</v>
-      </c>
-      <c r="P22" s="67">
-        <f t="shared" si="3"/>
-        <v>46298</v>
-      </c>
-      <c r="Q22" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="O22" s="67"/>
+      <c r="P22" s="67" t="str">
+        <f>IF(N22&lt;&gt;1,EDATE(O22,N22-1),"")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="40" t="str">
+        <f ca="1">IF(O22&lt;&gt;"",IFERROR(DATEDIF(O22,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="23" spans="3:17">
       <c r="C23" s="38"/>
-      <c r="D23" s="72" t="s">
-        <v>73</v>
+      <c r="D23" s="49" t="s">
+        <v>70</v>
       </c>
       <c r="E23" s="40" t="s">
         <v>1</v>
@@ -3986,224 +4012,234 @@
       </c>
       <c r="G23" s="40"/>
       <c r="H23" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E23:G23)</f>
         <v>2</v>
       </c>
       <c r="I23" s="41">
-        <v>725</v>
+        <v>22</v>
       </c>
       <c r="J23" s="41" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K23" s="41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L23" s="41">
-        <f t="shared" si="1"/>
-        <v>120.83333333333333</v>
+        <f>I23/N23</f>
+        <v>22</v>
       </c>
       <c r="M23" s="41">
-        <f t="shared" si="2"/>
-        <v>60.416666666666664</v>
+        <f>IFERROR(L23/H23,"")</f>
+        <v>11</v>
       </c>
       <c r="N23" s="42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O23" s="67">
-        <v>46145</v>
-      </c>
-      <c r="P23" s="67">
-        <f t="shared" si="3"/>
-        <v>46298</v>
+        <v>46206</v>
+      </c>
+      <c r="P23" s="67" t="str">
+        <f>IF(N23&lt;&gt;1,EDATE(O23,N23-1),"")</f>
+        <v/>
       </c>
       <c r="Q23" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <f ca="1">IF(O23&lt;&gt;"",IFERROR(DATEDIF(O23,TODAY(),"m")+1,""),"")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="3:17">
       <c r="C24" s="38"/>
-      <c r="D24" s="72" t="s">
-        <v>74</v>
+      <c r="D24" s="49" t="s">
+        <v>71</v>
       </c>
       <c r="E24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F24" s="40"/>
+      <c r="F24" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G24" s="40"/>
       <c r="H24" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E24:G24)</f>
+        <v>2</v>
       </c>
       <c r="I24" s="41">
-        <v>372.43</v>
-      </c>
-      <c r="J24" s="41" t="s">
+        <v>1780</v>
+      </c>
+      <c r="J24" s="71" t="s">
         <v>44</v>
       </c>
       <c r="K24" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L24" s="41">
-        <f t="shared" si="1"/>
-        <v>93.107500000000002</v>
+        <f>I24/N24</f>
+        <v>222.5</v>
       </c>
       <c r="M24" s="41">
-        <f t="shared" si="2"/>
-        <v>93.107500000000002</v>
+        <f>IFERROR(L24/H24,"")</f>
+        <v>111.25</v>
       </c>
       <c r="N24" s="42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O24" s="67">
-        <v>46206</v>
+        <v>46237</v>
       </c>
       <c r="P24" s="67">
-        <f t="shared" si="3"/>
-        <v>46298</v>
-      </c>
-      <c r="Q24" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f>IF(N24&lt;&gt;1,EDATE(O24,N24-1),"")</f>
+        <v>46449</v>
+      </c>
+      <c r="Q24" s="40" t="str">
+        <f ca="1">IF(O24&lt;&gt;"",IFERROR(DATEDIF(O24,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="25" spans="3:17">
       <c r="C25" s="38"/>
-      <c r="D25" s="72" t="s">
-        <v>75</v>
+      <c r="D25" s="39" t="s">
+        <v>73</v>
       </c>
       <c r="E25" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F25" s="40"/>
+      <c r="F25" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G25" s="40"/>
       <c r="H25" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E25:G25)</f>
+        <v>2</v>
       </c>
       <c r="I25" s="41">
-        <v>72</v>
+        <v>392</v>
       </c>
       <c r="J25" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="K25" s="41"/>
+      <c r="K25" s="40" t="s">
+        <v>74</v>
+      </c>
       <c r="L25" s="41">
-        <f t="shared" si="1"/>
-        <v>24</v>
+        <f>I25/N25</f>
+        <v>196</v>
       </c>
       <c r="M25" s="41">
-        <f t="shared" si="2"/>
-        <v>24</v>
+        <f>IFERROR(L25/H25,"")</f>
+        <v>98</v>
       </c>
       <c r="N25" s="42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O25" s="67">
-        <v>46240</v>
+        <v>46056</v>
       </c>
       <c r="P25" s="67">
-        <f t="shared" si="3"/>
-        <v>46301</v>
-      </c>
-      <c r="Q25" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <f>IF(N25&lt;&gt;1,EDATE(O25,N25-1),"")</f>
+        <v>46084</v>
+      </c>
+      <c r="Q25" s="40">
+        <f ca="1">IF(O25&lt;&gt;"",IFERROR(DATEDIF(O25,TODAY(),"m")+1,""),"")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="3:17">
       <c r="C26" s="38"/>
-      <c r="D26" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="40"/>
+      <c r="D26" s="69" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F26" s="40" t="s">
         <v>2</v>
       </c>
       <c r="G26" s="40"/>
       <c r="H26" s="40">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNTA(E26:G26)</f>
+        <v>2</v>
       </c>
       <c r="I26" s="41">
-        <v>161.72999999999999</v>
+        <v>3219</v>
       </c>
       <c r="J26" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="K26" s="41"/>
+      <c r="K26" s="41" t="s">
+        <v>72</v>
+      </c>
       <c r="L26" s="41">
-        <f t="shared" si="1"/>
-        <v>53.91</v>
+        <f>I26/N26</f>
+        <v>268.25</v>
       </c>
       <c r="M26" s="41">
-        <f t="shared" si="2"/>
-        <v>53.91</v>
+        <f>IFERROR(L26/H26,"")</f>
+        <v>134.125</v>
       </c>
       <c r="N26" s="42">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O26" s="67">
-        <v>46240</v>
+        <v>45903</v>
       </c>
       <c r="P26" s="67">
-        <f t="shared" si="3"/>
-        <v>46301</v>
-      </c>
-      <c r="Q26" s="40" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+        <f>IF(N26&lt;&gt;1,EDATE(O26,N26-1),"")</f>
+        <v>46237</v>
+      </c>
+      <c r="Q26" s="40">
+        <f ca="1">IF(O26&lt;&gt;"",IFERROR(DATEDIF(O26,TODAY(),"m")+1,""),"")</f>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="3:17">
       <c r="C27" s="38"/>
-      <c r="D27" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="D27" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="40"/>
       <c r="G27" s="40"/>
       <c r="H27" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E27:G27)</f>
         <v>1</v>
       </c>
       <c r="I27" s="41">
-        <v>973.02</v>
+        <v>1700</v>
       </c>
       <c r="J27" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K27" s="41" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L27" s="41">
-        <f t="shared" si="1"/>
-        <v>81.084999999999994</v>
+        <f>I27/N27</f>
+        <v>283.33333333333331</v>
       </c>
       <c r="M27" s="41">
-        <f t="shared" si="2"/>
-        <v>81.084999999999994</v>
+        <f>IFERROR(L27/H27,"")</f>
+        <v>283.33333333333331</v>
       </c>
       <c r="N27" s="42">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O27" s="67">
-        <v>45994</v>
+        <v>46084</v>
       </c>
       <c r="P27" s="67">
-        <f t="shared" si="3"/>
-        <v>46329</v>
+        <f>IF(N27&lt;&gt;1,EDATE(O27,N27-1),"")</f>
+        <v>46237</v>
       </c>
       <c r="Q27" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <f ca="1">IF(O27&lt;&gt;"",IFERROR(DATEDIF(O27,TODAY(),"m")+1,""),"")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="3:17">
       <c r="C28" s="38"/>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="69" t="s">
         <v>78</v>
       </c>
       <c r="E28" s="40" t="s">
@@ -4212,44 +4248,41 @@
       <c r="F28" s="40"/>
       <c r="G28" s="40"/>
       <c r="H28" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E28:G28)</f>
         <v>1</v>
       </c>
       <c r="I28" s="41">
-        <v>379</v>
+        <v>208</v>
       </c>
       <c r="J28" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K28" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L28" s="41">
-        <f t="shared" si="1"/>
-        <v>54.142857142857146</v>
+        <f>I28/N28</f>
+        <v>52</v>
       </c>
       <c r="M28" s="41">
-        <f t="shared" si="2"/>
-        <v>54.142857142857146</v>
+        <f>IFERROR(L28/H28,"")</f>
+        <v>52</v>
       </c>
       <c r="N28" s="42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O28" s="67">
         <v>46145</v>
       </c>
       <c r="P28" s="67">
-        <f t="shared" si="3"/>
-        <v>46329</v>
-      </c>
-      <c r="Q28" s="40">
-        <f t="shared" ca="1" si="4"/>
-        <v>3</v>
-      </c>
+        <f>IF(N28&lt;&gt;1,EDATE(O28,N28-1),"")</f>
+        <v>46237</v>
+      </c>
+      <c r="Q28" s="40"/>
     </row>
     <row r="29" spans="3:17">
       <c r="C29" s="38"/>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="69" t="s">
         <v>79</v>
       </c>
       <c r="E29" s="40" t="s">
@@ -4258,89 +4291,90 @@
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
       <c r="H29" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E29:G29)</f>
         <v>1</v>
       </c>
       <c r="I29" s="41">
-        <v>297</v>
+        <v>128.99</v>
       </c>
       <c r="J29" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K29" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L29" s="41">
-        <f t="shared" si="1"/>
-        <v>49.5</v>
+        <f>I29/N29</f>
+        <v>42.99666666666667</v>
       </c>
       <c r="M29" s="41">
-        <f t="shared" si="2"/>
-        <v>49.5</v>
+        <f>IFERROR(L29/H29,"")</f>
+        <v>42.99666666666667</v>
       </c>
       <c r="N29" s="42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O29" s="67">
         <v>46176</v>
       </c>
       <c r="P29" s="67">
-        <f t="shared" si="3"/>
-        <v>46329</v>
+        <f>IF(N29&lt;&gt;1,EDATE(O29,N29-1),"")</f>
+        <v>46237</v>
       </c>
       <c r="Q29" s="40">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF(O29&lt;&gt;"",IFERROR(DATEDIF(O29,TODAY(),"m")+1,""),"")</f>
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="3:17">
       <c r="C30" s="38"/>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="68" t="s">
         <v>80</v>
       </c>
       <c r="E30" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F30" s="40"/>
       <c r="G30" s="40"/>
       <c r="H30" s="40">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>COUNTA(E30:G30)</f>
+        <v>1</v>
       </c>
       <c r="I30" s="41">
-        <v>506</v>
+        <v>419</v>
       </c>
       <c r="J30" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K30" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L30" s="41">
-        <f t="shared" si="1"/>
-        <v>50.6</v>
+        <f>I30/N30</f>
+        <v>41.9</v>
       </c>
       <c r="M30" s="41">
-        <f t="shared" si="2"/>
-        <v>25.3</v>
+        <f>IFERROR(L30/H30,"")</f>
+        <v>41.9</v>
       </c>
       <c r="N30" s="42">
         <v>10</v>
       </c>
       <c r="O30" s="67">
-        <v>46115</v>
+        <v>45994</v>
       </c>
       <c r="P30" s="67">
-        <f t="shared" si="3"/>
-        <v>46390</v>
-      </c>
-      <c r="Q30" s="40"/>
+        <f>IF(N30&lt;&gt;1,EDATE(O30,N30-1),"")</f>
+        <v>46268</v>
+      </c>
+      <c r="Q30" s="40">
+        <f ca="1">IF(O30&lt;&gt;"",IFERROR(DATEDIF(O30,TODAY(),"m")+1,""),"")</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="31" spans="3:17">
       <c r="C31" s="38"/>
-      <c r="D31" s="49" t="s">
+      <c r="D31" s="68" t="s">
         <v>81</v>
       </c>
       <c r="E31" s="40" t="s">
@@ -4349,88 +4383,87 @@
       <c r="F31" s="40"/>
       <c r="G31" s="40"/>
       <c r="H31" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E31:G31)</f>
         <v>1</v>
       </c>
       <c r="I31" s="41">
-        <v>399.9</v>
+        <v>419</v>
       </c>
       <c r="J31" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K31" s="41" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="L31" s="41">
-        <f t="shared" si="1"/>
-        <v>57.128571428571426</v>
+        <f>I31/N31</f>
+        <v>41.9</v>
       </c>
       <c r="M31" s="41">
-        <f t="shared" si="2"/>
-        <v>57.128571428571426</v>
+        <f>IFERROR(L31/H31,"")</f>
+        <v>41.9</v>
       </c>
       <c r="N31" s="42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O31" s="67">
-        <v>46206</v>
+        <v>45994</v>
       </c>
       <c r="P31" s="67">
-        <f t="shared" si="3"/>
-        <v>46390</v>
+        <f>IF(N31&lt;&gt;1,EDATE(O31,N31-1),"")</f>
+        <v>46268</v>
       </c>
       <c r="Q31" s="40">
-        <f t="shared" ref="Q31:Q48" ca="1" si="5">IF(O31&lt;&gt;"",IFERROR(DATEDIF(O31,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <f ca="1">IF(O31&lt;&gt;"",IFERROR(DATEDIF(O31,TODAY(),"m")+1,""),"")</f>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="3:17">
       <c r="C32" s="38"/>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="40"/>
+      <c r="E32" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F32" s="40"/>
       <c r="G32" s="40"/>
       <c r="H32" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>COUNTA(E32:G32)</f>
+        <v>1</v>
       </c>
       <c r="I32" s="41">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="J32" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K32" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L32" s="41">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="M32" s="41" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f>I32/N32</f>
+        <v>88</v>
+      </c>
+      <c r="M32" s="41">
+        <f>IFERROR(L32/H32,"")</f>
+        <v>88</v>
       </c>
       <c r="N32" s="42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O32" s="67">
-        <v>46237</v>
+        <v>46145</v>
       </c>
       <c r="P32" s="67">
-        <f t="shared" si="3"/>
-        <v>46390</v>
-      </c>
-      <c r="Q32" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
+        <f>IF(N32&lt;&gt;1,EDATE(O32,N32-1),"")</f>
+        <v>46268</v>
+      </c>
+      <c r="Q32" s="40"/>
     </row>
     <row r="33" spans="3:17">
       <c r="C33" s="38"/>
-      <c r="D33" s="49" t="s">
+      <c r="D33" s="68" t="s">
         <v>83</v>
       </c>
       <c r="E33" s="40" t="s">
@@ -4439,11 +4472,11 @@
       <c r="F33" s="40"/>
       <c r="G33" s="40"/>
       <c r="H33" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E33:G33)</f>
         <v>1</v>
       </c>
       <c r="I33" s="41">
-        <v>284</v>
+        <v>313.83999999999997</v>
       </c>
       <c r="J33" s="41" t="s">
         <v>44</v>
@@ -4452,80 +4485,78 @@
         <v>72</v>
       </c>
       <c r="L33" s="41">
-        <f t="shared" si="1"/>
-        <v>47.333333333333336</v>
+        <f>I33/N33</f>
+        <v>78.459999999999994</v>
       </c>
       <c r="M33" s="41">
-        <f t="shared" si="2"/>
-        <v>47.333333333333336</v>
+        <f>IFERROR(L33/H33,"")</f>
+        <v>78.459999999999994</v>
       </c>
       <c r="N33" s="42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O33" s="67">
-        <v>46237</v>
+        <v>46176</v>
       </c>
       <c r="P33" s="67">
-        <f t="shared" si="3"/>
-        <v>46390</v>
-      </c>
-      <c r="Q33" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
+        <f>IF(N33&lt;&gt;1,EDATE(O33,N33-1),"")</f>
+        <v>46268</v>
+      </c>
+      <c r="Q33" s="40">
+        <f ca="1">IF(O33&lt;&gt;"",IFERROR(DATEDIF(O33,TODAY(),"m")+1,""),"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="3:17">
       <c r="C34" s="38"/>
-      <c r="D34" s="39" t="s">
+      <c r="D34" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="E34" s="40" t="s">
-        <v>1</v>
-      </c>
+      <c r="E34" s="40"/>
       <c r="F34" s="40" t="s">
         <v>2</v>
       </c>
       <c r="G34" s="40"/>
       <c r="H34" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E34:G34)</f>
+        <v>1</v>
+      </c>
+      <c r="I34" s="41">
+        <v>244.51</v>
+      </c>
+      <c r="J34" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="L34" s="41">
+        <f>I34/N34</f>
+        <v>61.127499999999998</v>
+      </c>
+      <c r="M34" s="41">
+        <f>IFERROR(L34/H34,"")</f>
+        <v>61.127499999999998</v>
+      </c>
+      <c r="N34" s="42">
+        <v>4</v>
+      </c>
+      <c r="O34" s="67">
+        <v>46176</v>
+      </c>
+      <c r="P34" s="67">
+        <f>IF(N34&lt;&gt;1,EDATE(O34,N34-1),"")</f>
+        <v>46268</v>
+      </c>
+      <c r="Q34" s="40">
+        <f ca="1">IF(O34&lt;&gt;"",IFERROR(DATEDIF(O34,TODAY(),"m")+1,""),"")</f>
         <v>2</v>
-      </c>
-      <c r="I34" s="41">
-        <v>1017.6</v>
-      </c>
-      <c r="J34" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K34" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="L34" s="41">
-        <f t="shared" si="1"/>
-        <v>84.8</v>
-      </c>
-      <c r="M34" s="41">
-        <f t="shared" si="2"/>
-        <v>42.4</v>
-      </c>
-      <c r="N34" s="42">
-        <v>12</v>
-      </c>
-      <c r="O34" s="67">
-        <v>46084</v>
-      </c>
-      <c r="P34" s="67">
-        <f t="shared" si="3"/>
-        <v>46421</v>
-      </c>
-      <c r="Q34" s="40">
-        <f t="shared" ca="1" si="5"/>
-        <v>5</v>
       </c>
     </row>
     <row r="35" spans="3:17">
       <c r="C35" s="38"/>
-      <c r="D35" s="49" t="s">
-        <v>85</v>
+      <c r="D35" s="68" t="s">
+        <v>86</v>
       </c>
       <c r="E35" s="40" t="s">
         <v>1</v>
@@ -4533,45 +4564,45 @@
       <c r="F35" s="40"/>
       <c r="G35" s="40"/>
       <c r="H35" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E35:G35)</f>
         <v>1</v>
       </c>
       <c r="I35" s="41">
-        <v>1900</v>
+        <v>628</v>
       </c>
       <c r="J35" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K35" s="41" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="L35" s="41">
-        <f t="shared" si="1"/>
-        <v>190</v>
+        <f>I35/N35</f>
+        <v>157</v>
       </c>
       <c r="M35" s="41">
-        <f t="shared" si="2"/>
-        <v>190</v>
+        <f>IFERROR(L35/H35,"")</f>
+        <v>157</v>
       </c>
       <c r="N35" s="42">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O35" s="67">
-        <v>46145</v>
+        <v>46176</v>
       </c>
       <c r="P35" s="67">
-        <f t="shared" si="3"/>
-        <v>46421</v>
+        <f>IF(N35&lt;&gt;1,EDATE(O35,N35-1),"")</f>
+        <v>46268</v>
       </c>
       <c r="Q35" s="40">
-        <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <f ca="1">IF(O35&lt;&gt;"",IFERROR(DATEDIF(O35,TODAY(),"m")+1,""),"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="3:17">
       <c r="C36" s="38"/>
-      <c r="D36" s="49" t="s">
-        <v>86</v>
+      <c r="D36" s="72" t="s">
+        <v>88</v>
       </c>
       <c r="E36" s="40" t="s">
         <v>1</v>
@@ -4579,45 +4610,45 @@
       <c r="F36" s="40"/>
       <c r="G36" s="40"/>
       <c r="H36" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E36:G36)</f>
         <v>1</v>
       </c>
       <c r="I36" s="41">
-        <v>474.33</v>
+        <v>659</v>
       </c>
       <c r="J36" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K36" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L36" s="41">
-        <f t="shared" si="1"/>
-        <v>52.703333333333333</v>
+        <f>I36/N36</f>
+        <v>54.916666666666664</v>
       </c>
       <c r="M36" s="41">
-        <f t="shared" si="2"/>
-        <v>52.703333333333333</v>
+        <f>IFERROR(L36/H36,"")</f>
+        <v>54.916666666666664</v>
       </c>
       <c r="N36" s="42">
+        <v>12</v>
+      </c>
+      <c r="O36" s="67">
+        <v>45964</v>
+      </c>
+      <c r="P36" s="67">
+        <f>IF(N36&lt;&gt;1,EDATE(O36,N36-1),"")</f>
+        <v>46298</v>
+      </c>
+      <c r="Q36" s="40">
+        <f ca="1">IF(O36&lt;&gt;"",IFERROR(DATEDIF(O36,TODAY(),"m")+1,""),"")</f>
         <v>9</v>
-      </c>
-      <c r="O36" s="67">
-        <v>46176</v>
-      </c>
-      <c r="P36" s="67">
-        <f t="shared" si="3"/>
-        <v>46421</v>
-      </c>
-      <c r="Q36" s="40">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
       </c>
     </row>
     <row r="37" spans="3:17">
       <c r="C37" s="38"/>
-      <c r="D37" s="49" t="s">
-        <v>87</v>
+      <c r="D37" s="72" t="s">
+        <v>89</v>
       </c>
       <c r="E37" s="40" t="s">
         <v>1</v>
@@ -4625,45 +4656,45 @@
       <c r="F37" s="40"/>
       <c r="G37" s="40"/>
       <c r="H37" s="40">
-        <f t="shared" si="0"/>
+        <f>COUNTA(E37:G37)</f>
         <v>1</v>
       </c>
       <c r="I37" s="41">
-        <v>286.39</v>
+        <v>2319.3000000000002</v>
       </c>
       <c r="J37" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K37" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L37" s="41">
-        <f t="shared" si="1"/>
-        <v>28.638999999999999</v>
+        <f>I37/N37</f>
+        <v>193.27500000000001</v>
       </c>
       <c r="M37" s="41">
-        <f t="shared" si="2"/>
-        <v>28.638999999999999</v>
+        <f>IFERROR(L37/H37,"")</f>
+        <v>193.27500000000001</v>
       </c>
       <c r="N37" s="42">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O37" s="67">
-        <v>46176</v>
+        <v>45964</v>
       </c>
       <c r="P37" s="67">
-        <f t="shared" si="3"/>
-        <v>46449</v>
+        <f>IF(N37&lt;&gt;1,EDATE(O37,N37-1),"")</f>
+        <v>46298</v>
       </c>
       <c r="Q37" s="40">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <f ca="1">IF(O37&lt;&gt;"",IFERROR(DATEDIF(O37,TODAY(),"m")+1,""),"")</f>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="38"/>
-      <c r="D38" s="49" t="s">
-        <v>88</v>
+      <c r="D38" s="72" t="s">
+        <v>90</v>
       </c>
       <c r="E38" s="40" t="s">
         <v>1</v>
@@ -4671,45 +4702,45 @@
       <c r="F38" s="40"/>
       <c r="G38" s="40"/>
       <c r="H38" s="40">
-        <f t="shared" ref="H38:H69" si="6">COUNTA(E38:G38)</f>
+        <f>COUNTA(E38:G38)</f>
         <v>1</v>
       </c>
       <c r="I38" s="41">
-        <v>1181.1400000000001</v>
+        <v>2000</v>
       </c>
       <c r="J38" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K38" s="41" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="L38" s="41">
-        <f t="shared" ref="L38:L69" si="7">I38/N38</f>
-        <v>118.114</v>
+        <f>I38/N38</f>
+        <v>166.66666666666666</v>
       </c>
       <c r="M38" s="41">
-        <f t="shared" ref="M38:M69" si="8">IFERROR(L38/H38,"")</f>
-        <v>118.114</v>
+        <f>IFERROR(L38/H38,"")</f>
+        <v>166.66666666666666</v>
       </c>
       <c r="N38" s="42">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O38" s="67">
-        <v>46206</v>
+        <v>45964</v>
       </c>
       <c r="P38" s="67">
-        <f t="shared" ref="P38:P69" si="9">IF(N38&lt;&gt;1,EDATE(O38,N38-1),"")</f>
-        <v>46480</v>
+        <f>IF(N38&lt;&gt;1,EDATE(O38,N38-1),"")</f>
+        <v>46298</v>
       </c>
       <c r="Q38" s="40">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <f ca="1">IF(O38&lt;&gt;"",IFERROR(DATEDIF(O38,TODAY(),"m")+1,""),"")</f>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="3:17">
       <c r="C39" s="38"/>
-      <c r="D39" s="49" t="s">
-        <v>89</v>
+      <c r="D39" s="72" t="s">
+        <v>92</v>
       </c>
       <c r="E39" s="40" t="s">
         <v>1</v>
@@ -4719,47 +4750,45 @@
       </c>
       <c r="G39" s="40"/>
       <c r="H39" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E39:G39)</f>
         <v>2</v>
       </c>
       <c r="I39" s="41">
-        <v>224.24</v>
+        <v>725</v>
       </c>
       <c r="J39" s="41" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K39" s="41" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L39" s="41">
-        <f t="shared" si="7"/>
-        <v>18.686666666666667</v>
+        <f>I39/N39</f>
+        <v>120.83333333333333</v>
       </c>
       <c r="M39" s="41">
-        <f t="shared" si="8"/>
-        <v>9.3433333333333337</v>
+        <f>IFERROR(L39/H39,"")</f>
+        <v>60.416666666666664</v>
       </c>
       <c r="N39" s="42">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O39" s="67">
-        <v>46176</v>
+        <v>46145</v>
       </c>
       <c r="P39" s="67">
-        <f t="shared" si="9"/>
-        <v>46510</v>
+        <f>IF(N39&lt;&gt;1,EDATE(O39,N39-1),"")</f>
+        <v>46298</v>
       </c>
       <c r="Q39" s="40">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <f ca="1">IF(O39&lt;&gt;"",IFERROR(DATEDIF(O39,TODAY(),"m")+1,""),"")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="3:17">
-      <c r="C40" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="49" t="s">
-        <v>92</v>
+      <c r="C40" s="38"/>
+      <c r="D40" s="72" t="s">
+        <v>93</v>
       </c>
       <c r="E40" s="40" t="s">
         <v>1</v>
@@ -4767,223 +4796,223 @@
       <c r="F40" s="40"/>
       <c r="G40" s="40"/>
       <c r="H40" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E40:G40)</f>
         <v>1</v>
       </c>
       <c r="I40" s="41">
-        <v>279</v>
+        <v>372.43</v>
       </c>
       <c r="J40" s="41" t="s">
         <v>44</v>
       </c>
       <c r="K40" s="41" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="L40" s="41">
-        <f t="shared" si="7"/>
-        <v>27.9</v>
+        <f>I40/N40</f>
+        <v>93.107500000000002</v>
       </c>
       <c r="M40" s="41">
-        <f t="shared" si="8"/>
-        <v>27.9</v>
+        <f>IFERROR(L40/H40,"")</f>
+        <v>93.107500000000002</v>
       </c>
       <c r="N40" s="42">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O40" s="67">
-        <v>46237</v>
+        <v>46206</v>
       </c>
       <c r="P40" s="67">
-        <f t="shared" si="9"/>
-        <v>46510</v>
-      </c>
-      <c r="Q40" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
+        <f>IF(N40&lt;&gt;1,EDATE(O40,N40-1),"")</f>
+        <v>46298</v>
+      </c>
+      <c r="Q40" s="40">
+        <f ca="1">IF(O40&lt;&gt;"",IFERROR(DATEDIF(O40,TODAY(),"m")+1,""),"")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="3:17">
       <c r="C41" s="38"/>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="72" t="s">
         <v>94</v>
       </c>
       <c r="E41" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F41" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F41" s="40"/>
       <c r="G41" s="40"/>
       <c r="H41" s="40">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>COUNTA(E41:G41)</f>
+        <v>1</v>
       </c>
       <c r="I41" s="41">
-        <v>22.45</v>
+        <v>72</v>
       </c>
       <c r="J41" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K41" s="40" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="K41" s="41" t="s">
+        <v>72</v>
       </c>
       <c r="L41" s="41">
-        <f t="shared" si="7"/>
-        <v>22.45</v>
+        <f>I41/N41</f>
+        <v>24</v>
       </c>
       <c r="M41" s="41">
-        <f t="shared" si="8"/>
-        <v>11.225</v>
+        <f>IFERROR(L41/H41,"")</f>
+        <v>24</v>
       </c>
       <c r="N41" s="42">
-        <v>1</v>
-      </c>
-      <c r="O41" s="67"/>
-      <c r="P41" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="O41" s="67">
+        <v>46240</v>
+      </c>
+      <c r="P41" s="67">
+        <f>IF(N41&lt;&gt;1,EDATE(O41,N41-1),"")</f>
+        <v>46301</v>
       </c>
       <c r="Q41" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(O41&lt;&gt;"",IFERROR(DATEDIF(O41,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="38"/>
-      <c r="D42" s="49" t="s">
+      <c r="D42" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="E42" s="40" t="s">
-        <v>1</v>
-      </c>
+      <c r="E42" s="40"/>
       <c r="F42" s="40" t="s">
         <v>2</v>
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>COUNTA(E42:G42)</f>
+        <v>1</v>
       </c>
       <c r="I42" s="41">
-        <v>60</v>
+        <v>161.72999999999999</v>
       </c>
       <c r="J42" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K42" s="40" t="s">
-        <v>54</v>
+        <v>44</v>
+      </c>
+      <c r="K42" s="41" t="s">
+        <v>72</v>
       </c>
       <c r="L42" s="41">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f>I42/N42</f>
+        <v>53.91</v>
       </c>
       <c r="M42" s="41">
-        <f t="shared" si="8"/>
-        <v>30</v>
+        <f>IFERROR(L42/H42,"")</f>
+        <v>53.91</v>
       </c>
       <c r="N42" s="42">
-        <v>1</v>
-      </c>
-      <c r="O42" s="67"/>
-      <c r="P42" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="O42" s="67">
+        <v>46240</v>
+      </c>
+      <c r="P42" s="67">
+        <f>IF(N42&lt;&gt;1,EDATE(O42,N42-1),"")</f>
+        <v>46301</v>
       </c>
       <c r="Q42" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(O42&lt;&gt;"",IFERROR(DATEDIF(O42,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="38"/>
-      <c r="D43" s="39" t="s">
+      <c r="D43" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="E43" s="40" t="s">
-        <v>1</v>
-      </c>
+      <c r="E43" s="40"/>
       <c r="F43" s="40" t="s">
         <v>2</v>
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>COUNTA(E43:G43)</f>
+        <v>1</v>
       </c>
       <c r="I43" s="41">
-        <v>395.54</v>
+        <v>973.02</v>
       </c>
       <c r="J43" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K43" s="40" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="K43" s="41" t="s">
+        <v>91</v>
       </c>
       <c r="L43" s="41">
-        <f t="shared" si="7"/>
-        <v>395.54</v>
+        <f>I43/N43</f>
+        <v>81.084999999999994</v>
       </c>
       <c r="M43" s="41">
-        <f t="shared" si="8"/>
-        <v>197.77</v>
+        <f>IFERROR(L43/H43,"")</f>
+        <v>81.084999999999994</v>
       </c>
       <c r="N43" s="42">
-        <v>1</v>
-      </c>
-      <c r="O43" s="67"/>
-      <c r="P43" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q43" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>12</v>
+      </c>
+      <c r="O43" s="67">
+        <v>45994</v>
+      </c>
+      <c r="P43" s="67">
+        <f>IF(N43&lt;&gt;1,EDATE(O43,N43-1),"")</f>
+        <v>46329</v>
+      </c>
+      <c r="Q43" s="40">
+        <f ca="1">IF(O43&lt;&gt;"",IFERROR(DATEDIF(O43,TODAY(),"m")+1,""),"")</f>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="38"/>
-      <c r="D44" s="39" t="s">
+      <c r="D44" s="49" t="s">
         <v>97</v>
       </c>
       <c r="E44" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F44" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F44" s="40"/>
       <c r="G44" s="40"/>
       <c r="H44" s="40">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>COUNTA(E44:G44)</f>
+        <v>1</v>
       </c>
       <c r="I44" s="41">
-        <v>215</v>
+        <v>379</v>
       </c>
       <c r="J44" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K44" s="40" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="K44" s="41" t="s">
+        <v>72</v>
       </c>
       <c r="L44" s="41">
-        <f t="shared" si="7"/>
-        <v>215</v>
+        <f>I44/N44</f>
+        <v>54.142857142857146</v>
       </c>
       <c r="M44" s="41">
-        <f t="shared" si="8"/>
-        <v>107.5</v>
+        <f>IFERROR(L44/H44,"")</f>
+        <v>54.142857142857146</v>
       </c>
       <c r="N44" s="42">
-        <v>1</v>
-      </c>
-      <c r="O44" s="67"/>
-      <c r="P44" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q44" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="O44" s="67">
+        <v>46145</v>
+      </c>
+      <c r="P44" s="67">
+        <f>IF(N44&lt;&gt;1,EDATE(O44,N44-1),"")</f>
+        <v>46329</v>
+      </c>
+      <c r="Q44" s="40">
+        <f ca="1">IF(O44&lt;&gt;"",IFERROR(DATEDIF(O44,TODAY(),"m")+1,""),"")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="3:17">
@@ -4994,47 +5023,47 @@
       <c r="E45" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F45" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F45" s="40"/>
       <c r="G45" s="40"/>
       <c r="H45" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E45:G45)</f>
+        <v>1</v>
+      </c>
+      <c r="I45" s="41">
+        <v>297</v>
+      </c>
+      <c r="J45" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="K45" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="L45" s="41">
+        <f>I45/N45</f>
+        <v>49.5</v>
+      </c>
+      <c r="M45" s="41">
+        <f>IFERROR(L45/H45,"")</f>
+        <v>49.5</v>
+      </c>
+      <c r="N45" s="42">
+        <v>6</v>
+      </c>
+      <c r="O45" s="67">
+        <v>46176</v>
+      </c>
+      <c r="P45" s="67">
+        <f>IF(N45&lt;&gt;1,EDATE(O45,N45-1),"")</f>
+        <v>46329</v>
+      </c>
+      <c r="Q45" s="40">
+        <f ca="1">IF(O45&lt;&gt;"",IFERROR(DATEDIF(O45,TODAY(),"m")+1,""),"")</f>
         <v>2</v>
-      </c>
-      <c r="I45" s="41">
-        <v>225</v>
-      </c>
-      <c r="J45" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K45" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="L45" s="41">
-        <f t="shared" si="7"/>
-        <v>225</v>
-      </c>
-      <c r="M45" s="41">
-        <f t="shared" si="8"/>
-        <v>112.5</v>
-      </c>
-      <c r="N45" s="42">
-        <v>1</v>
-      </c>
-      <c r="O45" s="67"/>
-      <c r="P45" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q45" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
       </c>
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="38"/>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="49" t="s">
         <v>99</v>
       </c>
       <c r="E46" s="40" t="s">
@@ -5045,38 +5074,37 @@
       </c>
       <c r="G46" s="40"/>
       <c r="H46" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E46:G46)</f>
         <v>2</v>
       </c>
       <c r="I46" s="41">
-        <v>166.15</v>
+        <v>506</v>
       </c>
       <c r="J46" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K46" s="40" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="K46" s="41" t="s">
+        <v>72</v>
       </c>
       <c r="L46" s="41">
-        <f t="shared" si="7"/>
-        <v>166.15</v>
+        <f>I46/N46</f>
+        <v>50.6</v>
       </c>
       <c r="M46" s="41">
-        <f t="shared" si="8"/>
-        <v>83.075000000000003</v>
+        <f>IFERROR(L46/H46,"")</f>
+        <v>25.3</v>
       </c>
       <c r="N46" s="42">
-        <v>1</v>
-      </c>
-      <c r="O46" s="67"/>
-      <c r="P46" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q46" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="O46" s="67">
+        <v>46115</v>
+      </c>
+      <c r="P46" s="67">
+        <f>IF(N46&lt;&gt;1,EDATE(O46,N46-1),"")</f>
+        <v>46390</v>
+      </c>
+      <c r="Q46" s="40"/>
     </row>
     <row r="47" spans="3:17">
       <c r="C47" s="38"/>
@@ -5089,37 +5117,39 @@
       <c r="F47" s="40"/>
       <c r="G47" s="40"/>
       <c r="H47" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E47:G47)</f>
         <v>1</v>
       </c>
       <c r="I47" s="41">
-        <v>284.05</v>
+        <v>399.9</v>
       </c>
       <c r="J47" s="41" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K47" s="41" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="L47" s="41">
-        <f t="shared" si="7"/>
-        <v>284.05</v>
+        <f>I47/N47</f>
+        <v>57.128571428571426</v>
       </c>
       <c r="M47" s="41">
-        <f t="shared" si="8"/>
-        <v>284.05</v>
+        <f>IFERROR(L47/H47,"")</f>
+        <v>57.128571428571426</v>
       </c>
       <c r="N47" s="42">
-        <v>1</v>
-      </c>
-      <c r="O47" s="67"/>
-      <c r="P47" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q47" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="O47" s="67">
+        <v>46206</v>
+      </c>
+      <c r="P47" s="67">
+        <f>IF(N47&lt;&gt;1,EDATE(O47,N47-1),"")</f>
+        <v>46390</v>
+      </c>
+      <c r="Q47" s="40">
+        <f ca="1">IF(O47&lt;&gt;"",IFERROR(DATEDIF(O47,TODAY(),"m")+1,""),"")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="3:17">
@@ -5127,42 +5157,42 @@
       <c r="D48" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="40" t="s">
-        <v>1</v>
-      </c>
+      <c r="E48" s="40"/>
       <c r="F48" s="40"/>
       <c r="G48" s="40"/>
       <c r="H48" s="40">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <f>COUNTA(E48:G48)</f>
+        <v>0</v>
       </c>
       <c r="I48" s="41">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="J48" s="41" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K48" s="41" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="L48" s="41">
-        <f t="shared" si="7"/>
-        <v>110</v>
-      </c>
-      <c r="M48" s="41">
-        <f t="shared" si="8"/>
-        <v>110</v>
+        <f>I48/N48</f>
+        <v>50</v>
+      </c>
+      <c r="M48" s="41" t="str">
+        <f>IFERROR(L48/H48,"")</f>
+        <v/>
       </c>
       <c r="N48" s="42">
-        <v>1</v>
-      </c>
-      <c r="O48" s="67"/>
-      <c r="P48" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="O48" s="67">
+        <v>46237</v>
+      </c>
+      <c r="P48" s="67">
+        <f>IF(N48&lt;&gt;1,EDATE(O48,N48-1),"")</f>
+        <v>46390</v>
       </c>
       <c r="Q48" s="40" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">IF(O48&lt;&gt;"",IFERROR(DATEDIF(O48,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -5177,86 +5207,91 @@
       <c r="F49" s="40"/>
       <c r="G49" s="40"/>
       <c r="H49" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E49:G49)</f>
         <v>1</v>
       </c>
       <c r="I49" s="41">
-        <v>117</v>
+        <v>284</v>
       </c>
       <c r="J49" s="41" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K49" s="41" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="L49" s="41">
-        <f t="shared" si="7"/>
-        <v>117</v>
+        <f>I49/N49</f>
+        <v>47.333333333333336</v>
       </c>
       <c r="M49" s="41">
-        <f t="shared" si="8"/>
-        <v>117</v>
+        <f>IFERROR(L49/H49,"")</f>
+        <v>47.333333333333336</v>
       </c>
       <c r="N49" s="42">
-        <v>1</v>
-      </c>
-      <c r="O49" s="67"/>
-      <c r="P49" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q49" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="O49" s="67">
+        <v>46237</v>
+      </c>
+      <c r="P49" s="67">
+        <f>IF(N49&lt;&gt;1,EDATE(O49,N49-1),"")</f>
+        <v>46390</v>
+      </c>
+      <c r="Q49" s="40" t="str">
+        <f ca="1">IF(O49&lt;&gt;"",IFERROR(DATEDIF(O49,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50" spans="3:17">
       <c r="C50" s="38"/>
-      <c r="D50" s="39" t="s">
-        <v>104</v>
+      <c r="D50" s="49" t="s">
+        <v>103</v>
       </c>
       <c r="E50" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F50" s="40"/>
       <c r="G50" s="40"/>
       <c r="H50" s="40">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>COUNTA(E50:G50)</f>
+        <v>1</v>
       </c>
       <c r="I50" s="41">
-        <v>19.899999999999999</v>
+        <v>1900</v>
       </c>
       <c r="J50" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K50" s="40" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="K50" s="41" t="s">
+        <v>72</v>
       </c>
       <c r="L50" s="41">
-        <f t="shared" si="7"/>
-        <v>19.899999999999999</v>
+        <f>I50/N50</f>
+        <v>190</v>
       </c>
       <c r="M50" s="41">
-        <f t="shared" si="8"/>
-        <v>9.9499999999999993</v>
+        <f>IFERROR(L50/H50,"")</f>
+        <v>190</v>
       </c>
       <c r="N50" s="42">
-        <v>1</v>
-      </c>
-      <c r="O50" s="67"/>
-      <c r="P50" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q50" s="40" t="str">
+        <v>10</v>
+      </c>
+      <c r="O50" s="67">
+        <v>46145</v>
+      </c>
+      <c r="P50" s="67">
+        <f>IF(N50&lt;&gt;1,EDATE(O50,N50-1),"")</f>
+        <v>46421</v>
+      </c>
+      <c r="Q50" s="40">
         <f ca="1">IF(O50&lt;&gt;"",IFERROR(DATEDIF(O50,TODAY(),"m")+1,""),"")</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="3:17">
       <c r="C51" s="38"/>
-      <c r="D51" s="39" t="s">
-        <v>105</v>
+      <c r="D51" s="49" t="s">
+        <v>104</v>
       </c>
       <c r="E51" s="40" t="s">
         <v>1</v>
@@ -5264,43 +5299,45 @@
       <c r="F51" s="40"/>
       <c r="G51" s="40"/>
       <c r="H51" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E51:G51)</f>
         <v>1</v>
       </c>
       <c r="I51" s="41">
-        <v>26.9</v>
+        <v>474.33</v>
       </c>
       <c r="J51" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K51" s="40" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="K51" s="41" t="s">
+        <v>72</v>
       </c>
       <c r="L51" s="41">
-        <f t="shared" si="7"/>
-        <v>26.9</v>
+        <f>I51/N51</f>
+        <v>52.703333333333333</v>
       </c>
       <c r="M51" s="41">
-        <f t="shared" si="8"/>
-        <v>26.9</v>
+        <f>IFERROR(L51/H51,"")</f>
+        <v>52.703333333333333</v>
       </c>
       <c r="N51" s="42">
-        <v>1</v>
-      </c>
-      <c r="O51" s="67"/>
-      <c r="P51" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q51" s="40" t="str">
+        <v>9</v>
+      </c>
+      <c r="O51" s="67">
+        <v>46176</v>
+      </c>
+      <c r="P51" s="67">
+        <f>IF(N51&lt;&gt;1,EDATE(O51,N51-1),"")</f>
+        <v>46421</v>
+      </c>
+      <c r="Q51" s="40">
         <f ca="1">IF(O51&lt;&gt;"",IFERROR(DATEDIF(O51,TODAY(),"m")+1,""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="38"/>
       <c r="D52" s="49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E52" s="40" t="s">
         <v>1</v>
@@ -5308,40 +5345,45 @@
       <c r="F52" s="40"/>
       <c r="G52" s="40"/>
       <c r="H52" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E52:G52)</f>
         <v>1</v>
       </c>
       <c r="I52" s="41">
-        <v>70</v>
+        <v>286.39</v>
       </c>
       <c r="J52" s="41" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K52" s="41" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="L52" s="41">
-        <f t="shared" si="7"/>
-        <v>70</v>
+        <f>I52/N52</f>
+        <v>28.638999999999999</v>
       </c>
       <c r="M52" s="41">
-        <f t="shared" si="8"/>
-        <v>70</v>
+        <f>IFERROR(L52/H52,"")</f>
+        <v>28.638999999999999</v>
       </c>
       <c r="N52" s="42">
-        <v>1</v>
-      </c>
-      <c r="O52" s="67"/>
-      <c r="P52" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q52" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="O52" s="67">
+        <v>46176</v>
+      </c>
+      <c r="P52" s="67">
+        <f>IF(N52&lt;&gt;1,EDATE(O52,N52-1),"")</f>
+        <v>46449</v>
+      </c>
+      <c r="Q52" s="40">
+        <f ca="1">IF(O52&lt;&gt;"",IFERROR(DATEDIF(O52,TODAY(),"m")+1,""),"")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="53" spans="3:17">
       <c r="C53" s="38"/>
-      <c r="D53" s="70" t="s">
-        <v>107</v>
+      <c r="D53" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="E53" s="40" t="s">
         <v>1</v>
@@ -5349,91 +5391,93 @@
       <c r="F53" s="40"/>
       <c r="G53" s="40"/>
       <c r="H53" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E53:G53)</f>
         <v>1</v>
       </c>
       <c r="I53" s="41">
-        <v>400</v>
+        <v>1181.1400000000001</v>
       </c>
       <c r="J53" s="41" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K53" s="41" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="L53" s="41">
-        <f t="shared" si="7"/>
-        <v>400</v>
+        <f>I53/N53</f>
+        <v>118.114</v>
       </c>
       <c r="M53" s="41">
-        <f t="shared" si="8"/>
-        <v>400</v>
+        <f>IFERROR(L53/H53,"")</f>
+        <v>118.114</v>
       </c>
       <c r="N53" s="42">
-        <v>1</v>
-      </c>
-      <c r="O53" s="67"/>
-      <c r="P53" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q53" s="40" t="str">
-        <f t="shared" ref="Q53:Q84" ca="1" si="10">IF(O53&lt;&gt;"",IFERROR(DATEDIF(O53,TODAY(),"m")+1,""),"")</f>
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="O53" s="67">
+        <v>46206</v>
+      </c>
+      <c r="P53" s="67">
+        <f>IF(N53&lt;&gt;1,EDATE(O53,N53-1),"")</f>
+        <v>46480</v>
+      </c>
+      <c r="Q53" s="40">
+        <f ca="1">IF(O53&lt;&gt;"",IFERROR(DATEDIF(O53,TODAY(),"m")+1,""),"")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="3:17">
-      <c r="C54" s="38"/>
+      <c r="C54" s="38" t="s">
+        <v>107</v>
+      </c>
       <c r="D54" s="49" t="s">
         <v>108</v>
       </c>
       <c r="E54" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F54" s="40" t="s">
-        <v>2</v>
-      </c>
+      <c r="F54" s="40"/>
       <c r="G54" s="40"/>
       <c r="H54" s="40">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>COUNTA(E54:G54)</f>
+        <v>1</v>
       </c>
       <c r="I54" s="41">
-        <v>22</v>
+        <v>279</v>
       </c>
       <c r="J54" s="41" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K54" s="41" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="L54" s="41">
-        <f t="shared" si="7"/>
-        <v>22</v>
+        <f>I54/N54</f>
+        <v>27.9</v>
       </c>
       <c r="M54" s="41">
-        <f t="shared" si="8"/>
-        <v>11</v>
+        <f>IFERROR(L54/H54,"")</f>
+        <v>27.9</v>
       </c>
       <c r="N54" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O54" s="67">
-        <v>46206</v>
-      </c>
-      <c r="P54" s="67" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q54" s="40">
-        <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>46237</v>
+      </c>
+      <c r="P54" s="67">
+        <f>IF(N54&lt;&gt;1,EDATE(O54,N54-1),"")</f>
+        <v>46510</v>
+      </c>
+      <c r="Q54" s="40" t="str">
+        <f ca="1">IF(O54&lt;&gt;"",IFERROR(DATEDIF(O54,TODAY(),"m")+1,""),"")</f>
+        <v/>
       </c>
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="38"/>
       <c r="D55" s="49" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E55" s="40" t="s">
         <v>1</v>
@@ -5441,7 +5485,7 @@
       <c r="F55" s="40"/>
       <c r="G55" s="40"/>
       <c r="H55" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E55:G55)</f>
         <v>1</v>
       </c>
       <c r="I55" s="41">
@@ -5451,14 +5495,14 @@
         <v>44</v>
       </c>
       <c r="K55" s="41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L55" s="41">
-        <f t="shared" si="7"/>
+        <f>I55/N55</f>
         <v>-41.9</v>
       </c>
       <c r="M55" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L55/H55,"")</f>
         <v>-41.9</v>
       </c>
       <c r="N55" s="42">
@@ -5468,18 +5512,18 @@
         <v>45994</v>
       </c>
       <c r="P55" s="67">
-        <f t="shared" si="9"/>
+        <f>IF(N55&lt;&gt;1,EDATE(O55,N55-1),"")</f>
         <v>46268</v>
       </c>
       <c r="Q55" s="40">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O55&lt;&gt;"",IFERROR(DATEDIF(O55,TODAY(),"m")+1,""),"")</f>
         <v>8</v>
       </c>
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="38"/>
       <c r="D56" s="49" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E56" s="40" t="s">
         <v>1</v>
@@ -5487,7 +5531,7 @@
       <c r="F56" s="40"/>
       <c r="G56" s="40"/>
       <c r="H56" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E56:G56)</f>
         <v>1</v>
       </c>
       <c r="I56" s="41">
@@ -5498,14 +5542,14 @@
         <v>44</v>
       </c>
       <c r="K56" s="41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L56" s="41">
-        <f t="shared" si="7"/>
+        <f>I56/N56</f>
         <v>-64.42</v>
       </c>
       <c r="M56" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L56/H56,"")</f>
         <v>-64.42</v>
       </c>
       <c r="N56" s="42">
@@ -5515,18 +5559,18 @@
         <v>45964</v>
       </c>
       <c r="P56" s="67">
-        <f t="shared" si="9"/>
+        <f>IF(N56&lt;&gt;1,EDATE(O56,N56-1),"")</f>
         <v>46298</v>
       </c>
       <c r="Q56" s="40">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O56&lt;&gt;"",IFERROR(DATEDIF(O56,TODAY(),"m")+1,""),"")</f>
         <v>9</v>
       </c>
     </row>
     <row r="57" spans="3:17">
       <c r="C57" s="38"/>
       <c r="D57" s="49" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E57" s="40" t="s">
         <v>1</v>
@@ -5534,24 +5578,24 @@
       <c r="F57" s="40"/>
       <c r="G57" s="40"/>
       <c r="H57" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E57:G57)</f>
         <v>1</v>
       </c>
       <c r="I57" s="41">
         <v>55</v>
       </c>
       <c r="J57" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K57" s="41" t="s">
         <v>45</v>
       </c>
       <c r="L57" s="41">
-        <f t="shared" si="7"/>
+        <f>I57/N57</f>
         <v>55</v>
       </c>
       <c r="M57" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L57/H57,"")</f>
         <v>55</v>
       </c>
       <c r="N57" s="42">
@@ -5561,18 +5605,18 @@
         <v>46237</v>
       </c>
       <c r="P57" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N57&lt;&gt;1,EDATE(O57,N57-1),"")</f>
         <v/>
       </c>
       <c r="Q57" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O57&lt;&gt;"",IFERROR(DATEDIF(O57,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="38"/>
       <c r="D58" s="49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E58" s="40" t="s">
         <v>1</v>
@@ -5580,24 +5624,24 @@
       <c r="F58" s="40"/>
       <c r="G58" s="40"/>
       <c r="H58" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E58:G58)</f>
         <v>1</v>
       </c>
       <c r="I58" s="41">
         <v>498</v>
       </c>
       <c r="J58" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K58" s="41" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="L58" s="41">
-        <f t="shared" si="7"/>
+        <f>I58/N58</f>
         <v>498</v>
       </c>
       <c r="M58" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L58/H58,"")</f>
         <v>498</v>
       </c>
       <c r="N58" s="42">
@@ -5605,18 +5649,18 @@
       </c>
       <c r="O58" s="67"/>
       <c r="P58" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N58&lt;&gt;1,EDATE(O58,N58-1),"")</f>
         <v/>
       </c>
       <c r="Q58" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O58&lt;&gt;"",IFERROR(DATEDIF(O58,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="38"/>
       <c r="D59" s="49" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E59" s="40" t="s">
         <v>1</v>
@@ -5626,24 +5670,24 @@
       </c>
       <c r="G59" s="40"/>
       <c r="H59" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E59:G59)</f>
         <v>2</v>
       </c>
       <c r="I59" s="41">
         <v>40</v>
       </c>
       <c r="J59" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K59" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L59" s="41">
-        <f t="shared" si="7"/>
+        <f>I59/N59</f>
         <v>40</v>
       </c>
       <c r="M59" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L59/H59,"")</f>
         <v>20</v>
       </c>
       <c r="N59" s="42">
@@ -5651,18 +5695,18 @@
       </c>
       <c r="O59" s="67"/>
       <c r="P59" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N59&lt;&gt;1,EDATE(O59,N59-1),"")</f>
         <v/>
       </c>
       <c r="Q59" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O59&lt;&gt;"",IFERROR(DATEDIF(O59,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="60" spans="3:17">
       <c r="C60" s="38"/>
       <c r="D60" s="49" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E60" s="40" t="s">
         <v>1</v>
@@ -5670,24 +5714,24 @@
       <c r="F60" s="40"/>
       <c r="G60" s="40"/>
       <c r="H60" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E60:G60)</f>
         <v>1</v>
       </c>
       <c r="I60" s="41">
         <v>32</v>
       </c>
       <c r="J60" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K60" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L60" s="41">
-        <f t="shared" si="7"/>
+        <f>I60/N60</f>
         <v>32</v>
       </c>
       <c r="M60" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L60/H60,"")</f>
         <v>32</v>
       </c>
       <c r="N60" s="42">
@@ -5695,18 +5739,18 @@
       </c>
       <c r="O60" s="67"/>
       <c r="P60" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N60&lt;&gt;1,EDATE(O60,N60-1),"")</f>
         <v/>
       </c>
       <c r="Q60" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O60&lt;&gt;"",IFERROR(DATEDIF(O60,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="61" spans="3:17">
       <c r="C61" s="38"/>
       <c r="D61" s="49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E61" s="40"/>
       <c r="F61" s="40" t="s">
@@ -5714,24 +5758,24 @@
       </c>
       <c r="G61" s="40"/>
       <c r="H61" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E61:G61)</f>
         <v>1</v>
       </c>
       <c r="I61" s="41">
         <v>166</v>
       </c>
       <c r="J61" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K61" s="41" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="L61" s="41">
-        <f t="shared" si="7"/>
+        <f>I61/N61</f>
         <v>166</v>
       </c>
       <c r="M61" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L61/H61,"")</f>
         <v>166</v>
       </c>
       <c r="N61" s="42">
@@ -5739,18 +5783,18 @@
       </c>
       <c r="O61" s="67"/>
       <c r="P61" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N61&lt;&gt;1,EDATE(O61,N61-1),"")</f>
         <v/>
       </c>
       <c r="Q61" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O61&lt;&gt;"",IFERROR(DATEDIF(O61,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="38"/>
       <c r="D62" s="49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E62" s="40" t="s">
         <v>1</v>
@@ -5760,24 +5804,24 @@
       </c>
       <c r="G62" s="40"/>
       <c r="H62" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E62:G62)</f>
         <v>2</v>
       </c>
       <c r="I62" s="41">
         <v>74</v>
       </c>
       <c r="J62" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K62" s="41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L62" s="41">
-        <f t="shared" si="7"/>
+        <f>I62/N62</f>
         <v>74</v>
       </c>
       <c r="M62" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L62/H62,"")</f>
         <v>37</v>
       </c>
       <c r="N62" s="42">
@@ -5785,18 +5829,18 @@
       </c>
       <c r="O62" s="67"/>
       <c r="P62" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N62&lt;&gt;1,EDATE(O62,N62-1),"")</f>
         <v/>
       </c>
       <c r="Q62" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O62&lt;&gt;"",IFERROR(DATEDIF(O62,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="38"/>
       <c r="D63" s="49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E63" s="40" t="s">
         <v>1</v>
@@ -5804,24 +5848,24 @@
       <c r="F63" s="40"/>
       <c r="G63" s="40"/>
       <c r="H63" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E63:G63)</f>
         <v>1</v>
       </c>
       <c r="I63" s="41">
         <v>-37</v>
       </c>
       <c r="J63" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K63" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L63" s="41">
-        <f t="shared" si="7"/>
+        <f>I63/N63</f>
         <v>-37</v>
       </c>
       <c r="M63" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L63/H63,"")</f>
         <v>-37</v>
       </c>
       <c r="N63" s="42">
@@ -5829,18 +5873,18 @@
       </c>
       <c r="O63" s="67"/>
       <c r="P63" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N63&lt;&gt;1,EDATE(O63,N63-1),"")</f>
         <v/>
       </c>
       <c r="Q63" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O63&lt;&gt;"",IFERROR(DATEDIF(O63,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="38"/>
       <c r="D64" s="49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E64" s="40" t="s">
         <v>1</v>
@@ -5850,24 +5894,24 @@
       </c>
       <c r="G64" s="40"/>
       <c r="H64" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E64:G64)</f>
         <v>2</v>
       </c>
       <c r="I64" s="41">
         <v>36</v>
       </c>
       <c r="J64" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K64" s="41" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="L64" s="41">
-        <f t="shared" si="7"/>
+        <f>I64/N64</f>
         <v>36</v>
       </c>
       <c r="M64" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L64/H64,"")</f>
         <v>18</v>
       </c>
       <c r="N64" s="42">
@@ -5875,18 +5919,18 @@
       </c>
       <c r="O64" s="67"/>
       <c r="P64" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N64&lt;&gt;1,EDATE(O64,N64-1),"")</f>
         <v/>
       </c>
       <c r="Q64" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O64&lt;&gt;"",IFERROR(DATEDIF(O64,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="65" spans="3:17">
       <c r="C65" s="38"/>
       <c r="D65" s="49" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E65" s="40" t="s">
         <v>1</v>
@@ -5894,24 +5938,24 @@
       <c r="F65" s="40"/>
       <c r="G65" s="40"/>
       <c r="H65" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E65:G65)</f>
         <v>1</v>
       </c>
       <c r="I65" s="41">
         <v>35</v>
       </c>
       <c r="J65" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K65" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L65" s="41">
-        <f t="shared" si="7"/>
+        <f>I65/N65</f>
         <v>35</v>
       </c>
       <c r="M65" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L65/H65,"")</f>
         <v>35</v>
       </c>
       <c r="N65" s="42">
@@ -5919,18 +5963,18 @@
       </c>
       <c r="O65" s="67"/>
       <c r="P65" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N65&lt;&gt;1,EDATE(O65,N65-1),"")</f>
         <v/>
       </c>
       <c r="Q65" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O65&lt;&gt;"",IFERROR(DATEDIF(O65,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="38"/>
       <c r="D66" s="49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E66" s="40" t="s">
         <v>1</v>
@@ -5940,24 +5984,24 @@
       </c>
       <c r="G66" s="40"/>
       <c r="H66" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E66:G66)</f>
         <v>2</v>
       </c>
       <c r="I66" s="41">
         <v>75</v>
       </c>
       <c r="J66" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K66" s="41" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="L66" s="41">
-        <f t="shared" si="7"/>
+        <f>I66/N66</f>
         <v>75</v>
       </c>
       <c r="M66" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L66/H66,"")</f>
         <v>37.5</v>
       </c>
       <c r="N66" s="42">
@@ -5965,18 +6009,18 @@
       </c>
       <c r="O66" s="67"/>
       <c r="P66" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N66&lt;&gt;1,EDATE(O66,N66-1),"")</f>
         <v/>
       </c>
       <c r="Q66" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O66&lt;&gt;"",IFERROR(DATEDIF(O66,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="67" spans="3:17">
       <c r="C67" s="38"/>
       <c r="D67" s="49" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E67" s="40" t="s">
         <v>1</v>
@@ -5986,24 +6030,24 @@
       </c>
       <c r="G67" s="40"/>
       <c r="H67" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E67:G67)</f>
         <v>2</v>
       </c>
       <c r="I67" s="41">
         <v>74</v>
       </c>
       <c r="J67" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K67" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L67" s="41">
-        <f t="shared" si="7"/>
+        <f>I67/N67</f>
         <v>74</v>
       </c>
       <c r="M67" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L67/H67,"")</f>
         <v>37</v>
       </c>
       <c r="N67" s="42">
@@ -6011,18 +6055,18 @@
       </c>
       <c r="O67" s="67"/>
       <c r="P67" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N67&lt;&gt;1,EDATE(O67,N67-1),"")</f>
         <v/>
       </c>
       <c r="Q67" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O67&lt;&gt;"",IFERROR(DATEDIF(O67,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="38"/>
       <c r="D68" s="49" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E68" s="40"/>
       <c r="F68" s="40" t="s">
@@ -6030,24 +6074,24 @@
       </c>
       <c r="G68" s="40"/>
       <c r="H68" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E68:G68)</f>
         <v>1</v>
       </c>
       <c r="I68" s="41">
         <v>107.5</v>
       </c>
       <c r="J68" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K68" s="41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L68" s="41">
-        <f t="shared" si="7"/>
+        <f>I68/N68</f>
         <v>107.5</v>
       </c>
       <c r="M68" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L68/H68,"")</f>
         <v>107.5</v>
       </c>
       <c r="N68" s="42">
@@ -6055,18 +6099,18 @@
       </c>
       <c r="O68" s="67"/>
       <c r="P68" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N68&lt;&gt;1,EDATE(O68,N68-1),"")</f>
         <v/>
       </c>
       <c r="Q68" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O68&lt;&gt;"",IFERROR(DATEDIF(O68,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="38"/>
       <c r="D69" s="49" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E69" s="40" t="s">
         <v>1</v>
@@ -6074,24 +6118,24 @@
       <c r="F69" s="40"/>
       <c r="G69" s="40"/>
       <c r="H69" s="40">
-        <f t="shared" si="6"/>
+        <f>COUNTA(E69:G69)</f>
         <v>1</v>
       </c>
       <c r="I69" s="41">
         <v>37.5</v>
       </c>
       <c r="J69" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K69" s="41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L69" s="41">
-        <f t="shared" si="7"/>
+        <f>I69/N69</f>
         <v>37.5</v>
       </c>
       <c r="M69" s="41">
-        <f t="shared" si="8"/>
+        <f>IFERROR(L69/H69,"")</f>
         <v>37.5</v>
       </c>
       <c r="N69" s="42">
@@ -6099,18 +6143,18 @@
       </c>
       <c r="O69" s="67"/>
       <c r="P69" s="67" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(N69&lt;&gt;1,EDATE(O69,N69-1),"")</f>
         <v/>
       </c>
       <c r="Q69" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O69&lt;&gt;"",IFERROR(DATEDIF(O69,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="70" spans="3:17">
       <c r="C70" s="38"/>
       <c r="D70" s="49" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E70" s="40" t="s">
         <v>1</v>
@@ -6118,24 +6162,24 @@
       <c r="F70" s="40"/>
       <c r="G70" s="40"/>
       <c r="H70" s="40">
-        <f t="shared" ref="H70:H100" si="11">COUNTA(E70:G70)</f>
+        <f>COUNTA(E70:G70)</f>
         <v>1</v>
       </c>
       <c r="I70" s="41">
         <v>50</v>
       </c>
       <c r="J70" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K70" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L70" s="41">
-        <f t="shared" ref="L70:L100" si="12">I70/N70</f>
+        <f>I70/N70</f>
         <v>50</v>
       </c>
       <c r="M70" s="41">
-        <f t="shared" ref="M70:M100" si="13">IFERROR(L70/H70,"")</f>
+        <f>IFERROR(L70/H70,"")</f>
         <v>50</v>
       </c>
       <c r="N70" s="42">
@@ -6143,18 +6187,18 @@
       </c>
       <c r="O70" s="38"/>
       <c r="P70" s="38" t="str">
-        <f t="shared" ref="P70:P100" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
+        <f>IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
         <v/>
       </c>
       <c r="Q70" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O70&lt;&gt;"",IFERROR(DATEDIF(O70,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="71" spans="3:17">
       <c r="C71" s="38"/>
       <c r="D71" s="49" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E71" s="40" t="s">
         <v>1</v>
@@ -6162,24 +6206,24 @@
       <c r="F71" s="40"/>
       <c r="G71" s="40"/>
       <c r="H71" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E71:G71)</f>
         <v>1</v>
       </c>
       <c r="I71" s="41">
         <v>35</v>
       </c>
       <c r="J71" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K71" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L71" s="41">
-        <f t="shared" si="12"/>
+        <f>I71/N71</f>
         <v>35</v>
       </c>
       <c r="M71" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L71/H71,"")</f>
         <v>35</v>
       </c>
       <c r="N71" s="42">
@@ -6187,18 +6231,18 @@
       </c>
       <c r="O71" s="38"/>
       <c r="P71" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N71&lt;&gt;1,EDATE(O71,N71-1),"")</f>
         <v/>
       </c>
       <c r="Q71" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O71&lt;&gt;"",IFERROR(DATEDIF(O71,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="38"/>
       <c r="D72" s="49" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E72" s="40" t="s">
         <v>1</v>
@@ -6206,24 +6250,24 @@
       <c r="F72" s="40"/>
       <c r="G72" s="40"/>
       <c r="H72" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E72:G72)</f>
         <v>1</v>
       </c>
       <c r="I72" s="41">
         <v>52.14</v>
       </c>
       <c r="J72" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K72" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L72" s="41">
-        <f t="shared" si="12"/>
+        <f>I72/N72</f>
         <v>52.14</v>
       </c>
       <c r="M72" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L72/H72,"")</f>
         <v>52.14</v>
       </c>
       <c r="N72" s="42">
@@ -6231,18 +6275,18 @@
       </c>
       <c r="O72" s="38"/>
       <c r="P72" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N72&lt;&gt;1,EDATE(O72,N72-1),"")</f>
         <v/>
       </c>
       <c r="Q72" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O72&lt;&gt;"",IFERROR(DATEDIF(O72,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="38"/>
       <c r="D73" s="49" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E73" s="40" t="s">
         <v>1</v>
@@ -6252,24 +6296,24 @@
       </c>
       <c r="G73" s="40"/>
       <c r="H73" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E73:G73)</f>
         <v>2</v>
       </c>
       <c r="I73" s="41">
         <v>130.01</v>
       </c>
       <c r="J73" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K73" s="41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L73" s="41">
-        <f t="shared" si="12"/>
+        <f>I73/N73</f>
         <v>130.01</v>
       </c>
       <c r="M73" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L73/H73,"")</f>
         <v>65.004999999999995</v>
       </c>
       <c r="N73" s="42">
@@ -6277,18 +6321,18 @@
       </c>
       <c r="O73" s="38"/>
       <c r="P73" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N73&lt;&gt;1,EDATE(O73,N73-1),"")</f>
         <v/>
       </c>
       <c r="Q73" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O73&lt;&gt;"",IFERROR(DATEDIF(O73,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="38"/>
       <c r="D74" s="49" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E74" s="40" t="s">
         <v>1</v>
@@ -6296,24 +6340,24 @@
       <c r="F74" s="40"/>
       <c r="G74" s="40"/>
       <c r="H74" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E74:G74)</f>
         <v>1</v>
       </c>
       <c r="I74" s="41">
         <v>99</v>
       </c>
       <c r="J74" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K74" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L74" s="41">
-        <f t="shared" si="12"/>
+        <f>I74/N74</f>
         <v>99</v>
       </c>
       <c r="M74" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L74/H74,"")</f>
         <v>99</v>
       </c>
       <c r="N74" s="42">
@@ -6321,18 +6365,18 @@
       </c>
       <c r="O74" s="38"/>
       <c r="P74" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N74&lt;&gt;1,EDATE(O74,N74-1),"")</f>
         <v/>
       </c>
       <c r="Q74" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O74&lt;&gt;"",IFERROR(DATEDIF(O74,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="38"/>
       <c r="D75" s="49" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E75" s="40" t="s">
         <v>1</v>
@@ -6340,24 +6384,24 @@
       <c r="F75" s="40"/>
       <c r="G75" s="40"/>
       <c r="H75" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E75:G75)</f>
         <v>1</v>
       </c>
       <c r="I75" s="41">
         <v>-99</v>
       </c>
       <c r="J75" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K75" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L75" s="41">
-        <f t="shared" si="12"/>
+        <f>I75/N75</f>
         <v>-99</v>
       </c>
       <c r="M75" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L75/H75,"")</f>
         <v>-99</v>
       </c>
       <c r="N75" s="42">
@@ -6365,18 +6409,18 @@
       </c>
       <c r="O75" s="38"/>
       <c r="P75" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N75&lt;&gt;1,EDATE(O75,N75-1),"")</f>
         <v/>
       </c>
       <c r="Q75" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O75&lt;&gt;"",IFERROR(DATEDIF(O75,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="38"/>
       <c r="D76" s="49" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E76" s="40" t="s">
         <v>1</v>
@@ -6386,24 +6430,24 @@
       </c>
       <c r="G76" s="40"/>
       <c r="H76" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E76:G76)</f>
         <v>2</v>
       </c>
       <c r="I76" s="41">
         <v>139</v>
       </c>
       <c r="J76" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K76" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L76" s="41">
-        <f t="shared" si="12"/>
+        <f>I76/N76</f>
         <v>139</v>
       </c>
       <c r="M76" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L76/H76,"")</f>
         <v>69.5</v>
       </c>
       <c r="N76" s="42">
@@ -6411,18 +6455,18 @@
       </c>
       <c r="O76" s="38"/>
       <c r="P76" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N76&lt;&gt;1,EDATE(O76,N76-1),"")</f>
         <v/>
       </c>
       <c r="Q76" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O76&lt;&gt;"",IFERROR(DATEDIF(O76,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="77" spans="3:17">
       <c r="C77" s="38"/>
       <c r="D77" s="49" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E77" s="40"/>
       <c r="F77" s="40" t="s">
@@ -6430,24 +6474,24 @@
       </c>
       <c r="G77" s="40"/>
       <c r="H77" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E77:G77)</f>
         <v>1</v>
       </c>
       <c r="I77" s="41">
         <v>100</v>
       </c>
       <c r="J77" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K77" s="41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L77" s="41">
-        <f t="shared" si="12"/>
+        <f>I77/N77</f>
         <v>100</v>
       </c>
       <c r="M77" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L77/H77,"")</f>
         <v>100</v>
       </c>
       <c r="N77" s="42">
@@ -6455,18 +6499,18 @@
       </c>
       <c r="O77" s="38"/>
       <c r="P77" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N77&lt;&gt;1,EDATE(O77,N77-1),"")</f>
         <v/>
       </c>
       <c r="Q77" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O77&lt;&gt;"",IFERROR(DATEDIF(O77,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="78" spans="3:17">
       <c r="C78" s="38"/>
       <c r="D78" s="49" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E78" s="40" t="s">
         <v>1</v>
@@ -6476,24 +6520,24 @@
       </c>
       <c r="G78" s="40"/>
       <c r="H78" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E78:G78)</f>
         <v>2</v>
       </c>
       <c r="I78" s="41">
         <v>90</v>
       </c>
       <c r="J78" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K78" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L78" s="41">
-        <f t="shared" si="12"/>
+        <f>I78/N78</f>
         <v>90</v>
       </c>
       <c r="M78" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L78/H78,"")</f>
         <v>45</v>
       </c>
       <c r="N78" s="42">
@@ -6501,18 +6545,18 @@
       </c>
       <c r="O78" s="38"/>
       <c r="P78" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N78&lt;&gt;1,EDATE(O78,N78-1),"")</f>
         <v/>
       </c>
       <c r="Q78" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O78&lt;&gt;"",IFERROR(DATEDIF(O78,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="38"/>
       <c r="D79" s="49" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E79" s="40" t="s">
         <v>1</v>
@@ -6520,24 +6564,24 @@
       <c r="F79" s="40"/>
       <c r="G79" s="40"/>
       <c r="H79" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E79:G79)</f>
         <v>1</v>
       </c>
       <c r="I79" s="41">
         <v>-45</v>
       </c>
       <c r="J79" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K79" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L79" s="41">
-        <f t="shared" si="12"/>
+        <f>I79/N79</f>
         <v>-45</v>
       </c>
       <c r="M79" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L79/H79,"")</f>
         <v>-45</v>
       </c>
       <c r="N79" s="42">
@@ -6545,18 +6589,18 @@
       </c>
       <c r="O79" s="38"/>
       <c r="P79" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N79&lt;&gt;1,EDATE(O79,N79-1),"")</f>
         <v/>
       </c>
       <c r="Q79" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O79&lt;&gt;"",IFERROR(DATEDIF(O79,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="80" spans="3:17">
       <c r="C80" s="38"/>
       <c r="D80" s="49" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E80" s="40" t="s">
         <v>1</v>
@@ -6566,24 +6610,24 @@
       </c>
       <c r="G80" s="40"/>
       <c r="H80" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E80:G80)</f>
         <v>2</v>
       </c>
       <c r="I80" s="41">
         <v>79</v>
       </c>
       <c r="J80" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K80" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L80" s="41">
-        <f t="shared" si="12"/>
+        <f>I80/N80</f>
         <v>79</v>
       </c>
       <c r="M80" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L80/H80,"")</f>
         <v>39.5</v>
       </c>
       <c r="N80" s="42">
@@ -6591,18 +6635,18 @@
       </c>
       <c r="O80" s="38"/>
       <c r="P80" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N80&lt;&gt;1,EDATE(O80,N80-1),"")</f>
         <v/>
       </c>
       <c r="Q80" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O80&lt;&gt;"",IFERROR(DATEDIF(O80,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="81" spans="3:17">
       <c r="C81" s="38"/>
       <c r="D81" s="49" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E81" s="40" t="s">
         <v>1</v>
@@ -6612,24 +6656,24 @@
       </c>
       <c r="G81" s="40"/>
       <c r="H81" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E81:G81)</f>
         <v>2</v>
       </c>
       <c r="I81" s="41">
         <v>56.27</v>
       </c>
       <c r="J81" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K81" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L81" s="41">
-        <f t="shared" si="12"/>
+        <f>I81/N81</f>
         <v>56.27</v>
       </c>
       <c r="M81" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L81/H81,"")</f>
         <v>28.135000000000002</v>
       </c>
       <c r="N81" s="42">
@@ -6637,18 +6681,18 @@
       </c>
       <c r="O81" s="38"/>
       <c r="P81" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N81&lt;&gt;1,EDATE(O81,N81-1),"")</f>
         <v/>
       </c>
       <c r="Q81" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O81&lt;&gt;"",IFERROR(DATEDIF(O81,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="38"/>
       <c r="D82" s="49" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E82" s="40" t="s">
         <v>1</v>
@@ -6658,24 +6702,24 @@
       </c>
       <c r="G82" s="40"/>
       <c r="H82" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E82:G82)</f>
         <v>2</v>
       </c>
       <c r="I82" s="41">
         <v>82.49</v>
       </c>
       <c r="J82" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K82" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L82" s="41">
-        <f t="shared" si="12"/>
+        <f>I82/N82</f>
         <v>82.49</v>
       </c>
       <c r="M82" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L82/H82,"")</f>
         <v>41.244999999999997</v>
       </c>
       <c r="N82" s="42">
@@ -6683,18 +6727,18 @@
       </c>
       <c r="O82" s="38"/>
       <c r="P82" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N82&lt;&gt;1,EDATE(O82,N82-1),"")</f>
         <v/>
       </c>
       <c r="Q82" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O82&lt;&gt;"",IFERROR(DATEDIF(O82,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="83" spans="3:17">
       <c r="C83" s="38"/>
       <c r="D83" s="49" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E83" s="40" t="s">
         <v>1</v>
@@ -6704,24 +6748,24 @@
       </c>
       <c r="G83" s="40"/>
       <c r="H83" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E83:G83)</f>
         <v>2</v>
       </c>
       <c r="I83" s="41">
         <v>49.91</v>
       </c>
       <c r="J83" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K83" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L83" s="41">
-        <f t="shared" si="12"/>
+        <f>I83/N83</f>
         <v>49.91</v>
       </c>
       <c r="M83" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L83/H83,"")</f>
         <v>24.954999999999998</v>
       </c>
       <c r="N83" s="42">
@@ -6729,18 +6773,18 @@
       </c>
       <c r="O83" s="38"/>
       <c r="P83" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N83&lt;&gt;1,EDATE(O83,N83-1),"")</f>
         <v/>
       </c>
       <c r="Q83" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O83&lt;&gt;"",IFERROR(DATEDIF(O83,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="84" spans="3:17">
       <c r="C84" s="38"/>
       <c r="D84" s="49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E84" s="40" t="s">
         <v>1</v>
@@ -6750,24 +6794,24 @@
       </c>
       <c r="G84" s="40"/>
       <c r="H84" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E84:G84)</f>
         <v>2</v>
       </c>
       <c r="I84" s="41">
         <v>41.5</v>
       </c>
       <c r="J84" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K84" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L84" s="41">
-        <f t="shared" si="12"/>
+        <f>I84/N84</f>
         <v>41.5</v>
       </c>
       <c r="M84" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L84/H84,"")</f>
         <v>20.75</v>
       </c>
       <c r="N84" s="42">
@@ -6775,18 +6819,18 @@
       </c>
       <c r="O84" s="38"/>
       <c r="P84" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N84&lt;&gt;1,EDATE(O84,N84-1),"")</f>
         <v/>
       </c>
       <c r="Q84" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">IF(O84&lt;&gt;"",IFERROR(DATEDIF(O84,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="38"/>
       <c r="D85" s="49" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E85" s="40" t="s">
         <v>1</v>
@@ -6794,24 +6838,24 @@
       <c r="F85" s="40"/>
       <c r="G85" s="40"/>
       <c r="H85" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E85:G85)</f>
         <v>1</v>
       </c>
       <c r="I85" s="41">
         <v>106.04</v>
       </c>
       <c r="J85" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K85" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L85" s="41">
-        <f t="shared" si="12"/>
+        <f>I85/N85</f>
         <v>106.04</v>
       </c>
       <c r="M85" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L85/H85,"")</f>
         <v>106.04</v>
       </c>
       <c r="N85" s="42">
@@ -6819,18 +6863,18 @@
       </c>
       <c r="O85" s="38"/>
       <c r="P85" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N85&lt;&gt;1,EDATE(O85,N85-1),"")</f>
         <v/>
       </c>
       <c r="Q85" s="40" t="str">
-        <f t="shared" ref="Q85:Q115" ca="1" si="15">IF(O85&lt;&gt;"",IFERROR(DATEDIF(O85,TODAY(),"m")+1,""),"")</f>
+        <f ca="1">IF(O85&lt;&gt;"",IFERROR(DATEDIF(O85,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="38"/>
       <c r="D86" s="49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E86" s="40" t="s">
         <v>1</v>
@@ -6838,24 +6882,24 @@
       <c r="F86" s="40"/>
       <c r="G86" s="40"/>
       <c r="H86" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E86:G86)</f>
         <v>1</v>
       </c>
       <c r="I86" s="41">
         <v>16.97</v>
       </c>
       <c r="J86" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K86" s="41" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="L86" s="41">
-        <f t="shared" si="12"/>
+        <f>I86/N86</f>
         <v>16.97</v>
       </c>
       <c r="M86" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L86/H86,"")</f>
         <v>16.97</v>
       </c>
       <c r="N86" s="42">
@@ -6863,18 +6907,18 @@
       </c>
       <c r="O86" s="38"/>
       <c r="P86" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N86&lt;&gt;1,EDATE(O86,N86-1),"")</f>
         <v/>
       </c>
       <c r="Q86" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O86&lt;&gt;"",IFERROR(DATEDIF(O86,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="87" spans="3:17">
       <c r="C87" s="38"/>
       <c r="D87" s="49" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E87" s="40" t="s">
         <v>1</v>
@@ -6882,24 +6926,24 @@
       <c r="F87" s="40"/>
       <c r="G87" s="40"/>
       <c r="H87" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E87:G87)</f>
         <v>1</v>
       </c>
       <c r="I87" s="41">
         <v>50</v>
       </c>
       <c r="J87" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K87" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L87" s="41">
-        <f t="shared" si="12"/>
+        <f>I87/N87</f>
         <v>50</v>
       </c>
       <c r="M87" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L87/H87,"")</f>
         <v>50</v>
       </c>
       <c r="N87" s="42">
@@ -6907,18 +6951,18 @@
       </c>
       <c r="O87" s="38"/>
       <c r="P87" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N87&lt;&gt;1,EDATE(O87,N87-1),"")</f>
         <v/>
       </c>
       <c r="Q87" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O87&lt;&gt;"",IFERROR(DATEDIF(O87,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="88" spans="3:17">
       <c r="C88" s="38"/>
       <c r="D88" s="49" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E88" s="40" t="s">
         <v>1</v>
@@ -6928,24 +6972,24 @@
       </c>
       <c r="G88" s="40"/>
       <c r="H88" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E88:G88)</f>
         <v>2</v>
       </c>
       <c r="I88" s="41">
         <v>53.97</v>
       </c>
       <c r="J88" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K88" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L88" s="41">
-        <f t="shared" si="12"/>
+        <f>I88/N88</f>
         <v>53.97</v>
       </c>
       <c r="M88" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L88/H88,"")</f>
         <v>26.984999999999999</v>
       </c>
       <c r="N88" s="42">
@@ -6953,18 +6997,18 @@
       </c>
       <c r="O88" s="38"/>
       <c r="P88" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N88&lt;&gt;1,EDATE(O88,N88-1),"")</f>
         <v/>
       </c>
       <c r="Q88" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O88&lt;&gt;"",IFERROR(DATEDIF(O88,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="89" spans="3:17">
       <c r="C89" s="38"/>
       <c r="D89" s="49" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E89" s="40" t="s">
         <v>1</v>
@@ -6972,7 +7016,7 @@
       <c r="F89" s="40"/>
       <c r="G89" s="40"/>
       <c r="H89" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E89:G89)</f>
         <v>1</v>
       </c>
       <c r="I89" s="41">
@@ -6980,17 +7024,17 @@
         <v>95.9</v>
       </c>
       <c r="J89" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K89" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L89" s="41">
-        <f t="shared" si="12"/>
+        <f>I89/N89</f>
         <v>95.9</v>
       </c>
       <c r="M89" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L89/H89,"")</f>
         <v>95.9</v>
       </c>
       <c r="N89" s="42">
@@ -6998,18 +7042,18 @@
       </c>
       <c r="O89" s="38"/>
       <c r="P89" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N89&lt;&gt;1,EDATE(O89,N89-1),"")</f>
         <v/>
       </c>
       <c r="Q89" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O89&lt;&gt;"",IFERROR(DATEDIF(O89,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="90" spans="3:17">
       <c r="C90" s="38"/>
       <c r="D90" s="49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E90" s="40" t="s">
         <v>1</v>
@@ -7019,24 +7063,24 @@
       </c>
       <c r="G90" s="40"/>
       <c r="H90" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E90:G90)</f>
         <v>2</v>
       </c>
       <c r="I90" s="41">
         <v>56</v>
       </c>
       <c r="J90" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K90" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L90" s="41">
-        <f t="shared" si="12"/>
+        <f>I90/N90</f>
         <v>56</v>
       </c>
       <c r="M90" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L90/H90,"")</f>
         <v>28</v>
       </c>
       <c r="N90" s="42">
@@ -7044,18 +7088,18 @@
       </c>
       <c r="O90" s="38"/>
       <c r="P90" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N90&lt;&gt;1,EDATE(O90,N90-1),"")</f>
         <v/>
       </c>
       <c r="Q90" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O90&lt;&gt;"",IFERROR(DATEDIF(O90,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="91" spans="3:17">
       <c r="C91" s="38"/>
       <c r="D91" s="49" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E91" s="40" t="s">
         <v>1</v>
@@ -7065,24 +7109,24 @@
       </c>
       <c r="G91" s="40"/>
       <c r="H91" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E91:G91)</f>
         <v>2</v>
       </c>
       <c r="I91" s="41">
         <v>20</v>
       </c>
       <c r="J91" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K91" s="41" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="L91" s="41">
-        <f t="shared" si="12"/>
+        <f>I91/N91</f>
         <v>20</v>
       </c>
       <c r="M91" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L91/H91,"")</f>
         <v>10</v>
       </c>
       <c r="N91" s="42">
@@ -7090,41 +7134,41 @@
       </c>
       <c r="O91" s="38"/>
       <c r="P91" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N91&lt;&gt;1,EDATE(O91,N91-1),"")</f>
         <v/>
       </c>
       <c r="Q91" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O91&lt;&gt;"",IFERROR(DATEDIF(O91,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="38"/>
       <c r="D92" s="49" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E92" s="40"/>
       <c r="F92" s="40"/>
       <c r="G92" s="40"/>
       <c r="H92" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E92:G92)</f>
         <v>0</v>
       </c>
       <c r="I92" s="41">
         <v>308.26</v>
       </c>
       <c r="J92" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K92" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L92" s="41">
-        <f t="shared" si="12"/>
+        <f>I92/N92</f>
         <v>308.26</v>
       </c>
       <c r="M92" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L92/H92,"")</f>
         <v/>
       </c>
       <c r="N92" s="42">
@@ -7134,41 +7178,41 @@
         <v>46237</v>
       </c>
       <c r="P92" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N92&lt;&gt;1,EDATE(O92,N92-1),"")</f>
         <v/>
       </c>
       <c r="Q92" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O92&lt;&gt;"",IFERROR(DATEDIF(O92,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="38"/>
       <c r="D93" s="49" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E93" s="40"/>
       <c r="F93" s="40"/>
       <c r="G93" s="40"/>
       <c r="H93" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E93:G93)</f>
         <v>0</v>
       </c>
       <c r="I93" s="41">
         <v>-308</v>
       </c>
       <c r="J93" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K93" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L93" s="41">
-        <f t="shared" si="12"/>
+        <f>I93/N93</f>
         <v>-308</v>
       </c>
       <c r="M93" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L93/H93,"")</f>
         <v/>
       </c>
       <c r="N93" s="42">
@@ -7178,18 +7222,18 @@
         <v>46237</v>
       </c>
       <c r="P93" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N93&lt;&gt;1,EDATE(O93,N93-1),"")</f>
         <v/>
       </c>
       <c r="Q93" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O93&lt;&gt;"",IFERROR(DATEDIF(O93,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="38"/>
       <c r="D94" s="49" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E94" s="40" t="s">
         <v>1</v>
@@ -7197,24 +7241,24 @@
       <c r="F94" s="40"/>
       <c r="G94" s="40"/>
       <c r="H94" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E94:G94)</f>
         <v>1</v>
       </c>
       <c r="I94" s="41">
         <v>169</v>
       </c>
       <c r="J94" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K94" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L94" s="41">
-        <f t="shared" si="12"/>
+        <f>I94/N94</f>
         <v>28.166666666666668</v>
       </c>
       <c r="M94" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L94/H94,"")</f>
         <v>28.166666666666668</v>
       </c>
       <c r="N94" s="42">
@@ -7224,18 +7268,18 @@
         <v>46237</v>
       </c>
       <c r="P94" s="38">
-        <f t="shared" si="14"/>
+        <f>IF(N94&lt;&gt;1,EDATE(O94,N94-1),"")</f>
         <v>46390</v>
       </c>
       <c r="Q94" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O94&lt;&gt;"",IFERROR(DATEDIF(O94,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="38"/>
       <c r="D95" s="49" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E95" s="40" t="s">
         <v>1</v>
@@ -7243,24 +7287,24 @@
       <c r="F95" s="40"/>
       <c r="G95" s="40"/>
       <c r="H95" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E95:G95)</f>
         <v>1</v>
       </c>
       <c r="I95" s="41">
         <v>30.4</v>
       </c>
       <c r="J95" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K95" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L95" s="41">
-        <f t="shared" si="12"/>
+        <f>I95/N95</f>
         <v>30.4</v>
       </c>
       <c r="M95" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L95/H95,"")</f>
         <v>30.4</v>
       </c>
       <c r="N95" s="42">
@@ -7268,18 +7312,18 @@
       </c>
       <c r="O95" s="38"/>
       <c r="P95" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N95&lt;&gt;1,EDATE(O95,N95-1),"")</f>
         <v/>
       </c>
       <c r="Q95" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O95&lt;&gt;"",IFERROR(DATEDIF(O95,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="96" spans="3:17">
       <c r="C96" s="38"/>
       <c r="D96" s="49" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E96" s="40" t="s">
         <v>1</v>
@@ -7289,24 +7333,24 @@
       </c>
       <c r="G96" s="40"/>
       <c r="H96" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E96:G96)</f>
         <v>2</v>
       </c>
       <c r="I96" s="41">
         <v>76</v>
       </c>
       <c r="J96" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K96" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L96" s="41">
-        <f t="shared" si="12"/>
+        <f>I96/N96</f>
         <v>76</v>
       </c>
       <c r="M96" s="41">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L96/H96,"")</f>
         <v>38</v>
       </c>
       <c r="N96" s="42">
@@ -7314,41 +7358,41 @@
       </c>
       <c r="O96" s="38"/>
       <c r="P96" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N96&lt;&gt;1,EDATE(O96,N96-1),"")</f>
         <v/>
       </c>
       <c r="Q96" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O96&lt;&gt;"",IFERROR(DATEDIF(O96,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="38"/>
       <c r="D97" s="49" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E97" s="40"/>
       <c r="F97" s="40"/>
       <c r="G97" s="40"/>
       <c r="H97" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E97:G97)</f>
         <v>0</v>
       </c>
       <c r="I97" s="41">
         <v>1344</v>
       </c>
       <c r="J97" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K97" s="41" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L97" s="41">
-        <f t="shared" si="12"/>
+        <f>I97/N97</f>
         <v>1344</v>
       </c>
       <c r="M97" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L97/H97,"")</f>
         <v/>
       </c>
       <c r="N97" s="42">
@@ -7356,41 +7400,41 @@
       </c>
       <c r="O97" s="38"/>
       <c r="P97" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N97&lt;&gt;1,EDATE(O97,N97-1),"")</f>
         <v/>
       </c>
       <c r="Q97" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O97&lt;&gt;"",IFERROR(DATEDIF(O97,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="98" spans="3:17">
       <c r="C98" s="38"/>
       <c r="D98" s="49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E98" s="40"/>
       <c r="F98" s="40"/>
       <c r="G98" s="40"/>
       <c r="H98" s="40">
-        <f t="shared" si="11"/>
+        <f>COUNTA(E98:G98)</f>
         <v>0</v>
       </c>
       <c r="I98" s="41">
         <v>-1344</v>
       </c>
       <c r="J98" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K98" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L98" s="41">
-        <f t="shared" si="12"/>
+        <f>I98/N98</f>
         <v>-1344</v>
       </c>
       <c r="M98" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f>IFERROR(L98/H98,"")</f>
         <v/>
       </c>
       <c r="N98" s="42">
@@ -7398,113 +7442,149 @@
       </c>
       <c r="O98" s="38"/>
       <c r="P98" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N98&lt;&gt;1,EDATE(O98,N98-1),"")</f>
         <v/>
       </c>
       <c r="Q98" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O98&lt;&gt;"",IFERROR(DATEDIF(O98,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="99" spans="3:17">
       <c r="C99" s="38"/>
-      <c r="D99" s="49"/>
-      <c r="E99" s="40"/>
-      <c r="F99" s="40"/>
+      <c r="D99" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="E99" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G99" s="40"/>
       <c r="H99" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I99" s="41"/>
-      <c r="J99" s="41"/>
-      <c r="K99" s="41"/>
+        <f>COUNTA(E99:G99)</f>
+        <v>2</v>
+      </c>
+      <c r="I99" s="41">
+        <v>-246</v>
+      </c>
+      <c r="J99" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="K99" s="41" t="s">
+        <v>123</v>
+      </c>
       <c r="L99" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M99" s="41" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>I99/N99</f>
+        <v>-246</v>
+      </c>
+      <c r="M99" s="41">
+        <f>IFERROR(L99/H99,"")</f>
+        <v>-123</v>
       </c>
       <c r="N99" s="42">
         <v>1</v>
       </c>
       <c r="O99" s="38"/>
       <c r="P99" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N99&lt;&gt;1,EDATE(O99,N99-1),"")</f>
         <v/>
       </c>
       <c r="Q99" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O99&lt;&gt;"",IFERROR(DATEDIF(O99,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="100" spans="3:17">
       <c r="C100" s="38"/>
-      <c r="D100" s="49"/>
-      <c r="E100" s="40"/>
-      <c r="F100" s="40"/>
+      <c r="D100" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="E100" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G100" s="40"/>
       <c r="H100" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="41"/>
-      <c r="J100" s="41"/>
-      <c r="K100" s="41"/>
+        <f>COUNTA(E100:G100)</f>
+        <v>2</v>
+      </c>
+      <c r="I100" s="41">
+        <v>140</v>
+      </c>
+      <c r="J100" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="K100" s="41" t="s">
+        <v>72</v>
+      </c>
       <c r="L100" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M100" s="41" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>I100/N100</f>
+        <v>140</v>
+      </c>
+      <c r="M100" s="41">
+        <f>IFERROR(L100/H100,"")</f>
+        <v>70</v>
       </c>
       <c r="N100" s="42">
         <v>1</v>
       </c>
       <c r="O100" s="38"/>
       <c r="P100" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f>IF(N100&lt;&gt;1,EDATE(O100,N100-1),"")</f>
         <v/>
       </c>
       <c r="Q100" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O100&lt;&gt;"",IFERROR(DATEDIF(O100,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="101" spans="3:17">
       <c r="C101" s="38"/>
-      <c r="D101" s="49"/>
-      <c r="E101" s="40"/>
-      <c r="F101" s="40"/>
+      <c r="D101" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="E101" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G101" s="40"/>
       <c r="H101" s="40">
-        <f t="shared" ref="H101:H132" si="16">COUNTA(E101:G101)</f>
-        <v>0</v>
-      </c>
-      <c r="I101" s="41"/>
-      <c r="J101" s="41"/>
-      <c r="K101" s="41"/>
+        <f>COUNTA(E101:G101)</f>
+        <v>2</v>
+      </c>
+      <c r="I101" s="41">
+        <v>20</v>
+      </c>
+      <c r="J101" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="K101" s="41" t="s">
+        <v>117</v>
+      </c>
       <c r="L101" s="41">
-        <f t="shared" ref="L101:L132" si="17">I101/N101</f>
-        <v>0</v>
-      </c>
-      <c r="M101" s="41" t="str">
-        <f t="shared" ref="M101:M132" si="18">IFERROR(L101/H101,"")</f>
-        <v/>
+        <f>I101/N101</f>
+        <v>20</v>
+      </c>
+      <c r="M101" s="41">
+        <f>IFERROR(L101/H101,"")</f>
+        <v>10</v>
       </c>
       <c r="N101" s="42">
         <v>1</v>
       </c>
       <c r="O101" s="38"/>
       <c r="P101" s="38" t="str">
-        <f t="shared" ref="P101:P132" si="19">IF(N101&lt;&gt;1,EDATE(O101,N101-1),"")</f>
+        <f>IF(N101&lt;&gt;1,EDATE(O101,N101-1),"")</f>
         <v/>
       </c>
       <c r="Q101" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O101&lt;&gt;"",IFERROR(DATEDIF(O101,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7515,18 +7595,18 @@
       <c r="F102" s="40"/>
       <c r="G102" s="40"/>
       <c r="H102" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E102:G102)</f>
         <v>0</v>
       </c>
       <c r="I102" s="41"/>
       <c r="J102" s="41"/>
       <c r="K102" s="41"/>
       <c r="L102" s="41">
-        <f t="shared" si="17"/>
+        <f>I102/N102</f>
         <v>0</v>
       </c>
       <c r="M102" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L102/H102,"")</f>
         <v/>
       </c>
       <c r="N102" s="42">
@@ -7534,11 +7614,11 @@
       </c>
       <c r="O102" s="38"/>
       <c r="P102" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
         <v/>
       </c>
       <c r="Q102" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O102&lt;&gt;"",IFERROR(DATEDIF(O102,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7549,18 +7629,18 @@
       <c r="F103" s="40"/>
       <c r="G103" s="40"/>
       <c r="H103" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E103:G103)</f>
         <v>0</v>
       </c>
       <c r="I103" s="41"/>
       <c r="J103" s="41"/>
       <c r="K103" s="41"/>
       <c r="L103" s="41">
-        <f t="shared" si="17"/>
+        <f>I103/N103</f>
         <v>0</v>
       </c>
       <c r="M103" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L103/H103,"")</f>
         <v/>
       </c>
       <c r="N103" s="42">
@@ -7568,11 +7648,11 @@
       </c>
       <c r="O103" s="38"/>
       <c r="P103" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N103&lt;&gt;1,EDATE(O103,N103-1),"")</f>
         <v/>
       </c>
       <c r="Q103" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O103&lt;&gt;"",IFERROR(DATEDIF(O103,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7583,18 +7663,18 @@
       <c r="F104" s="40"/>
       <c r="G104" s="40"/>
       <c r="H104" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E104:G104)</f>
         <v>0</v>
       </c>
       <c r="I104" s="41"/>
       <c r="J104" s="41"/>
       <c r="K104" s="41"/>
       <c r="L104" s="41">
-        <f t="shared" si="17"/>
+        <f>I104/N104</f>
         <v>0</v>
       </c>
       <c r="M104" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L104/H104,"")</f>
         <v/>
       </c>
       <c r="N104" s="42">
@@ -7602,11 +7682,11 @@
       </c>
       <c r="O104" s="38"/>
       <c r="P104" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N104&lt;&gt;1,EDATE(O104,N104-1),"")</f>
         <v/>
       </c>
       <c r="Q104" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O104&lt;&gt;"",IFERROR(DATEDIF(O104,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7617,18 +7697,18 @@
       <c r="F105" s="40"/>
       <c r="G105" s="40"/>
       <c r="H105" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E105:G105)</f>
         <v>0</v>
       </c>
       <c r="I105" s="41"/>
       <c r="J105" s="41"/>
       <c r="K105" s="41"/>
       <c r="L105" s="41">
-        <f t="shared" si="17"/>
+        <f>I105/N105</f>
         <v>0</v>
       </c>
       <c r="M105" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L105/H105,"")</f>
         <v/>
       </c>
       <c r="N105" s="42">
@@ -7636,11 +7716,11 @@
       </c>
       <c r="O105" s="38"/>
       <c r="P105" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N105&lt;&gt;1,EDATE(O105,N105-1),"")</f>
         <v/>
       </c>
       <c r="Q105" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O105&lt;&gt;"",IFERROR(DATEDIF(O105,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7651,18 +7731,18 @@
       <c r="F106" s="40"/>
       <c r="G106" s="40"/>
       <c r="H106" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E106:G106)</f>
         <v>0</v>
       </c>
       <c r="I106" s="41"/>
       <c r="J106" s="41"/>
       <c r="K106" s="41"/>
       <c r="L106" s="41">
-        <f t="shared" si="17"/>
+        <f>I106/N106</f>
         <v>0</v>
       </c>
       <c r="M106" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L106/H106,"")</f>
         <v/>
       </c>
       <c r="N106" s="42">
@@ -7670,11 +7750,11 @@
       </c>
       <c r="O106" s="38"/>
       <c r="P106" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N106&lt;&gt;1,EDATE(O106,N106-1),"")</f>
         <v/>
       </c>
       <c r="Q106" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O106&lt;&gt;"",IFERROR(DATEDIF(O106,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7685,18 +7765,18 @@
       <c r="F107" s="40"/>
       <c r="G107" s="40"/>
       <c r="H107" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E107:G107)</f>
         <v>0</v>
       </c>
       <c r="I107" s="41"/>
       <c r="J107" s="41"/>
       <c r="K107" s="41"/>
       <c r="L107" s="41">
-        <f t="shared" si="17"/>
+        <f>I107/N107</f>
         <v>0</v>
       </c>
       <c r="M107" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L107/H107,"")</f>
         <v/>
       </c>
       <c r="N107" s="42">
@@ -7704,11 +7784,11 @@
       </c>
       <c r="O107" s="38"/>
       <c r="P107" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N107&lt;&gt;1,EDATE(O107,N107-1),"")</f>
         <v/>
       </c>
       <c r="Q107" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O107&lt;&gt;"",IFERROR(DATEDIF(O107,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7719,18 +7799,18 @@
       <c r="F108" s="40"/>
       <c r="G108" s="40"/>
       <c r="H108" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E108:G108)</f>
         <v>0</v>
       </c>
       <c r="I108" s="41"/>
       <c r="J108" s="41"/>
       <c r="K108" s="41"/>
       <c r="L108" s="41">
-        <f t="shared" si="17"/>
+        <f>I108/N108</f>
         <v>0</v>
       </c>
       <c r="M108" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L108/H108,"")</f>
         <v/>
       </c>
       <c r="N108" s="42">
@@ -7738,11 +7818,11 @@
       </c>
       <c r="O108" s="38"/>
       <c r="P108" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N108&lt;&gt;1,EDATE(O108,N108-1),"")</f>
         <v/>
       </c>
       <c r="Q108" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O108&lt;&gt;"",IFERROR(DATEDIF(O108,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7753,18 +7833,18 @@
       <c r="F109" s="40"/>
       <c r="G109" s="40"/>
       <c r="H109" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E109:G109)</f>
         <v>0</v>
       </c>
       <c r="I109" s="41"/>
       <c r="J109" s="41"/>
       <c r="K109" s="41"/>
       <c r="L109" s="41">
-        <f t="shared" si="17"/>
+        <f>I109/N109</f>
         <v>0</v>
       </c>
       <c r="M109" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L109/H109,"")</f>
         <v/>
       </c>
       <c r="N109" s="42">
@@ -7772,11 +7852,11 @@
       </c>
       <c r="O109" s="38"/>
       <c r="P109" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N109&lt;&gt;1,EDATE(O109,N109-1),"")</f>
         <v/>
       </c>
       <c r="Q109" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O109&lt;&gt;"",IFERROR(DATEDIF(O109,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7787,18 +7867,18 @@
       <c r="F110" s="40"/>
       <c r="G110" s="40"/>
       <c r="H110" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E110:G110)</f>
         <v>0</v>
       </c>
       <c r="I110" s="41"/>
       <c r="J110" s="41"/>
       <c r="K110" s="41"/>
       <c r="L110" s="41">
-        <f t="shared" si="17"/>
+        <f>I110/N110</f>
         <v>0</v>
       </c>
       <c r="M110" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L110/H110,"")</f>
         <v/>
       </c>
       <c r="N110" s="42">
@@ -7806,11 +7886,11 @@
       </c>
       <c r="O110" s="38"/>
       <c r="P110" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N110&lt;&gt;1,EDATE(O110,N110-1),"")</f>
         <v/>
       </c>
       <c r="Q110" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O110&lt;&gt;"",IFERROR(DATEDIF(O110,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7821,18 +7901,18 @@
       <c r="F111" s="40"/>
       <c r="G111" s="40"/>
       <c r="H111" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E111:G111)</f>
         <v>0</v>
       </c>
       <c r="I111" s="41"/>
       <c r="J111" s="41"/>
       <c r="K111" s="41"/>
       <c r="L111" s="41">
-        <f t="shared" si="17"/>
+        <f>I111/N111</f>
         <v>0</v>
       </c>
       <c r="M111" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L111/H111,"")</f>
         <v/>
       </c>
       <c r="N111" s="42">
@@ -7840,11 +7920,11 @@
       </c>
       <c r="O111" s="38"/>
       <c r="P111" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N111&lt;&gt;1,EDATE(O111,N111-1),"")</f>
         <v/>
       </c>
       <c r="Q111" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O111&lt;&gt;"",IFERROR(DATEDIF(O111,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7855,18 +7935,18 @@
       <c r="F112" s="40"/>
       <c r="G112" s="40"/>
       <c r="H112" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E112:G112)</f>
         <v>0</v>
       </c>
       <c r="I112" s="41"/>
       <c r="J112" s="41"/>
       <c r="K112" s="41"/>
       <c r="L112" s="41">
-        <f t="shared" si="17"/>
+        <f>I112/N112</f>
         <v>0</v>
       </c>
       <c r="M112" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L112/H112,"")</f>
         <v/>
       </c>
       <c r="N112" s="42">
@@ -7874,11 +7954,11 @@
       </c>
       <c r="O112" s="38"/>
       <c r="P112" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N112&lt;&gt;1,EDATE(O112,N112-1),"")</f>
         <v/>
       </c>
       <c r="Q112" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O112&lt;&gt;"",IFERROR(DATEDIF(O112,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7889,18 +7969,18 @@
       <c r="F113" s="40"/>
       <c r="G113" s="40"/>
       <c r="H113" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E113:G113)</f>
         <v>0</v>
       </c>
       <c r="I113" s="41"/>
       <c r="J113" s="41"/>
       <c r="K113" s="41"/>
       <c r="L113" s="41">
-        <f t="shared" si="17"/>
+        <f>I113/N113</f>
         <v>0</v>
       </c>
       <c r="M113" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L113/H113,"")</f>
         <v/>
       </c>
       <c r="N113" s="42">
@@ -7908,11 +7988,11 @@
       </c>
       <c r="O113" s="38"/>
       <c r="P113" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N113&lt;&gt;1,EDATE(O113,N113-1),"")</f>
         <v/>
       </c>
       <c r="Q113" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O113&lt;&gt;"",IFERROR(DATEDIF(O113,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7923,18 +8003,18 @@
       <c r="F114" s="40"/>
       <c r="G114" s="40"/>
       <c r="H114" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E114:G114)</f>
         <v>0</v>
       </c>
       <c r="I114" s="41"/>
       <c r="J114" s="41"/>
       <c r="K114" s="41"/>
       <c r="L114" s="41">
-        <f t="shared" si="17"/>
+        <f>I114/N114</f>
         <v>0</v>
       </c>
       <c r="M114" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L114/H114,"")</f>
         <v/>
       </c>
       <c r="N114" s="42">
@@ -7942,11 +8022,11 @@
       </c>
       <c r="O114" s="38"/>
       <c r="P114" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N114&lt;&gt;1,EDATE(O114,N114-1),"")</f>
         <v/>
       </c>
       <c r="Q114" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O114&lt;&gt;"",IFERROR(DATEDIF(O114,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7957,18 +8037,18 @@
       <c r="F115" s="40"/>
       <c r="G115" s="40"/>
       <c r="H115" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E115:G115)</f>
         <v>0</v>
       </c>
       <c r="I115" s="41"/>
       <c r="J115" s="41"/>
       <c r="K115" s="41"/>
       <c r="L115" s="41">
-        <f t="shared" si="17"/>
+        <f>I115/N115</f>
         <v>0</v>
       </c>
       <c r="M115" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L115/H115,"")</f>
         <v/>
       </c>
       <c r="N115" s="42">
@@ -7976,11 +8056,11 @@
       </c>
       <c r="O115" s="38"/>
       <c r="P115" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N115&lt;&gt;1,EDATE(O115,N115-1),"")</f>
         <v/>
       </c>
       <c r="Q115" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(O115&lt;&gt;"",IFERROR(DATEDIF(O115,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7991,18 +8071,18 @@
       <c r="F116" s="40"/>
       <c r="G116" s="40"/>
       <c r="H116" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E116:G116)</f>
         <v>0</v>
       </c>
       <c r="I116" s="41"/>
       <c r="J116" s="41"/>
       <c r="K116" s="41"/>
       <c r="L116" s="41">
-        <f t="shared" si="17"/>
+        <f>I116/N116</f>
         <v>0</v>
       </c>
       <c r="M116" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L116/H116,"")</f>
         <v/>
       </c>
       <c r="N116" s="42">
@@ -8010,11 +8090,11 @@
       </c>
       <c r="O116" s="38"/>
       <c r="P116" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N116&lt;&gt;1,EDATE(O116,N116-1),"")</f>
         <v/>
       </c>
       <c r="Q116" s="40" t="str">
-        <f t="shared" ref="Q116:Q148" ca="1" si="20">IF(O116&lt;&gt;"",IFERROR(DATEDIF(O116,TODAY(),"m")+1,""),"")</f>
+        <f ca="1">IF(O116&lt;&gt;"",IFERROR(DATEDIF(O116,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8025,18 +8105,18 @@
       <c r="F117" s="40"/>
       <c r="G117" s="40"/>
       <c r="H117" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E117:G117)</f>
         <v>0</v>
       </c>
       <c r="I117" s="41"/>
       <c r="J117" s="41"/>
       <c r="K117" s="41"/>
       <c r="L117" s="41">
-        <f t="shared" si="17"/>
+        <f>I117/N117</f>
         <v>0</v>
       </c>
       <c r="M117" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L117/H117,"")</f>
         <v/>
       </c>
       <c r="N117" s="42">
@@ -8044,11 +8124,11 @@
       </c>
       <c r="O117" s="38"/>
       <c r="P117" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N117&lt;&gt;1,EDATE(O117,N117-1),"")</f>
         <v/>
       </c>
       <c r="Q117" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O117&lt;&gt;"",IFERROR(DATEDIF(O117,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8059,18 +8139,18 @@
       <c r="F118" s="40"/>
       <c r="G118" s="40"/>
       <c r="H118" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E118:G118)</f>
         <v>0</v>
       </c>
       <c r="I118" s="41"/>
       <c r="J118" s="41"/>
       <c r="K118" s="41"/>
       <c r="L118" s="41">
-        <f t="shared" si="17"/>
+        <f>I118/N118</f>
         <v>0</v>
       </c>
       <c r="M118" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L118/H118,"")</f>
         <v/>
       </c>
       <c r="N118" s="42">
@@ -8078,11 +8158,11 @@
       </c>
       <c r="O118" s="38"/>
       <c r="P118" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N118&lt;&gt;1,EDATE(O118,N118-1),"")</f>
         <v/>
       </c>
       <c r="Q118" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O118&lt;&gt;"",IFERROR(DATEDIF(O118,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8093,18 +8173,18 @@
       <c r="F119" s="40"/>
       <c r="G119" s="40"/>
       <c r="H119" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E119:G119)</f>
         <v>0</v>
       </c>
       <c r="I119" s="41"/>
       <c r="J119" s="41"/>
       <c r="K119" s="41"/>
       <c r="L119" s="41">
-        <f t="shared" si="17"/>
+        <f>I119/N119</f>
         <v>0</v>
       </c>
       <c r="M119" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L119/H119,"")</f>
         <v/>
       </c>
       <c r="N119" s="42">
@@ -8112,11 +8192,11 @@
       </c>
       <c r="O119" s="38"/>
       <c r="P119" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N119&lt;&gt;1,EDATE(O119,N119-1),"")</f>
         <v/>
       </c>
       <c r="Q119" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O119&lt;&gt;"",IFERROR(DATEDIF(O119,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8127,18 +8207,18 @@
       <c r="F120" s="40"/>
       <c r="G120" s="40"/>
       <c r="H120" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E120:G120)</f>
         <v>0</v>
       </c>
       <c r="I120" s="41"/>
       <c r="J120" s="41"/>
       <c r="K120" s="41"/>
       <c r="L120" s="41">
-        <f t="shared" si="17"/>
+        <f>I120/N120</f>
         <v>0</v>
       </c>
       <c r="M120" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L120/H120,"")</f>
         <v/>
       </c>
       <c r="N120" s="42">
@@ -8146,11 +8226,11 @@
       </c>
       <c r="O120" s="38"/>
       <c r="P120" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N120&lt;&gt;1,EDATE(O120,N120-1),"")</f>
         <v/>
       </c>
       <c r="Q120" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O120&lt;&gt;"",IFERROR(DATEDIF(O120,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8161,18 +8241,18 @@
       <c r="F121" s="40"/>
       <c r="G121" s="40"/>
       <c r="H121" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E121:G121)</f>
         <v>0</v>
       </c>
       <c r="I121" s="41"/>
       <c r="J121" s="41"/>
       <c r="K121" s="41"/>
       <c r="L121" s="41">
-        <f t="shared" si="17"/>
+        <f>I121/N121</f>
         <v>0</v>
       </c>
       <c r="M121" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L121/H121,"")</f>
         <v/>
       </c>
       <c r="N121" s="42">
@@ -8180,11 +8260,11 @@
       </c>
       <c r="O121" s="38"/>
       <c r="P121" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N121&lt;&gt;1,EDATE(O121,N121-1),"")</f>
         <v/>
       </c>
       <c r="Q121" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O121&lt;&gt;"",IFERROR(DATEDIF(O121,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8195,18 +8275,18 @@
       <c r="F122" s="40"/>
       <c r="G122" s="40"/>
       <c r="H122" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E122:G122)</f>
         <v>0</v>
       </c>
       <c r="I122" s="41"/>
       <c r="J122" s="41"/>
       <c r="K122" s="41"/>
       <c r="L122" s="41">
-        <f t="shared" si="17"/>
+        <f>I122/N122</f>
         <v>0</v>
       </c>
       <c r="M122" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L122/H122,"")</f>
         <v/>
       </c>
       <c r="N122" s="42">
@@ -8214,11 +8294,11 @@
       </c>
       <c r="O122" s="38"/>
       <c r="P122" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N122&lt;&gt;1,EDATE(O122,N122-1),"")</f>
         <v/>
       </c>
       <c r="Q122" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O122&lt;&gt;"",IFERROR(DATEDIF(O122,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8229,18 +8309,18 @@
       <c r="F123" s="40"/>
       <c r="G123" s="40"/>
       <c r="H123" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E123:G123)</f>
         <v>0</v>
       </c>
       <c r="I123" s="41"/>
       <c r="J123" s="41"/>
       <c r="K123" s="41"/>
       <c r="L123" s="41">
-        <f t="shared" si="17"/>
+        <f>I123/N123</f>
         <v>0</v>
       </c>
       <c r="M123" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L123/H123,"")</f>
         <v/>
       </c>
       <c r="N123" s="42">
@@ -8248,11 +8328,11 @@
       </c>
       <c r="O123" s="38"/>
       <c r="P123" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N123&lt;&gt;1,EDATE(O123,N123-1),"")</f>
         <v/>
       </c>
       <c r="Q123" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O123&lt;&gt;"",IFERROR(DATEDIF(O123,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8263,18 +8343,18 @@
       <c r="F124" s="40"/>
       <c r="G124" s="40"/>
       <c r="H124" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E124:G124)</f>
         <v>0</v>
       </c>
       <c r="I124" s="41"/>
       <c r="J124" s="41"/>
       <c r="K124" s="41"/>
       <c r="L124" s="41">
-        <f t="shared" si="17"/>
+        <f>I124/N124</f>
         <v>0</v>
       </c>
       <c r="M124" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L124/H124,"")</f>
         <v/>
       </c>
       <c r="N124" s="42">
@@ -8282,11 +8362,11 @@
       </c>
       <c r="O124" s="38"/>
       <c r="P124" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N124&lt;&gt;1,EDATE(O124,N124-1),"")</f>
         <v/>
       </c>
       <c r="Q124" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O124&lt;&gt;"",IFERROR(DATEDIF(O124,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8297,18 +8377,18 @@
       <c r="F125" s="40"/>
       <c r="G125" s="40"/>
       <c r="H125" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E125:G125)</f>
         <v>0</v>
       </c>
       <c r="I125" s="41"/>
       <c r="J125" s="41"/>
       <c r="K125" s="41"/>
       <c r="L125" s="41">
-        <f t="shared" si="17"/>
+        <f>I125/N125</f>
         <v>0</v>
       </c>
       <c r="M125" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L125/H125,"")</f>
         <v/>
       </c>
       <c r="N125" s="42">
@@ -8316,11 +8396,11 @@
       </c>
       <c r="O125" s="38"/>
       <c r="P125" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N125&lt;&gt;1,EDATE(O125,N125-1),"")</f>
         <v/>
       </c>
       <c r="Q125" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O125&lt;&gt;"",IFERROR(DATEDIF(O125,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8331,18 +8411,18 @@
       <c r="F126" s="40"/>
       <c r="G126" s="40"/>
       <c r="H126" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E126:G126)</f>
         <v>0</v>
       </c>
       <c r="I126" s="41"/>
       <c r="J126" s="41"/>
       <c r="K126" s="41"/>
       <c r="L126" s="41">
-        <f t="shared" si="17"/>
+        <f>I126/N126</f>
         <v>0</v>
       </c>
       <c r="M126" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L126/H126,"")</f>
         <v/>
       </c>
       <c r="N126" s="42">
@@ -8350,11 +8430,11 @@
       </c>
       <c r="O126" s="38"/>
       <c r="P126" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N126&lt;&gt;1,EDATE(O126,N126-1),"")</f>
         <v/>
       </c>
       <c r="Q126" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O126&lt;&gt;"",IFERROR(DATEDIF(O126,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8365,18 +8445,18 @@
       <c r="F127" s="40"/>
       <c r="G127" s="40"/>
       <c r="H127" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E127:G127)</f>
         <v>0</v>
       </c>
       <c r="I127" s="41"/>
       <c r="J127" s="41"/>
       <c r="K127" s="41"/>
       <c r="L127" s="41">
-        <f t="shared" si="17"/>
+        <f>I127/N127</f>
         <v>0</v>
       </c>
       <c r="M127" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L127/H127,"")</f>
         <v/>
       </c>
       <c r="N127" s="42">
@@ -8384,11 +8464,11 @@
       </c>
       <c r="O127" s="38"/>
       <c r="P127" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N127&lt;&gt;1,EDATE(O127,N127-1),"")</f>
         <v/>
       </c>
       <c r="Q127" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O127&lt;&gt;"",IFERROR(DATEDIF(O127,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8399,18 +8479,18 @@
       <c r="F128" s="40"/>
       <c r="G128" s="40"/>
       <c r="H128" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E128:G128)</f>
         <v>0</v>
       </c>
       <c r="I128" s="41"/>
       <c r="J128" s="41"/>
       <c r="K128" s="41"/>
       <c r="L128" s="41">
-        <f t="shared" si="17"/>
+        <f>I128/N128</f>
         <v>0</v>
       </c>
       <c r="M128" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L128/H128,"")</f>
         <v/>
       </c>
       <c r="N128" s="42">
@@ -8418,11 +8498,11 @@
       </c>
       <c r="O128" s="38"/>
       <c r="P128" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N128&lt;&gt;1,EDATE(O128,N128-1),"")</f>
         <v/>
       </c>
       <c r="Q128" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O128&lt;&gt;"",IFERROR(DATEDIF(O128,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8433,18 +8513,18 @@
       <c r="F129" s="40"/>
       <c r="G129" s="40"/>
       <c r="H129" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E129:G129)</f>
         <v>0</v>
       </c>
       <c r="I129" s="41"/>
       <c r="J129" s="41"/>
       <c r="K129" s="41"/>
       <c r="L129" s="41">
-        <f t="shared" si="17"/>
+        <f>I129/N129</f>
         <v>0</v>
       </c>
       <c r="M129" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L129/H129,"")</f>
         <v/>
       </c>
       <c r="N129" s="42">
@@ -8452,11 +8532,11 @@
       </c>
       <c r="O129" s="38"/>
       <c r="P129" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N129&lt;&gt;1,EDATE(O129,N129-1),"")</f>
         <v/>
       </c>
       <c r="Q129" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O129&lt;&gt;"",IFERROR(DATEDIF(O129,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8467,18 +8547,18 @@
       <c r="F130" s="40"/>
       <c r="G130" s="40"/>
       <c r="H130" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E130:G130)</f>
         <v>0</v>
       </c>
       <c r="I130" s="41"/>
       <c r="J130" s="41"/>
       <c r="K130" s="41"/>
       <c r="L130" s="41">
-        <f t="shared" si="17"/>
+        <f>I130/N130</f>
         <v>0</v>
       </c>
       <c r="M130" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L130/H130,"")</f>
         <v/>
       </c>
       <c r="N130" s="42">
@@ -8486,11 +8566,11 @@
       </c>
       <c r="O130" s="38"/>
       <c r="P130" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N130&lt;&gt;1,EDATE(O130,N130-1),"")</f>
         <v/>
       </c>
       <c r="Q130" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O130&lt;&gt;"",IFERROR(DATEDIF(O130,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8501,18 +8581,18 @@
       <c r="F131" s="40"/>
       <c r="G131" s="40"/>
       <c r="H131" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E131:G131)</f>
         <v>0</v>
       </c>
       <c r="I131" s="41"/>
       <c r="J131" s="41"/>
       <c r="K131" s="41"/>
       <c r="L131" s="41">
-        <f t="shared" si="17"/>
+        <f>I131/N131</f>
         <v>0</v>
       </c>
       <c r="M131" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L131/H131,"")</f>
         <v/>
       </c>
       <c r="N131" s="42">
@@ -8520,11 +8600,11 @@
       </c>
       <c r="O131" s="38"/>
       <c r="P131" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N131&lt;&gt;1,EDATE(O131,N131-1),"")</f>
         <v/>
       </c>
       <c r="Q131" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O131&lt;&gt;"",IFERROR(DATEDIF(O131,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8535,18 +8615,18 @@
       <c r="F132" s="40"/>
       <c r="G132" s="40"/>
       <c r="H132" s="40">
-        <f t="shared" si="16"/>
+        <f>COUNTA(E132:G132)</f>
         <v>0</v>
       </c>
       <c r="I132" s="41"/>
       <c r="J132" s="41"/>
       <c r="K132" s="41"/>
       <c r="L132" s="41">
-        <f t="shared" si="17"/>
+        <f>I132/N132</f>
         <v>0</v>
       </c>
       <c r="M132" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f>IFERROR(L132/H132,"")</f>
         <v/>
       </c>
       <c r="N132" s="42">
@@ -8554,11 +8634,11 @@
       </c>
       <c r="O132" s="38"/>
       <c r="P132" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(N132&lt;&gt;1,EDATE(O132,N132-1),"")</f>
         <v/>
       </c>
       <c r="Q132" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O132&lt;&gt;"",IFERROR(DATEDIF(O132,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8569,18 +8649,18 @@
       <c r="F133" s="40"/>
       <c r="G133" s="40"/>
       <c r="H133" s="40">
-        <f t="shared" ref="H133:H148" si="21">COUNTA(E133:G133)</f>
+        <f>COUNTA(E133:G133)</f>
         <v>0</v>
       </c>
       <c r="I133" s="41"/>
       <c r="J133" s="41"/>
       <c r="K133" s="41"/>
       <c r="L133" s="41">
-        <f t="shared" ref="L133:L148" si="22">I133/N133</f>
+        <f>I133/N133</f>
         <v>0</v>
       </c>
       <c r="M133" s="41" t="str">
-        <f t="shared" ref="M133:M148" si="23">IFERROR(L133/H133,"")</f>
+        <f>IFERROR(L133/H133,"")</f>
         <v/>
       </c>
       <c r="N133" s="42">
@@ -8588,11 +8668,11 @@
       </c>
       <c r="O133" s="38"/>
       <c r="P133" s="38" t="str">
-        <f t="shared" ref="P133:P148" si="24">IF(N133&lt;&gt;1,EDATE(O133,N133-1),"")</f>
+        <f>IF(N133&lt;&gt;1,EDATE(O133,N133-1),"")</f>
         <v/>
       </c>
       <c r="Q133" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O133&lt;&gt;"",IFERROR(DATEDIF(O133,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8603,18 +8683,18 @@
       <c r="F134" s="40"/>
       <c r="G134" s="40"/>
       <c r="H134" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E134:G134)</f>
         <v>0</v>
       </c>
       <c r="I134" s="41"/>
       <c r="J134" s="41"/>
       <c r="K134" s="41"/>
       <c r="L134" s="41">
-        <f t="shared" si="22"/>
+        <f>I134/N134</f>
         <v>0</v>
       </c>
       <c r="M134" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L134/H134,"")</f>
         <v/>
       </c>
       <c r="N134" s="42">
@@ -8622,11 +8702,11 @@
       </c>
       <c r="O134" s="38"/>
       <c r="P134" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N134&lt;&gt;1,EDATE(O134,N134-1),"")</f>
         <v/>
       </c>
       <c r="Q134" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O134&lt;&gt;"",IFERROR(DATEDIF(O134,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8637,18 +8717,18 @@
       <c r="F135" s="40"/>
       <c r="G135" s="40"/>
       <c r="H135" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E135:G135)</f>
         <v>0</v>
       </c>
       <c r="I135" s="41"/>
       <c r="J135" s="41"/>
       <c r="K135" s="41"/>
       <c r="L135" s="41">
-        <f t="shared" si="22"/>
+        <f>I135/N135</f>
         <v>0</v>
       </c>
       <c r="M135" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L135/H135,"")</f>
         <v/>
       </c>
       <c r="N135" s="42">
@@ -8656,11 +8736,11 @@
       </c>
       <c r="O135" s="38"/>
       <c r="P135" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N135&lt;&gt;1,EDATE(O135,N135-1),"")</f>
         <v/>
       </c>
       <c r="Q135" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O135&lt;&gt;"",IFERROR(DATEDIF(O135,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8671,18 +8751,18 @@
       <c r="F136" s="40"/>
       <c r="G136" s="40"/>
       <c r="H136" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E136:G136)</f>
         <v>0</v>
       </c>
       <c r="I136" s="41"/>
       <c r="J136" s="41"/>
       <c r="K136" s="41"/>
       <c r="L136" s="41">
-        <f t="shared" si="22"/>
+        <f>I136/N136</f>
         <v>0</v>
       </c>
       <c r="M136" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L136/H136,"")</f>
         <v/>
       </c>
       <c r="N136" s="42">
@@ -8690,11 +8770,11 @@
       </c>
       <c r="O136" s="38"/>
       <c r="P136" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N136&lt;&gt;1,EDATE(O136,N136-1),"")</f>
         <v/>
       </c>
       <c r="Q136" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O136&lt;&gt;"",IFERROR(DATEDIF(O136,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8705,18 +8785,18 @@
       <c r="F137" s="40"/>
       <c r="G137" s="40"/>
       <c r="H137" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E137:G137)</f>
         <v>0</v>
       </c>
       <c r="I137" s="41"/>
       <c r="J137" s="41"/>
       <c r="K137" s="41"/>
       <c r="L137" s="41">
-        <f t="shared" si="22"/>
+        <f>I137/N137</f>
         <v>0</v>
       </c>
       <c r="M137" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L137/H137,"")</f>
         <v/>
       </c>
       <c r="N137" s="42">
@@ -8724,11 +8804,11 @@
       </c>
       <c r="O137" s="38"/>
       <c r="P137" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N137&lt;&gt;1,EDATE(O137,N137-1),"")</f>
         <v/>
       </c>
       <c r="Q137" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O137&lt;&gt;"",IFERROR(DATEDIF(O137,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8739,18 +8819,18 @@
       <c r="F138" s="40"/>
       <c r="G138" s="40"/>
       <c r="H138" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E138:G138)</f>
         <v>0</v>
       </c>
       <c r="I138" s="41"/>
       <c r="J138" s="41"/>
       <c r="K138" s="41"/>
       <c r="L138" s="41">
-        <f t="shared" si="22"/>
+        <f>I138/N138</f>
         <v>0</v>
       </c>
       <c r="M138" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L138/H138,"")</f>
         <v/>
       </c>
       <c r="N138" s="42">
@@ -8758,11 +8838,11 @@
       </c>
       <c r="O138" s="38"/>
       <c r="P138" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N138&lt;&gt;1,EDATE(O138,N138-1),"")</f>
         <v/>
       </c>
       <c r="Q138" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O138&lt;&gt;"",IFERROR(DATEDIF(O138,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8773,18 +8853,18 @@
       <c r="F139" s="40"/>
       <c r="G139" s="40"/>
       <c r="H139" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E139:G139)</f>
         <v>0</v>
       </c>
       <c r="I139" s="41"/>
       <c r="J139" s="41"/>
       <c r="K139" s="41"/>
       <c r="L139" s="41">
-        <f t="shared" si="22"/>
+        <f>I139/N139</f>
         <v>0</v>
       </c>
       <c r="M139" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L139/H139,"")</f>
         <v/>
       </c>
       <c r="N139" s="42">
@@ -8792,11 +8872,11 @@
       </c>
       <c r="O139" s="38"/>
       <c r="P139" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N139&lt;&gt;1,EDATE(O139,N139-1),"")</f>
         <v/>
       </c>
       <c r="Q139" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O139&lt;&gt;"",IFERROR(DATEDIF(O139,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8807,18 +8887,18 @@
       <c r="F140" s="40"/>
       <c r="G140" s="40"/>
       <c r="H140" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E140:G140)</f>
         <v>0</v>
       </c>
       <c r="I140" s="41"/>
       <c r="J140" s="41"/>
       <c r="K140" s="41"/>
       <c r="L140" s="41">
-        <f t="shared" si="22"/>
+        <f>I140/N140</f>
         <v>0</v>
       </c>
       <c r="M140" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L140/H140,"")</f>
         <v/>
       </c>
       <c r="N140" s="42">
@@ -8826,11 +8906,11 @@
       </c>
       <c r="O140" s="38"/>
       <c r="P140" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N140&lt;&gt;1,EDATE(O140,N140-1),"")</f>
         <v/>
       </c>
       <c r="Q140" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O140&lt;&gt;"",IFERROR(DATEDIF(O140,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8841,18 +8921,18 @@
       <c r="F141" s="40"/>
       <c r="G141" s="40"/>
       <c r="H141" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E141:G141)</f>
         <v>0</v>
       </c>
       <c r="I141" s="41"/>
       <c r="J141" s="41"/>
       <c r="K141" s="41"/>
       <c r="L141" s="41">
-        <f t="shared" si="22"/>
+        <f>I141/N141</f>
         <v>0</v>
       </c>
       <c r="M141" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L141/H141,"")</f>
         <v/>
       </c>
       <c r="N141" s="42">
@@ -8860,11 +8940,11 @@
       </c>
       <c r="O141" s="38"/>
       <c r="P141" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N141&lt;&gt;1,EDATE(O141,N141-1),"")</f>
         <v/>
       </c>
       <c r="Q141" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O141&lt;&gt;"",IFERROR(DATEDIF(O141,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8875,18 +8955,18 @@
       <c r="F142" s="40"/>
       <c r="G142" s="40"/>
       <c r="H142" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E142:G142)</f>
         <v>0</v>
       </c>
       <c r="I142" s="41"/>
       <c r="J142" s="41"/>
       <c r="K142" s="41"/>
       <c r="L142" s="41">
-        <f t="shared" si="22"/>
+        <f>I142/N142</f>
         <v>0</v>
       </c>
       <c r="M142" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L142/H142,"")</f>
         <v/>
       </c>
       <c r="N142" s="42">
@@ -8894,11 +8974,11 @@
       </c>
       <c r="O142" s="38"/>
       <c r="P142" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N142&lt;&gt;1,EDATE(O142,N142-1),"")</f>
         <v/>
       </c>
       <c r="Q142" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O142&lt;&gt;"",IFERROR(DATEDIF(O142,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8909,18 +8989,18 @@
       <c r="F143" s="40"/>
       <c r="G143" s="40"/>
       <c r="H143" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E143:G143)</f>
         <v>0</v>
       </c>
       <c r="I143" s="41"/>
       <c r="J143" s="41"/>
       <c r="K143" s="41"/>
       <c r="L143" s="41">
-        <f t="shared" si="22"/>
+        <f>I143/N143</f>
         <v>0</v>
       </c>
       <c r="M143" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L143/H143,"")</f>
         <v/>
       </c>
       <c r="N143" s="42">
@@ -8928,11 +9008,11 @@
       </c>
       <c r="O143" s="38"/>
       <c r="P143" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N143&lt;&gt;1,EDATE(O143,N143-1),"")</f>
         <v/>
       </c>
       <c r="Q143" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O143&lt;&gt;"",IFERROR(DATEDIF(O143,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8943,18 +9023,18 @@
       <c r="F144" s="40"/>
       <c r="G144" s="40"/>
       <c r="H144" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E144:G144)</f>
         <v>0</v>
       </c>
       <c r="I144" s="41"/>
       <c r="J144" s="41"/>
       <c r="K144" s="41"/>
       <c r="L144" s="41">
-        <f t="shared" si="22"/>
+        <f>I144/N144</f>
         <v>0</v>
       </c>
       <c r="M144" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L144/H144,"")</f>
         <v/>
       </c>
       <c r="N144" s="42">
@@ -8962,11 +9042,11 @@
       </c>
       <c r="O144" s="38"/>
       <c r="P144" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N144&lt;&gt;1,EDATE(O144,N144-1),"")</f>
         <v/>
       </c>
       <c r="Q144" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O144&lt;&gt;"",IFERROR(DATEDIF(O144,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8977,18 +9057,18 @@
       <c r="F145" s="40"/>
       <c r="G145" s="40"/>
       <c r="H145" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E145:G145)</f>
         <v>0</v>
       </c>
       <c r="I145" s="41"/>
       <c r="J145" s="41"/>
       <c r="K145" s="41"/>
       <c r="L145" s="41">
-        <f t="shared" si="22"/>
+        <f>I145/N145</f>
         <v>0</v>
       </c>
       <c r="M145" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L145/H145,"")</f>
         <v/>
       </c>
       <c r="N145" s="42">
@@ -8996,11 +9076,11 @@
       </c>
       <c r="O145" s="38"/>
       <c r="P145" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N145&lt;&gt;1,EDATE(O145,N145-1),"")</f>
         <v/>
       </c>
       <c r="Q145" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O145&lt;&gt;"",IFERROR(DATEDIF(O145,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -9011,18 +9091,18 @@
       <c r="F146" s="40"/>
       <c r="G146" s="40"/>
       <c r="H146" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E146:G146)</f>
         <v>0</v>
       </c>
       <c r="I146" s="41"/>
       <c r="J146" s="41"/>
       <c r="K146" s="41"/>
       <c r="L146" s="41">
-        <f t="shared" si="22"/>
+        <f>I146/N146</f>
         <v>0</v>
       </c>
       <c r="M146" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L146/H146,"")</f>
         <v/>
       </c>
       <c r="N146" s="42">
@@ -9030,11 +9110,11 @@
       </c>
       <c r="O146" s="38"/>
       <c r="P146" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N146&lt;&gt;1,EDATE(O146,N146-1),"")</f>
         <v/>
       </c>
       <c r="Q146" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O146&lt;&gt;"",IFERROR(DATEDIF(O146,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -9045,18 +9125,18 @@
       <c r="F147" s="40"/>
       <c r="G147" s="40"/>
       <c r="H147" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E147:G147)</f>
         <v>0</v>
       </c>
       <c r="I147" s="41"/>
       <c r="J147" s="41"/>
       <c r="K147" s="41"/>
       <c r="L147" s="41">
-        <f t="shared" si="22"/>
+        <f>I147/N147</f>
         <v>0</v>
       </c>
       <c r="M147" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L147/H147,"")</f>
         <v/>
       </c>
       <c r="N147" s="42">
@@ -9064,11 +9144,11 @@
       </c>
       <c r="O147" s="44"/>
       <c r="P147" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N147&lt;&gt;1,EDATE(O147,N147-1),"")</f>
         <v/>
       </c>
       <c r="Q147" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O147&lt;&gt;"",IFERROR(DATEDIF(O147,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -9079,18 +9159,18 @@
       <c r="F148" s="40"/>
       <c r="G148" s="40"/>
       <c r="H148" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTA(E148:G148)</f>
         <v>0</v>
       </c>
       <c r="I148" s="41"/>
       <c r="J148" s="41"/>
       <c r="K148" s="41"/>
       <c r="L148" s="41">
-        <f t="shared" si="22"/>
+        <f>I148/N148</f>
         <v>0</v>
       </c>
       <c r="M148" s="41" t="str">
-        <f t="shared" si="23"/>
+        <f>IFERROR(L148/H148,"")</f>
         <v/>
       </c>
       <c r="N148" s="42">
@@ -9098,11 +9178,11 @@
       </c>
       <c r="O148" s="38"/>
       <c r="P148" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f>IF(N148&lt;&gt;1,EDATE(O148,N148-1),"")</f>
         <v/>
       </c>
       <c r="Q148" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f ca="1">IF(O148&lt;&gt;"",IFERROR(DATEDIF(O148,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -9124,34 +9204,38 @@
       <c r="Q149" s="40"/>
     </row>
   </sheetData>
-  <autoFilter ref="C5:Q149" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="C5:Q149" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q149">
+      <sortCondition sortBy="cellColor" ref="J5" dxfId="24"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="I6:I149">
-    <cfRule type="cellIs" dxfId="23" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J149">
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="6" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K149">
-    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K60">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K98">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+  <conditionalFormatting sqref="K98:K99">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9254,7 +9338,7 @@
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1">
       <c r="D4" s="58" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E4" s="59" t="s">
         <v>1</v>
@@ -9295,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>1</v>
@@ -9337,7 +9421,7 @@
         <v>2382.0700000000002</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E6" s="39" t="s">
         <v>1</v>
@@ -9375,7 +9459,7 @@
     <row r="7" spans="2:18" ht="16.5" customHeight="1">
       <c r="B7" s="63"/>
       <c r="D7" s="57" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E7" s="39" t="s">
         <v>1</v>
@@ -9415,7 +9499,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="E8" s="39" t="s">
         <v>1</v>
@@ -9456,7 +9540,7 @@
         <v>3382.07</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E9" s="39" t="s">
         <v>1</v>
@@ -9494,7 +9578,7 @@
     </row>
     <row r="10" spans="2:18">
       <c r="D10" s="57" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="40" t="s">
@@ -9695,7 +9779,7 @@
     <row r="1" spans="2:15">
       <c r="G1" s="2"/>
       <c r="N1" s="50" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="2:15" ht="14.25" customHeight="1">
@@ -9705,23 +9789,23 @@
     <row r="3" spans="2:15" ht="27.75" customHeight="1">
       <c r="G3" s="2"/>
       <c r="L3" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="M3" s="75" t="s">
-        <v>165</v>
+        <v>169</v>
+      </c>
+      <c r="M3" s="77" t="s">
+        <v>170</v>
       </c>
       <c r="N3" s="46">
         <f>SUM(N5:N21)</f>
-        <v>5351</v>
+        <v>5250</v>
       </c>
       <c r="O3" s="16"/>
     </row>
     <row r="4" spans="2:15">
       <c r="G4" s="2"/>
       <c r="L4" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="M4" s="76"/>
+        <v>171</v>
+      </c>
+      <c r="M4" s="78"/>
       <c r="N4" s="52"/>
     </row>
     <row r="5" spans="2:15">
@@ -9730,7 +9814,7 @@
       <c r="F5" s="16"/>
       <c r="G5" s="31"/>
       <c r="L5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="N5" s="1">
         <v>4912</v>
@@ -9739,12 +9823,7 @@
     </row>
     <row r="6" spans="2:15">
       <c r="G6" s="2"/>
-      <c r="L6" t="s">
-        <v>168</v>
-      </c>
-      <c r="N6" s="1">
-        <v>101</v>
-      </c>
+      <c r="N6" s="1"/>
     </row>
     <row r="7" spans="2:15">
       <c r="G7" s="2"/>
@@ -9754,10 +9833,10 @@
       <c r="F8" s="16"/>
       <c r="G8" s="53"/>
       <c r="L8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M8" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N8" s="1">
         <v>338</v>
@@ -9765,41 +9844,41 @@
     </row>
     <row r="9" spans="2:15">
       <c r="F9" s="50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G9" s="31"/>
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="2:15">
       <c r="E10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>10945.150000000001</v>
+        <v>6741.1500000000015</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I10" s="54" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="N10" s="46"/>
     </row>
     <row r="11" spans="2:15">
       <c r="E11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>10945.150000000001</v>
+        <v>6741.1500000000015</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>10945.150000000001</v>
+        <v>6741.1500000000015</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -9813,7 +9892,7 @@
     </row>
     <row r="12" spans="2:15">
       <c r="F12" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
@@ -9822,7 +9901,7 @@
     </row>
     <row r="13" spans="2:15">
       <c r="F13" s="74" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="74"/>
@@ -9833,7 +9912,7 @@
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
       <c r="F14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="56"/>
@@ -9844,7 +9923,7 @@
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
       <c r="F15" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G15" s="56">
         <v>773.35</v>
@@ -9857,7 +9936,7 @@
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
       <c r="F16" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G16" s="56">
         <v>-5148</v>
@@ -9870,7 +9949,7 @@
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
       <c r="F17" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G17" s="56">
         <v>-168</v>
@@ -9883,7 +9962,7 @@
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
       <c r="F18" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G18" s="56">
         <v>-1700</v>
@@ -9896,7 +9975,7 @@
       <c r="C19" s="56"/>
       <c r="D19" s="56"/>
       <c r="F19" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G19" s="56">
         <v>5148</v>
@@ -9909,7 +9988,7 @@
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
       <c r="F20" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G20" s="56">
         <v>-4938</v>
@@ -9922,7 +10001,7 @@
       <c r="C21" s="56"/>
       <c r="D21" s="56"/>
       <c r="F21" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G21" s="56">
         <v>-1595</v>
@@ -9935,7 +10014,7 @@
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
       <c r="F22" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G22" s="56">
         <v>-4677</v>
@@ -9948,7 +10027,7 @@
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
       <c r="F23" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G23" s="56">
         <v>-200</v>
@@ -9961,7 +10040,7 @@
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
       <c r="F24" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G24" s="56">
         <v>4677</v>
@@ -9974,7 +10053,7 @@
       <c r="C25" s="56"/>
       <c r="D25" s="56"/>
       <c r="F25" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G25" s="56">
         <v>-750</v>
@@ -9987,7 +10066,7 @@
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
       <c r="F26" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G26" s="56">
         <v>-652</v>
@@ -10000,7 +10079,7 @@
       <c r="C27" s="56"/>
       <c r="D27" s="56"/>
       <c r="F27" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G27" s="56">
         <v>11100</v>
@@ -10013,7 +10092,7 @@
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
       <c r="F28" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G28" s="56">
         <v>-396</v>
@@ -10026,7 +10105,7 @@
       <c r="C29" s="56"/>
       <c r="D29" s="56"/>
       <c r="F29" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G29" s="56">
         <v>-4211</v>
@@ -10039,7 +10118,7 @@
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
       <c r="F30" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G30" s="56">
         <v>-450</v>
@@ -10052,7 +10131,7 @@
       <c r="C31" s="56"/>
       <c r="D31" s="56"/>
       <c r="F31" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G31" s="56">
         <v>-1197</v>
@@ -10065,7 +10144,7 @@
       <c r="C32" s="56"/>
       <c r="D32" s="56"/>
       <c r="F32" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="G32" s="56">
         <v>-315</v>
@@ -10078,7 +10157,7 @@
       <c r="C33" s="56"/>
       <c r="D33" s="56"/>
       <c r="F33" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G33" s="56">
         <v>-830</v>
@@ -10091,7 +10170,7 @@
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
       <c r="F34" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G34" s="56">
         <v>4211</v>
@@ -10104,7 +10183,7 @@
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
       <c r="F35" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G35" s="56">
         <v>-200</v>
@@ -10117,7 +10196,7 @@
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
       <c r="F36" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G36" s="56">
         <v>10000</v>
@@ -10130,7 +10209,7 @@
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
       <c r="F37" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G37" s="56">
         <v>-200</v>
@@ -10143,7 +10222,7 @@
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
       <c r="F38" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G38" s="56">
         <v>-381</v>
@@ -10156,7 +10235,7 @@
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
       <c r="F39" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G39" s="56">
         <v>-4911</v>
@@ -10170,7 +10249,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G40" s="56">
         <v>-5700</v>
@@ -10183,7 +10262,7 @@
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
       <c r="F41" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G41" s="56">
         <v>-400</v>
@@ -10196,7 +10275,7 @@
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
       <c r="F42" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G42" s="56">
         <v>-450</v>
@@ -10209,7 +10288,7 @@
       <c r="C43" s="56"/>
       <c r="D43" s="56"/>
       <c r="F43" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G43" s="56">
         <v>-640</v>
@@ -10223,7 +10302,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G44" s="56">
         <v>5700</v>
@@ -10236,7 +10315,7 @@
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
       <c r="F45" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G45" s="56">
         <v>-130</v>
@@ -10249,7 +10328,7 @@
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
       <c r="F46" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G46" s="56">
         <v>-250</v>
@@ -10262,7 +10341,7 @@
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
       <c r="F47" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G47" s="56">
         <v>-112.2</v>
@@ -10275,7 +10354,7 @@
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
       <c r="F48" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G48" s="56">
         <v>4911</v>
@@ -10288,7 +10367,7 @@
       <c r="C49" s="56"/>
       <c r="D49" s="56"/>
       <c r="F49" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G49" s="56">
         <v>-3000</v>
@@ -10301,7 +10380,7 @@
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
       <c r="F50" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G50" s="56">
         <v>-4000</v>
@@ -10314,7 +10393,7 @@
       <c r="C51" s="56"/>
       <c r="D51" s="56"/>
       <c r="F51" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G51" s="56">
         <v>-200</v>
@@ -10327,7 +10406,7 @@
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
       <c r="F52" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G52" s="56">
         <v>-4612</v>
@@ -10338,7 +10417,7 @@
     </row>
     <row r="53" spans="3:14" outlineLevel="1">
       <c r="F53" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G53" s="56">
         <v>-700</v>
@@ -10349,7 +10428,7 @@
     </row>
     <row r="54" spans="3:14" outlineLevel="1">
       <c r="F54" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G54" s="56">
         <v>-880</v>
@@ -10360,7 +10439,7 @@
     </row>
     <row r="55" spans="3:14" outlineLevel="1">
       <c r="F55" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G55" s="56">
         <v>-310</v>
@@ -10371,7 +10450,7 @@
     </row>
     <row r="56" spans="3:14">
       <c r="F56" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G56" s="56">
         <v>-250</v>
@@ -10382,7 +10461,7 @@
     </row>
     <row r="57" spans="3:14">
       <c r="F57" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G57" s="56">
         <v>4690</v>
@@ -10393,7 +10472,7 @@
     </row>
     <row r="58" spans="3:14">
       <c r="F58" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G58" s="56">
         <v>-4440</v>
@@ -10404,7 +10483,7 @@
     </row>
     <row r="59" spans="3:14">
       <c r="F59" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G59" s="56">
         <v>-4697</v>
@@ -10414,7 +10493,7 @@
     </row>
     <row r="60" spans="3:14">
       <c r="F60" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G60" s="56">
         <v>-2500</v>
@@ -10424,7 +10503,7 @@
     </row>
     <row r="61" spans="3:14">
       <c r="F61" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G61" s="56">
         <v>-126</v>
@@ -10434,7 +10513,7 @@
     </row>
     <row r="62" spans="3:14">
       <c r="F62" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G62" s="56">
         <v>4742</v>
@@ -10444,7 +10523,7 @@
     </row>
     <row r="63" spans="3:14">
       <c r="F63" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G63" s="56">
         <v>-410</v>
@@ -10459,7 +10538,7 @@
     </row>
     <row r="65" spans="2:9">
       <c r="F65" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G65" s="56">
         <v>3320</v>
@@ -10469,7 +10548,7 @@
     </row>
     <row r="66" spans="2:9">
       <c r="F66" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G66" s="56">
         <v>4090</v>
@@ -10479,7 +10558,7 @@
     </row>
     <row r="67" spans="2:9">
       <c r="F67" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G67" s="56">
         <v>-5688</v>
@@ -10489,7 +10568,7 @@
     </row>
     <row r="68" spans="2:9">
       <c r="F68" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G68" s="56">
         <v>-4433</v>
@@ -10499,7 +10578,7 @@
     </row>
     <row r="69" spans="2:9">
       <c r="F69" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G69" s="56">
         <v>-250</v>
@@ -10509,7 +10588,7 @@
     </row>
     <row r="70" spans="2:9">
       <c r="F70" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G70" s="56">
         <v>-99</v>
@@ -10519,7 +10598,7 @@
     </row>
     <row r="71" spans="2:9">
       <c r="F71" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G71" s="56">
         <v>320</v>
@@ -10529,7 +10608,7 @@
     </row>
     <row r="72" spans="2:9">
       <c r="F72" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G72" s="56">
         <v>-1572</v>
@@ -10544,7 +10623,7 @@
     </row>
     <row r="74" spans="2:9">
       <c r="F74" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G74" s="56">
         <v>4433</v>
@@ -10554,7 +10633,7 @@
     </row>
     <row r="75" spans="2:9">
       <c r="F75" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G75" s="56">
         <v>8000</v>
@@ -10564,7 +10643,7 @@
     </row>
     <row r="76" spans="2:9">
       <c r="F76" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G76" s="56">
         <v>-1344</v>
@@ -10574,7 +10653,7 @@
     </row>
     <row r="77" spans="2:9">
       <c r="F77" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G77" s="56">
         <v>-308</v>
@@ -10583,13 +10662,18 @@
       <c r="I77" s="56"/>
     </row>
     <row r="78" spans="2:9" ht="14.25" customHeight="1">
-      <c r="G78" s="56"/>
+      <c r="F78" t="s">
+        <v>189</v>
+      </c>
+      <c r="G78" s="56">
+        <v>-4204</v>
+      </c>
       <c r="H78" s="56"/>
       <c r="I78" s="56"/>
     </row>
     <row r="79" spans="2:9">
       <c r="B79" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C79" s="56">
         <v>-50</v>
@@ -10601,21 +10685,17 @@
     </row>
     <row r="80" spans="2:9">
       <c r="B80" t="s">
-        <v>226</v>
-      </c>
-      <c r="C80" s="56">
-        <v>500</v>
-      </c>
-      <c r="D80" s="56">
-        <v>300</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C80" s="56"/>
+      <c r="D80" s="56"/>
       <c r="G80" s="56"/>
       <c r="H80" s="56"/>
       <c r="I80" s="56"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C81" s="56">
         <v>8000</v>
@@ -10626,7 +10706,12 @@
       <c r="I81" s="56"/>
     </row>
     <row r="82" spans="2:9">
-      <c r="C82" s="56"/>
+      <c r="B82" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="56">
+        <v>4124</v>
+      </c>
       <c r="D82" s="56"/>
       <c r="G82" s="56"/>
       <c r="H82" s="56"/>
@@ -10634,10 +10719,10 @@
     </row>
     <row r="83" spans="2:9">
       <c r="B83" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C83" s="56">
-        <v>-90</v>
+        <v>-50</v>
       </c>
       <c r="D83" s="56"/>
       <c r="G83" s="56"/>
@@ -10646,7 +10731,7 @@
     </row>
     <row r="84" spans="2:9">
       <c r="B84" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C84" s="56">
         <v>2000</v>
@@ -10660,7 +10745,7 @@
     </row>
     <row r="85" spans="2:9">
       <c r="B85" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C85" s="56">
         <v>-12807</v>
@@ -10679,7 +10764,7 @@
     </row>
     <row r="87" spans="2:9">
       <c r="B87" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C87" s="56">
         <v>5170</v>
@@ -10698,7 +10783,7 @@
     </row>
     <row r="89" spans="2:9">
       <c r="B89" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C89" s="56">
         <v>2000</v>
@@ -10712,10 +10797,10 @@
     </row>
     <row r="90" spans="2:9">
       <c r="B90" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C90" s="56">
-        <v>-90</v>
+        <v>-50</v>
       </c>
       <c r="D90" s="56"/>
       <c r="G90" s="56"/>
@@ -10724,10 +10809,10 @@
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C91" s="56">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="D91" s="56"/>
       <c r="G91" s="56"/>
@@ -10743,7 +10828,7 @@
     </row>
     <row r="93" spans="2:9">
       <c r="B93" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C93" s="56">
         <v>2000</v>
@@ -10757,7 +10842,7 @@
     </row>
     <row r="94" spans="2:9">
       <c r="B94" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C94" s="56">
         <v>-50</v>
@@ -10769,7 +10854,7 @@
     </row>
     <row r="95" spans="2:9">
       <c r="B95" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C95" s="56">
         <v>300</v>
@@ -10788,7 +10873,7 @@
     </row>
     <row r="97" spans="2:9">
       <c r="B97" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C97" s="56">
         <v>2000</v>
@@ -10802,7 +10887,7 @@
     </row>
     <row r="98" spans="2:9">
       <c r="B98" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C98" s="56">
         <v>8000</v>
@@ -10814,7 +10899,7 @@
     </row>
     <row r="99" spans="2:9">
       <c r="B99" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C99" s="56">
         <v>4180</v>
@@ -10833,7 +10918,7 @@
     </row>
     <row r="101" spans="2:9">
       <c r="B101" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C101" s="56">
         <v>2000</v>
@@ -10847,7 +10932,7 @@
     </row>
     <row r="102" spans="2:9">
       <c r="B102" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C102" s="56">
         <v>2000</v>
@@ -10861,7 +10946,7 @@
     </row>
     <row r="103" spans="2:9">
       <c r="B103" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C103" s="56">
         <v>2000</v>
@@ -10882,7 +10967,7 @@
     </row>
     <row r="105" spans="2:9">
       <c r="B105" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C105" s="56">
         <v>-20000</v>
@@ -10901,7 +10986,7 @@
     </row>
     <row r="107" spans="2:9">
       <c r="B107" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C107" s="56">
         <v>2000</v>
@@ -10915,7 +11000,7 @@
     </row>
     <row r="108" spans="2:9">
       <c r="B108" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C108" s="56">
         <v>2000</v>
@@ -10929,7 +11014,7 @@
     </row>
     <row r="109" spans="2:9">
       <c r="B109" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C109" s="56">
         <v>8000</v>
@@ -10941,7 +11026,7 @@
     </row>
     <row r="110" spans="2:9">
       <c r="B110" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C110" s="56">
         <v>2000</v>
@@ -10955,7 +11040,7 @@
     </row>
     <row r="111" spans="2:9">
       <c r="B111" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C111" s="56">
         <v>2000</v>
@@ -12163,54 +12248,78 @@
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C79:D111">
-    <cfRule type="cellIs" dxfId="17" priority="101" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="109" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="110" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:D52">
-    <cfRule type="cellIs" dxfId="15" priority="95" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="103" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="96" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="104" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G120:G1048576">
-    <cfRule type="cellIs" dxfId="13" priority="97" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="105" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="98" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="106" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I76 G102:I102 I77:I101 G110:I119 I103:I109">
-    <cfRule type="cellIs" dxfId="11" priority="11" operator="greaterThan">
+  <conditionalFormatting sqref="G14:I76 G112:I119 I77:I111">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H120:I266">
-    <cfRule type="cellIs" dxfId="9" priority="99" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="107" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="100" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="108" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G77:H78">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="17" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G88:H101">
+  <conditionalFormatting sqref="G88:H88">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G104:H104">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G81:H87">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G89:H103">
     <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -12218,7 +12327,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G103:H109">
+  <conditionalFormatting sqref="G105:H111">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -12226,7 +12335,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G79:H87">
+  <conditionalFormatting sqref="G79:H80">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -12252,94 +12361,76 @@
   <sheetData>
     <row r="1" spans="2:4">
       <c r="B1" s="65" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="2:4">
       <c r="B2" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="40" t="s">
-        <v>251</v>
-      </c>
+      <c r="C2" s="40"/>
       <c r="D2" s="57"/>
     </row>
     <row r="3" spans="2:4">
       <c r="B3" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>251</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C3" s="40"/>
       <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="57" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>252</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="C4" s="40"/>
       <c r="D4" s="57"/>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>251</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="C5" s="40"/>
       <c r="D5" s="57"/>
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="57" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>252</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C6" s="40"/>
       <c r="D6" s="57"/>
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>252</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C7" s="40"/>
       <c r="D7" s="57"/>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>252</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C8" s="40"/>
       <c r="D8" s="57"/>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="57" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>252</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C9" s="40"/>
       <c r="D9" s="57"/>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>251</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="C10" s="40"/>
       <c r="D10" s="57"/>
     </row>
     <row r="17" spans="3:3">

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/FEA781441E4F247C/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3D0428C4E0E4AF08C16F331DF5B9D519ABAF25DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_3D0428C4E0E4AF08C16F331DF5B9D519ABAF25DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8EF7688-1AC3-477A-BC02-719C8F704859}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,8 +25,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Itaú!$C$4:$Q$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$100</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -43,62 +46,164 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="255">
+  <si>
+    <t>Valor para o mês</t>
+  </si>
+  <si>
+    <t>Guilherme</t>
+  </si>
+  <si>
+    <t>Stella</t>
+  </si>
+  <si>
+    <t>Salário</t>
+  </si>
+  <si>
+    <t>Custos Totais</t>
+  </si>
+  <si>
+    <t>Resto o mês anterior</t>
+  </si>
+  <si>
+    <t>Cartão Itaú</t>
+  </si>
+  <si>
+    <t>Cartão NuBank</t>
+  </si>
+  <si>
+    <t>Compensasão no NuBank</t>
+  </si>
+  <si>
+    <t>Contas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Aluguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Internet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Luz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Água</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Gás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Seguranças+Câmera</t>
+  </si>
+  <si>
+    <t>Compensasões no cartão da Stella</t>
+  </si>
+  <si>
+    <t>Dinheiro para NuConta</t>
+  </si>
+  <si>
+    <t>Dinheiro Guardado na poupança</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       Seu João</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       Seguro</t>
+  </si>
+  <si>
+    <t>Aluguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Recolhimento INSS</t>
+  </si>
+  <si>
+    <t>Stella tem que transferir:</t>
+  </si>
+  <si>
+    <t>Valor fixado (Stella)</t>
+  </si>
+  <si>
+    <t>Data de fixação</t>
+  </si>
+  <si>
+    <t>Status pagamento Stella</t>
+  </si>
+  <si>
+    <t>Aguardando</t>
+  </si>
+  <si>
+    <t>Itaú Total</t>
+  </si>
+  <si>
+    <t>Pais</t>
+  </si>
+  <si>
+    <t>Data de compra</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Responsável 1</t>
+  </si>
+  <si>
+    <t>Responsável 2</t>
+  </si>
+  <si>
+    <t>Responsável 3</t>
+  </si>
+  <si>
+    <t>Divisão</t>
+  </si>
+  <si>
+    <t>Valor Total</t>
+  </si>
+  <si>
+    <t>Modo de pagamento</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Valor da Parcela</t>
+  </si>
+  <si>
+    <t>Valor por responsável</t>
+  </si>
+  <si>
+    <t>Parcelas</t>
+  </si>
+  <si>
+    <t>Primeira Parcela</t>
+  </si>
+  <si>
+    <t>Última Parcela</t>
+  </si>
+  <si>
+    <t>Parcelas pagas (vira todo dia 10)</t>
+  </si>
+  <si>
+    <t>ADIANTAR EM OUTUBRO</t>
+  </si>
+  <si>
+    <t>Control Resonant</t>
+  </si>
+  <si>
+    <t>Parcelado</t>
+  </si>
+  <si>
+    <t>Jogos</t>
+  </si>
   <si>
     <t>NuBank Total</t>
   </si>
   <si>
-    <t>Guilherme</t>
-  </si>
-  <si>
-    <t>Stella</t>
-  </si>
-  <si>
-    <t>Pais</t>
-  </si>
-  <si>
-    <t>Descrição</t>
-  </si>
-  <si>
-    <t>Responsável 1</t>
-  </si>
-  <si>
-    <t>Responsável 2</t>
-  </si>
-  <si>
-    <t>Responsável 3</t>
-  </si>
-  <si>
-    <t>Divisão</t>
-  </si>
-  <si>
-    <t>Valor Total</t>
-  </si>
-  <si>
     <t>Modo de Pagamento</t>
   </si>
   <si>
-    <t>Categoria</t>
-  </si>
-  <si>
-    <t>Valor da Parcela</t>
-  </si>
-  <si>
-    <t>Valor por responsável</t>
-  </si>
-  <si>
-    <t>Parcelas</t>
-  </si>
-  <si>
-    <t>Primeira Parcela</t>
-  </si>
-  <si>
-    <t>Última Parcela</t>
-  </si>
-  <si>
-    <t>Parcelas pagas (vira todo dia 10)</t>
-  </si>
-  <si>
     <t>Manual</t>
   </si>
   <si>
@@ -171,9 +276,6 @@
     <t>Pedrinho Bancos</t>
   </si>
   <si>
-    <t>Parcelado</t>
-  </si>
-  <si>
     <t>Produtos</t>
   </si>
   <si>
@@ -372,9 +474,6 @@
     <t>Indiana Jones A SER ESTORNADO</t>
   </si>
   <si>
-    <t>Jogos</t>
-  </si>
-  <si>
     <t>Indiana Jones Premium Edition</t>
   </si>
   <si>
@@ -387,103 +486,10 @@
     <t>Psiquiatra</t>
   </si>
   <si>
-    <t>As~ude</t>
-  </si>
-  <si>
-    <t>Valor para o mês</t>
-  </si>
-  <si>
-    <t>Salário</t>
-  </si>
-  <si>
-    <t>Custos Totais</t>
-  </si>
-  <si>
-    <t>Resto o mês anterior</t>
-  </si>
-  <si>
-    <t>Cartão Itaú</t>
-  </si>
-  <si>
-    <t>Cartão NuBank</t>
-  </si>
-  <si>
-    <t>Compensasão no NuBank</t>
-  </si>
-  <si>
-    <t>Contas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Aluguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Internet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Luz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Água</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Gás</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Seguranças+Câmera</t>
-  </si>
-  <si>
-    <t>Compensasões no cartão da Stella</t>
-  </si>
-  <si>
-    <t>Dinheiro para NuConta</t>
-  </si>
-  <si>
-    <t>Dinheiro Guardado na poupança</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       Seu João</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       Seguro</t>
-  </si>
-  <si>
-    <t>Aluguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Recolhimento INSS</t>
-  </si>
-  <si>
-    <t>Stella tem que transferir:</t>
-  </si>
-  <si>
-    <t>Valor fixado (Stella)</t>
-  </si>
-  <si>
-    <t>Data de fixação</t>
-  </si>
-  <si>
-    <t>Status pagamento Stella</t>
-  </si>
-  <si>
-    <t>Aguardando</t>
-  </si>
-  <si>
-    <t>Itaú Total</t>
-  </si>
-  <si>
-    <t>Data de compra</t>
-  </si>
-  <si>
-    <t>Modo de pagamento</t>
-  </si>
-  <si>
-    <t>ADIANTAR EM OUTUBRO</t>
-  </si>
-  <si>
-    <t>Control Resonant</t>
+    <t>Saúde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estorno Indiana Jones </t>
   </si>
   <si>
     <t>Vivo</t>
@@ -799,6 +805,12 @@
   </si>
   <si>
     <t>Dera</t>
+  </si>
+  <si>
+    <t>Presente Dimitri</t>
+  </si>
+  <si>
+    <t>Andiamo</t>
   </si>
 </sst>
 </file>
@@ -1278,25 +1290,45 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1498,6 +1530,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
@@ -1686,8 +1722,8 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="75" t="s">
-        <v>115</v>
+      <c r="B2" s="77" t="s">
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -1698,21 +1734,21 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="76"/>
+      <c r="B3" s="78"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C24+C25+C7</f>
-        <v>2317.2114047619039</v>
+        <v>2288.4539047619041</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E24+E25</f>
-        <v>2593.1741666666676</v>
+        <v>2619.4166666666679</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>116</v>
+        <v>3</v>
       </c>
       <c r="C5" s="8">
         <v>10500</v>
@@ -1724,21 +1760,21 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-7020.7885952380966</v>
+        <v>-7049.5460952380963</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-7406.8258333333333</v>
+        <v>-7380.583333333333</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="9"/>
@@ -1746,7 +1782,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="C8" s="8">
         <f>Itaú!E2</f>
@@ -1760,35 +1796,35 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>4568.0569285714291</v>
+        <v>4596.8144285714288</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1794.2558333333334</v>
+        <v>1768.0133333333333</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>4568.0569285714291</v>
+        <v>4596.8144285714288</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1794.2558333333334</v>
+        <v>1768.0133333333333</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="C11" s="8">
         <f>Contas!B6</f>
@@ -1802,7 +1838,7 @@
     </row>
     <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="C12" s="14">
         <f>Contas!K3</f>
@@ -1816,7 +1852,7 @@
     </row>
     <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="C13" s="14">
         <f>Contas!K4</f>
@@ -1830,7 +1866,7 @@
     </row>
     <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="C14" s="14">
         <f>Contas!K5</f>
@@ -1845,7 +1881,7 @@
     </row>
     <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="C15" s="14">
         <f>Contas!K6</f>
@@ -1859,7 +1895,7 @@
     </row>
     <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="C16" s="14">
         <f>Contas!K7</f>
@@ -1873,7 +1909,7 @@
     </row>
     <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="C17" s="14">
         <f>Contas!$K9</f>
@@ -1923,7 +1959,7 @@
     </row>
     <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B21" s="17" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="19"/>
@@ -1943,7 +1979,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="C24" s="8">
         <v>1500</v>
@@ -1953,7 +1989,7 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C25" s="8">
         <f>SUM(C26:C37)</f>
@@ -1967,7 +2003,7 @@
     </row>
     <row r="26" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="C26" s="14" t="str">
         <f>IF('NuConta e Poupança'!M5="Sim",'NuConta e Poupança'!N5,"")</f>
@@ -1978,7 +2014,7 @@
     </row>
     <row r="27" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="20"/>
@@ -2163,7 +2199,7 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="C3" s="8">
         <f>Saldo!E8</f>
@@ -2176,15 +2212,15 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1794.2558333333334</v>
+        <v>1768.0133333333333</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>4568.0569285714291</v>
+        <v>4596.8144285714288</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -2214,7 +2250,7 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="C10" s="8">
         <f>SUM(C11,C13:C16)</f>
@@ -2224,7 +2260,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="C11" s="14">
         <f>Saldo!E12</f>
@@ -2234,7 +2270,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="25" t="s">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="C12" s="26">
         <f>Contas!K4</f>
@@ -2244,7 +2280,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="C13" s="14">
         <f>Contas!K5</f>
@@ -2254,7 +2290,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="C14" s="14">
         <f>Contas!K6</f>
@@ -2264,7 +2300,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="C15" s="14">
         <f>Contas!K7</f>
@@ -2274,7 +2310,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="C16" s="14">
         <f>Saldo!E17</f>
@@ -2284,7 +2320,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
         <f>Saldo!E19</f>
@@ -2294,11 +2330,11 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>137</v>
+        <v>24</v>
       </c>
       <c r="C18" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>3872.4408333333331</v>
+        <v>3846.1983333333333</v>
       </c>
       <c r="D18" s="27"/>
     </row>
@@ -2307,26 +2343,26 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="73">
+        <v>25</v>
+      </c>
+      <c r="C20" s="72">
         <v>4204.74</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C21" s="74">
+        <v>26</v>
+      </c>
+      <c r="C21" s="73">
         <v>46245</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2358,7 +2394,7 @@
   <sheetData>
     <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="29" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -2367,7 +2403,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2390,57 +2426,57 @@
     </row>
     <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="33" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="34" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="70" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>1</v>
@@ -2455,10 +2491,10 @@
         <v>240.97</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="L5" s="38">
         <f t="shared" ref="L5:L15" si="1">I5/N5</f>
@@ -3043,7 +3079,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3075,7 +3111,7 @@
   <sheetData>
     <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="44" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -3084,7 +3120,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
@@ -3092,15 +3128,15 @@
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="45">
         <f>SUM(L6:L327)</f>
-        <v>9465.6787619047609</v>
+        <v>9691.9337619047601</v>
       </c>
       <c r="E2" s="32">
         <f>SUMIF($E$6:$E$327,E1,$M$6:$M$327)</f>
-        <v>4568.0569285714291</v>
+        <v>4596.8144285714288</v>
       </c>
       <c r="F2" s="32">
         <f>SUMIF($F$6:$F$327,F1,$M$6:$M$327)</f>
-        <v>1794.2558333333334</v>
+        <v>1768.0133333333333</v>
       </c>
       <c r="G2" s="32">
         <f>SUMIF($G$6:$G$327,G1,$M$6:$M$327)</f>
@@ -3119,52 +3155,52 @@
     <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="P5" s="33" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E6" s="37" t="s">
         <v>1</v>
@@ -3179,10 +3215,10 @@
         <v>258</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="L6" s="38">
         <f t="shared" ref="L6:L37" si="1">I6/N6</f>
@@ -3210,7 +3246,7 @@
     <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="35"/>
       <c r="D7" s="69" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>1</v>
@@ -3225,10 +3261,10 @@
         <v>1909.3</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="L7" s="38">
         <f t="shared" si="1"/>
@@ -3256,7 +3292,7 @@
     <row r="8" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C8" s="35"/>
       <c r="D8" s="36" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>1</v>
@@ -3273,10 +3309,10 @@
         <v>1017.6</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="L8" s="38">
         <f t="shared" si="1"/>
@@ -3304,7 +3340,7 @@
     <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="35"/>
       <c r="D9" s="46" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>1</v>
@@ -3321,10 +3357,10 @@
         <v>224.24</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K9" s="37" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="L9" s="38">
         <f t="shared" si="1"/>
@@ -3352,7 +3388,7 @@
     <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="35"/>
       <c r="D10" s="36" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>1</v>
@@ -3369,10 +3405,10 @@
         <v>22.45</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="L10" s="38">
         <f t="shared" si="1"/>
@@ -3398,7 +3434,7 @@
     <row r="11" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C11" s="35"/>
       <c r="D11" s="46" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>1</v>
@@ -3415,10 +3451,10 @@
         <v>60</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="L11" s="38">
         <f t="shared" si="1"/>
@@ -3444,7 +3480,7 @@
     <row r="12" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C12" s="35"/>
       <c r="D12" s="36" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>1</v>
@@ -3461,10 +3497,10 @@
         <v>395.54</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="L12" s="38">
         <f t="shared" si="1"/>
@@ -3490,7 +3526,7 @@
     <row r="13" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C13" s="35"/>
       <c r="D13" s="36" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>1</v>
@@ -3507,10 +3543,10 @@
         <v>319.42</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K13" s="37" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="L13" s="38">
         <f t="shared" si="1"/>
@@ -3536,7 +3572,7 @@
     <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="35"/>
       <c r="D14" s="46" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>1</v>
@@ -3553,10 +3589,10 @@
         <v>225</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="L14" s="38">
         <f t="shared" si="1"/>
@@ -3582,7 +3618,7 @@
     <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="35"/>
       <c r="D15" s="36" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="E15" s="37" t="s">
         <v>1</v>
@@ -3599,10 +3635,10 @@
         <v>166.15</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="L15" s="38">
         <f t="shared" si="1"/>
@@ -3628,7 +3664,7 @@
     <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" s="35"/>
       <c r="D16" s="46" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>1</v>
@@ -3643,10 +3679,10 @@
         <v>284.05</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="L16" s="38">
         <f t="shared" si="1"/>
@@ -3672,7 +3708,7 @@
     <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="35"/>
       <c r="D17" s="46" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>1</v>
@@ -3687,10 +3723,10 @@
         <v>110</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="L17" s="38">
         <f t="shared" si="1"/>
@@ -3716,7 +3752,7 @@
     <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="35"/>
       <c r="D18" s="46" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>1</v>
@@ -3731,10 +3767,10 @@
         <v>118.4</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="L18" s="38">
         <f t="shared" si="1"/>
@@ -3757,7 +3793,7 @@
     <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" s="35"/>
       <c r="D19" s="36" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>1</v>
@@ -3774,10 +3810,10 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K19" s="37" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="L19" s="38">
         <f t="shared" si="1"/>
@@ -3803,7 +3839,7 @@
     <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" s="35"/>
       <c r="D20" s="36" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1</v>
@@ -3818,10 +3854,10 @@
         <v>26.9</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="L20" s="38">
         <f t="shared" si="1"/>
@@ -3847,7 +3883,7 @@
     <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" s="35"/>
       <c r="D21" s="46" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>1</v>
@@ -3862,10 +3898,10 @@
         <v>70</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="L21" s="38">
         <f t="shared" si="1"/>
@@ -3888,7 +3924,7 @@
     <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" s="35"/>
       <c r="D22" s="67" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>1</v>
@@ -3903,10 +3939,10 @@
         <v>415</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="L22" s="38">
         <f t="shared" si="1"/>
@@ -3932,7 +3968,7 @@
     <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" s="35"/>
       <c r="D23" s="46" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>1</v>
@@ -3949,10 +3985,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="L23" s="38">
         <f t="shared" si="1"/>
@@ -3980,7 +4016,7 @@
     <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" s="35"/>
       <c r="D24" s="46" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="E24" s="37" t="s">
         <v>1</v>
@@ -3997,10 +4033,10 @@
         <v>1780</v>
       </c>
       <c r="J24" s="68" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L24" s="38">
         <f t="shared" si="1"/>
@@ -4028,7 +4064,7 @@
     <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" s="35"/>
       <c r="D25" s="36" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>1</v>
@@ -4045,10 +4081,10 @@
         <v>359</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K25" s="37" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="L25" s="38">
         <f t="shared" si="1"/>
@@ -4076,7 +4112,7 @@
     <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="35"/>
       <c r="D26" s="66" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>1</v>
@@ -4091,10 +4127,10 @@
         <v>419</v>
       </c>
       <c r="J26" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L26" s="38">
         <f t="shared" si="1"/>
@@ -4122,7 +4158,7 @@
     <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="35"/>
       <c r="D27" s="66" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>1</v>
@@ -4137,10 +4173,10 @@
         <v>419</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L27" s="38">
         <f t="shared" si="1"/>
@@ -4168,7 +4204,7 @@
     <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="35"/>
       <c r="D28" s="66" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>1</v>
@@ -4183,10 +4219,10 @@
         <v>440</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L28" s="38">
         <f t="shared" si="1"/>
@@ -4211,7 +4247,7 @@
     <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="35"/>
       <c r="D29" s="66" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>1</v>
@@ -4226,10 +4262,10 @@
         <v>313.83999999999997</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L29" s="38">
         <f t="shared" si="1"/>
@@ -4257,7 +4293,7 @@
     <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="35"/>
       <c r="D30" s="66" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="E30" s="37"/>
       <c r="F30" s="37" t="s">
@@ -4272,10 +4308,10 @@
         <v>244.51</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="L30" s="38">
         <f t="shared" si="1"/>
@@ -4303,7 +4339,7 @@
     <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="35"/>
       <c r="D31" s="66" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>1</v>
@@ -4318,10 +4354,10 @@
         <v>628</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="L31" s="38">
         <f t="shared" si="1"/>
@@ -4349,7 +4385,7 @@
     <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="35"/>
       <c r="D32" s="65" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>1</v>
@@ -4364,10 +4400,10 @@
         <v>659</v>
       </c>
       <c r="J32" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L32" s="38">
         <f t="shared" si="1"/>
@@ -4395,7 +4431,7 @@
     <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C33" s="35"/>
       <c r="D33" s="65" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>1</v>
@@ -4410,10 +4446,10 @@
         <v>2319.3000000000002</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L33" s="38">
         <f t="shared" si="1"/>
@@ -4441,7 +4477,7 @@
     <row r="34" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C34" s="35"/>
       <c r="D34" s="65" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="E34" s="37" t="s">
         <v>1</v>
@@ -4456,10 +4492,10 @@
         <v>2000</v>
       </c>
       <c r="J34" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="L34" s="38">
         <f t="shared" si="1"/>
@@ -4487,7 +4523,7 @@
     <row r="35" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C35" s="35"/>
       <c r="D35" s="65" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="E35" s="37" t="s">
         <v>1</v>
@@ -4504,10 +4540,10 @@
         <v>725</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L35" s="38">
         <f t="shared" si="1"/>
@@ -4535,7 +4571,7 @@
     <row r="36" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C36" s="35"/>
       <c r="D36" s="65" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>1</v>
@@ -4550,10 +4586,10 @@
         <v>372.43</v>
       </c>
       <c r="J36" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L36" s="38">
         <f t="shared" si="1"/>
@@ -4581,7 +4617,7 @@
     <row r="37" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C37" s="35"/>
       <c r="D37" s="65" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="E37" s="37" t="s">
         <v>1</v>
@@ -4596,10 +4632,10 @@
         <v>72</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L37" s="38">
         <f t="shared" si="1"/>
@@ -4627,7 +4663,7 @@
     <row r="38" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C38" s="35"/>
       <c r="D38" s="65" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="E38" s="37"/>
       <c r="F38" s="37" t="s">
@@ -4642,10 +4678,10 @@
         <v>161.72999999999999</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L38" s="38">
         <f t="shared" ref="L38:L69" si="8">I38/N38</f>
@@ -4673,7 +4709,7 @@
     <row r="39" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C39" s="35"/>
       <c r="D39" s="71" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="E39" s="37"/>
       <c r="F39" s="37" t="s">
@@ -4688,10 +4724,10 @@
         <v>973.02</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K39" s="38" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="L39" s="38">
         <f t="shared" si="8"/>
@@ -4719,7 +4755,7 @@
     <row r="40" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C40" s="35"/>
       <c r="D40" s="71" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E40" s="37" t="s">
         <v>1</v>
@@ -4734,10 +4770,10 @@
         <v>379</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L40" s="38">
         <f t="shared" si="8"/>
@@ -4765,7 +4801,7 @@
     <row r="41" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C41" s="35"/>
       <c r="D41" s="71" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="E41" s="37" t="s">
         <v>1</v>
@@ -4780,10 +4816,10 @@
         <v>297</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L41" s="38">
         <f t="shared" si="8"/>
@@ -4811,7 +4847,7 @@
     <row r="42" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C42" s="35"/>
       <c r="D42" s="46" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="E42" s="37" t="s">
         <v>1</v>
@@ -4828,10 +4864,10 @@
         <v>506</v>
       </c>
       <c r="J42" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L42" s="38">
         <f t="shared" si="8"/>
@@ -4856,7 +4892,7 @@
     <row r="43" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C43" s="35"/>
       <c r="D43" s="46" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="E43" s="37" t="s">
         <v>1</v>
@@ -4871,10 +4907,10 @@
         <v>399.9</v>
       </c>
       <c r="J43" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K43" s="38" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="L43" s="38">
         <f t="shared" si="8"/>
@@ -4902,7 +4938,7 @@
     <row r="44" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C44" s="35"/>
       <c r="D44" s="46" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
@@ -4915,10 +4951,10 @@
         <v>300</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L44" s="38">
         <f t="shared" si="8"/>
@@ -4946,7 +4982,7 @@
     <row r="45" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C45" s="35"/>
       <c r="D45" s="46" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="E45" s="37" t="s">
         <v>1</v>
@@ -4961,10 +4997,10 @@
         <v>284</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="L45" s="38">
         <f t="shared" si="8"/>
@@ -4992,7 +5028,7 @@
     <row r="46" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>1</v>
@@ -5007,10 +5043,10 @@
         <v>1900</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L46" s="38">
         <f t="shared" si="8"/>
@@ -5038,7 +5074,7 @@
     <row r="47" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="E47" s="37" t="s">
         <v>1</v>
@@ -5053,10 +5089,10 @@
         <v>474.33</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L47" s="38">
         <f t="shared" si="8"/>
@@ -5084,7 +5120,7 @@
     <row r="48" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>1</v>
@@ -5099,10 +5135,10 @@
         <v>286.39</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L48" s="38">
         <f t="shared" si="8"/>
@@ -5130,7 +5166,7 @@
     <row r="49" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C49" s="35"/>
       <c r="D49" s="46" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>1</v>
@@ -5145,10 +5181,10 @@
         <v>1181.1400000000001</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K49" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L49" s="38">
         <f t="shared" si="8"/>
@@ -5175,10 +5211,10 @@
     </row>
     <row r="50" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C50" s="35" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D50" s="46" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="E50" s="37" t="s">
         <v>1</v>
@@ -5193,10 +5229,10 @@
         <v>279</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="L50" s="38">
         <f t="shared" si="8"/>
@@ -5224,7 +5260,7 @@
     <row r="51" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C51" s="35"/>
       <c r="D51" s="46" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>1</v>
@@ -5239,10 +5275,10 @@
         <v>-419</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="L51" s="38">
         <f t="shared" si="8"/>
@@ -5270,7 +5306,7 @@
     <row r="52" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C52" s="35"/>
       <c r="D52" s="46" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="E52" s="37" t="s">
         <v>1</v>
@@ -5286,10 +5322,10 @@
         <v>-773.04</v>
       </c>
       <c r="J52" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="L52" s="38">
         <f t="shared" si="8"/>
@@ -5317,7 +5353,7 @@
     <row r="53" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C53" s="35"/>
       <c r="D53" s="46" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="E53" s="37" t="s">
         <v>1</v>
@@ -5332,10 +5368,10 @@
         <v>110</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="L53" s="38">
         <f t="shared" si="8"/>
@@ -5363,7 +5399,7 @@
     <row r="54" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C54" s="35"/>
       <c r="D54" s="46" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>1</v>
@@ -5378,10 +5414,10 @@
         <v>80</v>
       </c>
       <c r="J54" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L54" s="38">
         <f t="shared" si="8"/>
@@ -5409,7 +5445,7 @@
     <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="35"/>
       <c r="D55" s="46" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="E55" s="37" t="s">
         <v>1</v>
@@ -5424,10 +5460,10 @@
         <v>47</v>
       </c>
       <c r="J55" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="L55" s="38">
         <f t="shared" si="8"/>
@@ -5455,7 +5491,7 @@
     <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="35"/>
       <c r="D56" s="46" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="E56" s="37" t="s">
         <v>1</v>
@@ -5472,10 +5508,10 @@
         <v>43</v>
       </c>
       <c r="J56" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L56" s="38">
         <f t="shared" si="8"/>
@@ -5503,7 +5539,7 @@
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="35"/>
       <c r="D57" s="46" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E57" s="37" t="s">
         <v>1</v>
@@ -5521,10 +5557,10 @@
         <v>206.19</v>
       </c>
       <c r="J57" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L57" s="38">
         <f t="shared" si="8"/>
@@ -5552,7 +5588,7 @@
     <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="35"/>
       <c r="D58" s="46" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="E58" s="37" t="s">
         <v>1</v>
@@ -5567,10 +5603,10 @@
         <v>-175</v>
       </c>
       <c r="J58" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L58" s="38">
         <f t="shared" si="8"/>
@@ -5598,7 +5634,7 @@
     <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="35"/>
       <c r="D59" s="46" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="E59" s="37" t="s">
         <v>1</v>
@@ -5613,10 +5649,10 @@
         <v>72</v>
       </c>
       <c r="J59" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L59" s="38">
         <f t="shared" si="8"/>
@@ -5644,7 +5680,7 @@
     <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="35"/>
       <c r="D60" s="46" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E60" s="37" t="s">
         <v>1</v>
@@ -5659,10 +5695,10 @@
         <v>326.99</v>
       </c>
       <c r="J60" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L60" s="38">
         <f t="shared" si="8"/>
@@ -5690,7 +5726,7 @@
     <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C61" s="35"/>
       <c r="D61" s="46" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="E61" s="37" t="s">
         <v>1</v>
@@ -5705,10 +5741,10 @@
         <v>203.88</v>
       </c>
       <c r="J61" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L61" s="38">
         <f t="shared" si="8"/>
@@ -5736,7 +5772,7 @@
     <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="35"/>
       <c r="D62" s="46" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="E62" s="37" t="s">
         <v>1</v>
@@ -5751,10 +5787,10 @@
         <v>202.9</v>
       </c>
       <c r="J62" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L62" s="38">
         <f t="shared" si="8"/>
@@ -5782,7 +5818,7 @@
     <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="35"/>
       <c r="D63" s="46" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="E63" s="37"/>
       <c r="F63" s="37"/>
@@ -5795,10 +5831,10 @@
         <v>9831.94</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K63" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L63" s="38">
         <f t="shared" si="8"/>
@@ -5826,7 +5862,7 @@
     <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="35"/>
       <c r="D64" s="46" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="E64" s="37"/>
       <c r="F64" s="37"/>
@@ -5839,10 +5875,10 @@
         <v>1862.45</v>
       </c>
       <c r="J64" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L64" s="38">
         <f t="shared" si="8"/>
@@ -5870,7 +5906,7 @@
     <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="35"/>
       <c r="D65" s="46" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="E65" s="37"/>
       <c r="F65" s="37"/>
@@ -5883,10 +5919,10 @@
         <v>1732.22</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L65" s="38">
         <f t="shared" si="8"/>
@@ -5914,7 +5950,7 @@
     <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="35"/>
       <c r="D66" s="46" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="E66" s="37" t="s">
         <v>1</v>
@@ -5931,10 +5967,10 @@
         <v>79</v>
       </c>
       <c r="J66" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L66" s="38">
         <f t="shared" si="8"/>
@@ -5962,7 +5998,7 @@
     <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="35"/>
       <c r="D67" s="46" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E67" s="37" t="s">
         <v>1</v>
@@ -5977,10 +6013,10 @@
         <v>129</v>
       </c>
       <c r="J67" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L67" s="38">
         <f t="shared" si="8"/>
@@ -6008,7 +6044,7 @@
     <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="35"/>
       <c r="D68" s="46" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="E68" s="37" t="s">
         <v>1</v>
@@ -6023,10 +6059,10 @@
         <v>45</v>
       </c>
       <c r="J68" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L68" s="38">
         <f t="shared" si="8"/>
@@ -6054,7 +6090,7 @@
     <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="E69" s="37" t="s">
         <v>1</v>
@@ -6069,10 +6105,10 @@
         <v>-715</v>
       </c>
       <c r="J69" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L69" s="38">
         <f t="shared" si="8"/>
@@ -6100,7 +6136,7 @@
     <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="35"/>
       <c r="D70" s="46" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E70" s="37" t="s">
         <v>1</v>
@@ -6117,10 +6153,10 @@
         <v>242.03</v>
       </c>
       <c r="J70" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="L70" s="38">
         <f t="shared" ref="L70:L101" si="13">I70/N70</f>
@@ -6148,7 +6184,7 @@
     <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="35"/>
       <c r="D71" s="46" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="E71" s="37" t="s">
         <v>1</v>
@@ -6163,10 +6199,10 @@
         <v>-60</v>
       </c>
       <c r="J71" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L71" s="38">
         <f t="shared" si="13"/>
@@ -6194,7 +6230,7 @@
     <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="35"/>
       <c r="D72" s="46" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="E72" s="37" t="s">
         <v>1</v>
@@ -6211,10 +6247,10 @@
         <v>126.14</v>
       </c>
       <c r="J72" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L72" s="38">
         <f t="shared" si="13"/>
@@ -6242,7 +6278,7 @@
     <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="35"/>
       <c r="D73" s="46" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E73" s="37" t="s">
         <v>1</v>
@@ -6257,10 +6293,10 @@
         <v>-60</v>
       </c>
       <c r="J73" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="K73" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L73" s="38">
         <f t="shared" si="13"/>
@@ -6288,7 +6324,7 @@
     <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="35"/>
       <c r="D74" s="46" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="E74" s="37" t="s">
         <v>1</v>
@@ -6306,10 +6342,10 @@
         <v>232.66666666666666</v>
       </c>
       <c r="J74" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="L74" s="38">
         <f t="shared" si="13"/>
@@ -6337,7 +6373,7 @@
     <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="35"/>
       <c r="D75" s="46" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="E75" s="37" t="s">
         <v>1</v>
@@ -6346,7 +6382,7 @@
         <v>2</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="H75" s="37">
         <f t="shared" si="12"/>
@@ -6356,10 +6392,10 @@
         <v>103.5</v>
       </c>
       <c r="J75" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K75" s="38" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L75" s="38">
         <f t="shared" si="13"/>
@@ -6387,7 +6423,7 @@
     <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="35"/>
       <c r="D76" s="46" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="E76" s="37" t="s">
         <v>1</v>
@@ -6404,10 +6440,10 @@
         <v>209.94</v>
       </c>
       <c r="J76" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="L76" s="38">
         <f t="shared" si="13"/>
@@ -6435,7 +6471,7 @@
     <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="35"/>
       <c r="D77" s="46" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="E77" s="37" t="s">
         <v>1</v>
@@ -6452,10 +6488,10 @@
         <v>249.5</v>
       </c>
       <c r="J77" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K77" s="38" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="L77" s="38">
         <f t="shared" si="13"/>
@@ -6483,7 +6519,7 @@
     <row r="78" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C78" s="35"/>
       <c r="D78" s="46" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="E78" s="37" t="s">
         <v>1</v>
@@ -6500,10 +6536,10 @@
         <v>176</v>
       </c>
       <c r="J78" s="38" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L78" s="38">
         <f t="shared" si="13"/>
@@ -6531,7 +6567,7 @@
     <row r="79" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C79" s="35"/>
       <c r="D79" s="46" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="E79" s="37" t="s">
         <v>1</v>
@@ -6546,10 +6582,10 @@
         <v>-44</v>
       </c>
       <c r="J79" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="K79" s="38" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L79" s="38">
         <f t="shared" si="13"/>
@@ -6577,7 +6613,7 @@
     <row r="80" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C80" s="35"/>
       <c r="D80" s="46" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="E80" s="37" t="s">
         <v>1</v>
@@ -6592,10 +6628,10 @@
         <v>531</v>
       </c>
       <c r="J80" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K80" s="38" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="L80" s="38">
         <f t="shared" si="13"/>
@@ -6622,66 +6658,92 @@
     </row>
     <row r="81" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C81" s="35"/>
-      <c r="D81" s="46"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
+      <c r="D81" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G81" s="37"/>
       <c r="H81" s="37">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="38"/>
-      <c r="J81" s="38"/>
-      <c r="K81" s="38"/>
+        <f t="shared" ref="H81" si="17">COUNTA(E81:G81)</f>
+        <v>2</v>
+      </c>
+      <c r="I81" s="38">
+        <v>-209.94</v>
+      </c>
+      <c r="J81" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="K81" s="38" t="s">
+        <v>49</v>
+      </c>
       <c r="L81" s="38">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M81" s="38" t="str">
-        <f t="shared" si="14"/>
-        <v/>
+        <f t="shared" ref="L81" si="18">I81/N81</f>
+        <v>-52.484999999999999</v>
+      </c>
+      <c r="M81" s="38">
+        <f t="shared" ref="M81" si="19">IFERROR(L81/H81,"")</f>
+        <v>-26.2425</v>
       </c>
       <c r="N81" s="39">
-        <v>1</v>
-      </c>
-      <c r="O81" s="64"/>
-      <c r="P81" s="64" t="str">
-        <f t="shared" si="15"/>
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="O81" s="64">
+        <v>46268</v>
+      </c>
+      <c r="P81" s="64">
+        <f t="shared" ref="P81" si="20">IF(N81&lt;&gt;1,EDATE(O81,N81-1),"")</f>
+        <v>46359</v>
       </c>
       <c r="Q81" s="37" t="str">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ref="Q81" ca="1" si="21">IF(O81&lt;&gt;"",IFERROR(DATEDIF(O81,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C82" s="35"/>
-      <c r="D82" s="46"/>
-      <c r="E82" s="37"/>
+      <c r="D82" s="46" t="s">
+        <v>253</v>
+      </c>
+      <c r="E82" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F82" s="37"/>
       <c r="G82" s="37"/>
       <c r="H82" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I82" s="38">
+        <v>330</v>
+      </c>
+      <c r="J82" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="K82" s="38" t="s">
+        <v>76</v>
+      </c>
       <c r="L82" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="38" t="str">
+        <v>55</v>
+      </c>
+      <c r="M82" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>55</v>
       </c>
       <c r="N82" s="39">
-        <v>1</v>
-      </c>
-      <c r="O82" s="64"/>
-      <c r="P82" s="64" t="str">
+        <v>6</v>
+      </c>
+      <c r="O82" s="64">
+        <v>46268</v>
+      </c>
+      <c r="P82" s="64">
         <f t="shared" si="15"/>
-        <v/>
+        <v>46421</v>
       </c>
       <c r="Q82" s="37" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -6690,7 +6752,9 @@
     </row>
     <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="35"/>
-      <c r="D83" s="46"/>
+      <c r="D83" s="46" t="s">
+        <v>254</v>
+      </c>
       <c r="E83" s="37"/>
       <c r="F83" s="37"/>
       <c r="G83" s="37"/>
@@ -6698,12 +6762,18 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
-      <c r="K83" s="38"/>
+      <c r="I83" s="38">
+        <v>223.74</v>
+      </c>
+      <c r="J83" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="K83" s="38" t="s">
+        <v>118</v>
+      </c>
       <c r="L83" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>223.74</v>
       </c>
       <c r="M83" s="38" t="str">
         <f t="shared" si="14"/>
@@ -6712,7 +6782,9 @@
       <c r="N83" s="39">
         <v>1</v>
       </c>
-      <c r="O83" s="64"/>
+      <c r="O83" s="64">
+        <v>46268</v>
+      </c>
       <c r="P83" s="64" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -7341,18 +7413,18 @@
       <c r="F102" s="37"/>
       <c r="G102" s="37"/>
       <c r="H102" s="37">
-        <f t="shared" ref="H102:H133" si="17">COUNTA(E102:G102)</f>
+        <f t="shared" ref="H102:H133" si="22">COUNTA(E102:G102)</f>
         <v>0</v>
       </c>
       <c r="I102" s="38"/>
       <c r="J102" s="38"/>
       <c r="K102" s="38"/>
       <c r="L102" s="38">
-        <f t="shared" ref="L102:L133" si="18">I102/N102</f>
+        <f t="shared" ref="L102:L133" si="23">I102/N102</f>
         <v>0</v>
       </c>
       <c r="M102" s="38" t="str">
-        <f t="shared" ref="M102:M133" si="19">IFERROR(L102/H102,"")</f>
+        <f t="shared" ref="M102:M133" si="24">IFERROR(L102/H102,"")</f>
         <v/>
       </c>
       <c r="N102" s="39">
@@ -7360,7 +7432,7 @@
       </c>
       <c r="O102" s="64"/>
       <c r="P102" s="64" t="str">
-        <f t="shared" ref="P102:P133" si="20">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
+        <f t="shared" ref="P102:P133" si="25">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
         <v/>
       </c>
       <c r="Q102" s="37" t="str">
@@ -7375,18 +7447,18 @@
       <c r="F103" s="37"/>
       <c r="G103" s="37"/>
       <c r="H103" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I103" s="38"/>
       <c r="J103" s="38"/>
       <c r="K103" s="38"/>
       <c r="L103" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M103" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N103" s="39">
@@ -7394,7 +7466,7 @@
       </c>
       <c r="O103" s="64"/>
       <c r="P103" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q103" s="37" t="str">
@@ -7409,18 +7481,18 @@
       <c r="F104" s="37"/>
       <c r="G104" s="37"/>
       <c r="H104" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I104" s="38"/>
       <c r="J104" s="38"/>
       <c r="K104" s="38"/>
       <c r="L104" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M104" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N104" s="39">
@@ -7428,7 +7500,7 @@
       </c>
       <c r="O104" s="64"/>
       <c r="P104" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q104" s="37" t="str">
@@ -7443,18 +7515,18 @@
       <c r="F105" s="37"/>
       <c r="G105" s="37"/>
       <c r="H105" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I105" s="38"/>
       <c r="J105" s="38"/>
       <c r="K105" s="38"/>
       <c r="L105" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M105" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N105" s="39">
@@ -7462,7 +7534,7 @@
       </c>
       <c r="O105" s="64"/>
       <c r="P105" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q105" s="37" t="str">
@@ -7477,18 +7549,18 @@
       <c r="F106" s="37"/>
       <c r="G106" s="37"/>
       <c r="H106" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I106" s="38"/>
       <c r="J106" s="38"/>
       <c r="K106" s="38"/>
       <c r="L106" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M106" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N106" s="39">
@@ -7496,7 +7568,7 @@
       </c>
       <c r="O106" s="64"/>
       <c r="P106" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q106" s="37" t="str">
@@ -7511,18 +7583,18 @@
       <c r="F107" s="37"/>
       <c r="G107" s="37"/>
       <c r="H107" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I107" s="38"/>
       <c r="J107" s="38"/>
       <c r="K107" s="38"/>
       <c r="L107" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M107" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N107" s="39">
@@ -7530,11 +7602,11 @@
       </c>
       <c r="O107" s="64"/>
       <c r="P107" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q107" s="37" t="str">
-        <f t="shared" ref="Q107:Q138" ca="1" si="21">IF(O107&lt;&gt;"",IFERROR(DATEDIF(O107,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q107:Q138" ca="1" si="26">IF(O107&lt;&gt;"",IFERROR(DATEDIF(O107,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7545,18 +7617,18 @@
       <c r="F108" s="37"/>
       <c r="G108" s="37"/>
       <c r="H108" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I108" s="38"/>
       <c r="J108" s="38"/>
       <c r="K108" s="38"/>
       <c r="L108" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M108" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N108" s="39">
@@ -7564,11 +7636,11 @@
       </c>
       <c r="O108" s="64"/>
       <c r="P108" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q108" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7579,18 +7651,18 @@
       <c r="F109" s="37"/>
       <c r="G109" s="37"/>
       <c r="H109" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I109" s="38"/>
       <c r="J109" s="38"/>
       <c r="K109" s="38"/>
       <c r="L109" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M109" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N109" s="39">
@@ -7598,11 +7670,11 @@
       </c>
       <c r="O109" s="64"/>
       <c r="P109" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q109" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7613,18 +7685,18 @@
       <c r="F110" s="37"/>
       <c r="G110" s="37"/>
       <c r="H110" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I110" s="38"/>
       <c r="J110" s="38"/>
       <c r="K110" s="38"/>
       <c r="L110" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M110" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N110" s="39">
@@ -7632,11 +7704,11 @@
       </c>
       <c r="O110" s="64"/>
       <c r="P110" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q110" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7647,18 +7719,18 @@
       <c r="F111" s="37"/>
       <c r="G111" s="37"/>
       <c r="H111" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I111" s="38"/>
       <c r="J111" s="38"/>
       <c r="K111" s="38"/>
       <c r="L111" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M111" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N111" s="39">
@@ -7666,11 +7738,11 @@
       </c>
       <c r="O111" s="64"/>
       <c r="P111" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q111" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7681,18 +7753,18 @@
       <c r="F112" s="37"/>
       <c r="G112" s="37"/>
       <c r="H112" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I112" s="38"/>
       <c r="J112" s="38"/>
       <c r="K112" s="38"/>
       <c r="L112" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M112" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N112" s="39">
@@ -7700,11 +7772,11 @@
       </c>
       <c r="O112" s="64"/>
       <c r="P112" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q112" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7715,18 +7787,18 @@
       <c r="F113" s="37"/>
       <c r="G113" s="37"/>
       <c r="H113" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I113" s="38"/>
       <c r="J113" s="38"/>
       <c r="K113" s="38"/>
       <c r="L113" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M113" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N113" s="39">
@@ -7734,11 +7806,11 @@
       </c>
       <c r="O113" s="64"/>
       <c r="P113" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q113" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7749,18 +7821,18 @@
       <c r="F114" s="37"/>
       <c r="G114" s="37"/>
       <c r="H114" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I114" s="38"/>
       <c r="J114" s="38"/>
       <c r="K114" s="38"/>
       <c r="L114" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M114" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N114" s="39">
@@ -7768,11 +7840,11 @@
       </c>
       <c r="O114" s="64"/>
       <c r="P114" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q114" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7783,18 +7855,18 @@
       <c r="F115" s="37"/>
       <c r="G115" s="37"/>
       <c r="H115" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I115" s="38"/>
       <c r="J115" s="38"/>
       <c r="K115" s="38"/>
       <c r="L115" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M115" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N115" s="39">
@@ -7802,11 +7874,11 @@
       </c>
       <c r="O115" s="64"/>
       <c r="P115" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q115" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7817,18 +7889,18 @@
       <c r="F116" s="37"/>
       <c r="G116" s="37"/>
       <c r="H116" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I116" s="38"/>
       <c r="J116" s="38"/>
       <c r="K116" s="38"/>
       <c r="L116" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M116" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N116" s="39">
@@ -7836,11 +7908,11 @@
       </c>
       <c r="O116" s="64"/>
       <c r="P116" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q116" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7851,18 +7923,18 @@
       <c r="F117" s="37"/>
       <c r="G117" s="37"/>
       <c r="H117" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I117" s="38"/>
       <c r="J117" s="38"/>
       <c r="K117" s="38"/>
       <c r="L117" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M117" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N117" s="39">
@@ -7870,11 +7942,11 @@
       </c>
       <c r="O117" s="64"/>
       <c r="P117" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q117" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7885,18 +7957,18 @@
       <c r="F118" s="37"/>
       <c r="G118" s="37"/>
       <c r="H118" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I118" s="38"/>
       <c r="J118" s="38"/>
       <c r="K118" s="38"/>
       <c r="L118" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M118" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N118" s="39">
@@ -7904,11 +7976,11 @@
       </c>
       <c r="O118" s="64"/>
       <c r="P118" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q118" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7919,18 +7991,18 @@
       <c r="F119" s="37"/>
       <c r="G119" s="37"/>
       <c r="H119" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I119" s="38"/>
       <c r="J119" s="38"/>
       <c r="K119" s="38"/>
       <c r="L119" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M119" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N119" s="39">
@@ -7938,11 +8010,11 @@
       </c>
       <c r="O119" s="64"/>
       <c r="P119" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q119" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7953,18 +8025,18 @@
       <c r="F120" s="37"/>
       <c r="G120" s="37"/>
       <c r="H120" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I120" s="38"/>
       <c r="J120" s="38"/>
       <c r="K120" s="38"/>
       <c r="L120" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M120" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N120" s="39">
@@ -7972,11 +8044,11 @@
       </c>
       <c r="O120" s="64"/>
       <c r="P120" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q120" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -7987,18 +8059,18 @@
       <c r="F121" s="37"/>
       <c r="G121" s="37"/>
       <c r="H121" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I121" s="38"/>
       <c r="J121" s="38"/>
       <c r="K121" s="38"/>
       <c r="L121" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M121" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N121" s="39">
@@ -8006,11 +8078,11 @@
       </c>
       <c r="O121" s="64"/>
       <c r="P121" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q121" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8021,18 +8093,18 @@
       <c r="F122" s="37"/>
       <c r="G122" s="37"/>
       <c r="H122" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I122" s="38"/>
       <c r="J122" s="38"/>
       <c r="K122" s="38"/>
       <c r="L122" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M122" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N122" s="39">
@@ -8040,11 +8112,11 @@
       </c>
       <c r="O122" s="64"/>
       <c r="P122" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q122" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8055,18 +8127,18 @@
       <c r="F123" s="37"/>
       <c r="G123" s="37"/>
       <c r="H123" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I123" s="38"/>
       <c r="J123" s="38"/>
       <c r="K123" s="38"/>
       <c r="L123" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M123" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N123" s="39">
@@ -8074,11 +8146,11 @@
       </c>
       <c r="O123" s="64"/>
       <c r="P123" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q123" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8089,18 +8161,18 @@
       <c r="F124" s="37"/>
       <c r="G124" s="37"/>
       <c r="H124" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I124" s="38"/>
       <c r="J124" s="38"/>
       <c r="K124" s="38"/>
       <c r="L124" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M124" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N124" s="39">
@@ -8108,11 +8180,11 @@
       </c>
       <c r="O124" s="64"/>
       <c r="P124" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q124" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8123,18 +8195,18 @@
       <c r="F125" s="37"/>
       <c r="G125" s="37"/>
       <c r="H125" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I125" s="38"/>
       <c r="J125" s="38"/>
       <c r="K125" s="38"/>
       <c r="L125" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M125" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N125" s="39">
@@ -8142,11 +8214,11 @@
       </c>
       <c r="O125" s="64"/>
       <c r="P125" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q125" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8157,18 +8229,18 @@
       <c r="F126" s="37"/>
       <c r="G126" s="37"/>
       <c r="H126" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I126" s="38"/>
       <c r="J126" s="38"/>
       <c r="K126" s="38"/>
       <c r="L126" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M126" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N126" s="39">
@@ -8176,11 +8248,11 @@
       </c>
       <c r="O126" s="64"/>
       <c r="P126" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q126" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8191,18 +8263,18 @@
       <c r="F127" s="37"/>
       <c r="G127" s="37"/>
       <c r="H127" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I127" s="38"/>
       <c r="J127" s="38"/>
       <c r="K127" s="38"/>
       <c r="L127" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M127" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N127" s="39">
@@ -8210,11 +8282,11 @@
       </c>
       <c r="O127" s="64"/>
       <c r="P127" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q127" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8225,18 +8297,18 @@
       <c r="F128" s="37"/>
       <c r="G128" s="37"/>
       <c r="H128" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I128" s="38"/>
       <c r="J128" s="38"/>
       <c r="K128" s="38"/>
       <c r="L128" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M128" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N128" s="39">
@@ -8244,11 +8316,11 @@
       </c>
       <c r="O128" s="64"/>
       <c r="P128" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q128" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8259,18 +8331,18 @@
       <c r="F129" s="37"/>
       <c r="G129" s="37"/>
       <c r="H129" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I129" s="38"/>
       <c r="J129" s="38"/>
       <c r="K129" s="38"/>
       <c r="L129" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M129" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N129" s="39">
@@ -8278,11 +8350,11 @@
       </c>
       <c r="O129" s="64"/>
       <c r="P129" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q129" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8293,18 +8365,18 @@
       <c r="F130" s="37"/>
       <c r="G130" s="37"/>
       <c r="H130" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I130" s="38"/>
       <c r="J130" s="38"/>
       <c r="K130" s="38"/>
       <c r="L130" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M130" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N130" s="39">
@@ -8312,11 +8384,11 @@
       </c>
       <c r="O130" s="64"/>
       <c r="P130" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q130" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8327,18 +8399,18 @@
       <c r="F131" s="37"/>
       <c r="G131" s="37"/>
       <c r="H131" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I131" s="38"/>
       <c r="J131" s="38"/>
       <c r="K131" s="38"/>
       <c r="L131" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M131" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N131" s="39">
@@ -8346,11 +8418,11 @@
       </c>
       <c r="O131" s="64"/>
       <c r="P131" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q131" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8361,18 +8433,18 @@
       <c r="F132" s="37"/>
       <c r="G132" s="37"/>
       <c r="H132" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I132" s="38"/>
       <c r="J132" s="38"/>
       <c r="K132" s="38"/>
       <c r="L132" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M132" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N132" s="39">
@@ -8380,11 +8452,11 @@
       </c>
       <c r="O132" s="64"/>
       <c r="P132" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q132" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8395,18 +8467,18 @@
       <c r="F133" s="37"/>
       <c r="G133" s="37"/>
       <c r="H133" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I133" s="38"/>
       <c r="J133" s="38"/>
       <c r="K133" s="38"/>
       <c r="L133" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M133" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N133" s="39">
@@ -8414,11 +8486,11 @@
       </c>
       <c r="O133" s="64"/>
       <c r="P133" s="64" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q133" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8429,18 +8501,18 @@
       <c r="F134" s="37"/>
       <c r="G134" s="37"/>
       <c r="H134" s="37">
-        <f t="shared" ref="H134:H165" si="22">COUNTA(E134:G134)</f>
+        <f t="shared" ref="H134:H165" si="27">COUNTA(E134:G134)</f>
         <v>0</v>
       </c>
       <c r="I134" s="38"/>
       <c r="J134" s="38"/>
       <c r="K134" s="38"/>
       <c r="L134" s="38">
-        <f t="shared" ref="L134:L165" si="23">I134/N134</f>
+        <f t="shared" ref="L134:L165" si="28">I134/N134</f>
         <v>0</v>
       </c>
       <c r="M134" s="38" t="str">
-        <f t="shared" ref="M134:M165" si="24">IFERROR(L134/H134,"")</f>
+        <f t="shared" ref="M134:M165" si="29">IFERROR(L134/H134,"")</f>
         <v/>
       </c>
       <c r="N134" s="39">
@@ -8448,11 +8520,11 @@
       </c>
       <c r="O134" s="64"/>
       <c r="P134" s="64" t="str">
-        <f t="shared" ref="P134:P165" si="25">IF(N134&lt;&gt;1,EDATE(O134,N134-1),"")</f>
+        <f t="shared" ref="P134:P165" si="30">IF(N134&lt;&gt;1,EDATE(O134,N134-1),"")</f>
         <v/>
       </c>
       <c r="Q134" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8463,18 +8535,18 @@
       <c r="F135" s="37"/>
       <c r="G135" s="37"/>
       <c r="H135" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I135" s="38"/>
       <c r="J135" s="38"/>
       <c r="K135" s="38"/>
       <c r="L135" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M135" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N135" s="39">
@@ -8482,11 +8554,11 @@
       </c>
       <c r="O135" s="64"/>
       <c r="P135" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q135" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8497,18 +8569,18 @@
       <c r="F136" s="37"/>
       <c r="G136" s="37"/>
       <c r="H136" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I136" s="38"/>
       <c r="J136" s="38"/>
       <c r="K136" s="38"/>
       <c r="L136" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M136" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N136" s="39">
@@ -8516,11 +8588,11 @@
       </c>
       <c r="O136" s="64"/>
       <c r="P136" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q136" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8531,18 +8603,18 @@
       <c r="F137" s="37"/>
       <c r="G137" s="37"/>
       <c r="H137" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I137" s="38"/>
       <c r="J137" s="38"/>
       <c r="K137" s="38"/>
       <c r="L137" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M137" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N137" s="39">
@@ -8550,11 +8622,11 @@
       </c>
       <c r="O137" s="64"/>
       <c r="P137" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q137" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8565,18 +8637,18 @@
       <c r="F138" s="37"/>
       <c r="G138" s="37"/>
       <c r="H138" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I138" s="38"/>
       <c r="J138" s="38"/>
       <c r="K138" s="38"/>
       <c r="L138" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M138" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N138" s="39">
@@ -8584,11 +8656,11 @@
       </c>
       <c r="O138" s="64"/>
       <c r="P138" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q138" s="37" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="26"/>
         <v/>
       </c>
     </row>
@@ -8599,18 +8671,18 @@
       <c r="F139" s="37"/>
       <c r="G139" s="37"/>
       <c r="H139" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I139" s="38"/>
       <c r="J139" s="38"/>
       <c r="K139" s="38"/>
       <c r="L139" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M139" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N139" s="39">
@@ -8618,11 +8690,11 @@
       </c>
       <c r="O139" s="64"/>
       <c r="P139" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q139" s="37" t="str">
-        <f t="shared" ref="Q139:Q170" ca="1" si="26">IF(O139&lt;&gt;"",IFERROR(DATEDIF(O139,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q139:Q170" ca="1" si="31">IF(O139&lt;&gt;"",IFERROR(DATEDIF(O139,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8633,18 +8705,18 @@
       <c r="F140" s="37"/>
       <c r="G140" s="37"/>
       <c r="H140" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I140" s="38"/>
       <c r="J140" s="38"/>
       <c r="K140" s="38"/>
       <c r="L140" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M140" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N140" s="39">
@@ -8652,11 +8724,11 @@
       </c>
       <c r="O140" s="64"/>
       <c r="P140" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q140" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8667,18 +8739,18 @@
       <c r="F141" s="37"/>
       <c r="G141" s="37"/>
       <c r="H141" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I141" s="38"/>
       <c r="J141" s="38"/>
       <c r="K141" s="38"/>
       <c r="L141" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M141" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N141" s="39">
@@ -8686,11 +8758,11 @@
       </c>
       <c r="O141" s="64"/>
       <c r="P141" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q141" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8701,18 +8773,18 @@
       <c r="F142" s="37"/>
       <c r="G142" s="37"/>
       <c r="H142" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I142" s="38"/>
       <c r="J142" s="38"/>
       <c r="K142" s="38"/>
       <c r="L142" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M142" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N142" s="39">
@@ -8720,11 +8792,11 @@
       </c>
       <c r="O142" s="64"/>
       <c r="P142" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q142" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8735,18 +8807,18 @@
       <c r="F143" s="37"/>
       <c r="G143" s="37"/>
       <c r="H143" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I143" s="38"/>
       <c r="J143" s="38"/>
       <c r="K143" s="38"/>
       <c r="L143" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M143" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N143" s="39">
@@ -8754,11 +8826,11 @@
       </c>
       <c r="O143" s="64"/>
       <c r="P143" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q143" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8769,18 +8841,18 @@
       <c r="F144" s="37"/>
       <c r="G144" s="37"/>
       <c r="H144" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I144" s="38"/>
       <c r="J144" s="38"/>
       <c r="K144" s="38"/>
       <c r="L144" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M144" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N144" s="39">
@@ -8788,11 +8860,11 @@
       </c>
       <c r="O144" s="35"/>
       <c r="P144" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q144" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8803,18 +8875,18 @@
       <c r="F145" s="37"/>
       <c r="G145" s="37"/>
       <c r="H145" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I145" s="38"/>
       <c r="J145" s="38"/>
       <c r="K145" s="38"/>
       <c r="L145" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M145" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N145" s="39">
@@ -8822,11 +8894,11 @@
       </c>
       <c r="O145" s="35"/>
       <c r="P145" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q145" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8837,18 +8909,18 @@
       <c r="F146" s="37"/>
       <c r="G146" s="37"/>
       <c r="H146" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I146" s="38"/>
       <c r="J146" s="38"/>
       <c r="K146" s="38"/>
       <c r="L146" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M146" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N146" s="39">
@@ -8856,11 +8928,11 @@
       </c>
       <c r="O146" s="35"/>
       <c r="P146" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q146" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8871,18 +8943,18 @@
       <c r="F147" s="37"/>
       <c r="G147" s="37"/>
       <c r="H147" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I147" s="38"/>
       <c r="J147" s="38"/>
       <c r="K147" s="38"/>
       <c r="L147" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M147" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N147" s="39">
@@ -8890,11 +8962,11 @@
       </c>
       <c r="O147" s="35"/>
       <c r="P147" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q147" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8905,18 +8977,18 @@
       <c r="F148" s="37"/>
       <c r="G148" s="37"/>
       <c r="H148" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I148" s="38"/>
       <c r="J148" s="38"/>
       <c r="K148" s="38"/>
       <c r="L148" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M148" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N148" s="39">
@@ -8924,11 +8996,11 @@
       </c>
       <c r="O148" s="35"/>
       <c r="P148" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q148" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8939,18 +9011,18 @@
       <c r="F149" s="37"/>
       <c r="G149" s="37"/>
       <c r="H149" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I149" s="38"/>
       <c r="J149" s="38"/>
       <c r="K149" s="38"/>
       <c r="L149" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M149" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N149" s="39">
@@ -8958,11 +9030,11 @@
       </c>
       <c r="O149" s="35"/>
       <c r="P149" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q149" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -8973,18 +9045,18 @@
       <c r="F150" s="37"/>
       <c r="G150" s="37"/>
       <c r="H150" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I150" s="38"/>
       <c r="J150" s="38"/>
       <c r="K150" s="38"/>
       <c r="L150" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M150" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N150" s="39">
@@ -8992,11 +9064,11 @@
       </c>
       <c r="O150" s="35"/>
       <c r="P150" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q150" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9007,18 +9079,18 @@
       <c r="F151" s="37"/>
       <c r="G151" s="37"/>
       <c r="H151" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I151" s="38"/>
       <c r="J151" s="38"/>
       <c r="K151" s="38"/>
       <c r="L151" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M151" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N151" s="39">
@@ -9026,11 +9098,11 @@
       </c>
       <c r="O151" s="35"/>
       <c r="P151" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q151" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9041,18 +9113,18 @@
       <c r="F152" s="37"/>
       <c r="G152" s="37"/>
       <c r="H152" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I152" s="38"/>
       <c r="J152" s="38"/>
       <c r="K152" s="38"/>
       <c r="L152" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M152" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N152" s="39">
@@ -9060,11 +9132,11 @@
       </c>
       <c r="O152" s="35"/>
       <c r="P152" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q152" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9075,18 +9147,18 @@
       <c r="F153" s="37"/>
       <c r="G153" s="37"/>
       <c r="H153" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I153" s="38"/>
       <c r="J153" s="38"/>
       <c r="K153" s="38"/>
       <c r="L153" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M153" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N153" s="39">
@@ -9094,11 +9166,11 @@
       </c>
       <c r="O153" s="35"/>
       <c r="P153" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q153" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9109,18 +9181,18 @@
       <c r="F154" s="37"/>
       <c r="G154" s="37"/>
       <c r="H154" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I154" s="38"/>
       <c r="J154" s="38"/>
       <c r="K154" s="38"/>
       <c r="L154" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M154" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N154" s="39">
@@ -9128,11 +9200,11 @@
       </c>
       <c r="O154" s="35"/>
       <c r="P154" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q154" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9143,18 +9215,18 @@
       <c r="F155" s="37"/>
       <c r="G155" s="37"/>
       <c r="H155" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I155" s="38"/>
       <c r="J155" s="38"/>
       <c r="K155" s="38"/>
       <c r="L155" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M155" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N155" s="39">
@@ -9162,11 +9234,11 @@
       </c>
       <c r="O155" s="35"/>
       <c r="P155" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q155" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9177,18 +9249,18 @@
       <c r="F156" s="37"/>
       <c r="G156" s="37"/>
       <c r="H156" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I156" s="38"/>
       <c r="J156" s="38"/>
       <c r="K156" s="38"/>
       <c r="L156" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M156" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N156" s="39">
@@ -9196,11 +9268,11 @@
       </c>
       <c r="O156" s="35"/>
       <c r="P156" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q156" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9211,18 +9283,18 @@
       <c r="F157" s="37"/>
       <c r="G157" s="37"/>
       <c r="H157" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I157" s="38"/>
       <c r="J157" s="38"/>
       <c r="K157" s="38"/>
       <c r="L157" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M157" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N157" s="39">
@@ -9230,11 +9302,11 @@
       </c>
       <c r="O157" s="35"/>
       <c r="P157" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q157" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9245,18 +9317,18 @@
       <c r="F158" s="37"/>
       <c r="G158" s="37"/>
       <c r="H158" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I158" s="38"/>
       <c r="J158" s="38"/>
       <c r="K158" s="38"/>
       <c r="L158" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M158" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N158" s="39">
@@ -9264,11 +9336,11 @@
       </c>
       <c r="O158" s="35"/>
       <c r="P158" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q158" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9279,18 +9351,18 @@
       <c r="F159" s="37"/>
       <c r="G159" s="37"/>
       <c r="H159" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I159" s="38"/>
       <c r="J159" s="38"/>
       <c r="K159" s="38"/>
       <c r="L159" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M159" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N159" s="39">
@@ -9298,11 +9370,11 @@
       </c>
       <c r="O159" s="35"/>
       <c r="P159" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q159" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9313,18 +9385,18 @@
       <c r="F160" s="37"/>
       <c r="G160" s="37"/>
       <c r="H160" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I160" s="38"/>
       <c r="J160" s="38"/>
       <c r="K160" s="38"/>
       <c r="L160" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M160" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N160" s="39">
@@ -9332,11 +9404,11 @@
       </c>
       <c r="O160" s="35"/>
       <c r="P160" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q160" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9347,18 +9419,18 @@
       <c r="F161" s="37"/>
       <c r="G161" s="37"/>
       <c r="H161" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I161" s="38"/>
       <c r="J161" s="38"/>
       <c r="K161" s="38"/>
       <c r="L161" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M161" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N161" s="39">
@@ -9366,11 +9438,11 @@
       </c>
       <c r="O161" s="35"/>
       <c r="P161" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q161" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9381,18 +9453,18 @@
       <c r="F162" s="37"/>
       <c r="G162" s="37"/>
       <c r="H162" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I162" s="38"/>
       <c r="J162" s="38"/>
       <c r="K162" s="38"/>
       <c r="L162" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M162" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N162" s="39">
@@ -9400,11 +9472,11 @@
       </c>
       <c r="O162" s="35"/>
       <c r="P162" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q162" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9415,18 +9487,18 @@
       <c r="F163" s="37"/>
       <c r="G163" s="37"/>
       <c r="H163" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I163" s="38"/>
       <c r="J163" s="38"/>
       <c r="K163" s="38"/>
       <c r="L163" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M163" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N163" s="39">
@@ -9434,11 +9506,11 @@
       </c>
       <c r="O163" s="35"/>
       <c r="P163" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q163" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9449,18 +9521,18 @@
       <c r="F164" s="37"/>
       <c r="G164" s="37"/>
       <c r="H164" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I164" s="38"/>
       <c r="J164" s="38"/>
       <c r="K164" s="38"/>
       <c r="L164" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M164" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N164" s="39">
@@ -9468,11 +9540,11 @@
       </c>
       <c r="O164" s="35"/>
       <c r="P164" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q164" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9483,18 +9555,18 @@
       <c r="F165" s="37"/>
       <c r="G165" s="37"/>
       <c r="H165" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I165" s="38"/>
       <c r="J165" s="38"/>
       <c r="K165" s="38"/>
       <c r="L165" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M165" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N165" s="39">
@@ -9502,11 +9574,11 @@
       </c>
       <c r="O165" s="35"/>
       <c r="P165" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q165" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9517,18 +9589,18 @@
       <c r="F166" s="37"/>
       <c r="G166" s="37"/>
       <c r="H166" s="37">
-        <f t="shared" ref="H166:H197" si="27">COUNTA(E166:G166)</f>
+        <f t="shared" ref="H166:H189" si="32">COUNTA(E166:G166)</f>
         <v>0</v>
       </c>
       <c r="I166" s="38"/>
       <c r="J166" s="38"/>
       <c r="K166" s="38"/>
       <c r="L166" s="38">
-        <f t="shared" ref="L166:L189" si="28">I166/N166</f>
+        <f t="shared" ref="L166:L189" si="33">I166/N166</f>
         <v>0</v>
       </c>
       <c r="M166" s="38" t="str">
-        <f t="shared" ref="M166:M197" si="29">IFERROR(L166/H166,"")</f>
+        <f t="shared" ref="M166:M189" si="34">IFERROR(L166/H166,"")</f>
         <v/>
       </c>
       <c r="N166" s="39">
@@ -9536,11 +9608,11 @@
       </c>
       <c r="O166" s="35"/>
       <c r="P166" s="35" t="str">
-        <f t="shared" ref="P166:P197" si="30">IF(N166&lt;&gt;1,EDATE(O166,N166-1),"")</f>
+        <f t="shared" ref="P166:P189" si="35">IF(N166&lt;&gt;1,EDATE(O166,N166-1),"")</f>
         <v/>
       </c>
       <c r="Q166" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9551,18 +9623,18 @@
       <c r="F167" s="37"/>
       <c r="G167" s="37"/>
       <c r="H167" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I167" s="38"/>
       <c r="J167" s="38"/>
       <c r="K167" s="38"/>
       <c r="L167" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M167" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N167" s="39">
@@ -9570,11 +9642,11 @@
       </c>
       <c r="O167" s="35"/>
       <c r="P167" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q167" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9585,18 +9657,18 @@
       <c r="F168" s="37"/>
       <c r="G168" s="37"/>
       <c r="H168" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I168" s="38"/>
       <c r="J168" s="38"/>
       <c r="K168" s="38"/>
       <c r="L168" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M168" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N168" s="39">
@@ -9604,11 +9676,11 @@
       </c>
       <c r="O168" s="35"/>
       <c r="P168" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q168" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9619,18 +9691,18 @@
       <c r="F169" s="37"/>
       <c r="G169" s="37"/>
       <c r="H169" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I169" s="38"/>
       <c r="J169" s="38"/>
       <c r="K169" s="38"/>
       <c r="L169" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M169" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N169" s="39">
@@ -9638,11 +9710,11 @@
       </c>
       <c r="O169" s="35"/>
       <c r="P169" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q169" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9653,18 +9725,18 @@
       <c r="F170" s="37"/>
       <c r="G170" s="37"/>
       <c r="H170" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I170" s="38"/>
       <c r="J170" s="38"/>
       <c r="K170" s="38"/>
       <c r="L170" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M170" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N170" s="39">
@@ -9672,11 +9744,11 @@
       </c>
       <c r="O170" s="35"/>
       <c r="P170" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q170" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="31"/>
         <v/>
       </c>
     </row>
@@ -9687,18 +9759,18 @@
       <c r="F171" s="37"/>
       <c r="G171" s="37"/>
       <c r="H171" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I171" s="38"/>
       <c r="J171" s="38"/>
       <c r="K171" s="38"/>
       <c r="L171" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M171" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N171" s="39">
@@ -9706,11 +9778,11 @@
       </c>
       <c r="O171" s="35"/>
       <c r="P171" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q171" s="37" t="str">
-        <f t="shared" ref="Q171:Q189" ca="1" si="31">IF(O171&lt;&gt;"",IFERROR(DATEDIF(O171,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q171:Q189" ca="1" si="36">IF(O171&lt;&gt;"",IFERROR(DATEDIF(O171,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -9721,18 +9793,18 @@
       <c r="F172" s="37"/>
       <c r="G172" s="37"/>
       <c r="H172" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I172" s="38"/>
       <c r="J172" s="38"/>
       <c r="K172" s="38"/>
       <c r="L172" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M172" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N172" s="39">
@@ -9740,11 +9812,11 @@
       </c>
       <c r="O172" s="35"/>
       <c r="P172" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q172" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -9755,18 +9827,18 @@
       <c r="F173" s="37"/>
       <c r="G173" s="37"/>
       <c r="H173" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I173" s="38"/>
       <c r="J173" s="38"/>
       <c r="K173" s="38"/>
       <c r="L173" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M173" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N173" s="39">
@@ -9774,11 +9846,11 @@
       </c>
       <c r="O173" s="35"/>
       <c r="P173" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q173" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -9789,18 +9861,18 @@
       <c r="F174" s="37"/>
       <c r="G174" s="37"/>
       <c r="H174" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I174" s="38"/>
       <c r="J174" s="38"/>
       <c r="K174" s="38"/>
       <c r="L174" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M174" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N174" s="39">
@@ -9808,11 +9880,11 @@
       </c>
       <c r="O174" s="35"/>
       <c r="P174" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q174" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -9823,18 +9895,18 @@
       <c r="F175" s="37"/>
       <c r="G175" s="37"/>
       <c r="H175" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I175" s="38"/>
       <c r="J175" s="38"/>
       <c r="K175" s="38"/>
       <c r="L175" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M175" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N175" s="39">
@@ -9842,11 +9914,11 @@
       </c>
       <c r="O175" s="35"/>
       <c r="P175" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q175" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -9857,18 +9929,18 @@
       <c r="F176" s="37"/>
       <c r="G176" s="37"/>
       <c r="H176" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I176" s="38"/>
       <c r="J176" s="38"/>
       <c r="K176" s="38"/>
       <c r="L176" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M176" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N176" s="39">
@@ -9876,11 +9948,11 @@
       </c>
       <c r="O176" s="35"/>
       <c r="P176" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q176" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -9891,18 +9963,18 @@
       <c r="F177" s="37"/>
       <c r="G177" s="37"/>
       <c r="H177" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I177" s="38"/>
       <c r="J177" s="38"/>
       <c r="K177" s="38"/>
       <c r="L177" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M177" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N177" s="39">
@@ -9910,11 +9982,11 @@
       </c>
       <c r="O177" s="35"/>
       <c r="P177" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q177" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -9925,18 +9997,18 @@
       <c r="F178" s="37"/>
       <c r="G178" s="37"/>
       <c r="H178" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I178" s="38"/>
       <c r="J178" s="38"/>
       <c r="K178" s="38"/>
       <c r="L178" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M178" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N178" s="39">
@@ -9944,11 +10016,11 @@
       </c>
       <c r="O178" s="35"/>
       <c r="P178" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q178" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -9959,18 +10031,18 @@
       <c r="F179" s="37"/>
       <c r="G179" s="37"/>
       <c r="H179" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I179" s="38"/>
       <c r="J179" s="38"/>
       <c r="K179" s="38"/>
       <c r="L179" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M179" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N179" s="39">
@@ -9978,11 +10050,11 @@
       </c>
       <c r="O179" s="35"/>
       <c r="P179" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q179" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -9993,18 +10065,18 @@
       <c r="F180" s="37"/>
       <c r="G180" s="37"/>
       <c r="H180" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I180" s="38"/>
       <c r="J180" s="38"/>
       <c r="K180" s="38"/>
       <c r="L180" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M180" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N180" s="39">
@@ -10012,11 +10084,11 @@
       </c>
       <c r="O180" s="35"/>
       <c r="P180" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q180" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10027,18 +10099,18 @@
       <c r="F181" s="37"/>
       <c r="G181" s="37"/>
       <c r="H181" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I181" s="38"/>
       <c r="J181" s="38"/>
       <c r="K181" s="38"/>
       <c r="L181" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M181" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N181" s="39">
@@ -10046,11 +10118,11 @@
       </c>
       <c r="O181" s="35"/>
       <c r="P181" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q181" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10061,18 +10133,18 @@
       <c r="F182" s="37"/>
       <c r="G182" s="37"/>
       <c r="H182" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I182" s="38"/>
       <c r="J182" s="38"/>
       <c r="K182" s="38"/>
       <c r="L182" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M182" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N182" s="39">
@@ -10080,11 +10152,11 @@
       </c>
       <c r="O182" s="35"/>
       <c r="P182" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q182" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10095,18 +10167,18 @@
       <c r="F183" s="37"/>
       <c r="G183" s="37"/>
       <c r="H183" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I183" s="38"/>
       <c r="J183" s="38"/>
       <c r="K183" s="38"/>
       <c r="L183" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M183" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N183" s="39">
@@ -10114,11 +10186,11 @@
       </c>
       <c r="O183" s="35"/>
       <c r="P183" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q183" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10129,18 +10201,18 @@
       <c r="F184" s="37"/>
       <c r="G184" s="37"/>
       <c r="H184" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I184" s="38"/>
       <c r="J184" s="38"/>
       <c r="K184" s="38"/>
       <c r="L184" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M184" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N184" s="39">
@@ -10148,11 +10220,11 @@
       </c>
       <c r="O184" s="35"/>
       <c r="P184" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q184" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10163,18 +10235,18 @@
       <c r="F185" s="37"/>
       <c r="G185" s="37"/>
       <c r="H185" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I185" s="38"/>
       <c r="J185" s="38"/>
       <c r="K185" s="38"/>
       <c r="L185" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M185" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N185" s="39">
@@ -10182,11 +10254,11 @@
       </c>
       <c r="O185" s="35"/>
       <c r="P185" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q185" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10197,18 +10269,18 @@
       <c r="F186" s="37"/>
       <c r="G186" s="37"/>
       <c r="H186" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I186" s="38"/>
       <c r="J186" s="38"/>
       <c r="K186" s="38"/>
       <c r="L186" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M186" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N186" s="39">
@@ -10216,11 +10288,11 @@
       </c>
       <c r="O186" s="35"/>
       <c r="P186" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q186" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10231,18 +10303,18 @@
       <c r="F187" s="37"/>
       <c r="G187" s="37"/>
       <c r="H187" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I187" s="38"/>
       <c r="J187" s="38"/>
       <c r="K187" s="38"/>
       <c r="L187" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M187" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N187" s="39">
@@ -10250,11 +10322,11 @@
       </c>
       <c r="O187" s="35"/>
       <c r="P187" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q187" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10265,18 +10337,18 @@
       <c r="F188" s="37"/>
       <c r="G188" s="37"/>
       <c r="H188" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I188" s="38"/>
       <c r="J188" s="38"/>
       <c r="K188" s="38"/>
       <c r="L188" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M188" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N188" s="39">
@@ -10284,11 +10356,11 @@
       </c>
       <c r="O188" s="35"/>
       <c r="P188" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q188" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
@@ -10299,18 +10371,18 @@
       <c r="F189" s="37"/>
       <c r="G189" s="37"/>
       <c r="H189" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I189" s="38"/>
       <c r="J189" s="38"/>
       <c r="K189" s="38"/>
       <c r="L189" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M189" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N189" s="39">
@@ -10318,57 +10390,57 @@
       </c>
       <c r="O189" s="35"/>
       <c r="P189" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q189" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="36"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="C5:Q100" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q100">
-      <sortCondition sortBy="cellColor" ref="J5" dxfId="19"/>
+      <sortCondition sortBy="cellColor" ref="J5" dxfId="23"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="I6:I189">
-    <cfRule type="cellIs" dxfId="17" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="13" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J189">
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="12" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K189">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="5" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K69">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K71">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K73">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10395,45 +10467,45 @@
   <sheetData>
     <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="33" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="K2" s="34" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="O2" s="34" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="54" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>1</v>
@@ -10471,7 +10543,7 @@
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>1</v>
@@ -10512,7 +10584,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>1</v>
@@ -10554,7 +10626,7 @@
         <v>2412.5700000000002</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1</v>
@@ -10592,7 +10664,7 @@
     <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>1</v>
@@ -10632,7 +10704,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>1</v>
@@ -10673,7 +10745,7 @@
         <v>5612.57</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>1</v>
@@ -10711,7 +10783,7 @@
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D10" s="54" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
@@ -10746,7 +10818,7 @@
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D11" s="54" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="37" t="s">
@@ -10781,7 +10853,7 @@
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D12" s="54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="37" t="s">
@@ -10954,7 +11026,7 @@
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10964,10 +11036,10 @@
     <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="M3" s="77" t="s">
         <v>157</v>
+      </c>
+      <c r="M3" s="75" t="s">
+        <v>158</v>
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
@@ -10978,9 +11050,9 @@
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="M4" s="78"/>
+        <v>159</v>
+      </c>
+      <c r="M4" s="76"/>
       <c r="N4" s="49"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
@@ -10989,7 +11061,7 @@
       <c r="F5" s="16"/>
       <c r="G5" s="28"/>
       <c r="L5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N5" s="1">
         <v>4912</v>
@@ -11008,10 +11080,10 @@
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
       <c r="L8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N8" s="1">
         <v>338</v>
@@ -11019,41 +11091,41 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F9" s="47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="43"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>5007.6200000000026</v>
+        <v>4782.6200000000026</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N10" s="43"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>5007.6200000000026</v>
+        <v>4782.6200000000026</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>5007.6200000000026</v>
+        <v>4782.6200000000026</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -11067,7 +11139,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
@@ -11075,19 +11147,19 @@
       <c r="N12" s="43"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F13" s="72" t="s">
-        <v>158</v>
+      <c r="F13" s="74" t="s">
+        <v>159</v>
       </c>
       <c r="G13" s="52"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
       <c r="N13" s="43"/>
     </row>
     <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C14" s="53"/>
       <c r="D14" s="53"/>
       <c r="F14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
@@ -11098,7 +11170,7 @@
       <c r="C15" s="53"/>
       <c r="D15" s="53"/>
       <c r="F15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G15" s="53">
         <v>773.35</v>
@@ -11111,7 +11183,7 @@
       <c r="C16" s="53"/>
       <c r="D16" s="53"/>
       <c r="F16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G16" s="53">
         <v>-5148</v>
@@ -11124,7 +11196,7 @@
       <c r="C17" s="53"/>
       <c r="D17" s="53"/>
       <c r="F17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G17" s="53">
         <v>-168</v>
@@ -11137,7 +11209,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="F18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G18" s="53">
         <v>-1700</v>
@@ -11150,7 +11222,7 @@
       <c r="C19" s="53"/>
       <c r="D19" s="53"/>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G19" s="53">
         <v>5148</v>
@@ -11163,7 +11235,7 @@
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
       <c r="F20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G20" s="53">
         <v>-4938</v>
@@ -11176,7 +11248,7 @@
       <c r="C21" s="53"/>
       <c r="D21" s="53"/>
       <c r="F21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G21" s="53">
         <v>-1595</v>
@@ -11189,7 +11261,7 @@
       <c r="C22" s="53"/>
       <c r="D22" s="53"/>
       <c r="F22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G22" s="53">
         <v>-4677</v>
@@ -11202,7 +11274,7 @@
       <c r="C23" s="53"/>
       <c r="D23" s="53"/>
       <c r="F23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G23" s="53">
         <v>-200</v>
@@ -11215,7 +11287,7 @@
       <c r="C24" s="53"/>
       <c r="D24" s="53"/>
       <c r="F24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G24" s="53">
         <v>4677</v>
@@ -11228,7 +11300,7 @@
       <c r="C25" s="53"/>
       <c r="D25" s="53"/>
       <c r="F25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G25" s="53">
         <v>-750</v>
@@ -11241,7 +11313,7 @@
       <c r="C26" s="53"/>
       <c r="D26" s="53"/>
       <c r="F26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G26" s="53">
         <v>-652</v>
@@ -11254,7 +11326,7 @@
       <c r="C27" s="53"/>
       <c r="D27" s="53"/>
       <c r="F27" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G27" s="53">
         <v>11100</v>
@@ -11267,7 +11339,7 @@
       <c r="C28" s="53"/>
       <c r="D28" s="53"/>
       <c r="F28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G28" s="53">
         <v>-396</v>
@@ -11280,7 +11352,7 @@
       <c r="C29" s="53"/>
       <c r="D29" s="53"/>
       <c r="F29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G29" s="53">
         <v>-4211</v>
@@ -11293,7 +11365,7 @@
       <c r="C30" s="53"/>
       <c r="D30" s="53"/>
       <c r="F30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G30" s="53">
         <v>-450</v>
@@ -11306,7 +11378,7 @@
       <c r="C31" s="53"/>
       <c r="D31" s="53"/>
       <c r="F31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G31" s="53">
         <v>-1197</v>
@@ -11319,7 +11391,7 @@
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
       <c r="F32" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="G32" s="53">
         <v>-315</v>
@@ -11332,7 +11404,7 @@
       <c r="C33" s="53"/>
       <c r="D33" s="53"/>
       <c r="F33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G33" s="53">
         <v>-830</v>
@@ -11345,7 +11417,7 @@
       <c r="C34" s="53"/>
       <c r="D34" s="53"/>
       <c r="F34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G34" s="53">
         <v>4211</v>
@@ -11358,7 +11430,7 @@
       <c r="C35" s="53"/>
       <c r="D35" s="53"/>
       <c r="F35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G35" s="53">
         <v>-200</v>
@@ -11371,7 +11443,7 @@
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
       <c r="F36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G36" s="53">
         <v>10000</v>
@@ -11384,7 +11456,7 @@
       <c r="C37" s="53"/>
       <c r="D37" s="53"/>
       <c r="F37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G37" s="53">
         <v>-200</v>
@@ -11397,7 +11469,7 @@
       <c r="C38" s="53"/>
       <c r="D38" s="53"/>
       <c r="F38" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G38" s="53">
         <v>-381</v>
@@ -11410,7 +11482,7 @@
       <c r="C39" s="53"/>
       <c r="D39" s="53"/>
       <c r="F39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G39" s="53">
         <v>-4911</v>
@@ -11424,7 +11496,7 @@
       <c r="D40" s="53"/>
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G40" s="53">
         <v>-5700</v>
@@ -11437,7 +11509,7 @@
       <c r="C41" s="53"/>
       <c r="D41" s="53"/>
       <c r="F41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G41" s="53">
         <v>-400</v>
@@ -11450,7 +11522,7 @@
       <c r="C42" s="53"/>
       <c r="D42" s="53"/>
       <c r="F42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G42" s="53">
         <v>-450</v>
@@ -11463,7 +11535,7 @@
       <c r="C43" s="53"/>
       <c r="D43" s="53"/>
       <c r="F43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G43" s="53">
         <v>-640</v>
@@ -11477,7 +11549,7 @@
       <c r="D44" s="53"/>
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G44" s="53">
         <v>5700</v>
@@ -11490,7 +11562,7 @@
       <c r="C45" s="53"/>
       <c r="D45" s="53"/>
       <c r="F45" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G45" s="53">
         <v>-130</v>
@@ -11503,7 +11575,7 @@
       <c r="C46" s="53"/>
       <c r="D46" s="53"/>
       <c r="F46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G46" s="53">
         <v>-250</v>
@@ -11516,7 +11588,7 @@
       <c r="C47" s="53"/>
       <c r="D47" s="53"/>
       <c r="F47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G47" s="53">
         <v>-112.2</v>
@@ -11529,7 +11601,7 @@
       <c r="C48" s="53"/>
       <c r="D48" s="53"/>
       <c r="F48" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G48" s="53">
         <v>4911</v>
@@ -11542,7 +11614,7 @@
       <c r="C49" s="53"/>
       <c r="D49" s="53"/>
       <c r="F49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G49" s="53">
         <v>-3000</v>
@@ -11555,7 +11627,7 @@
       <c r="C50" s="53"/>
       <c r="D50" s="53"/>
       <c r="F50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G50" s="53">
         <v>-4000</v>
@@ -11568,7 +11640,7 @@
       <c r="C51" s="53"/>
       <c r="D51" s="53"/>
       <c r="F51" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G51" s="53">
         <v>-200</v>
@@ -11581,7 +11653,7 @@
       <c r="C52" s="53"/>
       <c r="D52" s="53"/>
       <c r="F52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G52" s="53">
         <v>-4612</v>
@@ -11592,7 +11664,7 @@
     </row>
     <row r="53" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G53" s="53">
         <v>-700</v>
@@ -11603,7 +11675,7 @@
     </row>
     <row r="54" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G54" s="53">
         <v>-880</v>
@@ -11614,7 +11686,7 @@
     </row>
     <row r="55" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G55" s="53">
         <v>-310</v>
@@ -11625,7 +11697,7 @@
     </row>
     <row r="56" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G56" s="53">
         <v>-250</v>
@@ -11636,7 +11708,7 @@
     </row>
     <row r="57" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G57" s="53">
         <v>4690</v>
@@ -11647,7 +11719,7 @@
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G58" s="53">
         <v>-4440</v>
@@ -11658,7 +11730,7 @@
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G59" s="53">
         <v>-4697</v>
@@ -11668,7 +11740,7 @@
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G60" s="53">
         <v>-2500</v>
@@ -11678,7 +11750,7 @@
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G61" s="53">
         <v>-126</v>
@@ -11688,7 +11760,7 @@
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G62" s="53">
         <v>4742</v>
@@ -11698,7 +11770,7 @@
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G63" s="53">
         <v>-410</v>
@@ -11713,7 +11785,7 @@
     </row>
     <row r="65" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G65" s="53">
         <v>3320</v>
@@ -11723,7 +11795,7 @@
     </row>
     <row r="66" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G66" s="53">
         <v>4090</v>
@@ -11733,7 +11805,7 @@
     </row>
     <row r="67" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G67" s="53">
         <v>-5688</v>
@@ -11743,7 +11815,7 @@
     </row>
     <row r="68" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G68" s="53">
         <v>-4433</v>
@@ -11753,7 +11825,7 @@
     </row>
     <row r="69" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F69" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G69" s="53">
         <v>-250</v>
@@ -11763,7 +11835,7 @@
     </row>
     <row r="70" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F70" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G70" s="53">
         <v>-99</v>
@@ -11773,7 +11845,7 @@
     </row>
     <row r="71" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G71" s="53">
         <v>320</v>
@@ -11783,7 +11855,7 @@
     </row>
     <row r="72" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F72" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G72" s="53">
         <v>-1572</v>
@@ -11798,7 +11870,7 @@
     </row>
     <row r="74" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F74" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G74" s="53">
         <v>4433</v>
@@ -11808,7 +11880,7 @@
     </row>
     <row r="75" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F75" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G75" s="53">
         <v>8000</v>
@@ -11818,7 +11890,7 @@
     </row>
     <row r="76" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G76" s="53">
         <v>-1344</v>
@@ -11828,7 +11900,7 @@
     </row>
     <row r="77" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F77" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G77" s="53">
         <v>-308</v>
@@ -11838,7 +11910,7 @@
     </row>
     <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F78" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G78" s="53">
         <v>-4204</v>
@@ -11848,7 +11920,7 @@
     </row>
     <row r="79" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F79" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G79" s="53">
         <v>-338</v>
@@ -11858,7 +11930,7 @@
     </row>
     <row r="80" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F80" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G80" s="53">
         <v>-50</v>
@@ -11867,10 +11939,8 @@
       <c r="I80" s="53"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C81" s="53"/>
-      <c r="D81" s="53"/>
       <c r="F81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G81" s="53">
         <v>338</v>
@@ -11879,10 +11949,15 @@
       <c r="I81" s="53"/>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C82" s="53"/>
+      <c r="B82" t="s">
+        <v>223</v>
+      </c>
+      <c r="C82" s="53">
+        <v>8000</v>
+      </c>
       <c r="D82" s="53"/>
       <c r="F82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G82" s="53">
         <v>-540</v>
@@ -11892,14 +11967,14 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C83" s="53">
-        <v>8000</v>
+        <v>5170</v>
       </c>
       <c r="D83" s="53"/>
       <c r="F83" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G83" s="53">
         <v>-184.31</v>
@@ -11909,14 +11984,14 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C84" s="53">
         <v>4124</v>
       </c>
       <c r="D84" s="53"/>
       <c r="F84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G84" s="53">
         <v>-1464.22</v>
@@ -11926,14 +12001,14 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C85" s="53">
         <v>-50</v>
       </c>
       <c r="D85" s="53"/>
       <c r="F85" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G85" s="53">
         <v>1005</v>
@@ -11943,14 +12018,14 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C86" s="53">
         <v>2000</v>
       </c>
       <c r="D86" s="53"/>
       <c r="F86" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G86" s="53">
         <v>-500</v>
@@ -11960,19 +12035,24 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C87" s="53">
         <v>-4500</v>
       </c>
       <c r="D87" s="53"/>
-      <c r="G87" s="53"/>
+      <c r="F87" t="s">
+        <v>254</v>
+      </c>
+      <c r="G87" s="53">
+        <v>-225</v>
+      </c>
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C88" s="53">
         <v>-12807</v>
@@ -11990,12 +12070,7 @@
       <c r="I89" s="53"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>227</v>
-      </c>
-      <c r="C90" s="53">
-        <v>5170</v>
-      </c>
+      <c r="C90" s="53"/>
       <c r="D90" s="53"/>
       <c r="G90" s="53"/>
       <c r="H90" s="53"/>
@@ -12010,7 +12085,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C92" s="53">
         <v>2000</v>
@@ -12024,7 +12099,7 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C93" s="53">
         <v>-50</v>
@@ -12036,7 +12111,7 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C94" s="53">
         <v>160</v>
@@ -12055,7 +12130,7 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C96" s="53">
         <v>2000</v>
@@ -12069,7 +12144,7 @@
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C97" s="53">
         <v>-50</v>
@@ -12081,7 +12156,7 @@
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C98" s="53">
         <v>300</v>
@@ -12100,7 +12175,7 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C100" s="53">
         <v>2000</v>
@@ -12114,7 +12189,7 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C101" s="53">
         <v>8000</v>
@@ -12126,7 +12201,7 @@
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C102" s="53">
         <v>4180</v>
@@ -12145,7 +12220,7 @@
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C104" s="53">
         <v>2000</v>
@@ -12159,7 +12234,7 @@
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C105" s="53">
         <v>2000</v>
@@ -12173,7 +12248,7 @@
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C106" s="53">
         <v>2000</v>
@@ -12194,7 +12269,7 @@
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C108" s="53">
         <v>-20000</v>
@@ -12213,7 +12288,7 @@
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C110" s="53">
         <v>2000</v>
@@ -12227,7 +12302,7 @@
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C111" s="53">
         <v>2000</v>
@@ -12241,7 +12316,7 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C112" s="53">
         <v>8000</v>
@@ -12253,7 +12328,7 @@
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C113" s="53">
         <v>2000</v>
@@ -12267,7 +12342,7 @@
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C114" s="53">
         <v>2000</v>
@@ -13457,43 +13532,43 @@
   <mergeCells count="1">
     <mergeCell ref="M3:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C81:D114">
-    <cfRule type="cellIs" dxfId="9" priority="133" operator="greaterThan">
+  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C82:D114">
+    <cfRule type="cellIs" dxfId="13" priority="135" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="134" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="136" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:D52">
-    <cfRule type="cellIs" dxfId="7" priority="127" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="129" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="128" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="130" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G120:G1048576">
-    <cfRule type="cellIs" dxfId="5" priority="129" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="131" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="130" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="132" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:I119">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H120:I266">
-    <cfRule type="cellIs" dxfId="1" priority="131" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="133" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="134" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13515,74 +13590,74 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="62" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="54" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="54"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C3" s="37"/>
       <c r="D3" s="54"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C4" s="37"/>
       <c r="D4" s="54"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="54" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C5" s="37"/>
       <c r="D5" s="54"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" s="37"/>
       <c r="D6" s="54"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="54"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C8" s="37"/>
       <c r="D8" s="54"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="54"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="54"/>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/FEA781441E4F247C/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_3D0428C4E0E4AF08C16F331DF5B9D519ABAF25DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8EF7688-1AC3-477A-BC02-719C8F704859}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="11_3D0428C4E0E4AF08C16F331DF5B9D519ABAF25DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{267B0311-4F52-421E-AD05-E435CE9EAF7E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Itaú!$C$4:$Q$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$99</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="266">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">        Gás</t>
   </si>
   <si>
-    <t xml:space="preserve">        Seguranças+Câmera</t>
+    <t xml:space="preserve">        Seguranças+Câmera+Seguro+Edilson</t>
   </si>
   <si>
     <t>Compensasões no cartão da Stella</t>
@@ -117,6 +117,9 @@
     <t xml:space="preserve">        Vivo</t>
   </si>
   <si>
+    <t xml:space="preserve">        Seguranças+Câmeras+Seguro+Edilson</t>
+  </si>
+  <si>
     <t xml:space="preserve">        Recolhimento INSS</t>
   </si>
   <si>
@@ -492,6 +495,39 @@
     <t xml:space="preserve">Estorno Indiana Jones </t>
   </si>
   <si>
+    <t>Presente Dimitri</t>
+  </si>
+  <si>
+    <t>Andiamo</t>
+  </si>
+  <si>
+    <t>Vans Loafer</t>
+  </si>
+  <si>
+    <t>Bonfa's Beer</t>
+  </si>
+  <si>
+    <t>Craft Beer</t>
+  </si>
+  <si>
+    <t>Pagamento Craft Beer</t>
+  </si>
+  <si>
+    <t>Tapete Higiênico</t>
+  </si>
+  <si>
+    <t>Pet</t>
+  </si>
+  <si>
+    <t>Estacionamento Scanntech</t>
+  </si>
+  <si>
+    <t>Sukyia</t>
+  </si>
+  <si>
+    <t>Gensho</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -516,6 +552,9 @@
     <t>Empréstimo</t>
   </si>
   <si>
+    <t>Honorários Edilson</t>
+  </si>
+  <si>
     <t>Dinheiro guardado para...</t>
   </si>
   <si>
@@ -714,10 +753,13 @@
     <t>Retorno reembolso</t>
   </si>
   <si>
+    <t>Ilumeo Agosto - 2º PPT</t>
+  </si>
+  <si>
     <t>Jogos e Restaurantes</t>
   </si>
   <si>
-    <t>Ilumeo Agosto - 2º PPT</t>
+    <t>Restituição IR</t>
   </si>
   <si>
     <t>INSS Stella</t>
@@ -732,9 +774,6 @@
     <t>Passagens - Compradas em agosto</t>
   </si>
   <si>
-    <t>Restituição IR</t>
-  </si>
-  <si>
     <t>Outubro</t>
   </si>
   <si>
@@ -805,12 +844,6 @@
   </si>
   <si>
     <t>Dera</t>
-  </si>
-  <si>
-    <t>Presente Dimitri</t>
-  </si>
-  <si>
-    <t>Andiamo</t>
   </si>
 </sst>
 </file>
@@ -822,7 +855,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1298,17 +1331,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1381,6 +1424,21 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E1F2"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor theme="4" tint="0.79989013336588644"/>
         </patternFill>
@@ -1438,14 +1496,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
-          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1528,10 +1578,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1711,7 +1757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
@@ -1720,8 +1766,8 @@
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" ht="15.75" customHeight="1"/>
+    <row r="2" spans="2:6" ht="23.25" customHeight="1">
       <c r="B2" s="77" t="s">
         <v>0</v>
       </c>
@@ -1733,20 +1779,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="24" customHeight="1">
       <c r="B3" s="78"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C24+C25+C7</f>
-        <v>2288.4539047619041</v>
+        <v>2255.4189047619043</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E24+E25</f>
-        <v>2619.4166666666679</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2121.3216666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="7.5" customHeight="1"/>
+    <row r="5" spans="2:6">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1758,21 +1804,21 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-7049.5460952380963</v>
+        <v>-7582.5810952380962</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-7380.583333333333</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+        <v>-7878.6783333333333</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1780,7 +1826,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6">
       <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1794,49 +1840,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6">
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>4596.8144285714288</v>
+        <v>5025.3494285714287</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1768.0133333333333</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2161.6083333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>4596.8144285714288</v>
+        <v>5025.3494285714287</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1768.0133333333333</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2161.6083333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="8">
         <f>Contas!B6</f>
-        <v>2412.5700000000002</v>
+        <v>2517.0700000000002</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="8">
         <f>Contas!B9</f>
-        <v>5612.57</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+        <v>5717.07</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" outlineLevel="1">
       <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
@@ -1850,7 +1896,7 @@
         <v>1617.835</v>
       </c>
     </row>
-    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" outlineLevel="1">
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1864,22 +1910,22 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" outlineLevel="1">
       <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="14">
         <f>Contas!K5</f>
-        <v>210.5</v>
+        <v>165</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="14">
         <f>Contas!K5</f>
-        <v>210.5</v>
+        <v>165</v>
       </c>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" outlineLevel="1">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
@@ -1893,7 +1939,7 @@
         <v>43.35</v>
       </c>
     </row>
-    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" outlineLevel="1">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
@@ -1907,21 +1953,21 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" outlineLevel="1">
       <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="14">
-        <f>Contas!$K9</f>
-        <v>183.5</v>
+        <f>Contas!$K9+Contas!$K13</f>
+        <v>333.5</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="14">
-        <f>Contas!K9</f>
-        <v>183.5</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+        <f>Contas!$K9+Contas!$K13</f>
+        <v>333.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" outlineLevel="1">
       <c r="B18" s="13" t="str">
         <f>Contas!$D10</f>
         <v>Cartão Itaú da Stella</v>
@@ -1933,7 +1979,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" outlineLevel="1">
       <c r="B19" s="13" t="str">
         <f>Contas!$D11</f>
         <v>Recolhimento INSS</v>
@@ -1945,7 +1991,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" outlineLevel="1">
       <c r="B20" s="13" t="str">
         <f>Contas!$D12</f>
         <v>Empréstimo</v>
@@ -1957,7 +2003,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" outlineLevel="1">
       <c r="B21" s="17" t="s">
         <v>16</v>
       </c>
@@ -1965,29 +2011,29 @@
       <c r="D21" s="19"/>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" outlineLevel="1">
       <c r="B22" s="13"/>
       <c r="C22" s="14"/>
       <c r="D22" s="15"/>
       <c r="E22" s="14"/>
     </row>
-    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" outlineLevel="1">
       <c r="B23" s="13"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
       <c r="E23" s="14"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5">
       <c r="B24" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="8">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5">
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
@@ -2001,7 +2047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" outlineLevel="1">
       <c r="B26" s="13" t="s">
         <v>19</v>
       </c>
@@ -2012,7 +2058,7 @@
       <c r="D26" s="15"/>
       <c r="E26" s="14"/>
     </row>
-    <row r="27" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" outlineLevel="1">
       <c r="B27" s="13" t="s">
         <v>20</v>
       </c>
@@ -2020,7 +2066,7 @@
       <c r="D27" s="20"/>
       <c r="E27" s="21"/>
     </row>
-    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" outlineLevel="1">
       <c r="B28" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
         <v xml:space="preserve">       </v>
@@ -2032,7 +2078,7 @@
       <c r="D28" s="20"/>
       <c r="E28" s="21"/>
     </row>
-    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" outlineLevel="1">
       <c r="B29" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       Reembolso Psicóloga</v>
@@ -2044,7 +2090,7 @@
       <c r="D29" s="20"/>
       <c r="E29" s="21"/>
     </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" outlineLevel="1">
       <c r="B30" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
@@ -2056,7 +2102,7 @@
       <c r="D30" s="20"/>
       <c r="E30" s="21"/>
     </row>
-    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" outlineLevel="1">
       <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
@@ -2068,7 +2114,7 @@
       <c r="D31" s="20"/>
       <c r="E31" s="21"/>
     </row>
-    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" outlineLevel="1">
       <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
@@ -2080,7 +2126,7 @@
       <c r="D32" s="20"/>
       <c r="E32" s="21"/>
     </row>
-    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" outlineLevel="1">
       <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
@@ -2092,7 +2138,7 @@
       <c r="D33" s="20"/>
       <c r="E33" s="21"/>
     </row>
-    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" outlineLevel="1">
       <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
@@ -2104,7 +2150,7 @@
       <c r="D34" s="20"/>
       <c r="E34" s="21"/>
     </row>
-    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" outlineLevel="1">
       <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
@@ -2116,7 +2162,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="21"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6">
       <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
@@ -2129,7 +2175,7 @@
       <c r="E36" s="21"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6">
       <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L17</f>
         <v xml:space="preserve">       </v>
@@ -2142,7 +2188,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="16"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6">
       <c r="B38" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
@@ -2154,7 +2200,7 @@
       <c r="D38" s="20"/>
       <c r="E38" s="21"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6">
       <c r="B39" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
@@ -2177,18 +2223,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:D22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:D23"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="39" customHeight="1"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1">
       <c r="B2" s="22"/>
       <c r="C2" s="23" t="s">
         <v>2</v>
@@ -2197,7 +2243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2210,55 +2256,55 @@
         <v>40.161666666666669</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1768.0133333333333</v>
+        <v>2161.6083333333331</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>4596.8144285714288</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+        <v>5025.3494285714287</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
       <c r="D7" s="24"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="13"/>
       <c r="C8" s="8"/>
       <c r="D8" s="24"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="13"/>
       <c r="C9" s="8"/>
       <c r="D9" s="24"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="8">
         <f>SUM(C11,C13:C16)</f>
-        <v>2078.1849999999999</v>
+        <v>2182.6849999999999</v>
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4">
       <c r="B11" s="13" t="s">
         <v>21</v>
       </c>
@@ -2268,7 +2314,7 @@
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4">
       <c r="B12" s="25" t="s">
         <v>22</v>
       </c>
@@ -2278,17 +2324,17 @@
       </c>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4">
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="14">
         <f>Contas!K5</f>
-        <v>210.5</v>
+        <v>165</v>
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4">
       <c r="B14" s="13" t="s">
         <v>13</v>
       </c>
@@ -2298,7 +2344,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4">
       <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
@@ -2308,19 +2354,19 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4">
       <c r="B16" s="13" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
         <f>Saldo!E17</f>
-        <v>183.5</v>
+        <v>333.5</v>
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4">
       <c r="B17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
         <f>Saldo!E19</f>
@@ -2328,41 +2374,46 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="11">
+    <row r="18" spans="2:4">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="13"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>3846.1983333333333</v>
-      </c>
-      <c r="D18" s="27"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="72">
-        <v>4204.74</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+        <v>4344.2933333333331</v>
+      </c>
+      <c r="D19" s="27"/>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="2:4">
       <c r="B21" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="73">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="72">
+        <v>4204.74</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
       <c r="B22" t="s">
         <v>27</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="73">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" t="s">
         <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2377,7 +2428,7 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="C1:Q67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="2" customWidth="1"/>
@@ -2392,9 +2443,9 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1">
       <c r="D1" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -2403,10 +2454,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="31">
         <f>SUM(L5:L21)</f>
         <v>40.161666666666669</v>
@@ -2424,59 +2475,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17" ht="30" customHeight="1">
       <c r="C4" s="33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="3:17" ht="16.5" customHeight="1">
       <c r="C5" s="70" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>1</v>
@@ -2491,10 +2542,10 @@
         <v>240.97</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5" s="38">
         <f t="shared" ref="L5:L15" si="1">I5/N5</f>
@@ -2519,7 +2570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17" ht="16.5" customHeight="1">
       <c r="C6" s="37"/>
       <c r="D6" s="36"/>
       <c r="E6" s="37"/>
@@ -2551,7 +2602,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" ht="16.5" customHeight="1">
       <c r="C7" s="35"/>
       <c r="D7" s="36"/>
       <c r="E7" s="37"/>
@@ -2580,7 +2631,7 @@
       <c r="P7" s="35"/>
       <c r="Q7" s="37"/>
     </row>
-    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17" ht="16.5" customHeight="1">
       <c r="C8" s="35"/>
       <c r="D8" s="36"/>
       <c r="E8" s="37"/>
@@ -2609,7 +2660,7 @@
       <c r="P8" s="35"/>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17" ht="16.5" customHeight="1">
       <c r="C9" s="35"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
@@ -2638,7 +2689,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="37"/>
     </row>
-    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" ht="16.5" customHeight="1">
       <c r="C10" s="35"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -2670,7 +2721,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17" ht="16.5" customHeight="1">
       <c r="C11" s="35"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
@@ -2699,7 +2750,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="37"/>
     </row>
-    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17" ht="16.5" customHeight="1">
       <c r="C12" s="37"/>
       <c r="D12" s="36"/>
       <c r="E12" s="37"/>
@@ -2728,7 +2779,7 @@
       <c r="P12" s="35"/>
       <c r="Q12" s="37"/>
     </row>
-    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" ht="16.5" customHeight="1">
       <c r="C13" s="37"/>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
@@ -2757,7 +2808,7 @@
       <c r="P13" s="35"/>
       <c r="Q13" s="37"/>
     </row>
-    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17" ht="16.5" customHeight="1">
       <c r="C14" s="37"/>
       <c r="D14" s="36"/>
       <c r="E14" s="37"/>
@@ -2786,7 +2837,7 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="37"/>
     </row>
-    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17" ht="16.5" customHeight="1">
       <c r="C15" s="37"/>
       <c r="D15" s="36"/>
       <c r="E15" s="37"/>
@@ -2815,7 +2866,7 @@
       <c r="P15" s="35"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" ht="16.5" customHeight="1">
       <c r="C16" s="37"/>
       <c r="D16" s="36"/>
       <c r="E16" s="37"/>
@@ -2832,7 +2883,7 @@
       <c r="P16" s="35"/>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" ht="16.5" customHeight="1">
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="37"/>
@@ -2849,7 +2900,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="37"/>
     </row>
-    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" ht="16.5" customHeight="1">
       <c r="C18" s="35"/>
       <c r="D18" s="36"/>
       <c r="E18" s="37"/>
@@ -2866,7 +2917,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" ht="16.5" customHeight="1">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -2877,198 +2928,198 @@
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17">
       <c r="H20" s="2"/>
       <c r="O20" s="42"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17">
       <c r="H21" s="2"/>
       <c r="O21" s="42"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17">
       <c r="H22" s="2"/>
       <c r="O22" s="42"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17">
       <c r="O23" s="42"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17">
       <c r="O24" s="42"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17">
       <c r="O25" s="42"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17">
       <c r="O26" s="42"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17">
       <c r="O27" s="42"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17">
       <c r="O28" s="42"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17">
       <c r="O29" s="42"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17">
       <c r="O30" s="42"/>
       <c r="P30" s="42"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17">
       <c r="O31" s="42"/>
       <c r="P31" s="42"/>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17">
       <c r="O32" s="42"/>
       <c r="P32" s="42"/>
     </row>
-    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="15:16">
       <c r="O33" s="42"/>
       <c r="P33" s="42"/>
     </row>
-    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="15:16">
       <c r="O34" s="42"/>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="15:16">
       <c r="O35" s="42"/>
       <c r="P35" s="42"/>
     </row>
-    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="15:16">
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
     </row>
-    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="15:16">
       <c r="O37" s="42"/>
       <c r="P37" s="42"/>
     </row>
-    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="15:16">
       <c r="O38" s="42"/>
       <c r="P38" s="42"/>
     </row>
-    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="15:16">
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
     </row>
-    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="15:16">
       <c r="O40" s="42"/>
       <c r="P40" s="42"/>
     </row>
-    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="15:16">
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
     </row>
-    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="15:16">
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
     </row>
-    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="15:16">
       <c r="O43" s="42"/>
       <c r="P43" s="42"/>
     </row>
-    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="15:16">
       <c r="O44" s="42"/>
       <c r="P44" s="42"/>
     </row>
-    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="15:16">
       <c r="O45" s="42"/>
       <c r="P45" s="42"/>
     </row>
-    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="15:16">
       <c r="O46" s="42"/>
       <c r="P46" s="42"/>
     </row>
-    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="15:16">
       <c r="O47" s="42"/>
       <c r="P47" s="42"/>
     </row>
-    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="15:16">
       <c r="O48" s="42"/>
       <c r="P48" s="42"/>
     </row>
-    <row r="49" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="15:16">
       <c r="O49" s="42"/>
       <c r="P49" s="42"/>
     </row>
-    <row r="50" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="15:16">
       <c r="O50" s="42"/>
       <c r="P50" s="42"/>
     </row>
-    <row r="51" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="15:16">
       <c r="O51" s="42"/>
       <c r="P51" s="42"/>
     </row>
-    <row r="52" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="15:16">
       <c r="O52" s="42"/>
       <c r="P52" s="42"/>
     </row>
-    <row r="53" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="15:16">
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
     </row>
-    <row r="54" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="15:16">
       <c r="O54" s="42"/>
       <c r="P54" s="42"/>
     </row>
-    <row r="55" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="15:16">
       <c r="O55" s="42"/>
       <c r="P55" s="42"/>
     </row>
-    <row r="56" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="15:16">
       <c r="O56" s="42"/>
       <c r="P56" s="42"/>
     </row>
-    <row r="57" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="15:16">
       <c r="O57" s="42"/>
       <c r="P57" s="42"/>
     </row>
-    <row r="58" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="15:16">
       <c r="O58" s="42"/>
       <c r="P58" s="42"/>
     </row>
-    <row r="59" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="15:16">
       <c r="O59" s="42"/>
       <c r="P59" s="42"/>
     </row>
-    <row r="60" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="15:16">
       <c r="O60" s="42"/>
       <c r="P60" s="42"/>
     </row>
-    <row r="61" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="15:16">
       <c r="O61" s="42"/>
       <c r="P61" s="42"/>
     </row>
-    <row r="62" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="15:16">
       <c r="O62" s="42"/>
       <c r="P62" s="42"/>
     </row>
-    <row r="63" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="15:16">
       <c r="O63" s="42"/>
       <c r="P63" s="42"/>
     </row>
-    <row r="64" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="15:16">
       <c r="O64" s="42"/>
       <c r="P64" s="42"/>
     </row>
-    <row r="65" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="15:16">
       <c r="O65" s="42"/>
       <c r="P65" s="42"/>
     </row>
-    <row r="66" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="15:16">
       <c r="O66" s="42"/>
       <c r="P66" s="42"/>
     </row>
-    <row r="67" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="15:16">
       <c r="O67" s="42"/>
       <c r="P67" s="42"/>
     </row>
@@ -3079,7 +3130,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3093,8 +3144,8 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="C1:Q189"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:Q188"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
@@ -3109,9 +3160,9 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1">
       <c r="D1" s="44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -3120,87 +3171,87 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="45">
-        <f>SUM(L6:L327)</f>
-        <v>9691.9337619047601</v>
+        <f>SUM(L6:L326)</f>
+        <v>10514.063761904759</v>
       </c>
       <c r="E2" s="32">
-        <f>SUMIF($E$6:$E$327,E1,$M$6:$M$327)</f>
-        <v>4596.8144285714288</v>
+        <f>SUMIF($E$6:$E$326,E1,$M$6:$M$326)</f>
+        <v>5025.3494285714287</v>
       </c>
       <c r="F2" s="32">
-        <f>SUMIF($F$6:$F$327,F1,$M$6:$M$327)</f>
-        <v>1768.0133333333333</v>
+        <f>SUMIF($F$6:$F$326,F1,$M$6:$M$326)</f>
+        <v>2161.6083333333331</v>
       </c>
       <c r="G2" s="32">
-        <f>SUMIF($G$6:$G$327,G1,$M$6:$M$327)</f>
+        <f>SUMIF($G$6:$G$326,G1,$M$6:$M$326)</f>
         <v>34.5</v>
       </c>
       <c r="L2" s="43"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17">
       <c r="L3" s="43"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17">
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="32.25" customHeight="1">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P5" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="37" t="s">
         <v>1</v>
@@ -3215,10 +3266,10 @@
         <v>258</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" s="38">
         <f t="shared" ref="L6:L37" si="1">I6/N6</f>
@@ -3243,10 +3294,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17">
       <c r="C7" s="35"/>
       <c r="D7" s="69" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>1</v>
@@ -3261,10 +3312,10 @@
         <v>1909.3</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" s="38">
         <f t="shared" si="1"/>
@@ -3289,10 +3340,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17">
       <c r="C8" s="35"/>
       <c r="D8" s="36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>1</v>
@@ -3309,10 +3360,10 @@
         <v>1017.6</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8" s="38">
         <f t="shared" si="1"/>
@@ -3337,10 +3388,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17">
       <c r="C9" s="35"/>
       <c r="D9" s="46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>1</v>
@@ -3357,10 +3408,10 @@
         <v>224.24</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L9" s="38">
         <f t="shared" si="1"/>
@@ -3385,10 +3436,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17">
       <c r="C10" s="35"/>
       <c r="D10" s="36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>1</v>
@@ -3405,10 +3456,10 @@
         <v>22.45</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L10" s="38">
         <f t="shared" si="1"/>
@@ -3431,10 +3482,10 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17">
       <c r="C11" s="35"/>
       <c r="D11" s="46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>1</v>
@@ -3451,10 +3502,10 @@
         <v>60</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L11" s="38">
         <f t="shared" si="1"/>
@@ -3477,10 +3528,10 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17">
       <c r="C12" s="35"/>
       <c r="D12" s="36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>1</v>
@@ -3497,10 +3548,10 @@
         <v>395.54</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L12" s="38">
         <f t="shared" si="1"/>
@@ -3523,10 +3574,10 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17">
       <c r="C13" s="35"/>
       <c r="D13" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>1</v>
@@ -3543,10 +3594,10 @@
         <v>319.42</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K13" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L13" s="38">
         <f t="shared" si="1"/>
@@ -3569,10 +3620,10 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17">
       <c r="C14" s="35"/>
       <c r="D14" s="46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>1</v>
@@ -3589,10 +3640,10 @@
         <v>225</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L14" s="38">
         <f t="shared" si="1"/>
@@ -3615,10 +3666,10 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17">
       <c r="C15" s="35"/>
       <c r="D15" s="36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" s="37" t="s">
         <v>1</v>
@@ -3635,10 +3686,10 @@
         <v>166.15</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L15" s="38">
         <f t="shared" si="1"/>
@@ -3661,10 +3712,10 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17">
       <c r="C16" s="35"/>
       <c r="D16" s="46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>1</v>
@@ -3679,10 +3730,10 @@
         <v>284.05</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L16" s="38">
         <f t="shared" si="1"/>
@@ -3705,10 +3756,10 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17">
       <c r="C17" s="35"/>
       <c r="D17" s="46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>1</v>
@@ -3723,10 +3774,10 @@
         <v>110</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L17" s="38">
         <f t="shared" si="1"/>
@@ -3749,10 +3800,10 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17">
       <c r="C18" s="35"/>
       <c r="D18" s="46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>1</v>
@@ -3767,10 +3818,10 @@
         <v>118.4</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L18" s="38">
         <f t="shared" si="1"/>
@@ -3790,10 +3841,10 @@
       </c>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17">
       <c r="C19" s="35"/>
       <c r="D19" s="36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>1</v>
@@ -3810,10 +3861,10 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K19" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L19" s="38">
         <f t="shared" si="1"/>
@@ -3836,10 +3887,10 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17">
       <c r="C20" s="35"/>
       <c r="D20" s="36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1</v>
@@ -3854,10 +3905,10 @@
         <v>26.9</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L20" s="38">
         <f t="shared" si="1"/>
@@ -3880,10 +3931,10 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17">
       <c r="C21" s="35"/>
       <c r="D21" s="46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>1</v>
@@ -3898,10 +3949,10 @@
         <v>70</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L21" s="38">
         <f t="shared" si="1"/>
@@ -3921,10 +3972,10 @@
       </c>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17">
       <c r="C22" s="35"/>
       <c r="D22" s="67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>1</v>
@@ -3939,10 +3990,10 @@
         <v>415</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L22" s="38">
         <f t="shared" si="1"/>
@@ -3965,10 +4016,10 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17">
       <c r="C23" s="35"/>
       <c r="D23" s="46" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>1</v>
@@ -3985,10 +4036,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L23" s="38">
         <f t="shared" si="1"/>
@@ -4013,10 +4064,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17">
       <c r="C24" s="35"/>
       <c r="D24" s="46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E24" s="37" t="s">
         <v>1</v>
@@ -4033,10 +4084,10 @@
         <v>1780</v>
       </c>
       <c r="J24" s="68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L24" s="38">
         <f t="shared" si="1"/>
@@ -4061,10 +4112,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17">
       <c r="C25" s="35"/>
       <c r="D25" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>1</v>
@@ -4081,10 +4132,10 @@
         <v>359</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" s="37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L25" s="38">
         <f t="shared" si="1"/>
@@ -4109,10 +4160,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17">
       <c r="C26" s="35"/>
       <c r="D26" s="66" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>1</v>
@@ -4127,10 +4178,10 @@
         <v>419</v>
       </c>
       <c r="J26" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L26" s="38">
         <f t="shared" si="1"/>
@@ -4155,10 +4206,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17">
       <c r="C27" s="35"/>
       <c r="D27" s="66" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>1</v>
@@ -4173,10 +4224,10 @@
         <v>419</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L27" s="38">
         <f t="shared" si="1"/>
@@ -4201,10 +4252,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17">
       <c r="C28" s="35"/>
       <c r="D28" s="66" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>1</v>
@@ -4219,10 +4270,10 @@
         <v>440</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L28" s="38">
         <f t="shared" si="1"/>
@@ -4244,10 +4295,10 @@
       </c>
       <c r="Q28" s="37"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17">
       <c r="C29" s="35"/>
       <c r="D29" s="66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>1</v>
@@ -4262,10 +4313,10 @@
         <v>313.83999999999997</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L29" s="38">
         <f t="shared" si="1"/>
@@ -4290,10 +4341,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17">
       <c r="C30" s="35"/>
       <c r="D30" s="66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="37"/>
       <c r="F30" s="37" t="s">
@@ -4308,10 +4359,10 @@
         <v>244.51</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L30" s="38">
         <f t="shared" si="1"/>
@@ -4336,10 +4387,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17">
       <c r="C31" s="35"/>
       <c r="D31" s="66" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>1</v>
@@ -4354,10 +4405,10 @@
         <v>628</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L31" s="38">
         <f t="shared" si="1"/>
@@ -4382,10 +4433,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17">
       <c r="C32" s="35"/>
       <c r="D32" s="65" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>1</v>
@@ -4400,10 +4451,10 @@
         <v>659</v>
       </c>
       <c r="J32" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L32" s="38">
         <f t="shared" si="1"/>
@@ -4428,10 +4479,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:17">
       <c r="C33" s="35"/>
       <c r="D33" s="65" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>1</v>
@@ -4446,10 +4497,10 @@
         <v>2319.3000000000002</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L33" s="38">
         <f t="shared" si="1"/>
@@ -4474,10 +4525,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:17">
       <c r="C34" s="35"/>
       <c r="D34" s="65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="37" t="s">
         <v>1</v>
@@ -4492,10 +4543,10 @@
         <v>2000</v>
       </c>
       <c r="J34" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L34" s="38">
         <f t="shared" si="1"/>
@@ -4520,10 +4571,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:17">
       <c r="C35" s="35"/>
       <c r="D35" s="65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E35" s="37" t="s">
         <v>1</v>
@@ -4540,10 +4591,10 @@
         <v>725</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L35" s="38">
         <f t="shared" si="1"/>
@@ -4568,10 +4619,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:17">
       <c r="C36" s="35"/>
       <c r="D36" s="65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>1</v>
@@ -4586,10 +4637,10 @@
         <v>372.43</v>
       </c>
       <c r="J36" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L36" s="38">
         <f t="shared" si="1"/>
@@ -4614,10 +4665,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:17">
       <c r="C37" s="35"/>
       <c r="D37" s="65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E37" s="37" t="s">
         <v>1</v>
@@ -4632,10 +4683,10 @@
         <v>72</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L37" s="38">
         <f t="shared" si="1"/>
@@ -4660,10 +4711,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:17">
       <c r="C38" s="35"/>
       <c r="D38" s="65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E38" s="37"/>
       <c r="F38" s="37" t="s">
@@ -4678,10 +4729,10 @@
         <v>161.72999999999999</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L38" s="38">
         <f t="shared" ref="L38:L69" si="8">I38/N38</f>
@@ -4706,10 +4757,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:17">
       <c r="C39" s="35"/>
       <c r="D39" s="71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E39" s="37"/>
       <c r="F39" s="37" t="s">
@@ -4724,10 +4775,10 @@
         <v>973.02</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K39" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L39" s="38">
         <f t="shared" si="8"/>
@@ -4752,10 +4803,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:17">
       <c r="C40" s="35"/>
       <c r="D40" s="71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E40" s="37" t="s">
         <v>1</v>
@@ -4770,10 +4821,10 @@
         <v>379</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L40" s="38">
         <f t="shared" si="8"/>
@@ -4798,10 +4849,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:17">
       <c r="C41" s="35"/>
       <c r="D41" s="71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E41" s="37" t="s">
         <v>1</v>
@@ -4816,10 +4867,10 @@
         <v>297</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L41" s="38">
         <f t="shared" si="8"/>
@@ -4844,10 +4895,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:17">
       <c r="C42" s="35"/>
       <c r="D42" s="46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E42" s="37" t="s">
         <v>1</v>
@@ -4864,10 +4915,10 @@
         <v>506</v>
       </c>
       <c r="J42" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L42" s="38">
         <f t="shared" si="8"/>
@@ -4889,10 +4940,10 @@
       </c>
       <c r="Q42" s="37"/>
     </row>
-    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:17">
       <c r="C43" s="35"/>
       <c r="D43" s="46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E43" s="37" t="s">
         <v>1</v>
@@ -4907,10 +4958,10 @@
         <v>399.9</v>
       </c>
       <c r="J43" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K43" s="38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L43" s="38">
         <f t="shared" si="8"/>
@@ -4935,10 +4986,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:17">
       <c r="C44" s="35"/>
       <c r="D44" s="46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
@@ -4951,10 +5002,10 @@
         <v>300</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L44" s="38">
         <f t="shared" si="8"/>
@@ -4979,10 +5030,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:17">
       <c r="C45" s="35"/>
       <c r="D45" s="46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E45" s="37" t="s">
         <v>1</v>
@@ -4997,10 +5048,10 @@
         <v>284</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L45" s="38">
         <f t="shared" si="8"/>
@@ -5025,10 +5076,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:17">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>1</v>
@@ -5043,10 +5094,10 @@
         <v>1900</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L46" s="38">
         <f t="shared" si="8"/>
@@ -5071,10 +5122,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:17">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E47" s="37" t="s">
         <v>1</v>
@@ -5089,10 +5140,10 @@
         <v>474.33</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L47" s="38">
         <f t="shared" si="8"/>
@@ -5117,10 +5168,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:17">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>1</v>
@@ -5135,10 +5186,10 @@
         <v>286.39</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L48" s="38">
         <f t="shared" si="8"/>
@@ -5163,10 +5214,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:17">
       <c r="C49" s="35"/>
       <c r="D49" s="46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>1</v>
@@ -5181,10 +5232,10 @@
         <v>1181.1400000000001</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K49" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L49" s="38">
         <f t="shared" si="8"/>
@@ -5209,12 +5260,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:17">
       <c r="C50" s="35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D50" s="46" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E50" s="37" t="s">
         <v>1</v>
@@ -5229,10 +5280,10 @@
         <v>279</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L50" s="38">
         <f t="shared" si="8"/>
@@ -5257,10 +5308,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:17">
       <c r="C51" s="35"/>
       <c r="D51" s="46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>1</v>
@@ -5275,10 +5326,10 @@
         <v>-419</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L51" s="38">
         <f t="shared" si="8"/>
@@ -5303,10 +5354,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:17">
       <c r="C52" s="35"/>
       <c r="D52" s="46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E52" s="37" t="s">
         <v>1</v>
@@ -5322,10 +5373,10 @@
         <v>-773.04</v>
       </c>
       <c r="J52" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L52" s="38">
         <f t="shared" si="8"/>
@@ -5350,10 +5401,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:17">
       <c r="C53" s="35"/>
       <c r="D53" s="46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E53" s="37" t="s">
         <v>1</v>
@@ -5368,10 +5419,10 @@
         <v>110</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L53" s="38">
         <f t="shared" si="8"/>
@@ -5396,10 +5447,10 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:17">
       <c r="C54" s="35"/>
       <c r="D54" s="46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>1</v>
@@ -5414,10 +5465,10 @@
         <v>80</v>
       </c>
       <c r="J54" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L54" s="38">
         <f t="shared" si="8"/>
@@ -5442,10 +5493,10 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:17">
       <c r="C55" s="35"/>
       <c r="D55" s="46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E55" s="37" t="s">
         <v>1</v>
@@ -5460,10 +5511,10 @@
         <v>47</v>
       </c>
       <c r="J55" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L55" s="38">
         <f t="shared" si="8"/>
@@ -5488,10 +5539,10 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:17">
       <c r="C56" s="35"/>
       <c r="D56" s="46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E56" s="37" t="s">
         <v>1</v>
@@ -5508,10 +5559,10 @@
         <v>43</v>
       </c>
       <c r="J56" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L56" s="38">
         <f t="shared" si="8"/>
@@ -5536,10 +5587,10 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:17">
       <c r="C57" s="35"/>
       <c r="D57" s="46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E57" s="37" t="s">
         <v>1</v>
@@ -5557,10 +5608,10 @@
         <v>206.19</v>
       </c>
       <c r="J57" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L57" s="38">
         <f t="shared" si="8"/>
@@ -5585,10 +5636,10 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:17">
       <c r="C58" s="35"/>
       <c r="D58" s="46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E58" s="37" t="s">
         <v>1</v>
@@ -5603,10 +5654,10 @@
         <v>-175</v>
       </c>
       <c r="J58" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L58" s="38">
         <f t="shared" si="8"/>
@@ -5631,10 +5682,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:17">
       <c r="C59" s="35"/>
       <c r="D59" s="46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E59" s="37" t="s">
         <v>1</v>
@@ -5649,10 +5700,10 @@
         <v>72</v>
       </c>
       <c r="J59" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L59" s="38">
         <f t="shared" si="8"/>
@@ -5677,10 +5728,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:17">
       <c r="C60" s="35"/>
       <c r="D60" s="46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E60" s="37" t="s">
         <v>1</v>
@@ -5695,10 +5746,10 @@
         <v>326.99</v>
       </c>
       <c r="J60" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L60" s="38">
         <f t="shared" si="8"/>
@@ -5723,10 +5774,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:17">
       <c r="C61" s="35"/>
       <c r="D61" s="46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E61" s="37" t="s">
         <v>1</v>
@@ -5741,10 +5792,10 @@
         <v>203.88</v>
       </c>
       <c r="J61" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L61" s="38">
         <f t="shared" si="8"/>
@@ -5769,10 +5820,10 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:17">
       <c r="C62" s="35"/>
       <c r="D62" s="46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E62" s="37" t="s">
         <v>1</v>
@@ -5787,10 +5838,10 @@
         <v>202.9</v>
       </c>
       <c r="J62" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L62" s="38">
         <f t="shared" si="8"/>
@@ -5815,10 +5866,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:17">
       <c r="C63" s="35"/>
       <c r="D63" s="46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E63" s="37"/>
       <c r="F63" s="37"/>
@@ -5831,10 +5882,10 @@
         <v>9831.94</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K63" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L63" s="38">
         <f t="shared" si="8"/>
@@ -5859,10 +5910,10 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:17">
       <c r="C64" s="35"/>
       <c r="D64" s="46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E64" s="37"/>
       <c r="F64" s="37"/>
@@ -5875,10 +5926,10 @@
         <v>1862.45</v>
       </c>
       <c r="J64" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L64" s="38">
         <f t="shared" si="8"/>
@@ -5903,10 +5954,10 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:17">
       <c r="C65" s="35"/>
       <c r="D65" s="46" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E65" s="37"/>
       <c r="F65" s="37"/>
@@ -5919,10 +5970,10 @@
         <v>1732.22</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L65" s="38">
         <f t="shared" si="8"/>
@@ -5947,10 +5998,10 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:17">
       <c r="C66" s="35"/>
       <c r="D66" s="46" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E66" s="37" t="s">
         <v>1</v>
@@ -5967,10 +6018,10 @@
         <v>79</v>
       </c>
       <c r="J66" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L66" s="38">
         <f t="shared" si="8"/>
@@ -5995,10 +6046,10 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:17">
       <c r="C67" s="35"/>
       <c r="D67" s="46" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E67" s="37" t="s">
         <v>1</v>
@@ -6013,10 +6064,10 @@
         <v>129</v>
       </c>
       <c r="J67" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L67" s="38">
         <f t="shared" si="8"/>
@@ -6041,10 +6092,10 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:17">
       <c r="C68" s="35"/>
       <c r="D68" s="46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E68" s="37" t="s">
         <v>1</v>
@@ -6059,10 +6110,10 @@
         <v>45</v>
       </c>
       <c r="J68" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L68" s="38">
         <f t="shared" si="8"/>
@@ -6087,10 +6138,10 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:17">
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E69" s="37" t="s">
         <v>1</v>
@@ -6105,10 +6156,10 @@
         <v>-715</v>
       </c>
       <c r="J69" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L69" s="38">
         <f t="shared" si="8"/>
@@ -6133,10 +6184,10 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:17">
       <c r="C70" s="35"/>
       <c r="D70" s="46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E70" s="37" t="s">
         <v>1</v>
@@ -6146,24 +6197,24 @@
       </c>
       <c r="G70" s="37"/>
       <c r="H70" s="37">
-        <f t="shared" ref="H70:H101" si="12">COUNTA(E70:G70)</f>
+        <f t="shared" ref="H70:H100" si="12">COUNTA(E70:G70)</f>
         <v>2</v>
       </c>
       <c r="I70" s="38">
         <v>242.03</v>
       </c>
       <c r="J70" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L70" s="38">
-        <f t="shared" ref="L70:L101" si="13">I70/N70</f>
+        <f t="shared" ref="L70:L100" si="13">I70/N70</f>
         <v>242.03</v>
       </c>
       <c r="M70" s="38">
-        <f t="shared" ref="M70:M101" si="14">IFERROR(L70/H70,"")</f>
+        <f t="shared" ref="M70:M100" si="14">IFERROR(L70/H70,"")</f>
         <v>121.015</v>
       </c>
       <c r="N70" s="39">
@@ -6173,7 +6224,7 @@
         <v>46268</v>
       </c>
       <c r="P70" s="64" t="str">
-        <f t="shared" ref="P70:P101" si="15">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
+        <f t="shared" ref="P70:P100" si="15">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
         <v/>
       </c>
       <c r="Q70" s="37" t="str">
@@ -6181,10 +6232,10 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:17">
       <c r="C71" s="35"/>
       <c r="D71" s="46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E71" s="37" t="s">
         <v>1</v>
@@ -6199,10 +6250,10 @@
         <v>-60</v>
       </c>
       <c r="J71" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L71" s="38">
         <f t="shared" si="13"/>
@@ -6227,10 +6278,10 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:17">
       <c r="C72" s="35"/>
       <c r="D72" s="46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E72" s="37" t="s">
         <v>1</v>
@@ -6247,10 +6298,10 @@
         <v>126.14</v>
       </c>
       <c r="J72" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L72" s="38">
         <f t="shared" si="13"/>
@@ -6275,10 +6326,10 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:17">
       <c r="C73" s="35"/>
       <c r="D73" s="46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E73" s="37" t="s">
         <v>1</v>
@@ -6293,10 +6344,10 @@
         <v>-60</v>
       </c>
       <c r="J73" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K73" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L73" s="38">
         <f t="shared" si="13"/>
@@ -6321,10 +6372,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:17">
       <c r="C74" s="35"/>
       <c r="D74" s="46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E74" s="37" t="s">
         <v>1</v>
@@ -6342,10 +6393,10 @@
         <v>232.66666666666666</v>
       </c>
       <c r="J74" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L74" s="38">
         <f t="shared" si="13"/>
@@ -6370,10 +6421,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:17">
       <c r="C75" s="35"/>
       <c r="D75" s="46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E75" s="37" t="s">
         <v>1</v>
@@ -6382,7 +6433,7 @@
         <v>2</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H75" s="37">
         <f t="shared" si="12"/>
@@ -6392,10 +6443,10 @@
         <v>103.5</v>
       </c>
       <c r="J75" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K75" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L75" s="38">
         <f t="shared" si="13"/>
@@ -6416,14 +6467,14 @@
         <v/>
       </c>
       <c r="Q75" s="37" t="str">
-        <f t="shared" ref="Q75:Q106" ca="1" si="16">IF(O75&lt;&gt;"",IFERROR(DATEDIF(O75,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q75:Q105" ca="1" si="16">IF(O75&lt;&gt;"",IFERROR(DATEDIF(O75,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="3:17">
       <c r="C76" s="35"/>
       <c r="D76" s="46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E76" s="37" t="s">
         <v>1</v>
@@ -6440,10 +6491,10 @@
         <v>209.94</v>
       </c>
       <c r="J76" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L76" s="38">
         <f t="shared" si="13"/>
@@ -6468,10 +6519,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:17">
       <c r="C77" s="35"/>
       <c r="D77" s="46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E77" s="37" t="s">
         <v>1</v>
@@ -6488,10 +6539,10 @@
         <v>249.5</v>
       </c>
       <c r="J77" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K77" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L77" s="38">
         <f t="shared" si="13"/>
@@ -6516,10 +6567,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:17">
       <c r="C78" s="35"/>
       <c r="D78" s="46" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E78" s="37" t="s">
         <v>1</v>
@@ -6536,10 +6587,10 @@
         <v>176</v>
       </c>
       <c r="J78" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L78" s="38">
         <f t="shared" si="13"/>
@@ -6564,10 +6615,10 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:17">
       <c r="C79" s="35"/>
       <c r="D79" s="46" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E79" s="37" t="s">
         <v>1</v>
@@ -6582,10 +6633,10 @@
         <v>-44</v>
       </c>
       <c r="J79" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K79" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L79" s="38">
         <f t="shared" si="13"/>
@@ -6610,10 +6661,10 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:17">
       <c r="C80" s="35"/>
       <c r="D80" s="46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E80" s="37" t="s">
         <v>1</v>
@@ -6628,10 +6679,10 @@
         <v>531</v>
       </c>
       <c r="J80" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K80" s="38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L80" s="38">
         <f t="shared" si="13"/>
@@ -6656,10 +6707,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:17">
       <c r="C81" s="35"/>
       <c r="D81" s="46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E81" s="37" t="s">
         <v>1</v>
@@ -6676,10 +6727,10 @@
         <v>-209.94</v>
       </c>
       <c r="J81" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K81" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L81" s="38">
         <f t="shared" ref="L81" si="18">I81/N81</f>
@@ -6704,10 +6755,10 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:17">
       <c r="C82" s="35"/>
       <c r="D82" s="46" t="s">
-        <v>253</v>
+        <v>149</v>
       </c>
       <c r="E82" s="37" t="s">
         <v>1</v>
@@ -6722,10 +6773,10 @@
         <v>330</v>
       </c>
       <c r="J82" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K82" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L82" s="38">
         <f t="shared" si="13"/>
@@ -6750,10 +6801,10 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:17">
       <c r="C83" s="35"/>
       <c r="D83" s="46" t="s">
-        <v>254</v>
+        <v>150</v>
       </c>
       <c r="E83" s="37"/>
       <c r="F83" s="37"/>
@@ -6766,10 +6817,10 @@
         <v>223.74</v>
       </c>
       <c r="J83" s="38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K83" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L83" s="38">
         <f t="shared" si="13"/>
@@ -6794,65 +6845,91 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:17">
       <c r="C84" s="35"/>
-      <c r="D84" s="46"/>
-      <c r="E84" s="37"/>
+      <c r="D84" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F84" s="37"/>
       <c r="G84" s="37"/>
       <c r="H84" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="38"/>
-      <c r="J84" s="38"/>
-      <c r="K84" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I84" s="38">
+        <v>500</v>
+      </c>
+      <c r="J84" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="K84" s="38" t="s">
+        <v>77</v>
+      </c>
       <c r="L84" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M84" s="38" t="str">
+        <v>100</v>
+      </c>
+      <c r="M84" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>100</v>
       </c>
       <c r="N84" s="39">
-        <v>1</v>
-      </c>
-      <c r="O84" s="64"/>
-      <c r="P84" s="64" t="str">
+        <v>5</v>
+      </c>
+      <c r="O84" s="64">
+        <v>46268</v>
+      </c>
+      <c r="P84" s="64">
         <f t="shared" si="15"/>
-        <v/>
+        <v>46390</v>
       </c>
       <c r="Q84" s="37" t="str">
         <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:17">
       <c r="C85" s="35"/>
-      <c r="D85" s="46"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
+      <c r="D85" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G85" s="37"/>
       <c r="H85" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="38"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I85" s="38">
+        <v>262.07</v>
+      </c>
+      <c r="J85" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K85" s="38" t="s">
+        <v>119</v>
+      </c>
       <c r="L85" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="38" t="str">
+        <v>262.07</v>
+      </c>
+      <c r="M85" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>131.035</v>
       </c>
       <c r="N85" s="39">
         <v>1</v>
       </c>
-      <c r="O85" s="64"/>
+      <c r="O85" s="64">
+        <v>46268</v>
+      </c>
       <c r="P85" s="64" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -6862,31 +6939,45 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:17">
       <c r="C86" s="35"/>
-      <c r="D86" s="46"/>
-      <c r="E86" s="37"/>
-      <c r="F86" s="37"/>
+      <c r="D86" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G86" s="37"/>
       <c r="H86" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="38"/>
-      <c r="J86" s="38"/>
-      <c r="K86" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I86" s="38">
+        <v>105</v>
+      </c>
+      <c r="J86" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K86" s="38" t="s">
+        <v>119</v>
+      </c>
       <c r="L86" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M86" s="38" t="str">
+        <v>105</v>
+      </c>
+      <c r="M86" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>52.5</v>
       </c>
       <c r="N86" s="39">
         <v>1</v>
       </c>
-      <c r="O86" s="64"/>
+      <c r="O86" s="64">
+        <v>46268</v>
+      </c>
       <c r="P86" s="64" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -6896,31 +6987,43 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:17">
       <c r="C87" s="35"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="37"/>
+      <c r="D87" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F87" s="37"/>
       <c r="G87" s="37"/>
       <c r="H87" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="38"/>
-      <c r="J87" s="38"/>
-      <c r="K87" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I87" s="38">
+        <v>-75</v>
+      </c>
+      <c r="J87" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="K87" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L87" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="38" t="str">
+        <v>-75</v>
+      </c>
+      <c r="M87" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>-75</v>
       </c>
       <c r="N87" s="39">
         <v>1</v>
       </c>
-      <c r="O87" s="64"/>
+      <c r="O87" s="64">
+        <v>46268</v>
+      </c>
       <c r="P87" s="64" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -6930,31 +7033,45 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:17">
       <c r="C88" s="35"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
+      <c r="D88" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G88" s="37"/>
       <c r="H88" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="38"/>
-      <c r="J88" s="38"/>
-      <c r="K88" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I88" s="38">
+        <v>100</v>
+      </c>
+      <c r="J88" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K88" s="38" t="s">
+        <v>156</v>
+      </c>
       <c r="L88" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="38" t="str">
+        <v>100</v>
+      </c>
+      <c r="M88" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>50</v>
       </c>
       <c r="N88" s="39">
         <v>1</v>
       </c>
-      <c r="O88" s="64"/>
+      <c r="O88" s="64">
+        <v>46268</v>
+      </c>
       <c r="P88" s="64" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -6964,26 +7081,36 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:17">
       <c r="C89" s="35"/>
-      <c r="D89" s="46"/>
-      <c r="E89" s="37"/>
+      <c r="D89" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F89" s="37"/>
       <c r="G89" s="37"/>
       <c r="H89" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="38"/>
-      <c r="J89" s="38"/>
-      <c r="K89" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I89" s="38">
+        <v>60</v>
+      </c>
+      <c r="J89" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K89" s="38" t="s">
+        <v>87</v>
+      </c>
       <c r="L89" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="38" t="str">
+        <v>60</v>
+      </c>
+      <c r="M89" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>60</v>
       </c>
       <c r="N89" s="39">
         <v>1</v>
@@ -6998,26 +7125,38 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:17">
       <c r="C90" s="35"/>
-      <c r="D90" s="46"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
+      <c r="D90" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G90" s="37"/>
       <c r="H90" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="38"/>
-      <c r="J90" s="38"/>
-      <c r="K90" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I90" s="38">
+        <v>100</v>
+      </c>
+      <c r="J90" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K90" s="38" t="s">
+        <v>119</v>
+      </c>
       <c r="L90" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="38" t="str">
+        <v>100</v>
+      </c>
+      <c r="M90" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>50</v>
       </c>
       <c r="N90" s="39">
         <v>1</v>
@@ -7032,26 +7171,36 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:17">
       <c r="C91" s="35"/>
-      <c r="D91" s="46"/>
-      <c r="E91" s="37"/>
+      <c r="D91" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F91" s="37"/>
       <c r="G91" s="37"/>
       <c r="H91" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="38"/>
-      <c r="J91" s="38"/>
-      <c r="K91" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I91" s="38">
+        <v>60</v>
+      </c>
+      <c r="J91" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K91" s="38" t="s">
+        <v>119</v>
+      </c>
       <c r="L91" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="38" t="str">
+        <v>60</v>
+      </c>
+      <c r="M91" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>60</v>
       </c>
       <c r="N91" s="39">
         <v>1</v>
@@ -7066,26 +7215,36 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:17">
       <c r="C92" s="35"/>
-      <c r="D92" s="46"/>
+      <c r="D92" s="46" t="s">
+        <v>159</v>
+      </c>
       <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
+      <c r="F92" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G92" s="37"/>
       <c r="H92" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="38"/>
-      <c r="J92" s="38"/>
-      <c r="K92" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I92" s="38">
+        <v>110.06</v>
+      </c>
+      <c r="J92" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K92" s="38" t="s">
+        <v>119</v>
+      </c>
       <c r="L92" s="38">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="38" t="str">
+        <v>110.06</v>
+      </c>
+      <c r="M92" s="38">
         <f t="shared" si="14"/>
-        <v/>
+        <v>110.06</v>
       </c>
       <c r="N92" s="39">
         <v>1</v>
@@ -7100,7 +7259,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:17">
       <c r="C93" s="35"/>
       <c r="D93" s="46"/>
       <c r="E93" s="37"/>
@@ -7134,7 +7293,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:17">
       <c r="C94" s="35"/>
       <c r="D94" s="46"/>
       <c r="E94" s="37"/>
@@ -7168,7 +7327,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:17">
       <c r="C95" s="35"/>
       <c r="D95" s="46"/>
       <c r="E95" s="37"/>
@@ -7202,7 +7361,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:17">
       <c r="C96" s="35"/>
       <c r="D96" s="46"/>
       <c r="E96" s="37"/>
@@ -7236,7 +7395,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:17">
       <c r="C97" s="35"/>
       <c r="D97" s="46"/>
       <c r="E97" s="37"/>
@@ -7270,7 +7429,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:17">
       <c r="C98" s="35"/>
       <c r="D98" s="46"/>
       <c r="E98" s="37"/>
@@ -7304,7 +7463,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:17">
       <c r="C99" s="35"/>
       <c r="D99" s="46"/>
       <c r="E99" s="37"/>
@@ -7338,7 +7497,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:17">
       <c r="C100" s="35"/>
       <c r="D100" s="46"/>
       <c r="E100" s="37"/>
@@ -7372,25 +7531,25 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:17">
       <c r="C101" s="35"/>
       <c r="D101" s="46"/>
       <c r="E101" s="37"/>
       <c r="F101" s="37"/>
       <c r="G101" s="37"/>
       <c r="H101" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="H101:H132" si="22">COUNTA(E101:G101)</f>
         <v>0</v>
       </c>
       <c r="I101" s="38"/>
       <c r="J101" s="38"/>
       <c r="K101" s="38"/>
       <c r="L101" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="L101:L132" si="23">I101/N101</f>
         <v>0</v>
       </c>
       <c r="M101" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="M101:M132" si="24">IFERROR(L101/H101,"")</f>
         <v/>
       </c>
       <c r="N101" s="39">
@@ -7398,7 +7557,7 @@
       </c>
       <c r="O101" s="64"/>
       <c r="P101" s="64" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="P101:P132" si="25">IF(N101&lt;&gt;1,EDATE(O101,N101-1),"")</f>
         <v/>
       </c>
       <c r="Q101" s="37" t="str">
@@ -7406,25 +7565,25 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:17">
       <c r="C102" s="35"/>
       <c r="D102" s="46"/>
       <c r="E102" s="37"/>
       <c r="F102" s="37"/>
       <c r="G102" s="37"/>
       <c r="H102" s="37">
-        <f t="shared" ref="H102:H133" si="22">COUNTA(E102:G102)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I102" s="38"/>
       <c r="J102" s="38"/>
       <c r="K102" s="38"/>
       <c r="L102" s="38">
-        <f t="shared" ref="L102:L133" si="23">I102/N102</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M102" s="38" t="str">
-        <f t="shared" ref="M102:M133" si="24">IFERROR(L102/H102,"")</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N102" s="39">
@@ -7432,7 +7591,7 @@
       </c>
       <c r="O102" s="64"/>
       <c r="P102" s="64" t="str">
-        <f t="shared" ref="P102:P133" si="25">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q102" s="37" t="str">
@@ -7440,7 +7599,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:17">
       <c r="C103" s="35"/>
       <c r="D103" s="46"/>
       <c r="E103" s="37"/>
@@ -7474,7 +7633,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:17">
       <c r="C104" s="35"/>
       <c r="D104" s="46"/>
       <c r="E104" s="37"/>
@@ -7508,7 +7667,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:17">
       <c r="C105" s="35"/>
       <c r="D105" s="46"/>
       <c r="E105" s="37"/>
@@ -7542,7 +7701,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:17">
       <c r="C106" s="35"/>
       <c r="D106" s="46"/>
       <c r="E106" s="37"/>
@@ -7572,11 +7731,11 @@
         <v/>
       </c>
       <c r="Q106" s="37" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q106:Q137" ca="1" si="26">IF(O106&lt;&gt;"",IFERROR(DATEDIF(O106,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="3:17">
       <c r="C107" s="35"/>
       <c r="D107" s="46"/>
       <c r="E107" s="37"/>
@@ -7606,11 +7765,11 @@
         <v/>
       </c>
       <c r="Q107" s="37" t="str">
-        <f t="shared" ref="Q107:Q138" ca="1" si="26">IF(O107&lt;&gt;"",IFERROR(DATEDIF(O107,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="26"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="3:17">
       <c r="C108" s="35"/>
       <c r="D108" s="46"/>
       <c r="E108" s="37"/>
@@ -7644,7 +7803,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:17">
       <c r="C109" s="35"/>
       <c r="D109" s="46"/>
       <c r="E109" s="37"/>
@@ -7678,7 +7837,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:17">
       <c r="C110" s="35"/>
       <c r="D110" s="46"/>
       <c r="E110" s="37"/>
@@ -7712,7 +7871,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:17">
       <c r="C111" s="35"/>
       <c r="D111" s="46"/>
       <c r="E111" s="37"/>
@@ -7746,7 +7905,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:17">
       <c r="C112" s="35"/>
       <c r="D112" s="46"/>
       <c r="E112" s="37"/>
@@ -7780,7 +7939,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:17">
       <c r="C113" s="35"/>
       <c r="D113" s="46"/>
       <c r="E113" s="37"/>
@@ -7814,7 +7973,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:17">
       <c r="C114" s="35"/>
       <c r="D114" s="46"/>
       <c r="E114" s="37"/>
@@ -7848,7 +8007,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:17">
       <c r="C115" s="35"/>
       <c r="D115" s="46"/>
       <c r="E115" s="37"/>
@@ -7882,7 +8041,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:17">
       <c r="C116" s="35"/>
       <c r="D116" s="46"/>
       <c r="E116" s="37"/>
@@ -7916,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:17">
       <c r="C117" s="35"/>
       <c r="D117" s="46"/>
       <c r="E117" s="37"/>
@@ -7950,7 +8109,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:17">
       <c r="C118" s="35"/>
       <c r="D118" s="46"/>
       <c r="E118" s="37"/>
@@ -7984,7 +8143,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:17">
       <c r="C119" s="35"/>
       <c r="D119" s="46"/>
       <c r="E119" s="37"/>
@@ -8018,7 +8177,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:17">
       <c r="C120" s="35"/>
       <c r="D120" s="46"/>
       <c r="E120" s="37"/>
@@ -8052,7 +8211,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:17">
       <c r="C121" s="35"/>
       <c r="D121" s="46"/>
       <c r="E121" s="37"/>
@@ -8086,7 +8245,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:17">
       <c r="C122" s="35"/>
       <c r="D122" s="46"/>
       <c r="E122" s="37"/>
@@ -8120,7 +8279,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:17">
       <c r="C123" s="35"/>
       <c r="D123" s="46"/>
       <c r="E123" s="37"/>
@@ -8154,7 +8313,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:17">
       <c r="C124" s="35"/>
       <c r="D124" s="46"/>
       <c r="E124" s="37"/>
@@ -8188,7 +8347,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:17">
       <c r="C125" s="35"/>
       <c r="D125" s="46"/>
       <c r="E125" s="37"/>
@@ -8222,7 +8381,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:17">
       <c r="C126" s="35"/>
       <c r="D126" s="46"/>
       <c r="E126" s="37"/>
@@ -8256,7 +8415,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:17">
       <c r="C127" s="35"/>
       <c r="D127" s="46"/>
       <c r="E127" s="37"/>
@@ -8290,7 +8449,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:17">
       <c r="C128" s="35"/>
       <c r="D128" s="46"/>
       <c r="E128" s="37"/>
@@ -8324,7 +8483,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:17">
       <c r="C129" s="35"/>
       <c r="D129" s="46"/>
       <c r="E129" s="37"/>
@@ -8358,7 +8517,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:17">
       <c r="C130" s="35"/>
       <c r="D130" s="46"/>
       <c r="E130" s="37"/>
@@ -8392,7 +8551,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:17">
       <c r="C131" s="35"/>
       <c r="D131" s="46"/>
       <c r="E131" s="37"/>
@@ -8426,7 +8585,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:17">
       <c r="C132" s="35"/>
       <c r="D132" s="46"/>
       <c r="E132" s="37"/>
@@ -8460,25 +8619,25 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:17">
       <c r="C133" s="35"/>
       <c r="D133" s="46"/>
       <c r="E133" s="37"/>
       <c r="F133" s="37"/>
       <c r="G133" s="37"/>
       <c r="H133" s="37">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="H133:H164" si="27">COUNTA(E133:G133)</f>
         <v>0</v>
       </c>
       <c r="I133" s="38"/>
       <c r="J133" s="38"/>
       <c r="K133" s="38"/>
       <c r="L133" s="38">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="L133:L164" si="28">I133/N133</f>
         <v>0</v>
       </c>
       <c r="M133" s="38" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="M133:M164" si="29">IFERROR(L133/H133,"")</f>
         <v/>
       </c>
       <c r="N133" s="39">
@@ -8486,7 +8645,7 @@
       </c>
       <c r="O133" s="64"/>
       <c r="P133" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="P133:P164" si="30">IF(N133&lt;&gt;1,EDATE(O133,N133-1),"")</f>
         <v/>
       </c>
       <c r="Q133" s="37" t="str">
@@ -8494,25 +8653,25 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:17">
       <c r="C134" s="35"/>
       <c r="D134" s="46"/>
       <c r="E134" s="37"/>
       <c r="F134" s="37"/>
       <c r="G134" s="37"/>
       <c r="H134" s="37">
-        <f t="shared" ref="H134:H165" si="27">COUNTA(E134:G134)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I134" s="38"/>
       <c r="J134" s="38"/>
       <c r="K134" s="38"/>
       <c r="L134" s="38">
-        <f t="shared" ref="L134:L165" si="28">I134/N134</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M134" s="38" t="str">
-        <f t="shared" ref="M134:M165" si="29">IFERROR(L134/H134,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N134" s="39">
@@ -8520,7 +8679,7 @@
       </c>
       <c r="O134" s="64"/>
       <c r="P134" s="64" t="str">
-        <f t="shared" ref="P134:P165" si="30">IF(N134&lt;&gt;1,EDATE(O134,N134-1),"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q134" s="37" t="str">
@@ -8528,7 +8687,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:17">
       <c r="C135" s="35"/>
       <c r="D135" s="46"/>
       <c r="E135" s="37"/>
@@ -8562,7 +8721,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:17">
       <c r="C136" s="35"/>
       <c r="D136" s="46"/>
       <c r="E136" s="37"/>
@@ -8596,7 +8755,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:17">
       <c r="C137" s="35"/>
       <c r="D137" s="46"/>
       <c r="E137" s="37"/>
@@ -8630,7 +8789,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:17">
       <c r="C138" s="35"/>
       <c r="D138" s="46"/>
       <c r="E138" s="37"/>
@@ -8660,11 +8819,11 @@
         <v/>
       </c>
       <c r="Q138" s="37" t="str">
-        <f t="shared" ca="1" si="26"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q138:Q169" ca="1" si="31">IF(O138&lt;&gt;"",IFERROR(DATEDIF(O138,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="3:17">
       <c r="C139" s="35"/>
       <c r="D139" s="46"/>
       <c r="E139" s="37"/>
@@ -8694,11 +8853,11 @@
         <v/>
       </c>
       <c r="Q139" s="37" t="str">
-        <f t="shared" ref="Q139:Q170" ca="1" si="31">IF(O139&lt;&gt;"",IFERROR(DATEDIF(O139,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="31"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="3:17">
       <c r="C140" s="35"/>
       <c r="D140" s="46"/>
       <c r="E140" s="37"/>
@@ -8732,7 +8891,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:17">
       <c r="C141" s="35"/>
       <c r="D141" s="46"/>
       <c r="E141" s="37"/>
@@ -8766,7 +8925,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:17">
       <c r="C142" s="35"/>
       <c r="D142" s="46"/>
       <c r="E142" s="37"/>
@@ -8800,7 +8959,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:17">
       <c r="C143" s="35"/>
       <c r="D143" s="46"/>
       <c r="E143" s="37"/>
@@ -8824,8 +8983,8 @@
       <c r="N143" s="39">
         <v>1</v>
       </c>
-      <c r="O143" s="64"/>
-      <c r="P143" s="64" t="str">
+      <c r="O143" s="35"/>
+      <c r="P143" s="35" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -8834,7 +8993,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:17">
       <c r="C144" s="35"/>
       <c r="D144" s="46"/>
       <c r="E144" s="37"/>
@@ -8868,7 +9027,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:17">
       <c r="C145" s="35"/>
       <c r="D145" s="46"/>
       <c r="E145" s="37"/>
@@ -8902,7 +9061,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:17">
       <c r="C146" s="35"/>
       <c r="D146" s="46"/>
       <c r="E146" s="37"/>
@@ -8936,7 +9095,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:17">
       <c r="C147" s="35"/>
       <c r="D147" s="46"/>
       <c r="E147" s="37"/>
@@ -8970,7 +9129,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:17">
       <c r="C148" s="35"/>
       <c r="D148" s="46"/>
       <c r="E148" s="37"/>
@@ -9004,7 +9163,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:17">
       <c r="C149" s="35"/>
       <c r="D149" s="46"/>
       <c r="E149" s="37"/>
@@ -9038,7 +9197,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:17">
       <c r="C150" s="35"/>
       <c r="D150" s="46"/>
       <c r="E150" s="37"/>
@@ -9072,7 +9231,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:17">
       <c r="C151" s="35"/>
       <c r="D151" s="46"/>
       <c r="E151" s="37"/>
@@ -9106,7 +9265,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:17">
       <c r="C152" s="35"/>
       <c r="D152" s="46"/>
       <c r="E152" s="37"/>
@@ -9140,7 +9299,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:17">
       <c r="C153" s="35"/>
       <c r="D153" s="46"/>
       <c r="E153" s="37"/>
@@ -9174,7 +9333,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:17">
       <c r="C154" s="35"/>
       <c r="D154" s="46"/>
       <c r="E154" s="37"/>
@@ -9208,7 +9367,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:17">
       <c r="C155" s="35"/>
       <c r="D155" s="46"/>
       <c r="E155" s="37"/>
@@ -9242,7 +9401,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:17">
       <c r="C156" s="35"/>
       <c r="D156" s="46"/>
       <c r="E156" s="37"/>
@@ -9276,7 +9435,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:17">
       <c r="C157" s="35"/>
       <c r="D157" s="46"/>
       <c r="E157" s="37"/>
@@ -9310,7 +9469,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:17">
       <c r="C158" s="35"/>
       <c r="D158" s="46"/>
       <c r="E158" s="37"/>
@@ -9344,7 +9503,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:17">
       <c r="C159" s="35"/>
       <c r="D159" s="46"/>
       <c r="E159" s="37"/>
@@ -9378,7 +9537,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:17">
       <c r="C160" s="35"/>
       <c r="D160" s="46"/>
       <c r="E160" s="37"/>
@@ -9412,7 +9571,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:17">
       <c r="C161" s="35"/>
       <c r="D161" s="46"/>
       <c r="E161" s="37"/>
@@ -9446,7 +9605,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:17">
       <c r="C162" s="35"/>
       <c r="D162" s="46"/>
       <c r="E162" s="37"/>
@@ -9480,7 +9639,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:17">
       <c r="C163" s="35"/>
       <c r="D163" s="46"/>
       <c r="E163" s="37"/>
@@ -9514,7 +9673,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:17">
       <c r="C164" s="35"/>
       <c r="D164" s="46"/>
       <c r="E164" s="37"/>
@@ -9548,25 +9707,25 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:17">
       <c r="C165" s="35"/>
       <c r="D165" s="46"/>
       <c r="E165" s="37"/>
       <c r="F165" s="37"/>
       <c r="G165" s="37"/>
       <c r="H165" s="37">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="H165:H188" si="32">COUNTA(E165:G165)</f>
         <v>0</v>
       </c>
       <c r="I165" s="38"/>
       <c r="J165" s="38"/>
       <c r="K165" s="38"/>
       <c r="L165" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="L165:L188" si="33">I165/N165</f>
         <v>0</v>
       </c>
       <c r="M165" s="38" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="M165:M188" si="34">IFERROR(L165/H165,"")</f>
         <v/>
       </c>
       <c r="N165" s="39">
@@ -9574,7 +9733,7 @@
       </c>
       <c r="O165" s="35"/>
       <c r="P165" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="P165:P188" si="35">IF(N165&lt;&gt;1,EDATE(O165,N165-1),"")</f>
         <v/>
       </c>
       <c r="Q165" s="37" t="str">
@@ -9582,25 +9741,25 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:17">
       <c r="C166" s="35"/>
       <c r="D166" s="46"/>
       <c r="E166" s="37"/>
       <c r="F166" s="37"/>
       <c r="G166" s="37"/>
       <c r="H166" s="37">
-        <f t="shared" ref="H166:H189" si="32">COUNTA(E166:G166)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I166" s="38"/>
       <c r="J166" s="38"/>
       <c r="K166" s="38"/>
       <c r="L166" s="38">
-        <f t="shared" ref="L166:L189" si="33">I166/N166</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M166" s="38" t="str">
-        <f t="shared" ref="M166:M189" si="34">IFERROR(L166/H166,"")</f>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N166" s="39">
@@ -9608,7 +9767,7 @@
       </c>
       <c r="O166" s="35"/>
       <c r="P166" s="35" t="str">
-        <f t="shared" ref="P166:P189" si="35">IF(N166&lt;&gt;1,EDATE(O166,N166-1),"")</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q166" s="37" t="str">
@@ -9616,7 +9775,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:17">
       <c r="C167" s="35"/>
       <c r="D167" s="46"/>
       <c r="E167" s="37"/>
@@ -9650,7 +9809,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:17">
       <c r="C168" s="35"/>
       <c r="D168" s="46"/>
       <c r="E168" s="37"/>
@@ -9684,7 +9843,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:17">
       <c r="C169" s="35"/>
       <c r="D169" s="46"/>
       <c r="E169" s="37"/>
@@ -9718,7 +9877,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:17">
       <c r="C170" s="35"/>
       <c r="D170" s="46"/>
       <c r="E170" s="37"/>
@@ -9748,11 +9907,11 @@
         <v/>
       </c>
       <c r="Q170" s="37" t="str">
-        <f t="shared" ca="1" si="31"/>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q170:Q188" ca="1" si="36">IF(O170&lt;&gt;"",IFERROR(DATEDIF(O170,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="3:17">
       <c r="C171" s="35"/>
       <c r="D171" s="46"/>
       <c r="E171" s="37"/>
@@ -9782,11 +9941,11 @@
         <v/>
       </c>
       <c r="Q171" s="37" t="str">
-        <f t="shared" ref="Q171:Q189" ca="1" si="36">IF(O171&lt;&gt;"",IFERROR(DATEDIF(O171,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="36"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="3:17">
       <c r="C172" s="35"/>
       <c r="D172" s="46"/>
       <c r="E172" s="37"/>
@@ -9820,7 +9979,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:17">
       <c r="C173" s="35"/>
       <c r="D173" s="46"/>
       <c r="E173" s="37"/>
@@ -9854,7 +10013,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:17">
       <c r="C174" s="35"/>
       <c r="D174" s="46"/>
       <c r="E174" s="37"/>
@@ -9888,7 +10047,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:17">
       <c r="C175" s="35"/>
       <c r="D175" s="46"/>
       <c r="E175" s="37"/>
@@ -9922,7 +10081,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:17">
       <c r="C176" s="35"/>
       <c r="D176" s="46"/>
       <c r="E176" s="37"/>
@@ -9956,7 +10115,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:17">
       <c r="C177" s="35"/>
       <c r="D177" s="46"/>
       <c r="E177" s="37"/>
@@ -9990,7 +10149,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:17">
       <c r="C178" s="35"/>
       <c r="D178" s="46"/>
       <c r="E178" s="37"/>
@@ -10024,7 +10183,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:17">
       <c r="C179" s="35"/>
       <c r="D179" s="46"/>
       <c r="E179" s="37"/>
@@ -10058,7 +10217,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:17">
       <c r="C180" s="35"/>
       <c r="D180" s="46"/>
       <c r="E180" s="37"/>
@@ -10092,7 +10251,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:17">
       <c r="C181" s="35"/>
       <c r="D181" s="46"/>
       <c r="E181" s="37"/>
@@ -10126,7 +10285,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:17">
       <c r="C182" s="35"/>
       <c r="D182" s="46"/>
       <c r="E182" s="37"/>
@@ -10160,7 +10319,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:17">
       <c r="C183" s="35"/>
       <c r="D183" s="46"/>
       <c r="E183" s="37"/>
@@ -10194,7 +10353,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:17">
       <c r="C184" s="35"/>
       <c r="D184" s="46"/>
       <c r="E184" s="37"/>
@@ -10228,7 +10387,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:17">
       <c r="C185" s="35"/>
       <c r="D185" s="46"/>
       <c r="E185" s="37"/>
@@ -10262,7 +10421,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:17">
       <c r="C186" s="35"/>
       <c r="D186" s="46"/>
       <c r="E186" s="37"/>
@@ -10296,7 +10455,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:17">
       <c r="C187" s="35"/>
       <c r="D187" s="46"/>
       <c r="E187" s="37"/>
@@ -10330,7 +10489,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:17">
       <c r="C188" s="35"/>
       <c r="D188" s="46"/>
       <c r="E188" s="37"/>
@@ -10364,83 +10523,54 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C189" s="35"/>
-      <c r="D189" s="46"/>
-      <c r="E189" s="37"/>
-      <c r="F189" s="37"/>
-      <c r="G189" s="37"/>
-      <c r="H189" s="37">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="I189" s="38"/>
-      <c r="J189" s="38"/>
-      <c r="K189" s="38"/>
-      <c r="L189" s="38">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="M189" s="38" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="N189" s="39">
-        <v>1</v>
-      </c>
-      <c r="O189" s="35"/>
-      <c r="P189" s="35" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q189" s="37" t="str">
-        <f t="shared" ca="1" si="36"/>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="C5:Q100" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q100">
-      <sortCondition sortBy="cellColor" ref="J5" dxfId="23"/>
+  <autoFilter ref="C5:Q99" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q99">
+      <sortCondition sortBy="cellColor" ref="J5" dxfId="16"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="I6:I189">
-    <cfRule type="cellIs" dxfId="21" priority="13" operator="lessThan">
+  <conditionalFormatting sqref="I6:I188">
+    <cfRule type="cellIs" dxfId="25" priority="15" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J189">
-    <cfRule type="cellIs" dxfId="20" priority="12" operator="equal">
+  <conditionalFormatting sqref="J6:J188">
+    <cfRule type="cellIs" dxfId="24" priority="14" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:K189">
-    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
+  <conditionalFormatting sqref="J6:K188">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58">
-    <cfRule type="cellIs" dxfId="18" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K69">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K71">
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K73">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K87">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10452,7 +10582,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:R20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" customWidth="1"/>
@@ -10460,50 +10590,50 @@
     <col min="4" max="4" width="33.85546875" customWidth="1"/>
     <col min="5" max="10" width="13.5703125" customWidth="1"/>
     <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="15" width="13.5703125" hidden="1" customWidth="1"/>
+    <col min="12" max="15" width="13.5703125" customWidth="1"/>
     <col min="16" max="16" width="53.42578125" customWidth="1"/>
     <col min="18" max="18" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="30" customHeight="1">
       <c r="D2" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" ht="16.5" customHeight="1">
       <c r="D3" s="54" t="s">
         <v>21</v>
       </c>
@@ -10541,9 +10671,9 @@
       </c>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="16.5" customHeight="1">
       <c r="D4" s="55" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>1</v>
@@ -10579,12 +10709,12 @@
       </c>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="16.5" customHeight="1">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>1</v>
@@ -10598,15 +10728,15 @@
         <v>2</v>
       </c>
       <c r="I5" s="38">
-        <v>421</v>
+        <v>330</v>
       </c>
       <c r="J5" s="38">
         <f t="shared" si="0"/>
-        <v>421</v>
+        <v>330</v>
       </c>
       <c r="K5" s="38">
         <f t="shared" si="1"/>
-        <v>210.5</v>
+        <v>165</v>
       </c>
       <c r="L5" s="37">
         <f t="shared" si="2"/>
@@ -10620,13 +10750,13 @@
       </c>
       <c r="P5" s="59"/>
     </row>
-    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" ht="16.5" customHeight="1">
       <c r="B6" s="32">
         <f>SUMIF($E$3:$E$34,B5,$K$3:$K$34)</f>
-        <v>2412.5700000000002</v>
+        <v>2517.0700000000002</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1</v>
@@ -10661,10 +10791,10 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" ht="16.5" customHeight="1">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>1</v>
@@ -10699,12 +10829,12 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" ht="16.5" customHeight="1">
       <c r="B8" s="30" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>1</v>
@@ -10739,13 +10869,13 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" ht="16.5" customHeight="1">
       <c r="B9" s="61">
         <f>SUMIF($F$3:$F$34,B8,$K$3:$K$34)</f>
-        <v>5612.57</v>
+        <v>5717.07</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>1</v>
@@ -10781,9 +10911,9 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18">
       <c r="D10" s="54" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
@@ -10816,9 +10946,9 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18">
       <c r="D11" s="54" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="37" t="s">
@@ -10851,9 +10981,9 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18">
       <c r="D12" s="54" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="37" t="s">
@@ -10886,21 +11016,44 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D13" s="37"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37"/>
+    <row r="13" spans="2:18">
+      <c r="D13" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
+      <c r="H13" s="37">
+        <f>COUNTA(E13:G13)</f>
+        <v>2</v>
+      </c>
+      <c r="I13" s="38">
+        <v>300</v>
+      </c>
+      <c r="J13" s="38">
+        <f t="shared" ref="J13" si="4">I13/L13</f>
+        <v>300</v>
+      </c>
+      <c r="K13" s="38">
+        <f t="shared" ref="K13" si="5">IFERROR(J13/H13,"")</f>
+        <v>150</v>
+      </c>
+      <c r="L13" s="37">
+        <f t="shared" ref="L13" si="6">(DATEDIF(M13,N13,"m")+1)</f>
+        <v>1</v>
+      </c>
       <c r="M13" s="38"/>
       <c r="N13" s="38"/>
-      <c r="O13" s="39"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O13" s="39">
+        <f t="shared" ref="O13" ca="1" si="7">IFERROR(DATEDIF(M13,TODAY(),"m")+1,"")</f>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18">
       <c r="D14" s="37"/>
       <c r="E14" s="36"/>
       <c r="F14" s="37"/>
@@ -10914,7 +11067,7 @@
       <c r="N14" s="38"/>
       <c r="O14" s="39"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18">
       <c r="D15" s="37"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37"/>
@@ -10928,7 +11081,7 @@
       <c r="N15" s="38"/>
       <c r="O15" s="39"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18">
       <c r="D16" s="37"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37"/>
@@ -10942,7 +11095,7 @@
       <c r="N16" s="38"/>
       <c r="O16" s="39"/>
     </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:15">
       <c r="D17" s="37"/>
       <c r="E17" s="36"/>
       <c r="F17" s="37"/>
@@ -10956,7 +11109,7 @@
       <c r="N17" s="38"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:15">
       <c r="D18" s="37"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37"/>
@@ -10970,7 +11123,7 @@
       <c r="N18" s="38"/>
       <c r="O18" s="39"/>
     </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:15">
       <c r="D19" s="37"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
@@ -10984,7 +11137,7 @@
       <c r="N19" s="38"/>
       <c r="O19" s="39"/>
     </row>
-    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:15">
       <c r="D20" s="37"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
@@ -11007,7 +11160,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O404"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
@@ -11023,23 +11176,23 @@
     <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" ht="14.25" customHeight="1">
       <c r="G2" s="2"/>
       <c r="N2" s="43"/>
     </row>
-    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="27.75" customHeight="1">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="M3" s="75" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
@@ -11047,77 +11200,77 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="M4" s="76"/>
       <c r="N4" s="49"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15">
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
       <c r="F5" s="16"/>
       <c r="G5" s="28"/>
       <c r="L5" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="N5" s="1">
         <v>4912</v>
       </c>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15">
       <c r="G6" s="2"/>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15">
       <c r="G7" s="2"/>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
       <c r="L8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="M8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="N8" s="1">
         <v>338</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15">
       <c r="F9" s="47" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="43"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15">
       <c r="E10" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
         <v>4782.6200000000026</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="N10" s="43"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15">
       <c r="E11" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
@@ -11137,40 +11290,36 @@
       </c>
       <c r="N11" s="43"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15">
       <c r="F12" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
       </c>
       <c r="N12" s="43"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15">
       <c r="F13" s="74" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="G13" s="52"/>
       <c r="H13" s="74"/>
       <c r="I13" s="74"/>
       <c r="N13" s="43"/>
     </row>
-    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
+    <row r="14" spans="2:15" outlineLevel="1">
       <c r="F14" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="N14" s="43"/>
     </row>
-    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
+    <row r="15" spans="2:15" outlineLevel="1">
       <c r="F15" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="G15" s="53">
         <v>773.35</v>
@@ -11179,11 +11328,9 @@
       <c r="I15" s="53"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
+    <row r="16" spans="2:15" outlineLevel="1">
       <c r="F16" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G16" s="53">
         <v>-5148</v>
@@ -11192,11 +11339,9 @@
       <c r="I16" s="53"/>
       <c r="N16" s="43"/>
     </row>
-    <row r="17" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
+    <row r="17" spans="6:14" outlineLevel="1">
       <c r="F17" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="G17" s="53">
         <v>-168</v>
@@ -11205,11 +11350,9 @@
       <c r="I17" s="53"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
+    <row r="18" spans="6:14" outlineLevel="1">
       <c r="F18" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="G18" s="53">
         <v>-1700</v>
@@ -11218,11 +11361,9 @@
       <c r="I18" s="53"/>
       <c r="N18" s="43"/>
     </row>
-    <row r="19" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
+    <row r="19" spans="6:14" outlineLevel="1">
       <c r="F19" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G19" s="53">
         <v>5148</v>
@@ -11231,11 +11372,9 @@
       <c r="I19" s="53"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
+    <row r="20" spans="6:14" outlineLevel="1">
       <c r="F20" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G20" s="53">
         <v>-4938</v>
@@ -11244,11 +11383,9 @@
       <c r="I20" s="53"/>
       <c r="N20" s="43"/>
     </row>
-    <row r="21" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
+    <row r="21" spans="6:14" outlineLevel="1">
       <c r="F21" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="G21" s="53">
         <v>-1595</v>
@@ -11257,11 +11394,9 @@
       <c r="I21" s="53"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
+    <row r="22" spans="6:14" outlineLevel="1">
       <c r="F22" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G22" s="53">
         <v>-4677</v>
@@ -11270,11 +11405,9 @@
       <c r="I22" s="53"/>
       <c r="N22" s="43"/>
     </row>
-    <row r="23" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
+    <row r="23" spans="6:14" outlineLevel="1">
       <c r="F23" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="G23" s="53">
         <v>-200</v>
@@ -11283,11 +11416,9 @@
       <c r="I23" s="53"/>
       <c r="N23" s="43"/>
     </row>
-    <row r="24" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
+    <row r="24" spans="6:14" outlineLevel="1">
       <c r="F24" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G24" s="53">
         <v>4677</v>
@@ -11296,11 +11427,9 @@
       <c r="I24" s="53"/>
       <c r="N24" s="43"/>
     </row>
-    <row r="25" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
+    <row r="25" spans="6:14" outlineLevel="1">
       <c r="F25" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="G25" s="53">
         <v>-750</v>
@@ -11309,11 +11438,9 @@
       <c r="I25" s="53"/>
       <c r="N25" s="43"/>
     </row>
-    <row r="26" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
+    <row r="26" spans="6:14" outlineLevel="1">
       <c r="F26" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="G26" s="53">
         <v>-652</v>
@@ -11322,11 +11449,9 @@
       <c r="I26" s="53"/>
       <c r="N26" s="43"/>
     </row>
-    <row r="27" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
+    <row r="27" spans="6:14" outlineLevel="1">
       <c r="F27" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="G27" s="53">
         <v>11100</v>
@@ -11335,11 +11460,9 @@
       <c r="I27" s="53"/>
       <c r="N27" s="43"/>
     </row>
-    <row r="28" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
+    <row r="28" spans="6:14" outlineLevel="1">
       <c r="F28" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="G28" s="53">
         <v>-396</v>
@@ -11348,11 +11471,9 @@
       <c r="I28" s="53"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
+    <row r="29" spans="6:14" outlineLevel="1">
       <c r="F29" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G29" s="53">
         <v>-4211</v>
@@ -11361,11 +11482,9 @@
       <c r="I29" s="53"/>
       <c r="N29" s="43"/>
     </row>
-    <row r="30" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
+    <row r="30" spans="6:14" outlineLevel="1">
       <c r="F30" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G30" s="53">
         <v>-450</v>
@@ -11374,11 +11493,9 @@
       <c r="I30" s="53"/>
       <c r="N30" s="43"/>
     </row>
-    <row r="31" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
+    <row r="31" spans="6:14" outlineLevel="1">
       <c r="F31" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="G31" s="53">
         <v>-1197</v>
@@ -11387,11 +11504,9 @@
       <c r="I31" s="53"/>
       <c r="N31" s="43"/>
     </row>
-    <row r="32" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
+    <row r="32" spans="6:14" outlineLevel="1">
       <c r="F32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G32" s="53">
         <v>-315</v>
@@ -11400,11 +11515,9 @@
       <c r="I32" s="53"/>
       <c r="N32" s="43"/>
     </row>
-    <row r="33" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
+    <row r="33" spans="5:14" outlineLevel="1">
       <c r="F33" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G33" s="53">
         <v>-830</v>
@@ -11413,11 +11526,9 @@
       <c r="I33" s="53"/>
       <c r="N33" s="43"/>
     </row>
-    <row r="34" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
+    <row r="34" spans="5:14" outlineLevel="1">
       <c r="F34" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G34" s="53">
         <v>4211</v>
@@ -11426,11 +11537,9 @@
       <c r="I34" s="53"/>
       <c r="N34" s="43"/>
     </row>
-    <row r="35" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
+    <row r="35" spans="5:14" outlineLevel="1">
       <c r="F35" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="G35" s="53">
         <v>-200</v>
@@ -11439,11 +11548,9 @@
       <c r="I35" s="53"/>
       <c r="N35" s="43"/>
     </row>
-    <row r="36" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
+    <row r="36" spans="5:14" outlineLevel="1">
       <c r="F36" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="G36" s="53">
         <v>10000</v>
@@ -11452,11 +11559,9 @@
       <c r="I36" s="53"/>
       <c r="N36" s="43"/>
     </row>
-    <row r="37" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
+    <row r="37" spans="5:14" outlineLevel="1">
       <c r="F37" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="G37" s="53">
         <v>-200</v>
@@ -11465,11 +11570,9 @@
       <c r="I37" s="53"/>
       <c r="N37" s="43"/>
     </row>
-    <row r="38" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
+    <row r="38" spans="5:14" outlineLevel="1">
       <c r="F38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G38" s="53">
         <v>-381</v>
@@ -11478,11 +11581,9 @@
       <c r="I38" s="53"/>
       <c r="N38" s="43"/>
     </row>
-    <row r="39" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
+    <row r="39" spans="5:14" outlineLevel="1">
       <c r="F39" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G39" s="53">
         <v>-4911</v>
@@ -11491,12 +11592,10 @@
       <c r="I39" s="53"/>
       <c r="N39" s="43"/>
     </row>
-    <row r="40" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
+    <row r="40" spans="5:14" outlineLevel="1">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="G40" s="53">
         <v>-5700</v>
@@ -11505,11 +11604,9 @@
       <c r="I40" s="53"/>
       <c r="N40" s="43"/>
     </row>
-    <row r="41" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
+    <row r="41" spans="5:14" outlineLevel="1">
       <c r="F41" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="G41" s="53">
         <v>-400</v>
@@ -11518,11 +11615,9 @@
       <c r="I41" s="53"/>
       <c r="N41" s="43"/>
     </row>
-    <row r="42" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="53"/>
-      <c r="D42" s="53"/>
+    <row r="42" spans="5:14" outlineLevel="1">
       <c r="F42" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="G42" s="53">
         <v>-450</v>
@@ -11531,11 +11626,9 @@
       <c r="I42" s="53"/>
       <c r="N42" s="43"/>
     </row>
-    <row r="43" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="53"/>
-      <c r="D43" s="53"/>
+    <row r="43" spans="5:14" outlineLevel="1">
       <c r="F43" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="G43" s="53">
         <v>-640</v>
@@ -11544,12 +11637,10 @@
       <c r="I43" s="53"/>
       <c r="N43" s="43"/>
     </row>
-    <row r="44" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
+    <row r="44" spans="5:14" outlineLevel="1">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="G44" s="53">
         <v>5700</v>
@@ -11558,11 +11649,9 @@
       <c r="I44" s="53"/>
       <c r="N44" s="43"/>
     </row>
-    <row r="45" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
+    <row r="45" spans="5:14" outlineLevel="1">
       <c r="F45" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="G45" s="53">
         <v>-130</v>
@@ -11571,11 +11660,9 @@
       <c r="I45" s="53"/>
       <c r="N45" s="43"/>
     </row>
-    <row r="46" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="53"/>
-      <c r="D46" s="53"/>
+    <row r="46" spans="5:14" outlineLevel="1">
       <c r="F46" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="G46" s="53">
         <v>-250</v>
@@ -11584,11 +11671,9 @@
       <c r="I46" s="53"/>
       <c r="N46" s="43"/>
     </row>
-    <row r="47" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
+    <row r="47" spans="5:14" outlineLevel="1">
       <c r="F47" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="G47" s="53">
         <v>-112.2</v>
@@ -11597,11 +11682,9 @@
       <c r="I47" s="53"/>
       <c r="N47" s="43"/>
     </row>
-    <row r="48" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
+    <row r="48" spans="5:14" outlineLevel="1">
       <c r="F48" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G48" s="53">
         <v>4911</v>
@@ -11610,11 +11693,9 @@
       <c r="I48" s="53"/>
       <c r="N48" s="43"/>
     </row>
-    <row r="49" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
+    <row r="49" spans="6:14" outlineLevel="1">
       <c r="F49" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G49" s="53">
         <v>-3000</v>
@@ -11623,11 +11704,9 @@
       <c r="I49" s="53"/>
       <c r="N49" s="43"/>
     </row>
-    <row r="50" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
+    <row r="50" spans="6:14" outlineLevel="1">
       <c r="F50" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="G50" s="53">
         <v>-4000</v>
@@ -11636,11 +11715,9 @@
       <c r="I50" s="53"/>
       <c r="N50" s="43"/>
     </row>
-    <row r="51" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
+    <row r="51" spans="6:14" outlineLevel="1">
       <c r="F51" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="G51" s="53">
         <v>-200</v>
@@ -11649,11 +11726,9 @@
       <c r="I51" s="53"/>
       <c r="N51" s="43"/>
     </row>
-    <row r="52" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="53"/>
-      <c r="D52" s="53"/>
+    <row r="52" spans="6:14" outlineLevel="1">
       <c r="F52" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G52" s="53">
         <v>-4612</v>
@@ -11662,9 +11737,9 @@
       <c r="I52" s="53"/>
       <c r="N52" s="43"/>
     </row>
-    <row r="53" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:14" outlineLevel="1">
       <c r="F53" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="G53" s="53">
         <v>-700</v>
@@ -11673,9 +11748,9 @@
       <c r="I53" s="53"/>
       <c r="N53" s="43"/>
     </row>
-    <row r="54" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:14" outlineLevel="1">
       <c r="F54" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="G54" s="53">
         <v>-880</v>
@@ -11684,9 +11759,9 @@
       <c r="I54" s="53"/>
       <c r="N54" s="43"/>
     </row>
-    <row r="55" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:14" outlineLevel="1">
       <c r="F55" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="G55" s="53">
         <v>-310</v>
@@ -11695,9 +11770,9 @@
       <c r="I55" s="53"/>
       <c r="N55" s="43"/>
     </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:14">
       <c r="F56" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="G56" s="53">
         <v>-250</v>
@@ -11706,9 +11781,9 @@
       <c r="I56" s="53"/>
       <c r="N56" s="43"/>
     </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:14">
       <c r="F57" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G57" s="53">
         <v>4690</v>
@@ -11717,9 +11792,9 @@
       <c r="I57" s="53"/>
       <c r="N57" s="43"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:14">
       <c r="F58" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G58" s="53">
         <v>-4440</v>
@@ -11728,9 +11803,9 @@
       <c r="I58" s="53"/>
       <c r="N58" s="43"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:14">
       <c r="F59" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="G59" s="53">
         <v>-4697</v>
@@ -11738,9 +11813,9 @@
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:14">
       <c r="F60" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G60" s="53">
         <v>-2500</v>
@@ -11748,9 +11823,9 @@
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:14">
       <c r="F61" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="G61" s="53">
         <v>-126</v>
@@ -11758,9 +11833,9 @@
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:14">
       <c r="F62" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="G62" s="53">
         <v>4742</v>
@@ -11768,9 +11843,9 @@
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:14">
       <c r="F63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G63" s="53">
         <v>-410</v>
@@ -11778,14 +11853,14 @@
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
     </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:14">
       <c r="G64" s="53"/>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
     </row>
-    <row r="65" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:9">
       <c r="F65" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="G65" s="53">
         <v>3320</v>
@@ -11793,9 +11868,9 @@
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
     </row>
-    <row r="66" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:9">
       <c r="F66" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="G66" s="53">
         <v>4090</v>
@@ -11803,9 +11878,9 @@
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
     </row>
-    <row r="67" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:9">
       <c r="F67" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="G67" s="53">
         <v>-5688</v>
@@ -11813,9 +11888,9 @@
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
     </row>
-    <row r="68" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:9">
       <c r="F68" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G68" s="53">
         <v>-4433</v>
@@ -11823,9 +11898,9 @@
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
     </row>
-    <row r="69" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:9">
       <c r="F69" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="G69" s="53">
         <v>-250</v>
@@ -11833,9 +11908,9 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
     </row>
-    <row r="70" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:9">
       <c r="F70" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="G70" s="53">
         <v>-99</v>
@@ -11843,9 +11918,9 @@
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
     </row>
-    <row r="71" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:9">
       <c r="F71" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="G71" s="53">
         <v>320</v>
@@ -11853,9 +11928,9 @@
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
     </row>
-    <row r="72" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:9">
       <c r="F72" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="G72" s="53">
         <v>-1572</v>
@@ -11863,14 +11938,14 @@
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
     </row>
-    <row r="73" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:9">
       <c r="G73" s="53"/>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
     </row>
-    <row r="74" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:9">
       <c r="F74" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G74" s="53">
         <v>4433</v>
@@ -11878,9 +11953,9 @@
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
     </row>
-    <row r="75" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:9">
       <c r="F75" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="G75" s="53">
         <v>8000</v>
@@ -11888,9 +11963,9 @@
       <c r="H75" s="53"/>
       <c r="I75" s="53"/>
     </row>
-    <row r="76" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:9">
       <c r="F76" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="G76" s="53">
         <v>-1344</v>
@@ -11898,9 +11973,9 @@
       <c r="H76" s="53"/>
       <c r="I76" s="53"/>
     </row>
-    <row r="77" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:9">
       <c r="F77" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="G77" s="53">
         <v>-308</v>
@@ -11908,9 +11983,9 @@
       <c r="H77" s="53"/>
       <c r="I77" s="53"/>
     </row>
-    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:9" ht="14.25" customHeight="1">
       <c r="F78" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G78" s="53">
         <v>-4204</v>
@@ -11918,9 +11993,9 @@
       <c r="H78" s="53"/>
       <c r="I78" s="53"/>
     </row>
-    <row r="79" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:9">
       <c r="F79" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="G79" s="53">
         <v>-338</v>
@@ -11928,9 +12003,9 @@
       <c r="H79" s="53"/>
       <c r="I79" s="53"/>
     </row>
-    <row r="80" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:9">
       <c r="F80" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="G80" s="53">
         <v>-50</v>
@@ -11938,9 +12013,9 @@
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9">
       <c r="F81" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="G81" s="53">
         <v>338</v>
@@ -11948,16 +12023,16 @@
       <c r="H81" s="53"/>
       <c r="I81" s="53"/>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9">
       <c r="B82" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C82" s="53">
         <v>8000</v>
       </c>
       <c r="D82" s="53"/>
       <c r="F82" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="G82" s="53">
         <v>-540</v>
@@ -11965,16 +12040,16 @@
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9">
       <c r="B83" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C83" s="53">
         <v>5170</v>
       </c>
       <c r="D83" s="53"/>
       <c r="F83" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="G83" s="53">
         <v>-184.31</v>
@@ -11982,16 +12057,16 @@
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9">
       <c r="B84" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C84" s="53">
         <v>4124</v>
       </c>
       <c r="D84" s="53"/>
       <c r="F84" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="G84" s="53">
         <v>-1464.22</v>
@@ -11999,16 +12074,16 @@
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9">
       <c r="B85" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C85" s="53">
         <v>-50</v>
       </c>
       <c r="D85" s="53"/>
       <c r="F85" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="G85" s="53">
         <v>1005</v>
@@ -12016,16 +12091,16 @@
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9">
       <c r="B86" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C86" s="53">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D86" s="53"/>
       <c r="F86" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G86" s="53">
         <v>-500</v>
@@ -12033,16 +12108,16 @@
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9">
       <c r="B87" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C87" s="53">
         <v>-4500</v>
       </c>
       <c r="D87" s="53"/>
       <c r="F87" t="s">
-        <v>254</v>
+        <v>150</v>
       </c>
       <c r="G87" s="53">
         <v>-225</v>
@@ -12050,9 +12125,9 @@
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9">
       <c r="B88" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C88" s="53">
         <v>-12807</v>
@@ -12062,30 +12137,30 @@
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9">
       <c r="C89" s="53"/>
       <c r="D89" s="53"/>
       <c r="G89" s="53"/>
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9">
       <c r="C90" s="53"/>
       <c r="D90" s="53"/>
       <c r="G90" s="53"/>
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9">
       <c r="C91" s="53"/>
       <c r="D91" s="53"/>
       <c r="G91" s="53"/>
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9">
       <c r="B92" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C92" s="53">
         <v>2000</v>
@@ -12097,9 +12172,9 @@
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9">
       <c r="B93" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C93" s="53">
         <v>-50</v>
@@ -12109,9 +12184,9 @@
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9">
       <c r="B94" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C94" s="53">
         <v>160</v>
@@ -12121,16 +12196,16 @@
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9">
       <c r="C95" s="53"/>
       <c r="D95" s="53"/>
       <c r="G95" s="53"/>
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9">
       <c r="B96" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C96" s="53">
         <v>2000</v>
@@ -12142,9 +12217,9 @@
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9">
       <c r="B97" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="C97" s="53">
         <v>-50</v>
@@ -12154,9 +12229,9 @@
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9">
       <c r="B98" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C98" s="53">
         <v>300</v>
@@ -12166,16 +12241,16 @@
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9">
       <c r="C99" s="53"/>
       <c r="D99" s="53"/>
       <c r="G99" s="53"/>
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9">
       <c r="B100" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C100" s="53">
         <v>2000</v>
@@ -12187,9 +12262,9 @@
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9">
       <c r="B101" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C101" s="53">
         <v>8000</v>
@@ -12199,9 +12274,9 @@
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9">
       <c r="B102" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="C102" s="53">
         <v>4180</v>
@@ -12211,16 +12286,16 @@
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9">
       <c r="C103" s="53"/>
       <c r="D103" s="53"/>
       <c r="G103" s="53"/>
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9">
       <c r="B104" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C104" s="53">
         <v>2000</v>
@@ -12232,9 +12307,9 @@
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9">
       <c r="B105" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C105" s="53">
         <v>2000</v>
@@ -12246,9 +12321,9 @@
       <c r="H105" s="53"/>
       <c r="I105" s="53"/>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9">
       <c r="B106" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="C106" s="53">
         <v>2000</v>
@@ -12260,16 +12335,16 @@
       <c r="H106" s="53"/>
       <c r="I106" s="53"/>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9">
       <c r="C107" s="53"/>
       <c r="D107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
       <c r="I107" s="53"/>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9">
       <c r="B108" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C108" s="53">
         <v>-20000</v>
@@ -12279,16 +12354,16 @@
       <c r="H108" s="53"/>
       <c r="I108" s="53"/>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9">
       <c r="C109" s="53"/>
       <c r="D109" s="53"/>
       <c r="G109" s="53"/>
       <c r="H109" s="53"/>
       <c r="I109" s="53"/>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9">
       <c r="B110" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C110" s="53">
         <v>2000</v>
@@ -12300,9 +12375,9 @@
       <c r="H110" s="53"/>
       <c r="I110" s="53"/>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9">
       <c r="B111" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C111" s="53">
         <v>2000</v>
@@ -12314,9 +12389,9 @@
       <c r="H111" s="53"/>
       <c r="I111" s="53"/>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9">
       <c r="B112" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C112" s="53">
         <v>8000</v>
@@ -12326,9 +12401,9 @@
       <c r="H112" s="53"/>
       <c r="I112" s="53"/>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9">
       <c r="B113" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C113" s="53">
         <v>2000</v>
@@ -12340,9 +12415,9 @@
       <c r="H113" s="53"/>
       <c r="I113" s="53"/>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9">
       <c r="B114" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C114" s="53">
         <v>2000</v>
@@ -12354,1178 +12429,1178 @@
       <c r="H114" s="53"/>
       <c r="I114" s="53"/>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9">
       <c r="G115" s="53"/>
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9">
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9">
       <c r="G117" s="53"/>
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9">
       <c r="G118" s="53"/>
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9">
       <c r="G119" s="53"/>
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9">
       <c r="G120" s="53"/>
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9">
       <c r="G121" s="53"/>
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9">
       <c r="G122" s="53"/>
       <c r="H122" s="53"/>
       <c r="I122" s="53"/>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9">
       <c r="G123" s="53"/>
       <c r="H123" s="53"/>
       <c r="I123" s="53"/>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9">
       <c r="G124" s="53"/>
       <c r="H124" s="53"/>
       <c r="I124" s="53"/>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9">
       <c r="G125" s="53"/>
       <c r="H125" s="53"/>
       <c r="I125" s="53"/>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9">
       <c r="G126" s="53"/>
       <c r="H126" s="53"/>
       <c r="I126" s="53"/>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9">
       <c r="G127" s="53"/>
       <c r="H127" s="53"/>
       <c r="I127" s="53"/>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9">
       <c r="G128" s="53"/>
       <c r="H128" s="53"/>
       <c r="I128" s="53"/>
     </row>
-    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:9">
       <c r="G129" s="53"/>
       <c r="H129" s="53"/>
       <c r="I129" s="53"/>
     </row>
-    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:9">
       <c r="G130" s="53"/>
       <c r="H130" s="53"/>
       <c r="I130" s="53"/>
     </row>
-    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:9">
       <c r="G131" s="53"/>
       <c r="H131" s="53"/>
       <c r="I131" s="53"/>
     </row>
-    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:9">
       <c r="G132" s="53"/>
       <c r="H132" s="53"/>
       <c r="I132" s="53"/>
     </row>
-    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:9">
       <c r="G133" s="53"/>
       <c r="H133" s="53"/>
       <c r="I133" s="53"/>
     </row>
-    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:9">
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
       <c r="I134" s="53"/>
     </row>
-    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:9">
       <c r="G135" s="53"/>
       <c r="H135" s="53"/>
       <c r="I135" s="53"/>
     </row>
-    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:9">
       <c r="G136" s="53"/>
       <c r="H136" s="53"/>
       <c r="I136" s="53"/>
     </row>
-    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:9">
       <c r="G137" s="53"/>
       <c r="H137" s="53"/>
       <c r="I137" s="53"/>
     </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:9">
       <c r="G138" s="53"/>
       <c r="H138" s="53"/>
       <c r="I138" s="53"/>
     </row>
-    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:9">
       <c r="G139" s="53"/>
       <c r="H139" s="53"/>
       <c r="I139" s="53"/>
     </row>
-    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:9">
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
       <c r="I140" s="53"/>
     </row>
-    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:9">
       <c r="G141" s="53"/>
       <c r="H141" s="53"/>
       <c r="I141" s="53"/>
     </row>
-    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:9">
       <c r="G142" s="53"/>
       <c r="H142" s="53"/>
       <c r="I142" s="53"/>
     </row>
-    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:9">
       <c r="G143" s="53"/>
       <c r="H143" s="53"/>
       <c r="I143" s="53"/>
     </row>
-    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:9">
       <c r="G144" s="53"/>
       <c r="H144" s="53"/>
       <c r="I144" s="53"/>
     </row>
-    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:9">
       <c r="G145" s="53"/>
       <c r="H145" s="53"/>
       <c r="I145" s="53"/>
     </row>
-    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:9">
       <c r="G146" s="53"/>
       <c r="H146" s="53"/>
       <c r="I146" s="53"/>
     </row>
-    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:9">
       <c r="G147" s="53"/>
       <c r="H147" s="53"/>
       <c r="I147" s="53"/>
     </row>
-    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:9">
       <c r="G148" s="53"/>
       <c r="H148" s="53"/>
       <c r="I148" s="53"/>
     </row>
-    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:9">
       <c r="G149" s="53"/>
       <c r="H149" s="53"/>
       <c r="I149" s="53"/>
     </row>
-    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:9">
       <c r="G150" s="53"/>
       <c r="H150" s="53"/>
       <c r="I150" s="53"/>
     </row>
-    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:9">
       <c r="G151" s="53"/>
       <c r="H151" s="53"/>
       <c r="I151" s="53"/>
     </row>
-    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:9">
       <c r="G152" s="53"/>
       <c r="H152" s="53"/>
       <c r="I152" s="53"/>
     </row>
-    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:9">
       <c r="G153" s="53"/>
       <c r="H153" s="53"/>
       <c r="I153" s="53"/>
     </row>
-    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:9">
       <c r="G154" s="53"/>
       <c r="H154" s="53"/>
       <c r="I154" s="53"/>
     </row>
-    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:9">
       <c r="G155" s="53"/>
       <c r="H155" s="53"/>
       <c r="I155" s="53"/>
     </row>
-    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:9">
       <c r="G156" s="53"/>
       <c r="H156" s="53"/>
       <c r="I156" s="53"/>
     </row>
-    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:9">
       <c r="G157" s="53"/>
       <c r="H157" s="53"/>
       <c r="I157" s="53"/>
     </row>
-    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:9">
       <c r="G158" s="53"/>
       <c r="H158" s="53"/>
       <c r="I158" s="53"/>
     </row>
-    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:9">
       <c r="G159" s="53"/>
       <c r="H159" s="53"/>
       <c r="I159" s="53"/>
     </row>
-    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:9">
       <c r="G160" s="53"/>
       <c r="H160" s="53"/>
       <c r="I160" s="53"/>
     </row>
-    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:9">
       <c r="G161" s="53"/>
       <c r="H161" s="53"/>
       <c r="I161" s="53"/>
     </row>
-    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:9">
       <c r="G162" s="53"/>
       <c r="H162" s="53"/>
       <c r="I162" s="53"/>
     </row>
-    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:9">
       <c r="G163" s="53"/>
       <c r="H163" s="53"/>
       <c r="I163" s="53"/>
     </row>
-    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:9">
       <c r="G164" s="53"/>
       <c r="H164" s="53"/>
       <c r="I164" s="53"/>
     </row>
-    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:9">
       <c r="G165" s="53"/>
       <c r="H165" s="53"/>
       <c r="I165" s="53"/>
     </row>
-    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:9">
       <c r="G166" s="53"/>
       <c r="H166" s="53"/>
       <c r="I166" s="53"/>
     </row>
-    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:9">
       <c r="G167" s="53"/>
       <c r="H167" s="53"/>
       <c r="I167" s="53"/>
     </row>
-    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:9">
       <c r="G168" s="53"/>
       <c r="H168" s="53"/>
       <c r="I168" s="53"/>
     </row>
-    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:9">
       <c r="G169" s="53"/>
       <c r="H169" s="53"/>
       <c r="I169" s="53"/>
     </row>
-    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:9">
       <c r="G170" s="53"/>
       <c r="H170" s="53"/>
       <c r="I170" s="53"/>
     </row>
-    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:9">
       <c r="G171" s="53"/>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
     </row>
-    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:9">
       <c r="G172" s="53"/>
       <c r="H172" s="53"/>
       <c r="I172" s="53"/>
     </row>
-    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:9">
       <c r="G173" s="53"/>
       <c r="H173" s="53"/>
       <c r="I173" s="53"/>
     </row>
-    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:9">
       <c r="G174" s="53"/>
       <c r="H174" s="53"/>
       <c r="I174" s="53"/>
     </row>
-    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:9">
       <c r="G175" s="53"/>
       <c r="H175" s="53"/>
       <c r="I175" s="53"/>
     </row>
-    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:9">
       <c r="G176" s="53"/>
       <c r="H176" s="53"/>
       <c r="I176" s="53"/>
     </row>
-    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:9">
       <c r="G177" s="53"/>
       <c r="H177" s="53"/>
       <c r="I177" s="53"/>
     </row>
-    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:9">
       <c r="G178" s="53"/>
       <c r="H178" s="53"/>
       <c r="I178" s="53"/>
     </row>
-    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:9">
       <c r="G179" s="53"/>
       <c r="H179" s="53"/>
       <c r="I179" s="53"/>
     </row>
-    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:9">
       <c r="G180" s="53"/>
       <c r="H180" s="53"/>
       <c r="I180" s="53"/>
     </row>
-    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:9">
       <c r="G181" s="53"/>
       <c r="H181" s="53"/>
       <c r="I181" s="53"/>
     </row>
-    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:9">
       <c r="G182" s="53"/>
       <c r="H182" s="53"/>
       <c r="I182" s="53"/>
     </row>
-    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:9">
       <c r="G183" s="53"/>
       <c r="H183" s="53"/>
       <c r="I183" s="53"/>
     </row>
-    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:9">
       <c r="G184" s="53"/>
       <c r="H184" s="53"/>
       <c r="I184" s="53"/>
     </row>
-    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:9">
       <c r="G185" s="53"/>
       <c r="H185" s="53"/>
       <c r="I185" s="53"/>
     </row>
-    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:9">
       <c r="G186" s="53"/>
       <c r="H186" s="53"/>
       <c r="I186" s="53"/>
     </row>
-    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:9">
       <c r="G187" s="53"/>
       <c r="H187" s="53"/>
       <c r="I187" s="53"/>
     </row>
-    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:9">
       <c r="G188" s="53"/>
       <c r="H188" s="53"/>
       <c r="I188" s="53"/>
     </row>
-    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:9">
       <c r="G189" s="53"/>
       <c r="H189" s="53"/>
       <c r="I189" s="53"/>
     </row>
-    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:9">
       <c r="G190" s="53"/>
       <c r="H190" s="53"/>
       <c r="I190" s="53"/>
     </row>
-    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:9">
       <c r="G191" s="53"/>
       <c r="H191" s="53"/>
       <c r="I191" s="53"/>
     </row>
-    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:9">
       <c r="G192" s="53"/>
       <c r="H192" s="53"/>
       <c r="I192" s="53"/>
     </row>
-    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:9">
       <c r="G193" s="53"/>
       <c r="H193" s="53"/>
       <c r="I193" s="53"/>
     </row>
-    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:9">
       <c r="G194" s="53"/>
       <c r="H194" s="53"/>
       <c r="I194" s="53"/>
     </row>
-    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:9">
       <c r="G195" s="53"/>
       <c r="H195" s="53"/>
       <c r="I195" s="53"/>
     </row>
-    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:9">
       <c r="G196" s="53"/>
       <c r="H196" s="53"/>
       <c r="I196" s="53"/>
     </row>
-    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:9">
       <c r="G197" s="53"/>
       <c r="H197" s="53"/>
       <c r="I197" s="53"/>
     </row>
-    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:9">
       <c r="G198" s="53"/>
       <c r="H198" s="53"/>
       <c r="I198" s="53"/>
     </row>
-    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:9">
       <c r="G199" s="53"/>
       <c r="H199" s="53"/>
       <c r="I199" s="53"/>
     </row>
-    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:9">
       <c r="G200" s="53"/>
       <c r="H200" s="53"/>
       <c r="I200" s="53"/>
     </row>
-    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:9">
       <c r="G201" s="53"/>
       <c r="H201" s="53"/>
       <c r="I201" s="53"/>
     </row>
-    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:9">
       <c r="G202" s="53"/>
       <c r="H202" s="53"/>
       <c r="I202" s="53"/>
     </row>
-    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:9">
       <c r="G203" s="53"/>
       <c r="H203" s="53"/>
       <c r="I203" s="53"/>
     </row>
-    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:9">
       <c r="G204" s="53"/>
       <c r="H204" s="53"/>
       <c r="I204" s="53"/>
     </row>
-    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:9">
       <c r="G205" s="53"/>
       <c r="H205" s="53"/>
       <c r="I205" s="53"/>
     </row>
-    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:9">
       <c r="G206" s="53"/>
       <c r="H206" s="53"/>
       <c r="I206" s="53"/>
     </row>
-    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:9">
       <c r="G207" s="53"/>
       <c r="H207" s="53"/>
       <c r="I207" s="53"/>
     </row>
-    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:9">
       <c r="G208" s="53"/>
       <c r="H208" s="53"/>
       <c r="I208" s="53"/>
     </row>
-    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:9">
       <c r="G209" s="53"/>
       <c r="H209" s="53"/>
       <c r="I209" s="53"/>
     </row>
-    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:9">
       <c r="G210" s="53"/>
       <c r="H210" s="53"/>
       <c r="I210" s="53"/>
     </row>
-    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:9">
       <c r="G211" s="53"/>
       <c r="H211" s="53"/>
       <c r="I211" s="53"/>
     </row>
-    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:9">
       <c r="G212" s="53"/>
       <c r="H212" s="53"/>
       <c r="I212" s="53"/>
     </row>
-    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:9">
       <c r="G213" s="53"/>
       <c r="H213" s="53"/>
       <c r="I213" s="53"/>
     </row>
-    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:9">
       <c r="G214" s="53"/>
       <c r="H214" s="53"/>
       <c r="I214" s="53"/>
     </row>
-    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:9">
       <c r="G215" s="53"/>
       <c r="H215" s="53"/>
       <c r="I215" s="53"/>
     </row>
-    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:9">
       <c r="G216" s="53"/>
       <c r="H216" s="53"/>
       <c r="I216" s="53"/>
     </row>
-    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:9">
       <c r="G217" s="53"/>
       <c r="H217" s="53"/>
       <c r="I217" s="53"/>
     </row>
-    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:9">
       <c r="G218" s="53"/>
       <c r="H218" s="53"/>
       <c r="I218" s="53"/>
     </row>
-    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:9">
       <c r="G219" s="53"/>
       <c r="H219" s="53"/>
       <c r="I219" s="53"/>
     </row>
-    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:9">
       <c r="G220" s="53"/>
       <c r="H220" s="53"/>
       <c r="I220" s="53"/>
     </row>
-    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:9">
       <c r="G221" s="53"/>
       <c r="H221" s="53"/>
       <c r="I221" s="53"/>
     </row>
-    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:9">
       <c r="G222" s="53"/>
       <c r="H222" s="53"/>
       <c r="I222" s="53"/>
     </row>
-    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:9">
       <c r="G223" s="53"/>
       <c r="H223" s="53"/>
       <c r="I223" s="53"/>
     </row>
-    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:9">
       <c r="G224" s="53"/>
       <c r="H224" s="53"/>
       <c r="I224" s="53"/>
     </row>
-    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:9">
       <c r="G225" s="53"/>
       <c r="H225" s="53"/>
       <c r="I225" s="53"/>
     </row>
-    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:9">
       <c r="G226" s="53"/>
       <c r="H226" s="53"/>
       <c r="I226" s="53"/>
     </row>
-    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:9">
       <c r="G227" s="53"/>
       <c r="H227" s="53"/>
       <c r="I227" s="53"/>
     </row>
-    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:9">
       <c r="G228" s="53"/>
       <c r="H228" s="53"/>
       <c r="I228" s="53"/>
     </row>
-    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:9">
       <c r="G229" s="53"/>
       <c r="H229" s="53"/>
       <c r="I229" s="53"/>
     </row>
-    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:9">
       <c r="G230" s="53"/>
       <c r="H230" s="53"/>
       <c r="I230" s="53"/>
     </row>
-    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:9">
       <c r="G231" s="53"/>
       <c r="H231" s="53"/>
       <c r="I231" s="53"/>
     </row>
-    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:9">
       <c r="G232" s="53"/>
       <c r="H232" s="53"/>
       <c r="I232" s="53"/>
     </row>
-    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:9">
       <c r="G233" s="53"/>
       <c r="H233" s="53"/>
       <c r="I233" s="53"/>
     </row>
-    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:9">
       <c r="G234" s="53"/>
       <c r="H234" s="53"/>
       <c r="I234" s="53"/>
     </row>
-    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:9">
       <c r="G235" s="53"/>
       <c r="H235" s="53"/>
       <c r="I235" s="53"/>
     </row>
-    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:9">
       <c r="G236" s="53"/>
       <c r="H236" s="53"/>
       <c r="I236" s="53"/>
     </row>
-    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:9">
       <c r="G237" s="53"/>
       <c r="H237" s="53"/>
       <c r="I237" s="53"/>
     </row>
-    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:9">
       <c r="G238" s="53"/>
       <c r="H238" s="53"/>
       <c r="I238" s="53"/>
     </row>
-    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:9">
       <c r="G239" s="53"/>
       <c r="H239" s="53"/>
       <c r="I239" s="53"/>
     </row>
-    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:9">
       <c r="G240" s="53"/>
       <c r="H240" s="53"/>
       <c r="I240" s="53"/>
     </row>
-    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:9">
       <c r="G241" s="53"/>
       <c r="H241" s="53"/>
       <c r="I241" s="53"/>
     </row>
-    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:9">
       <c r="G242" s="53"/>
       <c r="H242" s="53"/>
       <c r="I242" s="53"/>
     </row>
-    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:9">
       <c r="G243" s="53"/>
       <c r="H243" s="53"/>
       <c r="I243" s="53"/>
     </row>
-    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:9">
       <c r="G244" s="53"/>
       <c r="H244" s="53"/>
       <c r="I244" s="53"/>
     </row>
-    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:9">
       <c r="G245" s="53"/>
       <c r="H245" s="53"/>
       <c r="I245" s="53"/>
     </row>
-    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:9">
       <c r="G246" s="53"/>
       <c r="H246" s="53"/>
       <c r="I246" s="53"/>
     </row>
-    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:9">
       <c r="G247" s="53"/>
       <c r="H247" s="53"/>
       <c r="I247" s="53"/>
     </row>
-    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:9">
       <c r="G248" s="53"/>
       <c r="H248" s="53"/>
       <c r="I248" s="53"/>
     </row>
-    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:9">
       <c r="G249" s="53"/>
       <c r="H249" s="53"/>
       <c r="I249" s="53"/>
     </row>
-    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:9">
       <c r="G250" s="53"/>
       <c r="H250" s="53"/>
       <c r="I250" s="53"/>
     </row>
-    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:9">
       <c r="G251" s="53"/>
       <c r="H251" s="53"/>
       <c r="I251" s="53"/>
     </row>
-    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:9">
       <c r="G252" s="53"/>
       <c r="H252" s="53"/>
       <c r="I252" s="53"/>
     </row>
-    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:9">
       <c r="G253" s="53"/>
       <c r="H253" s="53"/>
       <c r="I253" s="53"/>
     </row>
-    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:9">
       <c r="G254" s="53"/>
       <c r="H254" s="53"/>
       <c r="I254" s="53"/>
     </row>
-    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:9">
       <c r="G255" s="53"/>
       <c r="H255" s="53"/>
       <c r="I255" s="53"/>
     </row>
-    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:9">
       <c r="G256" s="53"/>
       <c r="H256" s="53"/>
       <c r="I256" s="53"/>
     </row>
-    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:9">
       <c r="G257" s="53"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:9">
       <c r="G258" s="53"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:9">
       <c r="G259" s="53"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:9">
       <c r="G260" s="53"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:9">
       <c r="G261" s="53"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:9">
       <c r="G262" s="53"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:9">
       <c r="G263" s="53"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:9">
       <c r="G264" s="53"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:9">
       <c r="G265" s="53"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:9">
       <c r="G266" s="53"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:9">
       <c r="G267" s="53"/>
     </row>
-    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:9">
       <c r="G268" s="53"/>
     </row>
-    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:9">
       <c r="G269" s="53"/>
     </row>
-    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:9">
       <c r="G270" s="53"/>
     </row>
-    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:9">
       <c r="G271" s="53"/>
     </row>
-    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:9">
       <c r="G272" s="53"/>
     </row>
-    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:7">
       <c r="G273" s="53"/>
     </row>
-    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:7">
       <c r="G274" s="53"/>
     </row>
-    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:7">
       <c r="G275" s="53"/>
     </row>
-    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:7">
       <c r="G276" s="53"/>
     </row>
-    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:7">
       <c r="G277" s="53"/>
     </row>
-    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:7">
       <c r="G278" s="53"/>
     </row>
-    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:7">
       <c r="G279" s="53"/>
     </row>
-    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:7">
       <c r="G280" s="53"/>
     </row>
-    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:7">
       <c r="G281" s="53"/>
     </row>
-    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:7">
       <c r="G282" s="53"/>
     </row>
-    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:7">
       <c r="G283" s="53"/>
     </row>
-    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:7">
       <c r="G284" s="53"/>
     </row>
-    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:7">
       <c r="G285" s="53"/>
     </row>
-    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:7">
       <c r="G286" s="53"/>
     </row>
-    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:7">
       <c r="G287" s="53"/>
     </row>
-    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:7">
       <c r="G288" s="53"/>
     </row>
-    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:7">
       <c r="G289" s="53"/>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:7">
       <c r="G290" s="53"/>
     </row>
-    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:7">
       <c r="G291" s="53"/>
     </row>
-    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:7">
       <c r="G292" s="53"/>
     </row>
-    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:7">
       <c r="G293" s="53"/>
     </row>
-    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:7">
       <c r="G294" s="53"/>
     </row>
-    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:7">
       <c r="G295" s="53"/>
     </row>
-    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:7">
       <c r="G296" s="53"/>
     </row>
-    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:7">
       <c r="G297" s="53"/>
     </row>
-    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:7">
       <c r="G298" s="53"/>
     </row>
-    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:7">
       <c r="G299" s="53"/>
     </row>
-    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:7">
       <c r="G300" s="53"/>
     </row>
-    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:7">
       <c r="G301" s="53"/>
     </row>
-    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:7">
       <c r="G302" s="53"/>
     </row>
-    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:7">
       <c r="G303" s="53"/>
     </row>
-    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:7">
       <c r="G304" s="53"/>
     </row>
-    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:7">
       <c r="G305" s="53"/>
     </row>
-    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:7">
       <c r="G306" s="53"/>
     </row>
-    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:7">
       <c r="G307" s="53"/>
     </row>
-    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:7">
       <c r="G308" s="53"/>
     </row>
-    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:7">
       <c r="G309" s="53"/>
     </row>
-    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:7">
       <c r="G310" s="53"/>
     </row>
-    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:7">
       <c r="G311" s="53"/>
     </row>
-    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:7">
       <c r="G312" s="53"/>
     </row>
-    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:7">
       <c r="G313" s="53"/>
     </row>
-    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:7">
       <c r="G314" s="53"/>
     </row>
-    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:7">
       <c r="G315" s="53"/>
     </row>
-    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:7">
       <c r="G316" s="53"/>
     </row>
-    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:7">
       <c r="G317" s="53"/>
     </row>
-    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:7">
       <c r="G318" s="53"/>
     </row>
-    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:7">
       <c r="G319" s="53"/>
     </row>
-    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:7">
       <c r="G320" s="53"/>
     </row>
-    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:7">
       <c r="G321" s="53"/>
     </row>
-    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:7">
       <c r="G322" s="53"/>
     </row>
-    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:7">
       <c r="G323" s="53"/>
     </row>
-    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:7">
       <c r="G324" s="53"/>
     </row>
-    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:7">
       <c r="G325" s="53"/>
     </row>
-    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:7">
       <c r="G326" s="53"/>
     </row>
-    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:7">
       <c r="G327" s="53"/>
     </row>
-    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:7">
       <c r="G328" s="53"/>
     </row>
-    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:7">
       <c r="G329" s="53"/>
     </row>
-    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:7">
       <c r="G330" s="53"/>
     </row>
-    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:7">
       <c r="G331" s="53"/>
     </row>
-    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:7">
       <c r="G332" s="53"/>
     </row>
-    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:7">
       <c r="G333" s="53"/>
     </row>
-    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:7">
       <c r="G334" s="53"/>
     </row>
-    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:7">
       <c r="G335" s="53"/>
     </row>
-    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:7">
       <c r="G336" s="53"/>
     </row>
-    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:7">
       <c r="G337" s="53"/>
     </row>
-    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:7">
       <c r="G338" s="53"/>
     </row>
-    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:7">
       <c r="G339" s="53"/>
     </row>
-    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:7">
       <c r="G340" s="53"/>
     </row>
-    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:7">
       <c r="G341" s="53"/>
     </row>
-    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:7">
       <c r="G342" s="53"/>
     </row>
-    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:7">
       <c r="G343" s="53"/>
     </row>
-    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:7">
       <c r="G344" s="53"/>
     </row>
-    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:7">
       <c r="G345" s="53"/>
     </row>
-    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:7">
       <c r="G346" s="53"/>
     </row>
-    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:7">
       <c r="G347" s="53"/>
     </row>
-    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:7">
       <c r="G348" s="53"/>
     </row>
-    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:7">
       <c r="G349" s="53"/>
     </row>
-    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:7">
       <c r="G350" s="53"/>
     </row>
-    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:7">
       <c r="G351" s="53"/>
     </row>
-    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:7">
       <c r="G352" s="53"/>
     </row>
-    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:7">
       <c r="G353" s="53"/>
     </row>
-    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:7">
       <c r="G354" s="53"/>
     </row>
-    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:7">
       <c r="G355" s="53"/>
     </row>
-    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:7">
       <c r="G356" s="53"/>
     </row>
-    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:7">
       <c r="G357" s="53"/>
     </row>
-    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:7">
       <c r="G358" s="53"/>
     </row>
-    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:7">
       <c r="G359" s="53"/>
     </row>
-    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:7">
       <c r="G360" s="53"/>
     </row>
-    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:7">
       <c r="G361" s="53"/>
     </row>
-    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:7">
       <c r="G362" s="53"/>
     </row>
-    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:7">
       <c r="G363" s="53"/>
     </row>
-    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:7">
       <c r="G364" s="53"/>
     </row>
-    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:7">
       <c r="G365" s="53"/>
     </row>
-    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:7">
       <c r="G366" s="53"/>
     </row>
-    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:7">
       <c r="G367" s="53"/>
     </row>
-    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:7">
       <c r="G368" s="53"/>
     </row>
-    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:7">
       <c r="G369" s="53"/>
     </row>
-    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:7">
       <c r="G370" s="53"/>
     </row>
-    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:7">
       <c r="G371" s="53"/>
     </row>
-    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:7">
       <c r="G372" s="53"/>
     </row>
-    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:7">
       <c r="G373" s="53"/>
     </row>
-    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:7">
       <c r="G374" s="53"/>
     </row>
-    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:7">
       <c r="G375" s="53"/>
     </row>
-    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:7">
       <c r="G376" s="53"/>
     </row>
-    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:7">
       <c r="G377" s="53"/>
     </row>
-    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:7">
       <c r="G378" s="53"/>
     </row>
-    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:7">
       <c r="G379" s="53"/>
     </row>
-    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:7">
       <c r="G380" s="53"/>
     </row>
-    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:7">
       <c r="G381" s="53"/>
     </row>
-    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:7">
       <c r="G382" s="53"/>
     </row>
-    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:7">
       <c r="G383" s="53"/>
     </row>
-    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:7">
       <c r="G384" s="53"/>
     </row>
-    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="7:7">
       <c r="G385" s="53"/>
     </row>
-    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="7:7">
       <c r="G386" s="53"/>
     </row>
-    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="7:7">
       <c r="G387" s="53"/>
     </row>
-    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="7:7">
       <c r="G388" s="53"/>
     </row>
-    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="7:7">
       <c r="G389" s="53"/>
     </row>
-    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="7:7">
       <c r="G390" s="53"/>
     </row>
-    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="7:7">
       <c r="G391" s="53"/>
     </row>
-    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="7:7">
       <c r="G392" s="53"/>
     </row>
-    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="7:7">
       <c r="G393" s="53"/>
     </row>
-    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="7:7">
       <c r="G394" s="53"/>
     </row>
-    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="7:7">
       <c r="G395" s="53"/>
     </row>
-    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="7:7">
       <c r="G396" s="53"/>
     </row>
-    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="7:7">
       <c r="G397" s="53"/>
     </row>
-    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="7:7">
       <c r="G398" s="53"/>
     </row>
-    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="7:7">
       <c r="G399" s="53"/>
     </row>
-    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="7:7">
       <c r="G400" s="53"/>
     </row>
-    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="7:7">
       <c r="G401" s="53"/>
     </row>
-    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="7:7">
       <c r="G402" s="53"/>
     </row>
-    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="7:7">
       <c r="G403" s="53"/>
     </row>
-    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="7:7">
       <c r="G404" s="53"/>
     </row>
   </sheetData>
@@ -13533,42 +13608,66 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C82:D114">
-    <cfRule type="cellIs" dxfId="13" priority="135" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="143" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="136" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:D52">
-    <cfRule type="cellIs" dxfId="11" priority="129" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="130" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="144" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G120:G1048576">
-    <cfRule type="cellIs" dxfId="9" priority="131" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="139" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="140" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I119">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="G14:I88 G96:I96 I89:I95 G113:I113 I97:I112 G119:I119 I114:I118">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H120:I266">
-    <cfRule type="cellIs" dxfId="5" priority="133" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="141" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="134" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="142" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G89:H95">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G97:H107">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G108:H112">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G114:H118">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13580,7 +13679,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
@@ -13588,81 +13687,81 @@
     <col min="4" max="4" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4">
       <c r="B1" s="62" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4">
       <c r="B2" s="54" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="54"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" s="54" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C3" s="37"/>
       <c r="D3" s="54"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" s="54" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C4" s="37"/>
       <c r="D4" s="54"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4">
       <c r="B5" s="54" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C5" s="37"/>
       <c r="D5" s="54"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" s="54" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C6" s="37"/>
       <c r="D6" s="54"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" s="54" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="54"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="54" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C8" s="37"/>
       <c r="D8" s="54"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="54" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="54"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" s="54" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="54"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3">
       <c r="C17" s="28"/>
     </row>
   </sheetData>
